--- a/제작도_도면_1.xlsx
+++ b/제작도_도면_1.xlsx
@@ -3261,7 +3261,7 @@
       <c r="HB22" s="91" t="n"/>
       <c r="HC22" s="100" t="inlineStr">
         <is>
-          <t>{Input_19}</t>
+          <t>{Input_24}</t>
         </is>
       </c>
       <c r="HD22" s="90" t="n"/>
@@ -3280,7 +3280,7 @@
       <c r="HQ22" s="91" t="n"/>
       <c r="HR22" s="100" t="inlineStr">
         <is>
-          <t>{Input_34}</t>
+          <t>{Input_44}</t>
         </is>
       </c>
       <c r="HS22" s="90" t="n"/>
@@ -3297,7 +3297,7 @@
       <c r="ID22" s="91" t="n"/>
       <c r="IE22" s="100" t="inlineStr">
         <is>
-          <t>{Input_49}</t>
+          <t>{Input_64}</t>
         </is>
       </c>
       <c r="IF22" s="90" t="n"/>
@@ -3324,7 +3324,7 @@
       <c r="JA22" s="91" t="n"/>
       <c r="JB22" s="100" t="inlineStr">
         <is>
-          <t>{Input_64}</t>
+          <t>{Input_84}</t>
         </is>
       </c>
       <c r="JC22" s="90" t="n"/>
@@ -3333,7 +3333,7 @@
       <c r="JF22" s="91" t="n"/>
       <c r="JG22" s="100" t="inlineStr">
         <is>
-          <t>{Input_79}</t>
+          <t>{Input_104}</t>
         </is>
       </c>
       <c r="JH22" s="90" t="n"/>
@@ -3345,7 +3345,7 @@
       <c r="JN22" s="91" t="n"/>
       <c r="JO22" s="100" t="inlineStr">
         <is>
-          <t>{Input_94}</t>
+          <t>{Input_124}</t>
         </is>
       </c>
       <c r="JP22" s="90" t="n"/>
@@ -3354,7 +3354,7 @@
       <c r="JS22" s="91" t="n"/>
       <c r="JT22" s="100" t="inlineStr">
         <is>
-          <t>{Input_109}</t>
+          <t>{Input_144}</t>
         </is>
       </c>
       <c r="JU22" s="90" t="n"/>
@@ -3597,7 +3597,7 @@
       <c r="HB26" s="91" t="n"/>
       <c r="HC26" s="100" t="inlineStr">
         <is>
-          <t>{Input_20}</t>
+          <t>{Input_25}</t>
         </is>
       </c>
       <c r="HD26" s="90" t="n"/>
@@ -3616,7 +3616,7 @@
       <c r="HQ26" s="91" t="n"/>
       <c r="HR26" s="100" t="inlineStr">
         <is>
-          <t>{Input_35}</t>
+          <t>{Input_45}</t>
         </is>
       </c>
       <c r="HS26" s="90" t="n"/>
@@ -3633,7 +3633,7 @@
       <c r="ID26" s="91" t="n"/>
       <c r="IE26" s="100" t="inlineStr">
         <is>
-          <t>{Input_50}</t>
+          <t>{Input_65}</t>
         </is>
       </c>
       <c r="IF26" s="90" t="n"/>
@@ -3660,7 +3660,7 @@
       <c r="JA26" s="91" t="n"/>
       <c r="JB26" s="100" t="inlineStr">
         <is>
-          <t>{Input_65}</t>
+          <t>{Input_85}</t>
         </is>
       </c>
       <c r="JC26" s="90" t="n"/>
@@ -3669,7 +3669,7 @@
       <c r="JF26" s="91" t="n"/>
       <c r="JG26" s="100" t="inlineStr">
         <is>
-          <t>{Input_80}</t>
+          <t>{Input_105}</t>
         </is>
       </c>
       <c r="JH26" s="90" t="n"/>
@@ -3681,7 +3681,7 @@
       <c r="JN26" s="91" t="n"/>
       <c r="JO26" s="100" t="inlineStr">
         <is>
-          <t>{Input_95}</t>
+          <t>{Input_125}</t>
         </is>
       </c>
       <c r="JP26" s="90" t="n"/>
@@ -3690,7 +3690,7 @@
       <c r="JS26" s="91" t="n"/>
       <c r="JT26" s="100" t="inlineStr">
         <is>
-          <t>{Input_110}</t>
+          <t>{Input_145}</t>
         </is>
       </c>
       <c r="JU26" s="90" t="n"/>
@@ -3933,7 +3933,7 @@
       <c r="HB30" s="91" t="n"/>
       <c r="HC30" s="100" t="inlineStr">
         <is>
-          <t>{Input_21}</t>
+          <t>{Input_26}</t>
         </is>
       </c>
       <c r="HD30" s="90" t="n"/>
@@ -3952,7 +3952,7 @@
       <c r="HQ30" s="91" t="n"/>
       <c r="HR30" s="100" t="inlineStr">
         <is>
-          <t>{Input_36}</t>
+          <t>{Input_46}</t>
         </is>
       </c>
       <c r="HS30" s="90" t="n"/>
@@ -3969,7 +3969,7 @@
       <c r="ID30" s="91" t="n"/>
       <c r="IE30" s="100" t="inlineStr">
         <is>
-          <t>{Input_51}</t>
+          <t>{Input_66}</t>
         </is>
       </c>
       <c r="IF30" s="90" t="n"/>
@@ -3996,7 +3996,7 @@
       <c r="JA30" s="91" t="n"/>
       <c r="JB30" s="100" t="inlineStr">
         <is>
-          <t>{Input_66}</t>
+          <t>{Input_86}</t>
         </is>
       </c>
       <c r="JC30" s="90" t="n"/>
@@ -4005,7 +4005,7 @@
       <c r="JF30" s="91" t="n"/>
       <c r="JG30" s="100" t="inlineStr">
         <is>
-          <t>{Input_81}</t>
+          <t>{Input_106}</t>
         </is>
       </c>
       <c r="JH30" s="90" t="n"/>
@@ -4017,7 +4017,7 @@
       <c r="JN30" s="91" t="n"/>
       <c r="JO30" s="100" t="inlineStr">
         <is>
-          <t>{Input_96}</t>
+          <t>{Input_126}</t>
         </is>
       </c>
       <c r="JP30" s="90" t="n"/>
@@ -4026,7 +4026,7 @@
       <c r="JS30" s="91" t="n"/>
       <c r="JT30" s="100" t="inlineStr">
         <is>
-          <t>{Input_111}</t>
+          <t>{Input_146}</t>
         </is>
       </c>
       <c r="JU30" s="90" t="n"/>
@@ -4269,7 +4269,7 @@
       <c r="HB34" s="91" t="n"/>
       <c r="HC34" s="100" t="inlineStr">
         <is>
-          <t>{Input_22}</t>
+          <t>{Input_27}</t>
         </is>
       </c>
       <c r="HD34" s="90" t="n"/>
@@ -4288,7 +4288,7 @@
       <c r="HQ34" s="91" t="n"/>
       <c r="HR34" s="100" t="inlineStr">
         <is>
-          <t>{Input_37}</t>
+          <t>{Input_47}</t>
         </is>
       </c>
       <c r="HS34" s="90" t="n"/>
@@ -4305,7 +4305,7 @@
       <c r="ID34" s="91" t="n"/>
       <c r="IE34" s="100" t="inlineStr">
         <is>
-          <t>{Input_52}</t>
+          <t>{Input_67}</t>
         </is>
       </c>
       <c r="IF34" s="90" t="n"/>
@@ -4332,7 +4332,7 @@
       <c r="JA34" s="91" t="n"/>
       <c r="JB34" s="100" t="inlineStr">
         <is>
-          <t>{Input_67}</t>
+          <t>{Input_87}</t>
         </is>
       </c>
       <c r="JC34" s="90" t="n"/>
@@ -4341,7 +4341,7 @@
       <c r="JF34" s="91" t="n"/>
       <c r="JG34" s="100" t="inlineStr">
         <is>
-          <t>{Input_82}</t>
+          <t>{Input_107}</t>
         </is>
       </c>
       <c r="JH34" s="90" t="n"/>
@@ -4353,7 +4353,7 @@
       <c r="JN34" s="91" t="n"/>
       <c r="JO34" s="100" t="inlineStr">
         <is>
-          <t>{Input_97}</t>
+          <t>{Input_127}</t>
         </is>
       </c>
       <c r="JP34" s="90" t="n"/>
@@ -4362,7 +4362,7 @@
       <c r="JS34" s="91" t="n"/>
       <c r="JT34" s="100" t="inlineStr">
         <is>
-          <t>{Input_112}</t>
+          <t>{Input_147}</t>
         </is>
       </c>
       <c r="JU34" s="90" t="n"/>
@@ -4605,7 +4605,7 @@
       <c r="HB38" s="91" t="n"/>
       <c r="HC38" s="100" t="inlineStr">
         <is>
-          <t>{Input_23}</t>
+          <t>{Input_28}</t>
         </is>
       </c>
       <c r="HD38" s="90" t="n"/>
@@ -4624,7 +4624,7 @@
       <c r="HQ38" s="91" t="n"/>
       <c r="HR38" s="100" t="inlineStr">
         <is>
-          <t>{Input_38}</t>
+          <t>{Input_48}</t>
         </is>
       </c>
       <c r="HS38" s="90" t="n"/>
@@ -4641,7 +4641,7 @@
       <c r="ID38" s="91" t="n"/>
       <c r="IE38" s="100" t="inlineStr">
         <is>
-          <t>{Input_53}</t>
+          <t>{Input_68}</t>
         </is>
       </c>
       <c r="IF38" s="90" t="n"/>
@@ -4668,7 +4668,7 @@
       <c r="JA38" s="91" t="n"/>
       <c r="JB38" s="100" t="inlineStr">
         <is>
-          <t>{Input_68}</t>
+          <t>{Input_88}</t>
         </is>
       </c>
       <c r="JC38" s="90" t="n"/>
@@ -4677,7 +4677,7 @@
       <c r="JF38" s="91" t="n"/>
       <c r="JG38" s="100" t="inlineStr">
         <is>
-          <t>{Input_83}</t>
+          <t>{Input_108}</t>
         </is>
       </c>
       <c r="JH38" s="90" t="n"/>
@@ -4689,7 +4689,7 @@
       <c r="JN38" s="91" t="n"/>
       <c r="JO38" s="100" t="inlineStr">
         <is>
-          <t>{Input_98}</t>
+          <t>{Input_128}</t>
         </is>
       </c>
       <c r="JP38" s="90" t="n"/>
@@ -4698,7 +4698,7 @@
       <c r="JS38" s="91" t="n"/>
       <c r="JT38" s="100" t="inlineStr">
         <is>
-          <t>{Input_113}</t>
+          <t>{Input_148}</t>
         </is>
       </c>
       <c r="JU38" s="90" t="n"/>
@@ -4961,7 +4961,7 @@
       <c r="HB42" s="91" t="n"/>
       <c r="HC42" s="100" t="inlineStr">
         <is>
-          <t>{Input_24}</t>
+          <t>{Input_29}</t>
         </is>
       </c>
       <c r="HD42" s="90" t="n"/>
@@ -4980,7 +4980,7 @@
       <c r="HQ42" s="91" t="n"/>
       <c r="HR42" s="100" t="inlineStr">
         <is>
-          <t>{Input_39}</t>
+          <t>{Input_49}</t>
         </is>
       </c>
       <c r="HS42" s="90" t="n"/>
@@ -4997,7 +4997,7 @@
       <c r="ID42" s="91" t="n"/>
       <c r="IE42" s="100" t="inlineStr">
         <is>
-          <t>{Input_54}</t>
+          <t>{Input_69}</t>
         </is>
       </c>
       <c r="IF42" s="90" t="n"/>
@@ -5024,7 +5024,7 @@
       <c r="JA42" s="91" t="n"/>
       <c r="JB42" s="100" t="inlineStr">
         <is>
-          <t>{Input_69}</t>
+          <t>{Input_89}</t>
         </is>
       </c>
       <c r="JC42" s="90" t="n"/>
@@ -5033,7 +5033,7 @@
       <c r="JF42" s="91" t="n"/>
       <c r="JG42" s="100" t="inlineStr">
         <is>
-          <t>{Input_84}</t>
+          <t>{Input_109}</t>
         </is>
       </c>
       <c r="JH42" s="90" t="n"/>
@@ -5045,7 +5045,7 @@
       <c r="JN42" s="91" t="n"/>
       <c r="JO42" s="100" t="inlineStr">
         <is>
-          <t>{Input_99}</t>
+          <t>{Input_129}</t>
         </is>
       </c>
       <c r="JP42" s="90" t="n"/>
@@ -5054,7 +5054,7 @@
       <c r="JS42" s="91" t="n"/>
       <c r="JT42" s="100" t="inlineStr">
         <is>
-          <t>{Input_114}</t>
+          <t>{Input_149}</t>
         </is>
       </c>
       <c r="JU42" s="90" t="n"/>
@@ -5337,7 +5337,7 @@
       <c r="HB46" s="91" t="n"/>
       <c r="HC46" s="100" t="inlineStr">
         <is>
-          <t>{Input_25}</t>
+          <t>{Input_30}</t>
         </is>
       </c>
       <c r="HD46" s="90" t="n"/>
@@ -5356,7 +5356,7 @@
       <c r="HQ46" s="91" t="n"/>
       <c r="HR46" s="100" t="inlineStr">
         <is>
-          <t>{Input_40}</t>
+          <t>{Input_50}</t>
         </is>
       </c>
       <c r="HS46" s="90" t="n"/>
@@ -5373,7 +5373,7 @@
       <c r="ID46" s="91" t="n"/>
       <c r="IE46" s="100" t="inlineStr">
         <is>
-          <t>{Input_55}</t>
+          <t>{Input_70}</t>
         </is>
       </c>
       <c r="IF46" s="90" t="n"/>
@@ -5400,7 +5400,7 @@
       <c r="JA46" s="91" t="n"/>
       <c r="JB46" s="100" t="inlineStr">
         <is>
-          <t>{Input_70}</t>
+          <t>{Input_90}</t>
         </is>
       </c>
       <c r="JC46" s="90" t="n"/>
@@ -5409,7 +5409,7 @@
       <c r="JF46" s="91" t="n"/>
       <c r="JG46" s="100" t="inlineStr">
         <is>
-          <t>{Input_85}</t>
+          <t>{Input_110}</t>
         </is>
       </c>
       <c r="JH46" s="90" t="n"/>
@@ -5421,7 +5421,7 @@
       <c r="JN46" s="91" t="n"/>
       <c r="JO46" s="100" t="inlineStr">
         <is>
-          <t>{Input_100}</t>
+          <t>{Input_130}</t>
         </is>
       </c>
       <c r="JP46" s="90" t="n"/>
@@ -5430,7 +5430,7 @@
       <c r="JS46" s="91" t="n"/>
       <c r="JT46" s="100" t="inlineStr">
         <is>
-          <t>{Input_115}</t>
+          <t>{Input_150}</t>
         </is>
       </c>
       <c r="JU46" s="90" t="n"/>
@@ -5713,7 +5713,7 @@
       <c r="HB50" s="91" t="n"/>
       <c r="HC50" s="100" t="inlineStr">
         <is>
-          <t>{Input_26}</t>
+          <t>{Input_31}</t>
         </is>
       </c>
       <c r="HD50" s="90" t="n"/>
@@ -5732,7 +5732,7 @@
       <c r="HQ50" s="91" t="n"/>
       <c r="HR50" s="100" t="inlineStr">
         <is>
-          <t>{Input_41}</t>
+          <t>{Input_51}</t>
         </is>
       </c>
       <c r="HS50" s="90" t="n"/>
@@ -5749,7 +5749,7 @@
       <c r="ID50" s="91" t="n"/>
       <c r="IE50" s="100" t="inlineStr">
         <is>
-          <t>{Input_56}</t>
+          <t>{Input_71}</t>
         </is>
       </c>
       <c r="IF50" s="90" t="n"/>
@@ -5776,7 +5776,7 @@
       <c r="JA50" s="91" t="n"/>
       <c r="JB50" s="100" t="inlineStr">
         <is>
-          <t>{Input_71}</t>
+          <t>{Input_91}</t>
         </is>
       </c>
       <c r="JC50" s="90" t="n"/>
@@ -5785,7 +5785,7 @@
       <c r="JF50" s="91" t="n"/>
       <c r="JG50" s="100" t="inlineStr">
         <is>
-          <t>{Input_86}</t>
+          <t>{Input_111}</t>
         </is>
       </c>
       <c r="JH50" s="90" t="n"/>
@@ -5797,7 +5797,7 @@
       <c r="JN50" s="91" t="n"/>
       <c r="JO50" s="100" t="inlineStr">
         <is>
-          <t>{Input_101}</t>
+          <t>{Input_131}</t>
         </is>
       </c>
       <c r="JP50" s="90" t="n"/>
@@ -5806,7 +5806,7 @@
       <c r="JS50" s="91" t="n"/>
       <c r="JT50" s="100" t="inlineStr">
         <is>
-          <t>{Input_116}</t>
+          <t>{Input_151}</t>
         </is>
       </c>
       <c r="JU50" s="90" t="n"/>
@@ -6089,7 +6089,7 @@
       <c r="HB54" s="91" t="n"/>
       <c r="HC54" s="100" t="inlineStr">
         <is>
-          <t>{Input_27}</t>
+          <t>{Input_32}</t>
         </is>
       </c>
       <c r="HD54" s="90" t="n"/>
@@ -6108,7 +6108,7 @@
       <c r="HQ54" s="91" t="n"/>
       <c r="HR54" s="100" t="inlineStr">
         <is>
-          <t>{Input_42}</t>
+          <t>{Input_52}</t>
         </is>
       </c>
       <c r="HS54" s="90" t="n"/>
@@ -6125,7 +6125,7 @@
       <c r="ID54" s="91" t="n"/>
       <c r="IE54" s="100" t="inlineStr">
         <is>
-          <t>{Input_57}</t>
+          <t>{Input_72}</t>
         </is>
       </c>
       <c r="IF54" s="90" t="n"/>
@@ -6152,7 +6152,7 @@
       <c r="JA54" s="91" t="n"/>
       <c r="JB54" s="100" t="inlineStr">
         <is>
-          <t>{Input_72}</t>
+          <t>{Input_92}</t>
         </is>
       </c>
       <c r="JC54" s="90" t="n"/>
@@ -6161,7 +6161,7 @@
       <c r="JF54" s="91" t="n"/>
       <c r="JG54" s="100" t="inlineStr">
         <is>
-          <t>{Input_87}</t>
+          <t>{Input_112}</t>
         </is>
       </c>
       <c r="JH54" s="90" t="n"/>
@@ -6173,7 +6173,7 @@
       <c r="JN54" s="91" t="n"/>
       <c r="JO54" s="100" t="inlineStr">
         <is>
-          <t>{Input_102}</t>
+          <t>{Input_132}</t>
         </is>
       </c>
       <c r="JP54" s="90" t="n"/>
@@ -6182,7 +6182,7 @@
       <c r="JS54" s="91" t="n"/>
       <c r="JT54" s="100" t="inlineStr">
         <is>
-          <t>{Input_117}</t>
+          <t>{Input_152}</t>
         </is>
       </c>
       <c r="JU54" s="90" t="n"/>
@@ -6478,7 +6478,7 @@
       <c r="HB58" s="91" t="n"/>
       <c r="HC58" s="100" t="inlineStr">
         <is>
-          <t>{Input_28}</t>
+          <t>{Input_33}</t>
         </is>
       </c>
       <c r="HD58" s="90" t="n"/>
@@ -6497,7 +6497,7 @@
       <c r="HQ58" s="91" t="n"/>
       <c r="HR58" s="100" t="inlineStr">
         <is>
-          <t>{Input_43}</t>
+          <t>{Input_53}</t>
         </is>
       </c>
       <c r="HS58" s="90" t="n"/>
@@ -6514,7 +6514,7 @@
       <c r="ID58" s="91" t="n"/>
       <c r="IE58" s="100" t="inlineStr">
         <is>
-          <t>{Input_58}</t>
+          <t>{Input_73}</t>
         </is>
       </c>
       <c r="IF58" s="90" t="n"/>
@@ -6541,7 +6541,7 @@
       <c r="JA58" s="91" t="n"/>
       <c r="JB58" s="100" t="inlineStr">
         <is>
-          <t>{Input_73}</t>
+          <t>{Input_93}</t>
         </is>
       </c>
       <c r="JC58" s="90" t="n"/>
@@ -6550,7 +6550,7 @@
       <c r="JF58" s="91" t="n"/>
       <c r="JG58" s="100" t="inlineStr">
         <is>
-          <t>{Input_88}</t>
+          <t>{Input_113}</t>
         </is>
       </c>
       <c r="JH58" s="90" t="n"/>
@@ -6562,7 +6562,7 @@
       <c r="JN58" s="91" t="n"/>
       <c r="JO58" s="100" t="inlineStr">
         <is>
-          <t>{Input_103}</t>
+          <t>{Input_133}</t>
         </is>
       </c>
       <c r="JP58" s="90" t="n"/>
@@ -6571,7 +6571,7 @@
       <c r="JS58" s="91" t="n"/>
       <c r="JT58" s="100" t="inlineStr">
         <is>
-          <t>{Input_118}</t>
+          <t>{Input_153}</t>
         </is>
       </c>
       <c r="JU58" s="90" t="n"/>
@@ -6861,7 +6861,7 @@
       <c r="HB62" s="91" t="n"/>
       <c r="HC62" s="100" t="inlineStr">
         <is>
-          <t>{Input_29}</t>
+          <t>{Input_34}</t>
         </is>
       </c>
       <c r="HD62" s="90" t="n"/>
@@ -6880,7 +6880,7 @@
       <c r="HQ62" s="91" t="n"/>
       <c r="HR62" s="100" t="inlineStr">
         <is>
-          <t>{Input_44}</t>
+          <t>{Input_54}</t>
         </is>
       </c>
       <c r="HS62" s="90" t="n"/>
@@ -6897,7 +6897,7 @@
       <c r="ID62" s="91" t="n"/>
       <c r="IE62" s="100" t="inlineStr">
         <is>
-          <t>{Input_59}</t>
+          <t>{Input_74}</t>
         </is>
       </c>
       <c r="IF62" s="90" t="n"/>
@@ -6924,7 +6924,7 @@
       <c r="JA62" s="91" t="n"/>
       <c r="JB62" s="100" t="inlineStr">
         <is>
-          <t>{Input_74}</t>
+          <t>{Input_94}</t>
         </is>
       </c>
       <c r="JC62" s="90" t="n"/>
@@ -6933,7 +6933,7 @@
       <c r="JF62" s="91" t="n"/>
       <c r="JG62" s="100" t="inlineStr">
         <is>
-          <t>{Input_89}</t>
+          <t>{Input_114}</t>
         </is>
       </c>
       <c r="JH62" s="90" t="n"/>
@@ -6945,7 +6945,7 @@
       <c r="JN62" s="91" t="n"/>
       <c r="JO62" s="100" t="inlineStr">
         <is>
-          <t>{Input_104}</t>
+          <t>{Input_134}</t>
         </is>
       </c>
       <c r="JP62" s="90" t="n"/>
@@ -6954,7 +6954,7 @@
       <c r="JS62" s="91" t="n"/>
       <c r="JT62" s="100" t="inlineStr">
         <is>
-          <t>{Input_119}</t>
+          <t>{Input_154}</t>
         </is>
       </c>
       <c r="JU62" s="90" t="n"/>
@@ -7237,7 +7237,7 @@
       <c r="HB66" s="91" t="n"/>
       <c r="HC66" s="100" t="inlineStr">
         <is>
-          <t>{Input_30}</t>
+          <t>{Input_35}</t>
         </is>
       </c>
       <c r="HD66" s="90" t="n"/>
@@ -7256,7 +7256,7 @@
       <c r="HQ66" s="91" t="n"/>
       <c r="HR66" s="100" t="inlineStr">
         <is>
-          <t>{Input_45}</t>
+          <t>{Input_55}</t>
         </is>
       </c>
       <c r="HS66" s="90" t="n"/>
@@ -7273,7 +7273,7 @@
       <c r="ID66" s="91" t="n"/>
       <c r="IE66" s="100" t="inlineStr">
         <is>
-          <t>{Input_60}</t>
+          <t>{Input_75}</t>
         </is>
       </c>
       <c r="IF66" s="90" t="n"/>
@@ -7300,7 +7300,7 @@
       <c r="JA66" s="91" t="n"/>
       <c r="JB66" s="100" t="inlineStr">
         <is>
-          <t>{Input_75}</t>
+          <t>{Input_95}</t>
         </is>
       </c>
       <c r="JC66" s="90" t="n"/>
@@ -7309,7 +7309,7 @@
       <c r="JF66" s="91" t="n"/>
       <c r="JG66" s="100" t="inlineStr">
         <is>
-          <t>{Input_90}</t>
+          <t>{Input_115}</t>
         </is>
       </c>
       <c r="JH66" s="90" t="n"/>
@@ -7321,7 +7321,7 @@
       <c r="JN66" s="91" t="n"/>
       <c r="JO66" s="100" t="inlineStr">
         <is>
-          <t>{Input_105}</t>
+          <t>{Input_135}</t>
         </is>
       </c>
       <c r="JP66" s="90" t="n"/>
@@ -7330,7 +7330,7 @@
       <c r="JS66" s="91" t="n"/>
       <c r="JT66" s="100" t="inlineStr">
         <is>
-          <t>{Input_120}</t>
+          <t>{Input_155}</t>
         </is>
       </c>
       <c r="JU66" s="90" t="n"/>
@@ -7613,7 +7613,7 @@
       <c r="HB70" s="91" t="n"/>
       <c r="HC70" s="100" t="inlineStr">
         <is>
-          <t>{Input_31}</t>
+          <t>{Input_36}</t>
         </is>
       </c>
       <c r="HD70" s="90" t="n"/>
@@ -7632,7 +7632,7 @@
       <c r="HQ70" s="91" t="n"/>
       <c r="HR70" s="100" t="inlineStr">
         <is>
-          <t>{Input_46}</t>
+          <t>{Input_56}</t>
         </is>
       </c>
       <c r="HS70" s="90" t="n"/>
@@ -7649,7 +7649,7 @@
       <c r="ID70" s="91" t="n"/>
       <c r="IE70" s="100" t="inlineStr">
         <is>
-          <t>{Input_61}</t>
+          <t>{Input_76}</t>
         </is>
       </c>
       <c r="IF70" s="90" t="n"/>
@@ -7676,7 +7676,7 @@
       <c r="JA70" s="91" t="n"/>
       <c r="JB70" s="100" t="inlineStr">
         <is>
-          <t>{Input_76}</t>
+          <t>{Input_96}</t>
         </is>
       </c>
       <c r="JC70" s="90" t="n"/>
@@ -7685,7 +7685,7 @@
       <c r="JF70" s="91" t="n"/>
       <c r="JG70" s="100" t="inlineStr">
         <is>
-          <t>{Input_91}</t>
+          <t>{Input_116}</t>
         </is>
       </c>
       <c r="JH70" s="90" t="n"/>
@@ -7697,7 +7697,7 @@
       <c r="JN70" s="91" t="n"/>
       <c r="JO70" s="100" t="inlineStr">
         <is>
-          <t>{Input_106}</t>
+          <t>{Input_136}</t>
         </is>
       </c>
       <c r="JP70" s="90" t="n"/>
@@ -7706,7 +7706,7 @@
       <c r="JS70" s="91" t="n"/>
       <c r="JT70" s="100" t="inlineStr">
         <is>
-          <t>{Input_121}</t>
+          <t>{Input_156}</t>
         </is>
       </c>
       <c r="JU70" s="90" t="n"/>
@@ -7989,7 +7989,7 @@
       <c r="HB74" s="91" t="n"/>
       <c r="HC74" s="100" t="inlineStr">
         <is>
-          <t>{Input_32}</t>
+          <t>{Input_37}</t>
         </is>
       </c>
       <c r="HD74" s="90" t="n"/>
@@ -8008,7 +8008,7 @@
       <c r="HQ74" s="91" t="n"/>
       <c r="HR74" s="100" t="inlineStr">
         <is>
-          <t>{Input_47}</t>
+          <t>{Input_57}</t>
         </is>
       </c>
       <c r="HS74" s="90" t="n"/>
@@ -8025,7 +8025,7 @@
       <c r="ID74" s="91" t="n"/>
       <c r="IE74" s="100" t="inlineStr">
         <is>
-          <t>{Input_62}</t>
+          <t>{Input_77}</t>
         </is>
       </c>
       <c r="IF74" s="90" t="n"/>
@@ -8052,7 +8052,7 @@
       <c r="JA74" s="91" t="n"/>
       <c r="JB74" s="100" t="inlineStr">
         <is>
-          <t>{Input_77}</t>
+          <t>{Input_97}</t>
         </is>
       </c>
       <c r="JC74" s="90" t="n"/>
@@ -8061,7 +8061,7 @@
       <c r="JF74" s="91" t="n"/>
       <c r="JG74" s="100" t="inlineStr">
         <is>
-          <t>{Input_92}</t>
+          <t>{Input_117}</t>
         </is>
       </c>
       <c r="JH74" s="90" t="n"/>
@@ -8073,7 +8073,7 @@
       <c r="JN74" s="91" t="n"/>
       <c r="JO74" s="100" t="inlineStr">
         <is>
-          <t>{Input_107}</t>
+          <t>{Input_137}</t>
         </is>
       </c>
       <c r="JP74" s="90" t="n"/>
@@ -8082,7 +8082,7 @@
       <c r="JS74" s="91" t="n"/>
       <c r="JT74" s="100" t="inlineStr">
         <is>
-          <t>{Input_122}</t>
+          <t>{Input_157}</t>
         </is>
       </c>
       <c r="JU74" s="90" t="n"/>
@@ -8365,7 +8365,7 @@
       <c r="HB78" s="91" t="n"/>
       <c r="HC78" s="100" t="inlineStr">
         <is>
-          <t>{Input_33}</t>
+          <t>{Input_38}</t>
         </is>
       </c>
       <c r="HD78" s="90" t="n"/>
@@ -8384,7 +8384,7 @@
       <c r="HQ78" s="91" t="n"/>
       <c r="HR78" s="100" t="inlineStr">
         <is>
-          <t>{Input_48}</t>
+          <t>{Input_58}</t>
         </is>
       </c>
       <c r="HS78" s="90" t="n"/>
@@ -8401,7 +8401,7 @@
       <c r="ID78" s="91" t="n"/>
       <c r="IE78" s="100" t="inlineStr">
         <is>
-          <t>{Input_63}</t>
+          <t>{Input_78}</t>
         </is>
       </c>
       <c r="IF78" s="90" t="n"/>
@@ -8428,7 +8428,7 @@
       <c r="JA78" s="91" t="n"/>
       <c r="JB78" s="100" t="inlineStr">
         <is>
-          <t>{Input_78}</t>
+          <t>{Input_98}</t>
         </is>
       </c>
       <c r="JC78" s="90" t="n"/>
@@ -8437,7 +8437,7 @@
       <c r="JF78" s="91" t="n"/>
       <c r="JG78" s="100" t="inlineStr">
         <is>
-          <t>{Input_93}</t>
+          <t>{Input_118}</t>
         </is>
       </c>
       <c r="JH78" s="90" t="n"/>
@@ -8449,7 +8449,7 @@
       <c r="JN78" s="91" t="n"/>
       <c r="JO78" s="100" t="inlineStr">
         <is>
-          <t>{Input_108}</t>
+          <t>{Input_138}</t>
         </is>
       </c>
       <c r="JP78" s="90" t="n"/>
@@ -8458,7 +8458,7 @@
       <c r="JS78" s="91" t="n"/>
       <c r="JT78" s="100" t="inlineStr">
         <is>
-          <t>{Input_123}</t>
+          <t>{Input_158}</t>
         </is>
       </c>
       <c r="JU78" s="90" t="n"/>
@@ -8729,13 +8729,21 @@
       <c r="GT82" s="82" t="n"/>
       <c r="GU82" s="82" t="n"/>
       <c r="GV82" s="82" t="n"/>
-      <c r="GW82" s="100" t="n"/>
+      <c r="GW82" s="100" t="inlineStr">
+        <is>
+          <t>{Input_19}</t>
+        </is>
+      </c>
       <c r="GX82" s="90" t="n"/>
       <c r="GY82" s="90" t="n"/>
       <c r="GZ82" s="90" t="n"/>
       <c r="HA82" s="90" t="n"/>
       <c r="HB82" s="91" t="n"/>
-      <c r="HC82" s="100" t="n"/>
+      <c r="HC82" s="100" t="inlineStr">
+        <is>
+          <t>{Input_39}</t>
+        </is>
+      </c>
       <c r="HD82" s="90" t="n"/>
       <c r="HE82" s="90" t="n"/>
       <c r="HF82" s="90" t="n"/>
@@ -8750,7 +8758,11 @@
       <c r="HO82" s="90" t="n"/>
       <c r="HP82" s="90" t="n"/>
       <c r="HQ82" s="91" t="n"/>
-      <c r="HR82" s="100" t="n"/>
+      <c r="HR82" s="100" t="inlineStr">
+        <is>
+          <t>{Input_59}</t>
+        </is>
+      </c>
       <c r="HS82" s="90" t="n"/>
       <c r="HT82" s="90" t="n"/>
       <c r="HU82" s="90" t="n"/>
@@ -8763,7 +8775,11 @@
       <c r="IB82" s="90" t="n"/>
       <c r="IC82" s="90" t="n"/>
       <c r="ID82" s="91" t="n"/>
-      <c r="IE82" s="100" t="n"/>
+      <c r="IE82" s="100" t="inlineStr">
+        <is>
+          <t>{Input_79}</t>
+        </is>
+      </c>
       <c r="IF82" s="90" t="n"/>
       <c r="IG82" s="90" t="n"/>
       <c r="IH82" s="90" t="n"/>
@@ -8786,12 +8802,20 @@
       <c r="IY82" s="90" t="n"/>
       <c r="IZ82" s="90" t="n"/>
       <c r="JA82" s="91" t="n"/>
-      <c r="JB82" s="100" t="n"/>
+      <c r="JB82" s="100" t="inlineStr">
+        <is>
+          <t>{Input_99}</t>
+        </is>
+      </c>
       <c r="JC82" s="90" t="n"/>
       <c r="JD82" s="90" t="n"/>
       <c r="JE82" s="90" t="n"/>
       <c r="JF82" s="91" t="n"/>
-      <c r="JG82" s="100" t="n"/>
+      <c r="JG82" s="100" t="inlineStr">
+        <is>
+          <t>{Input_119}</t>
+        </is>
+      </c>
       <c r="JH82" s="90" t="n"/>
       <c r="JI82" s="90" t="n"/>
       <c r="JJ82" s="90" t="n"/>
@@ -8799,12 +8823,20 @@
       <c r="JL82" s="90" t="n"/>
       <c r="JM82" s="90" t="n"/>
       <c r="JN82" s="91" t="n"/>
-      <c r="JO82" s="100" t="n"/>
+      <c r="JO82" s="100" t="inlineStr">
+        <is>
+          <t>{Input_139}</t>
+        </is>
+      </c>
       <c r="JP82" s="90" t="n"/>
       <c r="JQ82" s="90" t="n"/>
       <c r="JR82" s="90" t="n"/>
       <c r="JS82" s="91" t="n"/>
-      <c r="JT82" s="100" t="n"/>
+      <c r="JT82" s="100" t="inlineStr">
+        <is>
+          <t>{Input_159}</t>
+        </is>
+      </c>
       <c r="JU82" s="90" t="n"/>
       <c r="JV82" s="90" t="n"/>
       <c r="JW82" s="90" t="n"/>
@@ -9073,13 +9105,21 @@
       <c r="GT86" s="82" t="n"/>
       <c r="GU86" s="82" t="n"/>
       <c r="GV86" s="82" t="n"/>
-      <c r="GW86" s="100" t="n"/>
+      <c r="GW86" s="100" t="inlineStr">
+        <is>
+          <t>{Input_20}</t>
+        </is>
+      </c>
       <c r="GX86" s="90" t="n"/>
       <c r="GY86" s="90" t="n"/>
       <c r="GZ86" s="90" t="n"/>
       <c r="HA86" s="90" t="n"/>
       <c r="HB86" s="91" t="n"/>
-      <c r="HC86" s="100" t="n"/>
+      <c r="HC86" s="100" t="inlineStr">
+        <is>
+          <t>{Input_40}</t>
+        </is>
+      </c>
       <c r="HD86" s="90" t="n"/>
       <c r="HE86" s="90" t="n"/>
       <c r="HF86" s="90" t="n"/>
@@ -9094,7 +9134,11 @@
       <c r="HO86" s="90" t="n"/>
       <c r="HP86" s="90" t="n"/>
       <c r="HQ86" s="91" t="n"/>
-      <c r="HR86" s="100" t="n"/>
+      <c r="HR86" s="100" t="inlineStr">
+        <is>
+          <t>{Input_60}</t>
+        </is>
+      </c>
       <c r="HS86" s="90" t="n"/>
       <c r="HT86" s="90" t="n"/>
       <c r="HU86" s="90" t="n"/>
@@ -9107,7 +9151,11 @@
       <c r="IB86" s="90" t="n"/>
       <c r="IC86" s="90" t="n"/>
       <c r="ID86" s="91" t="n"/>
-      <c r="IE86" s="100" t="n"/>
+      <c r="IE86" s="100" t="inlineStr">
+        <is>
+          <t>{Input_80}</t>
+        </is>
+      </c>
       <c r="IF86" s="90" t="n"/>
       <c r="IG86" s="90" t="n"/>
       <c r="IH86" s="90" t="n"/>
@@ -9130,12 +9178,20 @@
       <c r="IY86" s="90" t="n"/>
       <c r="IZ86" s="90" t="n"/>
       <c r="JA86" s="91" t="n"/>
-      <c r="JB86" s="100" t="n"/>
+      <c r="JB86" s="100" t="inlineStr">
+        <is>
+          <t>{Input_100}</t>
+        </is>
+      </c>
       <c r="JC86" s="90" t="n"/>
       <c r="JD86" s="90" t="n"/>
       <c r="JE86" s="90" t="n"/>
       <c r="JF86" s="91" t="n"/>
-      <c r="JG86" s="100" t="n"/>
+      <c r="JG86" s="100" t="inlineStr">
+        <is>
+          <t>{Input_120}</t>
+        </is>
+      </c>
       <c r="JH86" s="90" t="n"/>
       <c r="JI86" s="90" t="n"/>
       <c r="JJ86" s="90" t="n"/>
@@ -9143,12 +9199,20 @@
       <c r="JL86" s="90" t="n"/>
       <c r="JM86" s="90" t="n"/>
       <c r="JN86" s="91" t="n"/>
-      <c r="JO86" s="100" t="n"/>
+      <c r="JO86" s="100" t="inlineStr">
+        <is>
+          <t>{Input_140}</t>
+        </is>
+      </c>
       <c r="JP86" s="90" t="n"/>
       <c r="JQ86" s="90" t="n"/>
       <c r="JR86" s="90" t="n"/>
       <c r="JS86" s="91" t="n"/>
-      <c r="JT86" s="100" t="n"/>
+      <c r="JT86" s="100" t="inlineStr">
+        <is>
+          <t>{Input_160}</t>
+        </is>
+      </c>
       <c r="JU86" s="90" t="n"/>
       <c r="JV86" s="90" t="n"/>
       <c r="JW86" s="90" t="n"/>
@@ -9417,13 +9481,21 @@
       <c r="GT90" s="82" t="n"/>
       <c r="GU90" s="82" t="n"/>
       <c r="GV90" s="82" t="n"/>
-      <c r="GW90" s="100" t="n"/>
+      <c r="GW90" s="100" t="inlineStr">
+        <is>
+          <t>{Input_21}</t>
+        </is>
+      </c>
       <c r="GX90" s="90" t="n"/>
       <c r="GY90" s="90" t="n"/>
       <c r="GZ90" s="90" t="n"/>
       <c r="HA90" s="90" t="n"/>
       <c r="HB90" s="91" t="n"/>
-      <c r="HC90" s="100" t="n"/>
+      <c r="HC90" s="100" t="inlineStr">
+        <is>
+          <t>{Input_41}</t>
+        </is>
+      </c>
       <c r="HD90" s="90" t="n"/>
       <c r="HE90" s="90" t="n"/>
       <c r="HF90" s="90" t="n"/>
@@ -9438,7 +9510,11 @@
       <c r="HO90" s="90" t="n"/>
       <c r="HP90" s="90" t="n"/>
       <c r="HQ90" s="91" t="n"/>
-      <c r="HR90" s="100" t="n"/>
+      <c r="HR90" s="100" t="inlineStr">
+        <is>
+          <t>{Input_61}</t>
+        </is>
+      </c>
       <c r="HS90" s="90" t="n"/>
       <c r="HT90" s="90" t="n"/>
       <c r="HU90" s="90" t="n"/>
@@ -9451,7 +9527,11 @@
       <c r="IB90" s="90" t="n"/>
       <c r="IC90" s="90" t="n"/>
       <c r="ID90" s="91" t="n"/>
-      <c r="IE90" s="100" t="n"/>
+      <c r="IE90" s="100" t="inlineStr">
+        <is>
+          <t>{Input_81}</t>
+        </is>
+      </c>
       <c r="IF90" s="90" t="n"/>
       <c r="IG90" s="90" t="n"/>
       <c r="IH90" s="90" t="n"/>
@@ -9474,12 +9554,20 @@
       <c r="IY90" s="90" t="n"/>
       <c r="IZ90" s="90" t="n"/>
       <c r="JA90" s="91" t="n"/>
-      <c r="JB90" s="100" t="n"/>
+      <c r="JB90" s="100" t="inlineStr">
+        <is>
+          <t>{Input_101}</t>
+        </is>
+      </c>
       <c r="JC90" s="90" t="n"/>
       <c r="JD90" s="90" t="n"/>
       <c r="JE90" s="90" t="n"/>
       <c r="JF90" s="91" t="n"/>
-      <c r="JG90" s="100" t="n"/>
+      <c r="JG90" s="100" t="inlineStr">
+        <is>
+          <t>{Input_121}</t>
+        </is>
+      </c>
       <c r="JH90" s="90" t="n"/>
       <c r="JI90" s="90" t="n"/>
       <c r="JJ90" s="90" t="n"/>
@@ -9487,12 +9575,20 @@
       <c r="JL90" s="90" t="n"/>
       <c r="JM90" s="90" t="n"/>
       <c r="JN90" s="91" t="n"/>
-      <c r="JO90" s="100" t="n"/>
+      <c r="JO90" s="100" t="inlineStr">
+        <is>
+          <t>{Input_141}</t>
+        </is>
+      </c>
       <c r="JP90" s="90" t="n"/>
       <c r="JQ90" s="90" t="n"/>
       <c r="JR90" s="90" t="n"/>
       <c r="JS90" s="91" t="n"/>
-      <c r="JT90" s="100" t="n"/>
+      <c r="JT90" s="100" t="inlineStr">
+        <is>
+          <t>{Input_161}</t>
+        </is>
+      </c>
       <c r="JU90" s="90" t="n"/>
       <c r="JV90" s="90" t="n"/>
       <c r="JW90" s="90" t="n"/>
@@ -9761,13 +9857,21 @@
       <c r="GT94" s="82" t="n"/>
       <c r="GU94" s="82" t="n"/>
       <c r="GV94" s="82" t="n"/>
-      <c r="GW94" s="100" t="n"/>
+      <c r="GW94" s="100" t="inlineStr">
+        <is>
+          <t>{Input_22}</t>
+        </is>
+      </c>
       <c r="GX94" s="90" t="n"/>
       <c r="GY94" s="90" t="n"/>
       <c r="GZ94" s="90" t="n"/>
       <c r="HA94" s="90" t="n"/>
       <c r="HB94" s="91" t="n"/>
-      <c r="HC94" s="100" t="n"/>
+      <c r="HC94" s="100" t="inlineStr">
+        <is>
+          <t>{Input_42}</t>
+        </is>
+      </c>
       <c r="HD94" s="90" t="n"/>
       <c r="HE94" s="90" t="n"/>
       <c r="HF94" s="90" t="n"/>
@@ -9782,7 +9886,11 @@
       <c r="HO94" s="90" t="n"/>
       <c r="HP94" s="90" t="n"/>
       <c r="HQ94" s="91" t="n"/>
-      <c r="HR94" s="100" t="n"/>
+      <c r="HR94" s="100" t="inlineStr">
+        <is>
+          <t>{Input_62}</t>
+        </is>
+      </c>
       <c r="HS94" s="90" t="n"/>
       <c r="HT94" s="90" t="n"/>
       <c r="HU94" s="90" t="n"/>
@@ -9795,7 +9903,11 @@
       <c r="IB94" s="90" t="n"/>
       <c r="IC94" s="90" t="n"/>
       <c r="ID94" s="91" t="n"/>
-      <c r="IE94" s="100" t="n"/>
+      <c r="IE94" s="100" t="inlineStr">
+        <is>
+          <t>{Input_82}</t>
+        </is>
+      </c>
       <c r="IF94" s="90" t="n"/>
       <c r="IG94" s="90" t="n"/>
       <c r="IH94" s="90" t="n"/>
@@ -9818,12 +9930,20 @@
       <c r="IY94" s="90" t="n"/>
       <c r="IZ94" s="90" t="n"/>
       <c r="JA94" s="91" t="n"/>
-      <c r="JB94" s="100" t="n"/>
+      <c r="JB94" s="100" t="inlineStr">
+        <is>
+          <t>{Input_102}</t>
+        </is>
+      </c>
       <c r="JC94" s="90" t="n"/>
       <c r="JD94" s="90" t="n"/>
       <c r="JE94" s="90" t="n"/>
       <c r="JF94" s="91" t="n"/>
-      <c r="JG94" s="100" t="n"/>
+      <c r="JG94" s="100" t="inlineStr">
+        <is>
+          <t>{Input_122}</t>
+        </is>
+      </c>
       <c r="JH94" s="90" t="n"/>
       <c r="JI94" s="90" t="n"/>
       <c r="JJ94" s="90" t="n"/>
@@ -9831,12 +9951,20 @@
       <c r="JL94" s="90" t="n"/>
       <c r="JM94" s="90" t="n"/>
       <c r="JN94" s="91" t="n"/>
-      <c r="JO94" s="100" t="n"/>
+      <c r="JO94" s="100" t="inlineStr">
+        <is>
+          <t>{Input_142}</t>
+        </is>
+      </c>
       <c r="JP94" s="90" t="n"/>
       <c r="JQ94" s="90" t="n"/>
       <c r="JR94" s="90" t="n"/>
       <c r="JS94" s="91" t="n"/>
-      <c r="JT94" s="100" t="n"/>
+      <c r="JT94" s="100" t="inlineStr">
+        <is>
+          <t>{Input_162}</t>
+        </is>
+      </c>
       <c r="JU94" s="90" t="n"/>
       <c r="JV94" s="90" t="n"/>
       <c r="JW94" s="90" t="n"/>
@@ -10105,13 +10233,21 @@
       <c r="GT98" s="82" t="n"/>
       <c r="GU98" s="82" t="n"/>
       <c r="GV98" s="82" t="n"/>
-      <c r="GW98" s="100" t="n"/>
+      <c r="GW98" s="100" t="inlineStr">
+        <is>
+          <t>{Input_23}</t>
+        </is>
+      </c>
       <c r="GX98" s="90" t="n"/>
       <c r="GY98" s="90" t="n"/>
       <c r="GZ98" s="90" t="n"/>
       <c r="HA98" s="90" t="n"/>
       <c r="HB98" s="91" t="n"/>
-      <c r="HC98" s="100" t="n"/>
+      <c r="HC98" s="100" t="inlineStr">
+        <is>
+          <t>{Input_43}</t>
+        </is>
+      </c>
       <c r="HD98" s="90" t="n"/>
       <c r="HE98" s="90" t="n"/>
       <c r="HF98" s="90" t="n"/>
@@ -10126,7 +10262,11 @@
       <c r="HO98" s="90" t="n"/>
       <c r="HP98" s="90" t="n"/>
       <c r="HQ98" s="91" t="n"/>
-      <c r="HR98" s="100" t="n"/>
+      <c r="HR98" s="100" t="inlineStr">
+        <is>
+          <t>{Input_63}</t>
+        </is>
+      </c>
       <c r="HS98" s="90" t="n"/>
       <c r="HT98" s="90" t="n"/>
       <c r="HU98" s="90" t="n"/>
@@ -10139,7 +10279,11 @@
       <c r="IB98" s="90" t="n"/>
       <c r="IC98" s="90" t="n"/>
       <c r="ID98" s="91" t="n"/>
-      <c r="IE98" s="100" t="n"/>
+      <c r="IE98" s="100" t="inlineStr">
+        <is>
+          <t>{Input_83}</t>
+        </is>
+      </c>
       <c r="IF98" s="90" t="n"/>
       <c r="IG98" s="90" t="n"/>
       <c r="IH98" s="90" t="n"/>
@@ -10162,12 +10306,20 @@
       <c r="IY98" s="90" t="n"/>
       <c r="IZ98" s="90" t="n"/>
       <c r="JA98" s="91" t="n"/>
-      <c r="JB98" s="100" t="n"/>
+      <c r="JB98" s="100" t="inlineStr">
+        <is>
+          <t>{Input_103}</t>
+        </is>
+      </c>
       <c r="JC98" s="90" t="n"/>
       <c r="JD98" s="90" t="n"/>
       <c r="JE98" s="90" t="n"/>
       <c r="JF98" s="91" t="n"/>
-      <c r="JG98" s="100" t="n"/>
+      <c r="JG98" s="100" t="inlineStr">
+        <is>
+          <t>{Input_123}</t>
+        </is>
+      </c>
       <c r="JH98" s="90" t="n"/>
       <c r="JI98" s="90" t="n"/>
       <c r="JJ98" s="90" t="n"/>
@@ -10175,12 +10327,20 @@
       <c r="JL98" s="90" t="n"/>
       <c r="JM98" s="90" t="n"/>
       <c r="JN98" s="91" t="n"/>
-      <c r="JO98" s="100" t="n"/>
+      <c r="JO98" s="100" t="inlineStr">
+        <is>
+          <t>{Input_143}</t>
+        </is>
+      </c>
       <c r="JP98" s="90" t="n"/>
       <c r="JQ98" s="90" t="n"/>
       <c r="JR98" s="90" t="n"/>
       <c r="JS98" s="91" t="n"/>
-      <c r="JT98" s="100" t="n"/>
+      <c r="JT98" s="100" t="inlineStr">
+        <is>
+          <t>{Input_163}</t>
+        </is>
+      </c>
       <c r="JU98" s="90" t="n"/>
       <c r="JV98" s="90" t="n"/>
       <c r="JW98" s="90" t="n"/>
@@ -12097,7 +12257,7 @@
       <c r="HB109" s="90" t="n"/>
       <c r="HC109" s="102" t="inlineStr">
         <is>
-          <t>{Input_124}</t>
+          <t>{Input_164}</t>
         </is>
       </c>
       <c r="HD109" s="90" t="n"/>
@@ -13405,7 +13565,7 @@
       <c r="GV138" s="82" t="n"/>
       <c r="GW138" s="100" t="inlineStr">
         <is>
-          <t>{Input_130}</t>
+          <t>{Input_170}</t>
         </is>
       </c>
       <c r="GX138" s="90" t="n"/>
@@ -13414,7 +13574,7 @@
       <c r="HA138" s="91" t="n"/>
       <c r="HB138" s="100" t="inlineStr">
         <is>
-          <t>{Input_131}</t>
+          <t>{Input_171}</t>
         </is>
       </c>
       <c r="HC138" s="90" t="n"/>
@@ -13428,7 +13588,7 @@
       <c r="HK138" s="91" t="n"/>
       <c r="HL138" s="100" t="inlineStr">
         <is>
-          <t>{Input_132}</t>
+          <t>{Input_172}</t>
         </is>
       </c>
       <c r="HM138" s="90" t="n"/>
@@ -13463,7 +13623,7 @@
       <c r="IP138" s="91" t="n"/>
       <c r="IQ138" s="100" t="inlineStr">
         <is>
-          <t>{Input_133}</t>
+          <t>{Input_173}</t>
         </is>
       </c>
       <c r="IR138" s="90" t="n"/>
@@ -13478,7 +13638,7 @@
       <c r="JA138" s="91" t="n"/>
       <c r="JB138" s="100" t="inlineStr">
         <is>
-          <t>{Input_134}</t>
+          <t>{Input_174}</t>
         </is>
       </c>
       <c r="JC138" s="90" t="n"/>
@@ -13493,7 +13653,7 @@
       <c r="JL138" s="91" t="n"/>
       <c r="JM138" s="100" t="inlineStr">
         <is>
-          <t>{Input_135}</t>
+          <t>{Input_175}</t>
         </is>
       </c>
       <c r="JN138" s="90" t="n"/>
@@ -13715,7 +13875,7 @@
       <c r="GV141" s="82" t="n"/>
       <c r="GW141" s="100" t="inlineStr">
         <is>
-          <t>{Input_136}</t>
+          <t>{Input_176}</t>
         </is>
       </c>
       <c r="GX141" s="90" t="n"/>
@@ -13724,7 +13884,7 @@
       <c r="HA141" s="91" t="n"/>
       <c r="HB141" s="100" t="inlineStr">
         <is>
-          <t>{Input_137}</t>
+          <t>{Input_177}</t>
         </is>
       </c>
       <c r="HC141" s="90" t="n"/>
@@ -13738,7 +13898,7 @@
       <c r="HK141" s="91" t="n"/>
       <c r="HL141" s="100" t="inlineStr">
         <is>
-          <t>{Input_138}</t>
+          <t>{Input_178}</t>
         </is>
       </c>
       <c r="HM141" s="90" t="n"/>
@@ -13773,7 +13933,7 @@
       <c r="IP141" s="91" t="n"/>
       <c r="IQ141" s="100" t="inlineStr">
         <is>
-          <t>{Input_139}</t>
+          <t>{Input_179}</t>
         </is>
       </c>
       <c r="IR141" s="90" t="n"/>
@@ -13788,7 +13948,7 @@
       <c r="JA141" s="91" t="n"/>
       <c r="JB141" s="100" t="inlineStr">
         <is>
-          <t>{Input_140}</t>
+          <t>{Input_180}</t>
         </is>
       </c>
       <c r="JC141" s="90" t="n"/>
@@ -13803,7 +13963,7 @@
       <c r="JL141" s="91" t="n"/>
       <c r="JM141" s="100" t="inlineStr">
         <is>
-          <t>{Input_141}</t>
+          <t>{Input_181}</t>
         </is>
       </c>
       <c r="JN141" s="90" t="n"/>
@@ -14025,7 +14185,7 @@
       <c r="GV144" s="82" t="n"/>
       <c r="GW144" s="100" t="inlineStr">
         <is>
-          <t>{Input_142}</t>
+          <t>{Input_182}</t>
         </is>
       </c>
       <c r="GX144" s="90" t="n"/>
@@ -14034,7 +14194,7 @@
       <c r="HA144" s="91" t="n"/>
       <c r="HB144" s="100" t="inlineStr">
         <is>
-          <t>{Input_143}</t>
+          <t>{Input_183}</t>
         </is>
       </c>
       <c r="HC144" s="90" t="n"/>
@@ -14048,7 +14208,7 @@
       <c r="HK144" s="91" t="n"/>
       <c r="HL144" s="100" t="inlineStr">
         <is>
-          <t>{Input_144}</t>
+          <t>{Input_184}</t>
         </is>
       </c>
       <c r="HM144" s="90" t="n"/>
@@ -14083,7 +14243,7 @@
       <c r="IP144" s="91" t="n"/>
       <c r="IQ144" s="100" t="inlineStr">
         <is>
-          <t>{Input_145}</t>
+          <t>{Input_185}</t>
         </is>
       </c>
       <c r="IR144" s="90" t="n"/>
@@ -14098,7 +14258,7 @@
       <c r="JA144" s="91" t="n"/>
       <c r="JB144" s="100" t="inlineStr">
         <is>
-          <t>{Input_146}</t>
+          <t>{Input_186}</t>
         </is>
       </c>
       <c r="JC144" s="90" t="n"/>
@@ -14113,7 +14273,7 @@
       <c r="JL144" s="91" t="n"/>
       <c r="JM144" s="100" t="inlineStr">
         <is>
-          <t>{Input_147}</t>
+          <t>{Input_187}</t>
         </is>
       </c>
       <c r="JN144" s="90" t="n"/>
@@ -14335,7 +14495,7 @@
       <c r="GV147" s="82" t="n"/>
       <c r="GW147" s="100" t="inlineStr">
         <is>
-          <t>{Input_148}</t>
+          <t>{Input_188}</t>
         </is>
       </c>
       <c r="GX147" s="90" t="n"/>
@@ -14344,7 +14504,7 @@
       <c r="HA147" s="91" t="n"/>
       <c r="HB147" s="100" t="inlineStr">
         <is>
-          <t>{Input_149}</t>
+          <t>{Input_189}</t>
         </is>
       </c>
       <c r="HC147" s="90" t="n"/>
@@ -14358,7 +14518,7 @@
       <c r="HK147" s="91" t="n"/>
       <c r="HL147" s="100" t="inlineStr">
         <is>
-          <t>{Input_150}</t>
+          <t>{Input_190}</t>
         </is>
       </c>
       <c r="HM147" s="90" t="n"/>
@@ -14393,7 +14553,7 @@
       <c r="IP147" s="91" t="n"/>
       <c r="IQ147" s="100" t="inlineStr">
         <is>
-          <t>{Input_151}</t>
+          <t>{Input_191}</t>
         </is>
       </c>
       <c r="IR147" s="90" t="n"/>
@@ -14408,7 +14568,7 @@
       <c r="JA147" s="91" t="n"/>
       <c r="JB147" s="100" t="inlineStr">
         <is>
-          <t>{Input_152}</t>
+          <t>{Input_192}</t>
         </is>
       </c>
       <c r="JC147" s="90" t="n"/>
@@ -14423,7 +14583,7 @@
       <c r="JL147" s="91" t="n"/>
       <c r="JM147" s="100" t="inlineStr">
         <is>
-          <t>{Input_153}</t>
+          <t>{Input_193}</t>
         </is>
       </c>
       <c r="JN147" s="90" t="n"/>
@@ -14645,7 +14805,7 @@
       <c r="GV150" s="82" t="n"/>
       <c r="GW150" s="100" t="inlineStr">
         <is>
-          <t>{Input_154}</t>
+          <t>{Input_194}</t>
         </is>
       </c>
       <c r="GX150" s="90" t="n"/>
@@ -14654,7 +14814,7 @@
       <c r="HA150" s="91" t="n"/>
       <c r="HB150" s="100" t="inlineStr">
         <is>
-          <t>{Input_155}</t>
+          <t>{Input_195}</t>
         </is>
       </c>
       <c r="HC150" s="90" t="n"/>
@@ -14668,7 +14828,7 @@
       <c r="HK150" s="91" t="n"/>
       <c r="HL150" s="100" t="inlineStr">
         <is>
-          <t>{Input_156}</t>
+          <t>{Input_196}</t>
         </is>
       </c>
       <c r="HM150" s="90" t="n"/>
@@ -14703,7 +14863,7 @@
       <c r="IP150" s="91" t="n"/>
       <c r="IQ150" s="100" t="inlineStr">
         <is>
-          <t>{Input_157}</t>
+          <t>{Input_197}</t>
         </is>
       </c>
       <c r="IR150" s="90" t="n"/>
@@ -14718,7 +14878,7 @@
       <c r="JA150" s="91" t="n"/>
       <c r="JB150" s="100" t="inlineStr">
         <is>
-          <t>{Input_158}</t>
+          <t>{Input_198}</t>
         </is>
       </c>
       <c r="JC150" s="90" t="n"/>
@@ -14733,7 +14893,7 @@
       <c r="JL150" s="91" t="n"/>
       <c r="JM150" s="100" t="inlineStr">
         <is>
-          <t>{Input_159}</t>
+          <t>{Input_199}</t>
         </is>
       </c>
       <c r="JN150" s="90" t="n"/>
@@ -15304,7 +15464,7 @@
       <c r="HK156" s="91" t="n"/>
       <c r="HL156" s="100" t="inlineStr">
         <is>
-          <t>{Input_125}</t>
+          <t>{Input_165}</t>
         </is>
       </c>
       <c r="HM156" s="90" t="n"/>
@@ -15577,18 +15737,18 @@
       <c r="GV159" s="82" t="n"/>
       <c r="GW159" s="104" t="inlineStr">
         <is>
-          <t>{Input_126}</t>
+          <t>{Input_166}</t>
         </is>
       </c>
       <c r="HK159" s="93" t="n"/>
       <c r="HL159" s="15" t="inlineStr">
         <is>
-          <t>{Input_127}</t>
+          <t>{Input_167}</t>
         </is>
       </c>
       <c r="IQ159" s="100" t="inlineStr">
         <is>
-          <t>{Input_128}</t>
+          <t>{Input_168}</t>
         </is>
       </c>
       <c r="IR159" s="90" t="n"/>
@@ -17733,7 +17893,7 @@
       <c r="HB194" s="90" t="n"/>
       <c r="HC194" s="102" t="inlineStr">
         <is>
-          <t>{Input_129}</t>
+          <t>{Input_169}</t>
         </is>
       </c>
       <c r="HD194" s="90" t="n"/>
@@ -19640,10 +19800,10 @@
     <mergeCell ref="JY11:KC57"/>
     <mergeCell ref="JG94:JN97"/>
     <mergeCell ref="JT66:JX69"/>
-    <mergeCell ref="HB153:HK155"/>
     <mergeCell ref="JT18:JX21"/>
     <mergeCell ref="JT30:JX33"/>
     <mergeCell ref="JM141:JX143"/>
+    <mergeCell ref="HB153:HK155"/>
     <mergeCell ref="JG22:JN25"/>
     <mergeCell ref="HR94:ID97"/>
     <mergeCell ref="IE18:JA21"/>

--- a/제작도_도면_1.xlsx
+++ b/제작도_도면_1.xlsx
@@ -998,7 +998,7 @@
     <col width="3.09765625" customWidth="1" style="88" min="1" max="297"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.95" customHeight="1" s="88">
+    <row r="1" ht="4" customHeight="1" s="88">
       <c r="U1" s="1" t="n"/>
       <c r="V1" s="1" t="n"/>
       <c r="W1" s="1" t="n"/>
@@ -1277,19 +1277,19 @@
       <c r="KJ1" s="1" t="n"/>
       <c r="KK1" s="2" t="n"/>
     </row>
-    <row r="2" ht="16.95" customHeight="1" s="88">
+    <row r="2" ht="4" customHeight="1" s="88">
       <c r="KK2" s="4" t="n"/>
     </row>
-    <row r="3" ht="16.95" customHeight="1" s="88">
+    <row r="3" ht="4" customHeight="1" s="88">
       <c r="KK3" s="4" t="n"/>
     </row>
-    <row r="4" ht="16.95" customHeight="1" s="88">
+    <row r="4" ht="4" customHeight="1" s="88">
       <c r="KK4" s="4" t="n"/>
     </row>
-    <row r="5" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="5" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="KK5" s="4" t="n"/>
     </row>
-    <row r="6" ht="16.95" customHeight="1" s="88">
+    <row r="6" ht="4" customHeight="1" s="88">
       <c r="U6" s="89" t="n">
         <v>1</v>
       </c>
@@ -1570,7 +1570,7 @@
       <c r="JZ6" s="8" t="n"/>
       <c r="KK6" s="4" t="n"/>
     </row>
-    <row r="7" ht="16.95" customHeight="1" s="88">
+    <row r="7" ht="4" customHeight="1" s="88">
       <c r="U7" s="92" t="n"/>
       <c r="BL7" s="93" t="n"/>
       <c r="BM7" s="92" t="n"/>
@@ -1587,7 +1587,7 @@
       <c r="JZ7" s="8" t="n"/>
       <c r="KK7" s="4" t="n"/>
     </row>
-    <row r="8" ht="16.95" customHeight="1" s="88">
+    <row r="8" ht="4" customHeight="1" s="88">
       <c r="U8" s="92" t="n"/>
       <c r="BL8" s="93" t="n"/>
       <c r="BM8" s="92" t="n"/>
@@ -1604,7 +1604,7 @@
       <c r="JZ8" s="8" t="n"/>
       <c r="KK8" s="4" t="n"/>
     </row>
-    <row r="9" ht="16.95" customHeight="1" s="88">
+    <row r="9" ht="4" customHeight="1" s="88">
       <c r="U9" s="92" t="n"/>
       <c r="BL9" s="93" t="n"/>
       <c r="BM9" s="92" t="n"/>
@@ -1621,7 +1621,7 @@
       <c r="JZ9" s="8" t="n"/>
       <c r="KK9" s="4" t="n"/>
     </row>
-    <row r="10" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="10" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="U10" s="94" t="n"/>
       <c r="V10" s="95" t="n"/>
       <c r="W10" s="95" t="n"/>
@@ -1891,7 +1891,7 @@
       <c r="KA10" s="6" t="n"/>
       <c r="KK10" s="4" t="n"/>
     </row>
-    <row r="11" ht="16.95" customHeight="1" s="88">
+    <row r="11" ht="4" customHeight="1" s="88">
       <c r="A11" s="3" t="n"/>
       <c r="P11" s="89" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
       <c r="KC11" s="91" t="n"/>
       <c r="KK11" s="4" t="n"/>
     </row>
-    <row r="12" ht="16.95" customHeight="1" s="88">
+    <row r="12" ht="4" customHeight="1" s="88">
       <c r="A12" s="3" t="n"/>
       <c r="P12" s="92" t="n"/>
       <c r="T12" s="93" t="n"/>
@@ -2271,7 +2271,7 @@
       <c r="KC12" s="93" t="n"/>
       <c r="KK12" s="4" t="n"/>
     </row>
-    <row r="13" ht="16.95" customHeight="1" s="88">
+    <row r="13" ht="4" customHeight="1" s="88">
       <c r="A13" s="3" t="n"/>
       <c r="P13" s="92" t="n"/>
       <c r="T13" s="93" t="n"/>
@@ -2445,7 +2445,7 @@
       <c r="KC13" s="93" t="n"/>
       <c r="KK13" s="4" t="n"/>
     </row>
-    <row r="14" ht="16.95" customHeight="1" s="88">
+    <row r="14" ht="4" customHeight="1" s="88">
       <c r="A14" s="3" t="n"/>
       <c r="P14" s="92" t="n"/>
       <c r="T14" s="93" t="n"/>
@@ -2619,7 +2619,7 @@
       <c r="KC14" s="93" t="n"/>
       <c r="KK14" s="4" t="n"/>
     </row>
-    <row r="15" ht="16.95" customHeight="1" s="88">
+    <row r="15" ht="4" customHeight="1" s="88">
       <c r="A15" s="3" t="n"/>
       <c r="P15" s="92" t="n"/>
       <c r="T15" s="93" t="n"/>
@@ -2793,7 +2793,7 @@
       <c r="KC15" s="93" t="n"/>
       <c r="KK15" s="4" t="n"/>
     </row>
-    <row r="16" ht="16.95" customHeight="1" s="88">
+    <row r="16" ht="4" customHeight="1" s="88">
       <c r="A16" s="3" t="n"/>
       <c r="P16" s="92" t="n"/>
       <c r="T16" s="93" t="n"/>
@@ -2823,7 +2823,7 @@
       <c r="KC16" s="93" t="n"/>
       <c r="KK16" s="4" t="n"/>
     </row>
-    <row r="17" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="17" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A17" s="3" t="n"/>
       <c r="P17" s="92" t="n"/>
       <c r="T17" s="93" t="n"/>
@@ -2921,7 +2921,7 @@
       <c r="KC17" s="93" t="n"/>
       <c r="KK17" s="4" t="n"/>
     </row>
-    <row r="18" ht="16.95" customHeight="1" s="88">
+    <row r="18" ht="4" customHeight="1" s="88">
       <c r="A18" s="3" t="n"/>
       <c r="P18" s="92" t="n"/>
       <c r="T18" s="93" t="n"/>
@@ -3051,7 +3051,7 @@
       <c r="KC18" s="93" t="n"/>
       <c r="KK18" s="4" t="n"/>
     </row>
-    <row r="19" ht="16.95" customHeight="1" s="88">
+    <row r="19" ht="4" customHeight="1" s="88">
       <c r="A19" s="3" t="n"/>
       <c r="P19" s="92" t="n"/>
       <c r="T19" s="93" t="n"/>
@@ -3084,7 +3084,7 @@
       <c r="KC19" s="93" t="n"/>
       <c r="KK19" s="4" t="n"/>
     </row>
-    <row r="20" ht="16.95" customHeight="1" s="88">
+    <row r="20" ht="4" customHeight="1" s="88">
       <c r="A20" s="3" t="n"/>
       <c r="P20" s="92" t="n"/>
       <c r="T20" s="93" t="n"/>
@@ -3117,7 +3117,7 @@
       <c r="KC20" s="93" t="n"/>
       <c r="KK20" s="4" t="n"/>
     </row>
-    <row r="21" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="21" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A21" s="3" t="n"/>
       <c r="P21" s="92" t="n"/>
       <c r="T21" s="93" t="n"/>
@@ -3225,7 +3225,7 @@
       <c r="KC21" s="93" t="n"/>
       <c r="KK21" s="4" t="n"/>
     </row>
-    <row r="22" ht="16.95" customHeight="1" s="88">
+    <row r="22" ht="4" customHeight="1" s="88">
       <c r="A22" s="3" t="n"/>
       <c r="P22" s="92" t="n"/>
       <c r="T22" s="93" t="n"/>
@@ -3365,7 +3365,7 @@
       <c r="KC22" s="93" t="n"/>
       <c r="KK22" s="4" t="n"/>
     </row>
-    <row r="23" ht="16.95" customHeight="1" s="88">
+    <row r="23" ht="4" customHeight="1" s="88">
       <c r="A23" s="3" t="n"/>
       <c r="P23" s="92" t="n"/>
       <c r="T23" s="93" t="n"/>
@@ -3409,7 +3409,7 @@
       <c r="KC23" s="93" t="n"/>
       <c r="KK23" s="4" t="n"/>
     </row>
-    <row r="24" ht="16.95" customHeight="1" s="88">
+    <row r="24" ht="4" customHeight="1" s="88">
       <c r="A24" s="3" t="n"/>
       <c r="P24" s="92" t="n"/>
       <c r="T24" s="93" t="n"/>
@@ -3453,7 +3453,7 @@
       <c r="KC24" s="93" t="n"/>
       <c r="KK24" s="4" t="n"/>
     </row>
-    <row r="25" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="25" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A25" s="3" t="n"/>
       <c r="P25" s="92" t="n"/>
       <c r="T25" s="93" t="n"/>
@@ -3561,7 +3561,7 @@
       <c r="KC25" s="93" t="n"/>
       <c r="KK25" s="4" t="n"/>
     </row>
-    <row r="26" ht="16.95" customHeight="1" s="88">
+    <row r="26" ht="4" customHeight="1" s="88">
       <c r="A26" s="3" t="n"/>
       <c r="P26" s="92" t="n"/>
       <c r="T26" s="93" t="n"/>
@@ -3701,7 +3701,7 @@
       <c r="KC26" s="93" t="n"/>
       <c r="KK26" s="4" t="n"/>
     </row>
-    <row r="27" ht="16.95" customHeight="1" s="88">
+    <row r="27" ht="4" customHeight="1" s="88">
       <c r="A27" s="3" t="n"/>
       <c r="P27" s="92" t="n"/>
       <c r="T27" s="93" t="n"/>
@@ -3745,7 +3745,7 @@
       <c r="KC27" s="93" t="n"/>
       <c r="KK27" s="4" t="n"/>
     </row>
-    <row r="28" ht="16.95" customHeight="1" s="88">
+    <row r="28" ht="4" customHeight="1" s="88">
       <c r="A28" s="3" t="n"/>
       <c r="P28" s="92" t="n"/>
       <c r="T28" s="93" t="n"/>
@@ -3789,7 +3789,7 @@
       <c r="KC28" s="93" t="n"/>
       <c r="KK28" s="4" t="n"/>
     </row>
-    <row r="29" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="29" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A29" s="3" t="n"/>
       <c r="P29" s="92" t="n"/>
       <c r="T29" s="93" t="n"/>
@@ -3897,7 +3897,7 @@
       <c r="KC29" s="93" t="n"/>
       <c r="KK29" s="4" t="n"/>
     </row>
-    <row r="30" ht="16.95" customHeight="1" s="88">
+    <row r="30" ht="4" customHeight="1" s="88">
       <c r="A30" s="3" t="n"/>
       <c r="P30" s="92" t="n"/>
       <c r="T30" s="93" t="n"/>
@@ -4037,7 +4037,7 @@
       <c r="KC30" s="93" t="n"/>
       <c r="KK30" s="4" t="n"/>
     </row>
-    <row r="31" ht="16.95" customHeight="1" s="88">
+    <row r="31" ht="4" customHeight="1" s="88">
       <c r="A31" s="3" t="n"/>
       <c r="P31" s="92" t="n"/>
       <c r="T31" s="93" t="n"/>
@@ -4081,7 +4081,7 @@
       <c r="KC31" s="93" t="n"/>
       <c r="KK31" s="4" t="n"/>
     </row>
-    <row r="32" ht="16.95" customHeight="1" s="88">
+    <row r="32" ht="4" customHeight="1" s="88">
       <c r="A32" s="3" t="n"/>
       <c r="P32" s="92" t="n"/>
       <c r="T32" s="93" t="n"/>
@@ -4125,7 +4125,7 @@
       <c r="KC32" s="93" t="n"/>
       <c r="KK32" s="4" t="n"/>
     </row>
-    <row r="33" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="33" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A33" s="3" t="n"/>
       <c r="P33" s="92" t="n"/>
       <c r="T33" s="93" t="n"/>
@@ -4233,7 +4233,7 @@
       <c r="KC33" s="93" t="n"/>
       <c r="KK33" s="4" t="n"/>
     </row>
-    <row r="34" ht="16.95" customHeight="1" s="88">
+    <row r="34" ht="4" customHeight="1" s="88">
       <c r="A34" s="3" t="n"/>
       <c r="P34" s="92" t="n"/>
       <c r="T34" s="93" t="n"/>
@@ -4373,7 +4373,7 @@
       <c r="KC34" s="93" t="n"/>
       <c r="KK34" s="4" t="n"/>
     </row>
-    <row r="35" ht="16.95" customHeight="1" s="88">
+    <row r="35" ht="4" customHeight="1" s="88">
       <c r="A35" s="3" t="n"/>
       <c r="P35" s="92" t="n"/>
       <c r="T35" s="93" t="n"/>
@@ -4417,7 +4417,7 @@
       <c r="KC35" s="93" t="n"/>
       <c r="KK35" s="4" t="n"/>
     </row>
-    <row r="36" ht="16.95" customHeight="1" s="88">
+    <row r="36" ht="4" customHeight="1" s="88">
       <c r="A36" s="3" t="n"/>
       <c r="P36" s="92" t="n"/>
       <c r="T36" s="93" t="n"/>
@@ -4461,7 +4461,7 @@
       <c r="KC36" s="93" t="n"/>
       <c r="KK36" s="4" t="n"/>
     </row>
-    <row r="37" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="37" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A37" s="3" t="n"/>
       <c r="P37" s="92" t="n"/>
       <c r="T37" s="93" t="n"/>
@@ -4569,7 +4569,7 @@
       <c r="KC37" s="93" t="n"/>
       <c r="KK37" s="4" t="n"/>
     </row>
-    <row r="38" ht="16.95" customHeight="1" s="88">
+    <row r="38" ht="4" customHeight="1" s="88">
       <c r="A38" s="3" t="n"/>
       <c r="P38" s="92" t="n"/>
       <c r="T38" s="93" t="n"/>
@@ -4709,7 +4709,7 @@
       <c r="KC38" s="93" t="n"/>
       <c r="KK38" s="4" t="n"/>
     </row>
-    <row r="39" ht="16.95" customHeight="1" s="88">
+    <row r="39" ht="4" customHeight="1" s="88">
       <c r="A39" s="3" t="n"/>
       <c r="P39" s="92" t="n"/>
       <c r="T39" s="93" t="n"/>
@@ -4753,7 +4753,7 @@
       <c r="KC39" s="93" t="n"/>
       <c r="KK39" s="4" t="n"/>
     </row>
-    <row r="40" ht="16.95" customHeight="1" s="88">
+    <row r="40" ht="4" customHeight="1" s="88">
       <c r="A40" s="3" t="n"/>
       <c r="P40" s="92" t="n"/>
       <c r="T40" s="93" t="n"/>
@@ -4797,7 +4797,7 @@
       <c r="KC40" s="93" t="n"/>
       <c r="KK40" s="4" t="n"/>
     </row>
-    <row r="41" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="41" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A41" s="3" t="n"/>
       <c r="P41" s="92" t="n"/>
       <c r="T41" s="93" t="n"/>
@@ -4915,7 +4915,7 @@
       <c r="KC41" s="93" t="n"/>
       <c r="KK41" s="4" t="n"/>
     </row>
-    <row r="42" ht="16.95" customHeight="1" s="88">
+    <row r="42" ht="4" customHeight="1" s="88">
       <c r="A42" s="3" t="n"/>
       <c r="P42" s="92" t="n"/>
       <c r="T42" s="93" t="n"/>
@@ -5065,7 +5065,7 @@
       <c r="KC42" s="93" t="n"/>
       <c r="KK42" s="4" t="n"/>
     </row>
-    <row r="43" ht="16.95" customHeight="1" s="88">
+    <row r="43" ht="4" customHeight="1" s="88">
       <c r="A43" s="3" t="n"/>
       <c r="P43" s="92" t="n"/>
       <c r="T43" s="93" t="n"/>
@@ -5119,7 +5119,7 @@
       <c r="KC43" s="93" t="n"/>
       <c r="KK43" s="4" t="n"/>
     </row>
-    <row r="44" ht="16.95" customHeight="1" s="88">
+    <row r="44" ht="4" customHeight="1" s="88">
       <c r="A44" s="3" t="n"/>
       <c r="P44" s="92" t="n"/>
       <c r="T44" s="93" t="n"/>
@@ -5173,7 +5173,7 @@
       <c r="KC44" s="93" t="n"/>
       <c r="KK44" s="4" t="n"/>
     </row>
-    <row r="45" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="45" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A45" s="3" t="n"/>
       <c r="P45" s="92" t="n"/>
       <c r="T45" s="93" t="n"/>
@@ -5291,7 +5291,7 @@
       <c r="KC45" s="93" t="n"/>
       <c r="KK45" s="4" t="n"/>
     </row>
-    <row r="46" ht="16.95" customHeight="1" s="88">
+    <row r="46" ht="4" customHeight="1" s="88">
       <c r="A46" s="3" t="n"/>
       <c r="P46" s="92" t="n"/>
       <c r="T46" s="93" t="n"/>
@@ -5441,7 +5441,7 @@
       <c r="KC46" s="93" t="n"/>
       <c r="KK46" s="4" t="n"/>
     </row>
-    <row r="47" ht="16.95" customHeight="1" s="88">
+    <row r="47" ht="4" customHeight="1" s="88">
       <c r="A47" s="3" t="n"/>
       <c r="P47" s="92" t="n"/>
       <c r="T47" s="93" t="n"/>
@@ -5495,7 +5495,7 @@
       <c r="KC47" s="93" t="n"/>
       <c r="KK47" s="4" t="n"/>
     </row>
-    <row r="48" ht="16.95" customHeight="1" s="88">
+    <row r="48" ht="4" customHeight="1" s="88">
       <c r="A48" s="3" t="n"/>
       <c r="P48" s="92" t="n"/>
       <c r="T48" s="93" t="n"/>
@@ -5549,7 +5549,7 @@
       <c r="KC48" s="93" t="n"/>
       <c r="KK48" s="4" t="n"/>
     </row>
-    <row r="49" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="49" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A49" s="3" t="n"/>
       <c r="P49" s="92" t="n"/>
       <c r="T49" s="93" t="n"/>
@@ -5667,7 +5667,7 @@
       <c r="KC49" s="93" t="n"/>
       <c r="KK49" s="4" t="n"/>
     </row>
-    <row r="50" ht="16.95" customHeight="1" s="88">
+    <row r="50" ht="4" customHeight="1" s="88">
       <c r="A50" s="3" t="n"/>
       <c r="P50" s="92" t="n"/>
       <c r="T50" s="93" t="n"/>
@@ -5817,7 +5817,7 @@
       <c r="KC50" s="93" t="n"/>
       <c r="KK50" s="4" t="n"/>
     </row>
-    <row r="51" ht="16.95" customHeight="1" s="88">
+    <row r="51" ht="4" customHeight="1" s="88">
       <c r="A51" s="3" t="n"/>
       <c r="P51" s="92" t="n"/>
       <c r="T51" s="93" t="n"/>
@@ -5871,7 +5871,7 @@
       <c r="KC51" s="93" t="n"/>
       <c r="KK51" s="4" t="n"/>
     </row>
-    <row r="52" ht="16.95" customHeight="1" s="88">
+    <row r="52" ht="4" customHeight="1" s="88">
       <c r="A52" s="3" t="n"/>
       <c r="P52" s="92" t="n"/>
       <c r="T52" s="93" t="n"/>
@@ -5925,7 +5925,7 @@
       <c r="KC52" s="93" t="n"/>
       <c r="KK52" s="4" t="n"/>
     </row>
-    <row r="53" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="53" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A53" s="3" t="n"/>
       <c r="P53" s="92" t="n"/>
       <c r="T53" s="93" t="n"/>
@@ -6043,7 +6043,7 @@
       <c r="KC53" s="93" t="n"/>
       <c r="KK53" s="4" t="n"/>
     </row>
-    <row r="54" ht="16.95" customHeight="1" s="88">
+    <row r="54" ht="4" customHeight="1" s="88">
       <c r="A54" s="3" t="n"/>
       <c r="P54" s="92" t="n"/>
       <c r="T54" s="93" t="n"/>
@@ -6193,7 +6193,7 @@
       <c r="KC54" s="93" t="n"/>
       <c r="KK54" s="4" t="n"/>
     </row>
-    <row r="55" ht="16.95" customHeight="1" s="88">
+    <row r="55" ht="4" customHeight="1" s="88">
       <c r="A55" s="3" t="n"/>
       <c r="P55" s="92" t="n"/>
       <c r="T55" s="93" t="n"/>
@@ -6247,7 +6247,7 @@
       <c r="KC55" s="93" t="n"/>
       <c r="KK55" s="4" t="n"/>
     </row>
-    <row r="56" ht="16.95" customHeight="1" s="88">
+    <row r="56" ht="4" customHeight="1" s="88">
       <c r="A56" s="3" t="n"/>
       <c r="P56" s="92" t="n"/>
       <c r="T56" s="93" t="n"/>
@@ -6301,7 +6301,7 @@
       <c r="KC56" s="93" t="n"/>
       <c r="KK56" s="4" t="n"/>
     </row>
-    <row r="57" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="57" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A57" s="3" t="n"/>
       <c r="P57" s="94" t="n"/>
       <c r="Q57" s="95" t="n"/>
@@ -6425,7 +6425,7 @@
       <c r="KC57" s="96" t="n"/>
       <c r="KK57" s="4" t="n"/>
     </row>
-    <row r="58" ht="16.95" customHeight="1" s="88">
+    <row r="58" ht="4" customHeight="1" s="88">
       <c r="A58" s="3" t="n"/>
       <c r="P58" s="89" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
       <c r="KC58" s="91" t="n"/>
       <c r="KK58" s="4" t="n"/>
     </row>
-    <row r="59" ht="16.95" customHeight="1" s="88">
+    <row r="59" ht="4" customHeight="1" s="88">
       <c r="A59" s="3" t="n"/>
       <c r="P59" s="92" t="n"/>
       <c r="T59" s="93" t="n"/>
@@ -6643,7 +6643,7 @@
       <c r="KC59" s="93" t="n"/>
       <c r="KK59" s="4" t="n"/>
     </row>
-    <row r="60" ht="16.95" customHeight="1" s="88">
+    <row r="60" ht="4" customHeight="1" s="88">
       <c r="A60" s="3" t="n"/>
       <c r="P60" s="92" t="n"/>
       <c r="T60" s="93" t="n"/>
@@ -6697,7 +6697,7 @@
       <c r="KC60" s="93" t="n"/>
       <c r="KK60" s="4" t="n"/>
     </row>
-    <row r="61" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="61" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A61" s="3" t="n"/>
       <c r="P61" s="92" t="n"/>
       <c r="T61" s="93" t="n"/>
@@ -6815,7 +6815,7 @@
       <c r="KC61" s="93" t="n"/>
       <c r="KK61" s="4" t="n"/>
     </row>
-    <row r="62" ht="16.95" customHeight="1" s="88">
+    <row r="62" ht="4" customHeight="1" s="88">
       <c r="A62" s="3" t="n"/>
       <c r="P62" s="92" t="n"/>
       <c r="T62" s="93" t="n"/>
@@ -6965,7 +6965,7 @@
       <c r="KC62" s="93" t="n"/>
       <c r="KK62" s="4" t="n"/>
     </row>
-    <row r="63" ht="16.95" customHeight="1" s="88">
+    <row r="63" ht="4" customHeight="1" s="88">
       <c r="A63" s="3" t="n"/>
       <c r="P63" s="92" t="n"/>
       <c r="T63" s="93" t="n"/>
@@ -7019,7 +7019,7 @@
       <c r="KC63" s="93" t="n"/>
       <c r="KK63" s="4" t="n"/>
     </row>
-    <row r="64" ht="16.95" customHeight="1" s="88">
+    <row r="64" ht="4" customHeight="1" s="88">
       <c r="A64" s="3" t="n"/>
       <c r="P64" s="92" t="n"/>
       <c r="T64" s="93" t="n"/>
@@ -7073,7 +7073,7 @@
       <c r="KC64" s="93" t="n"/>
       <c r="KK64" s="4" t="n"/>
     </row>
-    <row r="65" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="65" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A65" s="3" t="n"/>
       <c r="P65" s="92" t="n"/>
       <c r="T65" s="93" t="n"/>
@@ -7191,7 +7191,7 @@
       <c r="KC65" s="93" t="n"/>
       <c r="KK65" s="4" t="n"/>
     </row>
-    <row r="66" ht="16.95" customHeight="1" s="88">
+    <row r="66" ht="4" customHeight="1" s="88">
       <c r="A66" s="3" t="n"/>
       <c r="P66" s="92" t="n"/>
       <c r="T66" s="93" t="n"/>
@@ -7341,7 +7341,7 @@
       <c r="KC66" s="93" t="n"/>
       <c r="KK66" s="4" t="n"/>
     </row>
-    <row r="67" ht="16.95" customHeight="1" s="88">
+    <row r="67" ht="4" customHeight="1" s="88">
       <c r="A67" s="3" t="n"/>
       <c r="P67" s="92" t="n"/>
       <c r="T67" s="93" t="n"/>
@@ -7395,7 +7395,7 @@
       <c r="KC67" s="93" t="n"/>
       <c r="KK67" s="4" t="n"/>
     </row>
-    <row r="68" ht="16.95" customHeight="1" s="88">
+    <row r="68" ht="4" customHeight="1" s="88">
       <c r="A68" s="3" t="n"/>
       <c r="P68" s="92" t="n"/>
       <c r="T68" s="93" t="n"/>
@@ -7449,7 +7449,7 @@
       <c r="KC68" s="93" t="n"/>
       <c r="KK68" s="4" t="n"/>
     </row>
-    <row r="69" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="69" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A69" s="3" t="n"/>
       <c r="P69" s="92" t="n"/>
       <c r="T69" s="93" t="n"/>
@@ -7567,7 +7567,7 @@
       <c r="KC69" s="93" t="n"/>
       <c r="KK69" s="4" t="n"/>
     </row>
-    <row r="70" ht="16.95" customHeight="1" s="88">
+    <row r="70" ht="4" customHeight="1" s="88">
       <c r="A70" s="3" t="n"/>
       <c r="P70" s="92" t="n"/>
       <c r="T70" s="93" t="n"/>
@@ -7717,7 +7717,7 @@
       <c r="KC70" s="93" t="n"/>
       <c r="KK70" s="4" t="n"/>
     </row>
-    <row r="71" ht="16.95" customHeight="1" s="88">
+    <row r="71" ht="4" customHeight="1" s="88">
       <c r="A71" s="3" t="n"/>
       <c r="P71" s="92" t="n"/>
       <c r="T71" s="93" t="n"/>
@@ -7771,7 +7771,7 @@
       <c r="KC71" s="93" t="n"/>
       <c r="KK71" s="4" t="n"/>
     </row>
-    <row r="72" ht="16.95" customHeight="1" s="88">
+    <row r="72" ht="4" customHeight="1" s="88">
       <c r="A72" s="3" t="n"/>
       <c r="P72" s="92" t="n"/>
       <c r="T72" s="93" t="n"/>
@@ -7825,7 +7825,7 @@
       <c r="KC72" s="93" t="n"/>
       <c r="KK72" s="4" t="n"/>
     </row>
-    <row r="73" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="73" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A73" s="3" t="n"/>
       <c r="P73" s="92" t="n"/>
       <c r="T73" s="93" t="n"/>
@@ -7943,7 +7943,7 @@
       <c r="KC73" s="93" t="n"/>
       <c r="KK73" s="4" t="n"/>
     </row>
-    <row r="74" ht="16.95" customHeight="1" s="88">
+    <row r="74" ht="4" customHeight="1" s="88">
       <c r="A74" s="3" t="n"/>
       <c r="P74" s="92" t="n"/>
       <c r="T74" s="93" t="n"/>
@@ -8093,7 +8093,7 @@
       <c r="KC74" s="93" t="n"/>
       <c r="KK74" s="4" t="n"/>
     </row>
-    <row r="75" ht="16.95" customHeight="1" s="88">
+    <row r="75" ht="4" customHeight="1" s="88">
       <c r="A75" s="3" t="n"/>
       <c r="P75" s="92" t="n"/>
       <c r="T75" s="93" t="n"/>
@@ -8147,7 +8147,7 @@
       <c r="KC75" s="93" t="n"/>
       <c r="KK75" s="4" t="n"/>
     </row>
-    <row r="76" ht="16.95" customHeight="1" s="88">
+    <row r="76" ht="4" customHeight="1" s="88">
       <c r="A76" s="3" t="n"/>
       <c r="P76" s="92" t="n"/>
       <c r="T76" s="93" t="n"/>
@@ -8201,7 +8201,7 @@
       <c r="KC76" s="93" t="n"/>
       <c r="KK76" s="4" t="n"/>
     </row>
-    <row r="77" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="77" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A77" s="3" t="n"/>
       <c r="P77" s="92" t="n"/>
       <c r="T77" s="93" t="n"/>
@@ -8319,7 +8319,7 @@
       <c r="KC77" s="93" t="n"/>
       <c r="KK77" s="4" t="n"/>
     </row>
-    <row r="78" ht="16.95" customHeight="1" s="88">
+    <row r="78" ht="4" customHeight="1" s="88">
       <c r="A78" s="3" t="n"/>
       <c r="P78" s="92" t="n"/>
       <c r="T78" s="93" t="n"/>
@@ -8469,7 +8469,7 @@
       <c r="KC78" s="93" t="n"/>
       <c r="KK78" s="4" t="n"/>
     </row>
-    <row r="79" ht="16.95" customHeight="1" s="88">
+    <row r="79" ht="4" customHeight="1" s="88">
       <c r="A79" s="3" t="n"/>
       <c r="P79" s="92" t="n"/>
       <c r="T79" s="93" t="n"/>
@@ -8523,7 +8523,7 @@
       <c r="KC79" s="93" t="n"/>
       <c r="KK79" s="4" t="n"/>
     </row>
-    <row r="80" ht="16.95" customHeight="1" s="88">
+    <row r="80" ht="4" customHeight="1" s="88">
       <c r="A80" s="3" t="n"/>
       <c r="P80" s="92" t="n"/>
       <c r="T80" s="93" t="n"/>
@@ -8577,7 +8577,7 @@
       <c r="KC80" s="93" t="n"/>
       <c r="KK80" s="4" t="n"/>
     </row>
-    <row r="81" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="81" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A81" s="3" t="n"/>
       <c r="P81" s="92" t="n"/>
       <c r="T81" s="93" t="n"/>
@@ -8695,7 +8695,7 @@
       <c r="KC81" s="93" t="n"/>
       <c r="KK81" s="4" t="n"/>
     </row>
-    <row r="82" ht="16.95" customHeight="1" s="88">
+    <row r="82" ht="4" customHeight="1" s="88">
       <c r="A82" s="3" t="n"/>
       <c r="P82" s="92" t="n"/>
       <c r="T82" s="93" t="n"/>
@@ -8845,7 +8845,7 @@
       <c r="KC82" s="93" t="n"/>
       <c r="KK82" s="4" t="n"/>
     </row>
-    <row r="83" ht="16.95" customHeight="1" s="88">
+    <row r="83" ht="4" customHeight="1" s="88">
       <c r="A83" s="3" t="n"/>
       <c r="P83" s="92" t="n"/>
       <c r="T83" s="93" t="n"/>
@@ -8899,7 +8899,7 @@
       <c r="KC83" s="93" t="n"/>
       <c r="KK83" s="4" t="n"/>
     </row>
-    <row r="84" ht="16.95" customHeight="1" s="88">
+    <row r="84" ht="4" customHeight="1" s="88">
       <c r="A84" s="3" t="n"/>
       <c r="P84" s="92" t="n"/>
       <c r="T84" s="93" t="n"/>
@@ -8953,7 +8953,7 @@
       <c r="KC84" s="93" t="n"/>
       <c r="KK84" s="4" t="n"/>
     </row>
-    <row r="85" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="85" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A85" s="3" t="n"/>
       <c r="P85" s="92" t="n"/>
       <c r="T85" s="93" t="n"/>
@@ -9071,7 +9071,7 @@
       <c r="KC85" s="93" t="n"/>
       <c r="KK85" s="4" t="n"/>
     </row>
-    <row r="86" ht="16.95" customHeight="1" s="88">
+    <row r="86" ht="4" customHeight="1" s="88">
       <c r="A86" s="3" t="n"/>
       <c r="P86" s="92" t="n"/>
       <c r="T86" s="93" t="n"/>
@@ -9221,7 +9221,7 @@
       <c r="KC86" s="93" t="n"/>
       <c r="KK86" s="4" t="n"/>
     </row>
-    <row r="87" ht="16.95" customHeight="1" s="88">
+    <row r="87" ht="4" customHeight="1" s="88">
       <c r="A87" s="3" t="n"/>
       <c r="P87" s="92" t="n"/>
       <c r="T87" s="93" t="n"/>
@@ -9275,7 +9275,7 @@
       <c r="KC87" s="93" t="n"/>
       <c r="KK87" s="4" t="n"/>
     </row>
-    <row r="88" ht="16.95" customHeight="1" s="88">
+    <row r="88" ht="4" customHeight="1" s="88">
       <c r="A88" s="3" t="n"/>
       <c r="P88" s="92" t="n"/>
       <c r="T88" s="93" t="n"/>
@@ -9329,7 +9329,7 @@
       <c r="KC88" s="93" t="n"/>
       <c r="KK88" s="4" t="n"/>
     </row>
-    <row r="89" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="89" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A89" s="3" t="n"/>
       <c r="P89" s="92" t="n"/>
       <c r="T89" s="93" t="n"/>
@@ -9447,7 +9447,7 @@
       <c r="KC89" s="93" t="n"/>
       <c r="KK89" s="4" t="n"/>
     </row>
-    <row r="90" ht="16.95" customHeight="1" s="88">
+    <row r="90" ht="4" customHeight="1" s="88">
       <c r="A90" s="3" t="n"/>
       <c r="P90" s="92" t="n"/>
       <c r="T90" s="93" t="n"/>
@@ -9597,7 +9597,7 @@
       <c r="KC90" s="93" t="n"/>
       <c r="KK90" s="4" t="n"/>
     </row>
-    <row r="91" ht="16.95" customHeight="1" s="88">
+    <row r="91" ht="4" customHeight="1" s="88">
       <c r="A91" s="3" t="n"/>
       <c r="P91" s="92" t="n"/>
       <c r="T91" s="93" t="n"/>
@@ -9651,7 +9651,7 @@
       <c r="KC91" s="93" t="n"/>
       <c r="KK91" s="4" t="n"/>
     </row>
-    <row r="92" ht="16.95" customHeight="1" s="88">
+    <row r="92" ht="4" customHeight="1" s="88">
       <c r="A92" s="3" t="n"/>
       <c r="P92" s="92" t="n"/>
       <c r="T92" s="93" t="n"/>
@@ -9705,7 +9705,7 @@
       <c r="KC92" s="93" t="n"/>
       <c r="KK92" s="4" t="n"/>
     </row>
-    <row r="93" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="93" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A93" s="3" t="n"/>
       <c r="P93" s="92" t="n"/>
       <c r="T93" s="93" t="n"/>
@@ -9823,7 +9823,7 @@
       <c r="KC93" s="93" t="n"/>
       <c r="KK93" s="4" t="n"/>
     </row>
-    <row r="94" ht="16.95" customHeight="1" s="88">
+    <row r="94" ht="4" customHeight="1" s="88">
       <c r="A94" s="3" t="n"/>
       <c r="P94" s="92" t="n"/>
       <c r="T94" s="93" t="n"/>
@@ -9973,7 +9973,7 @@
       <c r="KC94" s="93" t="n"/>
       <c r="KK94" s="4" t="n"/>
     </row>
-    <row r="95" ht="16.95" customHeight="1" s="88">
+    <row r="95" ht="4" customHeight="1" s="88">
       <c r="A95" s="3" t="n"/>
       <c r="P95" s="92" t="n"/>
       <c r="T95" s="93" t="n"/>
@@ -10027,7 +10027,7 @@
       <c r="KC95" s="93" t="n"/>
       <c r="KK95" s="4" t="n"/>
     </row>
-    <row r="96" ht="16.95" customHeight="1" s="88">
+    <row r="96" ht="4" customHeight="1" s="88">
       <c r="A96" s="3" t="n"/>
       <c r="P96" s="92" t="n"/>
       <c r="T96" s="93" t="n"/>
@@ -10081,7 +10081,7 @@
       <c r="KC96" s="93" t="n"/>
       <c r="KK96" s="4" t="n"/>
     </row>
-    <row r="97" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="97" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A97" s="3" t="n"/>
       <c r="P97" s="92" t="n"/>
       <c r="T97" s="93" t="n"/>
@@ -10199,7 +10199,7 @@
       <c r="KC97" s="93" t="n"/>
       <c r="KK97" s="4" t="n"/>
     </row>
-    <row r="98" ht="16.95" customHeight="1" s="88">
+    <row r="98" ht="4" customHeight="1" s="88">
       <c r="A98" s="3" t="n"/>
       <c r="P98" s="92" t="n"/>
       <c r="T98" s="93" t="n"/>
@@ -10349,7 +10349,7 @@
       <c r="KC98" s="93" t="n"/>
       <c r="KK98" s="4" t="n"/>
     </row>
-    <row r="99" ht="16.95" customHeight="1" s="88">
+    <row r="99" ht="4" customHeight="1" s="88">
       <c r="A99" s="3" t="n"/>
       <c r="P99" s="92" t="n"/>
       <c r="T99" s="93" t="n"/>
@@ -10403,7 +10403,7 @@
       <c r="KC99" s="93" t="n"/>
       <c r="KK99" s="4" t="n"/>
     </row>
-    <row r="100" ht="16.95" customHeight="1" s="88">
+    <row r="100" ht="4" customHeight="1" s="88">
       <c r="A100" s="3" t="n"/>
       <c r="P100" s="92" t="n"/>
       <c r="T100" s="93" t="n"/>
@@ -10581,7 +10581,7 @@
       <c r="KC100" s="93" t="n"/>
       <c r="KK100" s="4" t="n"/>
     </row>
-    <row r="101" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="101" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A101" s="3" t="n"/>
       <c r="P101" s="92" t="n"/>
       <c r="T101" s="93" t="n"/>
@@ -10813,7 +10813,7 @@
       <c r="KC101" s="93" t="n"/>
       <c r="KK101" s="4" t="n"/>
     </row>
-    <row r="102" ht="16.95" customHeight="1" s="88">
+    <row r="102" ht="4" customHeight="1" s="88">
       <c r="A102" s="3" t="n"/>
       <c r="P102" s="92" t="n"/>
       <c r="T102" s="93" t="n"/>
@@ -10965,7 +10965,7 @@
       <c r="KC102" s="93" t="n"/>
       <c r="KK102" s="4" t="n"/>
     </row>
-    <row r="103" ht="16.95" customHeight="1" s="88">
+    <row r="103" ht="4" customHeight="1" s="88">
       <c r="A103" s="3" t="n"/>
       <c r="P103" s="92" t="n"/>
       <c r="T103" s="93" t="n"/>
@@ -11117,7 +11117,7 @@
       <c r="KC103" s="93" t="n"/>
       <c r="KK103" s="4" t="n"/>
     </row>
-    <row r="104" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="104" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A104" s="3" t="n"/>
       <c r="P104" s="94" t="n"/>
       <c r="Q104" s="95" t="n"/>
@@ -11275,7 +11275,7 @@
       <c r="KC104" s="96" t="n"/>
       <c r="KK104" s="4" t="n"/>
     </row>
-    <row r="105" ht="16.95" customHeight="1" s="88">
+    <row r="105" ht="4" customHeight="1" s="88">
       <c r="A105" s="3" t="n"/>
       <c r="P105" s="89" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
       <c r="KC105" s="91" t="n"/>
       <c r="KK105" s="4" t="n"/>
     </row>
-    <row r="106" ht="16.95" customHeight="1" s="88">
+    <row r="106" ht="4" customHeight="1" s="88">
       <c r="A106" s="3" t="n"/>
       <c r="P106" s="92" t="n"/>
       <c r="T106" s="93" t="n"/>
@@ -11673,7 +11673,7 @@
       <c r="KC106" s="93" t="n"/>
       <c r="KK106" s="4" t="n"/>
     </row>
-    <row r="107" ht="16.95" customHeight="1" s="88">
+    <row r="107" ht="4" customHeight="1" s="88">
       <c r="A107" s="3" t="n"/>
       <c r="P107" s="92" t="n"/>
       <c r="T107" s="93" t="n"/>
@@ -11865,7 +11865,7 @@
       <c r="KC107" s="93" t="n"/>
       <c r="KK107" s="4" t="n"/>
     </row>
-    <row r="108" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="108" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A108" s="3" t="n"/>
       <c r="P108" s="92" t="n"/>
       <c r="T108" s="93" t="n"/>
@@ -12057,7 +12057,7 @@
       <c r="KC108" s="93" t="n"/>
       <c r="KK108" s="4" t="n"/>
     </row>
-    <row r="109" ht="16.95" customHeight="1" s="88">
+    <row r="109" ht="4" customHeight="1" s="88">
       <c r="A109" s="3" t="n"/>
       <c r="P109" s="92" t="n"/>
       <c r="T109" s="93" t="n"/>
@@ -12337,7 +12337,7 @@
       <c r="KC109" s="93" t="n"/>
       <c r="KK109" s="4" t="n"/>
     </row>
-    <row r="110" ht="16.95" customHeight="1" s="88">
+    <row r="110" ht="4" customHeight="1" s="88">
       <c r="A110" s="3" t="n"/>
       <c r="P110" s="92" t="n"/>
       <c r="T110" s="93" t="n"/>
@@ -12387,7 +12387,7 @@
       <c r="KC110" s="93" t="n"/>
       <c r="KK110" s="4" t="n"/>
     </row>
-    <row r="111" ht="16.95" customHeight="1" s="88">
+    <row r="111" ht="4" customHeight="1" s="88">
       <c r="A111" s="3" t="n"/>
       <c r="P111" s="92" t="n"/>
       <c r="T111" s="93" t="n"/>
@@ -12427,7 +12427,7 @@
       <c r="KC111" s="93" t="n"/>
       <c r="KK111" s="4" t="n"/>
     </row>
-    <row r="112" ht="16.95" customHeight="1" s="88">
+    <row r="112" ht="4" customHeight="1" s="88">
       <c r="A112" s="3" t="n"/>
       <c r="P112" s="92" t="n"/>
       <c r="T112" s="93" t="n"/>
@@ -12467,7 +12467,7 @@
       <c r="KC112" s="93" t="n"/>
       <c r="KK112" s="4" t="n"/>
     </row>
-    <row r="113" ht="16.95" customHeight="1" s="88">
+    <row r="113" ht="4" customHeight="1" s="88">
       <c r="A113" s="3" t="n"/>
       <c r="P113" s="92" t="n"/>
       <c r="T113" s="93" t="n"/>
@@ -12507,7 +12507,7 @@
       <c r="KC113" s="93" t="n"/>
       <c r="KK113" s="4" t="n"/>
     </row>
-    <row r="114" ht="16.95" customHeight="1" s="88">
+    <row r="114" ht="4" customHeight="1" s="88">
       <c r="A114" s="3" t="n"/>
       <c r="P114" s="92" t="n"/>
       <c r="T114" s="93" t="n"/>
@@ -12547,7 +12547,7 @@
       <c r="KC114" s="93" t="n"/>
       <c r="KK114" s="4" t="n"/>
     </row>
-    <row r="115" ht="16.95" customHeight="1" s="88">
+    <row r="115" ht="4" customHeight="1" s="88">
       <c r="A115" s="3" t="n"/>
       <c r="P115" s="92" t="n"/>
       <c r="T115" s="93" t="n"/>
@@ -12587,7 +12587,7 @@
       <c r="KC115" s="93" t="n"/>
       <c r="KK115" s="4" t="n"/>
     </row>
-    <row r="116" ht="16.95" customHeight="1" s="88">
+    <row r="116" ht="4" customHeight="1" s="88">
       <c r="A116" s="3" t="n"/>
       <c r="P116" s="92" t="n"/>
       <c r="T116" s="93" t="n"/>
@@ -12627,7 +12627,7 @@
       <c r="KC116" s="93" t="n"/>
       <c r="KK116" s="4" t="n"/>
     </row>
-    <row r="117" ht="16.95" customHeight="1" s="88">
+    <row r="117" ht="4" customHeight="1" s="88">
       <c r="A117" s="3" t="n"/>
       <c r="P117" s="92" t="n"/>
       <c r="T117" s="93" t="n"/>
@@ -12667,7 +12667,7 @@
       <c r="KC117" s="93" t="n"/>
       <c r="KK117" s="4" t="n"/>
     </row>
-    <row r="118" ht="16.95" customHeight="1" s="88">
+    <row r="118" ht="4" customHeight="1" s="88">
       <c r="A118" s="3" t="n"/>
       <c r="P118" s="92" t="n"/>
       <c r="T118" s="93" t="n"/>
@@ -12707,7 +12707,7 @@
       <c r="KC118" s="93" t="n"/>
       <c r="KK118" s="4" t="n"/>
     </row>
-    <row r="119" ht="16.95" customHeight="1" s="88">
+    <row r="119" ht="4" customHeight="1" s="88">
       <c r="A119" s="3" t="n"/>
       <c r="P119" s="92" t="n"/>
       <c r="T119" s="93" t="n"/>
@@ -12747,7 +12747,7 @@
       <c r="KC119" s="93" t="n"/>
       <c r="KK119" s="4" t="n"/>
     </row>
-    <row r="120" ht="16.95" customHeight="1" s="88">
+    <row r="120" ht="4" customHeight="1" s="88">
       <c r="A120" s="3" t="n"/>
       <c r="P120" s="92" t="n"/>
       <c r="T120" s="93" t="n"/>
@@ -12787,7 +12787,7 @@
       <c r="KC120" s="93" t="n"/>
       <c r="KK120" s="4" t="n"/>
     </row>
-    <row r="121" ht="16.95" customHeight="1" s="88">
+    <row r="121" ht="4" customHeight="1" s="88">
       <c r="A121" s="3" t="n"/>
       <c r="P121" s="92" t="n"/>
       <c r="T121" s="93" t="n"/>
@@ -12827,7 +12827,7 @@
       <c r="KC121" s="93" t="n"/>
       <c r="KK121" s="4" t="n"/>
     </row>
-    <row r="122" ht="16.95" customHeight="1" s="88">
+    <row r="122" ht="4" customHeight="1" s="88">
       <c r="A122" s="3" t="n"/>
       <c r="P122" s="92" t="n"/>
       <c r="T122" s="93" t="n"/>
@@ -12867,7 +12867,7 @@
       <c r="KC122" s="93" t="n"/>
       <c r="KK122" s="4" t="n"/>
     </row>
-    <row r="123" ht="16.95" customHeight="1" s="88">
+    <row r="123" ht="4" customHeight="1" s="88">
       <c r="A123" s="3" t="n"/>
       <c r="P123" s="92" t="n"/>
       <c r="T123" s="93" t="n"/>
@@ -12907,7 +12907,7 @@
       <c r="KC123" s="93" t="n"/>
       <c r="KK123" s="4" t="n"/>
     </row>
-    <row r="124" ht="16.95" customHeight="1" s="88">
+    <row r="124" ht="4" customHeight="1" s="88">
       <c r="A124" s="3" t="n"/>
       <c r="P124" s="92" t="n"/>
       <c r="T124" s="93" t="n"/>
@@ -12947,7 +12947,7 @@
       <c r="KC124" s="93" t="n"/>
       <c r="KK124" s="4" t="n"/>
     </row>
-    <row r="125" ht="16.95" customHeight="1" s="88">
+    <row r="125" ht="4" customHeight="1" s="88">
       <c r="A125" s="3" t="n"/>
       <c r="P125" s="92" t="n"/>
       <c r="T125" s="93" t="n"/>
@@ -12987,7 +12987,7 @@
       <c r="KC125" s="93" t="n"/>
       <c r="KK125" s="4" t="n"/>
     </row>
-    <row r="126" ht="16.95" customHeight="1" s="88">
+    <row r="126" ht="4" customHeight="1" s="88">
       <c r="A126" s="3" t="n"/>
       <c r="P126" s="92" t="n"/>
       <c r="T126" s="93" t="n"/>
@@ -13027,7 +13027,7 @@
       <c r="KC126" s="93" t="n"/>
       <c r="KK126" s="4" t="n"/>
     </row>
-    <row r="127" ht="16.95" customHeight="1" s="88">
+    <row r="127" ht="4" customHeight="1" s="88">
       <c r="A127" s="3" t="n"/>
       <c r="P127" s="92" t="n"/>
       <c r="T127" s="93" t="n"/>
@@ -13067,7 +13067,7 @@
       <c r="KC127" s="93" t="n"/>
       <c r="KK127" s="4" t="n"/>
     </row>
-    <row r="128" ht="16.95" customHeight="1" s="88">
+    <row r="128" ht="4" customHeight="1" s="88">
       <c r="A128" s="3" t="n"/>
       <c r="P128" s="92" t="n"/>
       <c r="T128" s="93" t="n"/>
@@ -13107,7 +13107,7 @@
       <c r="KC128" s="93" t="n"/>
       <c r="KK128" s="4" t="n"/>
     </row>
-    <row r="129" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="129" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A129" s="3" t="n"/>
       <c r="P129" s="92" t="n"/>
       <c r="T129" s="93" t="n"/>
@@ -13225,7 +13225,7 @@
       <c r="KC129" s="93" t="n"/>
       <c r="KK129" s="4" t="n"/>
     </row>
-    <row r="130" ht="16.95" customHeight="1" s="88">
+    <row r="130" ht="4" customHeight="1" s="88">
       <c r="A130" s="3" t="n"/>
       <c r="P130" s="92" t="n"/>
       <c r="T130" s="93" t="n"/>
@@ -13263,7 +13263,7 @@
       <c r="KC130" s="93" t="n"/>
       <c r="KK130" s="4" t="n"/>
     </row>
-    <row r="131" ht="16.95" customHeight="1" s="88">
+    <row r="131" ht="4" customHeight="1" s="88">
       <c r="A131" s="3" t="n"/>
       <c r="P131" s="92" t="n"/>
       <c r="T131" s="93" t="n"/>
@@ -13301,7 +13301,7 @@
       <c r="KC131" s="93" t="n"/>
       <c r="KK131" s="4" t="n"/>
     </row>
-    <row r="132" ht="16.95" customHeight="1" s="88">
+    <row r="132" ht="4" customHeight="1" s="88">
       <c r="A132" s="3" t="n"/>
       <c r="P132" s="92" t="n"/>
       <c r="T132" s="93" t="n"/>
@@ -13339,7 +13339,7 @@
       <c r="KC132" s="93" t="n"/>
       <c r="KK132" s="4" t="n"/>
     </row>
-    <row r="133" ht="16.95" customHeight="1" s="88">
+    <row r="133" ht="4" customHeight="1" s="88">
       <c r="A133" s="3" t="n"/>
       <c r="P133" s="92" t="n"/>
       <c r="T133" s="93" t="n"/>
@@ -13377,7 +13377,7 @@
       <c r="KC133" s="93" t="n"/>
       <c r="KK133" s="4" t="n"/>
     </row>
-    <row r="134" ht="16.95" customHeight="1" s="88">
+    <row r="134" ht="4" customHeight="1" s="88">
       <c r="A134" s="3" t="n"/>
       <c r="P134" s="92" t="n"/>
       <c r="T134" s="93" t="n"/>
@@ -13415,7 +13415,7 @@
       <c r="KC134" s="93" t="n"/>
       <c r="KK134" s="4" t="n"/>
     </row>
-    <row r="135" ht="16.95" customHeight="1" s="88">
+    <row r="135" ht="4" customHeight="1" s="88">
       <c r="A135" s="3" t="n"/>
       <c r="P135" s="92" t="n"/>
       <c r="T135" s="93" t="n"/>
@@ -13453,7 +13453,7 @@
       <c r="KC135" s="93" t="n"/>
       <c r="KK135" s="4" t="n"/>
     </row>
-    <row r="136" ht="16.95" customHeight="1" s="88">
+    <row r="136" ht="4" customHeight="1" s="88">
       <c r="A136" s="3" t="n"/>
       <c r="P136" s="92" t="n"/>
       <c r="T136" s="93" t="n"/>
@@ -13491,7 +13491,7 @@
       <c r="KC136" s="93" t="n"/>
       <c r="KK136" s="4" t="n"/>
     </row>
-    <row r="137" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="137" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A137" s="3" t="n"/>
       <c r="P137" s="92" t="n"/>
       <c r="T137" s="93" t="n"/>
@@ -13529,7 +13529,7 @@
       <c r="KC137" s="93" t="n"/>
       <c r="KK137" s="4" t="n"/>
     </row>
-    <row r="138" ht="16.95" customHeight="1" s="88">
+    <row r="138" ht="4" customHeight="1" s="88">
       <c r="A138" s="3" t="n"/>
       <c r="P138" s="92" t="n"/>
       <c r="T138" s="93" t="n"/>
@@ -13671,7 +13671,7 @@
       <c r="KC138" s="93" t="n"/>
       <c r="KK138" s="4" t="n"/>
     </row>
-    <row r="139" ht="16.95" customHeight="1" s="88">
+    <row r="139" ht="4" customHeight="1" s="88">
       <c r="A139" s="3" t="n"/>
       <c r="P139" s="92" t="n"/>
       <c r="T139" s="93" t="n"/>
@@ -13721,7 +13721,7 @@
       <c r="KC139" s="93" t="n"/>
       <c r="KK139" s="4" t="n"/>
     </row>
-    <row r="140" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="140" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A140" s="3" t="n"/>
       <c r="P140" s="92" t="n"/>
       <c r="T140" s="93" t="n"/>
@@ -13839,7 +13839,7 @@
       <c r="KC140" s="93" t="n"/>
       <c r="KK140" s="4" t="n"/>
     </row>
-    <row r="141" ht="16.95" customHeight="1" s="88">
+    <row r="141" ht="4" customHeight="1" s="88">
       <c r="A141" s="3" t="n"/>
       <c r="P141" s="92" t="n"/>
       <c r="T141" s="93" t="n"/>
@@ -13981,7 +13981,7 @@
       <c r="KC141" s="93" t="n"/>
       <c r="KK141" s="4" t="n"/>
     </row>
-    <row r="142" ht="16.95" customHeight="1" s="88">
+    <row r="142" ht="4" customHeight="1" s="88">
       <c r="A142" s="3" t="n"/>
       <c r="P142" s="92" t="n"/>
       <c r="T142" s="93" t="n"/>
@@ -14031,7 +14031,7 @@
       <c r="KC142" s="93" t="n"/>
       <c r="KK142" s="4" t="n"/>
     </row>
-    <row r="143" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="143" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A143" s="3" t="n"/>
       <c r="P143" s="92" t="n"/>
       <c r="T143" s="93" t="n"/>
@@ -14149,7 +14149,7 @@
       <c r="KC143" s="93" t="n"/>
       <c r="KK143" s="4" t="n"/>
     </row>
-    <row r="144" ht="16.95" customHeight="1" s="88">
+    <row r="144" ht="4" customHeight="1" s="88">
       <c r="A144" s="3" t="n"/>
       <c r="P144" s="92" t="n"/>
       <c r="T144" s="93" t="n"/>
@@ -14291,7 +14291,7 @@
       <c r="KC144" s="93" t="n"/>
       <c r="KK144" s="4" t="n"/>
     </row>
-    <row r="145" ht="16.95" customHeight="1" s="88">
+    <row r="145" ht="4" customHeight="1" s="88">
       <c r="A145" s="3" t="n"/>
       <c r="P145" s="92" t="n"/>
       <c r="T145" s="93" t="n"/>
@@ -14341,7 +14341,7 @@
       <c r="KC145" s="93" t="n"/>
       <c r="KK145" s="4" t="n"/>
     </row>
-    <row r="146" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="146" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A146" s="3" t="n"/>
       <c r="P146" s="92" t="n"/>
       <c r="T146" s="93" t="n"/>
@@ -14459,7 +14459,7 @@
       <c r="KC146" s="93" t="n"/>
       <c r="KK146" s="4" t="n"/>
     </row>
-    <row r="147" ht="16.95" customHeight="1" s="88">
+    <row r="147" ht="4" customHeight="1" s="88">
       <c r="A147" s="3" t="n"/>
       <c r="P147" s="92" t="n"/>
       <c r="T147" s="93" t="n"/>
@@ -14601,7 +14601,7 @@
       <c r="KC147" s="93" t="n"/>
       <c r="KK147" s="4" t="n"/>
     </row>
-    <row r="148" ht="16.95" customHeight="1" s="88">
+    <row r="148" ht="4" customHeight="1" s="88">
       <c r="A148" s="3" t="n"/>
       <c r="P148" s="92" t="n"/>
       <c r="T148" s="93" t="n"/>
@@ -14651,7 +14651,7 @@
       <c r="KC148" s="93" t="n"/>
       <c r="KK148" s="4" t="n"/>
     </row>
-    <row r="149" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="149" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A149" s="3" t="n"/>
       <c r="P149" s="92" t="n"/>
       <c r="T149" s="93" t="n"/>
@@ -14769,7 +14769,7 @@
       <c r="KC149" s="93" t="n"/>
       <c r="KK149" s="4" t="n"/>
     </row>
-    <row r="150" ht="16.95" customHeight="1" s="88">
+    <row r="150" ht="4" customHeight="1" s="88">
       <c r="A150" s="3" t="n"/>
       <c r="P150" s="92" t="n"/>
       <c r="T150" s="93" t="n"/>
@@ -14911,7 +14911,7 @@
       <c r="KC150" s="93" t="n"/>
       <c r="KK150" s="4" t="n"/>
     </row>
-    <row r="151" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="151" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A151" s="3" t="n"/>
       <c r="P151" s="94" t="n"/>
       <c r="Q151" s="95" t="n"/>
@@ -14967,7 +14967,7 @@
       <c r="KC151" s="96" t="n"/>
       <c r="KK151" s="4" t="n"/>
     </row>
-    <row r="152" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="152" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A152" s="3" t="n"/>
       <c r="P152" s="89" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
       <c r="KC152" s="91" t="n"/>
       <c r="KK152" s="4" t="n"/>
     </row>
-    <row r="153" ht="16.95" customHeight="1" s="88">
+    <row r="153" ht="4" customHeight="1" s="88">
       <c r="A153" s="3" t="n"/>
       <c r="P153" s="92" t="n"/>
       <c r="T153" s="93" t="n"/>
@@ -15241,7 +15241,7 @@
       <c r="KC153" s="93" t="n"/>
       <c r="KK153" s="4" t="n"/>
     </row>
-    <row r="154" ht="16.95" customHeight="1" s="88">
+    <row r="154" ht="4" customHeight="1" s="88">
       <c r="A154" s="3" t="n"/>
       <c r="P154" s="92" t="n"/>
       <c r="T154" s="93" t="n"/>
@@ -15291,7 +15291,7 @@
       <c r="KC154" s="93" t="n"/>
       <c r="KK154" s="4" t="n"/>
     </row>
-    <row r="155" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="155" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A155" s="3" t="n"/>
       <c r="P155" s="92" t="n"/>
       <c r="T155" s="93" t="n"/>
@@ -15409,7 +15409,7 @@
       <c r="KC155" s="93" t="n"/>
       <c r="KK155" s="4" t="n"/>
     </row>
-    <row r="156" ht="16.95" customHeight="1" s="88">
+    <row r="156" ht="4" customHeight="1" s="88">
       <c r="A156" s="3" t="n"/>
       <c r="P156" s="92" t="n"/>
       <c r="T156" s="93" t="n"/>
@@ -15539,7 +15539,7 @@
       <c r="KC156" s="93" t="n"/>
       <c r="KK156" s="4" t="n"/>
     </row>
-    <row r="157" ht="16.95" customHeight="1" s="88">
+    <row r="157" ht="4" customHeight="1" s="88">
       <c r="A157" s="3" t="n"/>
       <c r="P157" s="92" t="n"/>
       <c r="T157" s="93" t="n"/>
@@ -15583,7 +15583,7 @@
       <c r="KC157" s="93" t="n"/>
       <c r="KK157" s="4" t="n"/>
     </row>
-    <row r="158" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="158" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A158" s="3" t="n"/>
       <c r="P158" s="92" t="n"/>
       <c r="T158" s="93" t="n"/>
@@ -15701,7 +15701,7 @@
       <c r="KC158" s="93" t="n"/>
       <c r="KK158" s="4" t="n"/>
     </row>
-    <row r="159" ht="16.95" customHeight="1" s="88">
+    <row r="159" ht="4" customHeight="1" s="88">
       <c r="A159" s="3" t="n"/>
       <c r="P159" s="92" t="n"/>
       <c r="T159" s="93" t="n"/>
@@ -15788,7 +15788,7 @@
       <c r="KC159" s="93" t="n"/>
       <c r="KK159" s="4" t="n"/>
     </row>
-    <row r="160" ht="16.95" customHeight="1" s="88">
+    <row r="160" ht="4" customHeight="1" s="88">
       <c r="A160" s="3" t="n"/>
       <c r="P160" s="92" t="n"/>
       <c r="T160" s="93" t="n"/>
@@ -15831,7 +15831,7 @@
       <c r="KC160" s="93" t="n"/>
       <c r="KK160" s="4" t="n"/>
     </row>
-    <row r="161" ht="16.95" customHeight="1" s="88">
+    <row r="161" ht="4" customHeight="1" s="88">
       <c r="A161" s="3" t="n"/>
       <c r="P161" s="92" t="n"/>
       <c r="T161" s="93" t="n"/>
@@ -15874,7 +15874,7 @@
       <c r="KC161" s="93" t="n"/>
       <c r="KK161" s="4" t="n"/>
     </row>
-    <row r="162" ht="16.95" customHeight="1" s="88">
+    <row r="162" ht="4" customHeight="1" s="88">
       <c r="A162" s="3" t="n"/>
       <c r="P162" s="92" t="n"/>
       <c r="T162" s="93" t="n"/>
@@ -15917,7 +15917,7 @@
       <c r="KC162" s="93" t="n"/>
       <c r="KK162" s="4" t="n"/>
     </row>
-    <row r="163" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="163" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A163" s="3" t="n"/>
       <c r="P163" s="92" t="n"/>
       <c r="T163" s="93" t="n"/>
@@ -16035,7 +16035,7 @@
       <c r="KC163" s="93" t="n"/>
       <c r="KK163" s="4" t="n"/>
     </row>
-    <row r="164" ht="16.95" customHeight="1" s="88">
+    <row r="164" ht="4" customHeight="1" s="88">
       <c r="A164" s="3" t="n"/>
       <c r="P164" s="92" t="n"/>
       <c r="T164" s="93" t="n"/>
@@ -16161,7 +16161,7 @@
       <c r="KC164" s="93" t="n"/>
       <c r="KK164" s="4" t="n"/>
     </row>
-    <row r="165" ht="16.95" customHeight="1" s="88">
+    <row r="165" ht="4" customHeight="1" s="88">
       <c r="A165" s="3" t="n"/>
       <c r="P165" s="92" t="n"/>
       <c r="T165" s="93" t="n"/>
@@ -16203,7 +16203,7 @@
       <c r="KC165" s="93" t="n"/>
       <c r="KK165" s="4" t="n"/>
     </row>
-    <row r="166" ht="16.95" customHeight="1" s="88">
+    <row r="166" ht="4" customHeight="1" s="88">
       <c r="A166" s="3" t="n"/>
       <c r="P166" s="92" t="n"/>
       <c r="T166" s="93" t="n"/>
@@ -16245,7 +16245,7 @@
       <c r="KC166" s="93" t="n"/>
       <c r="KK166" s="4" t="n"/>
     </row>
-    <row r="167" ht="16.95" customHeight="1" s="88">
+    <row r="167" ht="4" customHeight="1" s="88">
       <c r="A167" s="3" t="n"/>
       <c r="P167" s="92" t="n"/>
       <c r="T167" s="93" t="n"/>
@@ -16291,7 +16291,7 @@
       <c r="KC167" s="93" t="n"/>
       <c r="KK167" s="4" t="n"/>
     </row>
-    <row r="168" ht="16.95" customHeight="1" s="88">
+    <row r="168" ht="4" customHeight="1" s="88">
       <c r="A168" s="3" t="n"/>
       <c r="P168" s="92" t="n"/>
       <c r="T168" s="93" t="n"/>
@@ -16333,7 +16333,7 @@
       <c r="KC168" s="93" t="n"/>
       <c r="KK168" s="4" t="n"/>
     </row>
-    <row r="169" ht="16.95" customHeight="1" s="88">
+    <row r="169" ht="4" customHeight="1" s="88">
       <c r="A169" s="3" t="n"/>
       <c r="P169" s="92" t="n"/>
       <c r="T169" s="93" t="n"/>
@@ -16375,7 +16375,7 @@
       <c r="KC169" s="93" t="n"/>
       <c r="KK169" s="4" t="n"/>
     </row>
-    <row r="170" ht="16.95" customHeight="1" s="88">
+    <row r="170" ht="4" customHeight="1" s="88">
       <c r="A170" s="3" t="n"/>
       <c r="P170" s="92" t="n"/>
       <c r="T170" s="93" t="n"/>
@@ -16417,7 +16417,7 @@
       <c r="KC170" s="93" t="n"/>
       <c r="KK170" s="4" t="n"/>
     </row>
-    <row r="171" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="171" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A171" s="3" t="n"/>
       <c r="P171" s="92" t="n"/>
       <c r="T171" s="93" t="n"/>
@@ -16507,7 +16507,7 @@
       <c r="KC171" s="93" t="n"/>
       <c r="KK171" s="4" t="n"/>
     </row>
-    <row r="172" ht="16.95" customHeight="1" s="88">
+    <row r="172" ht="4" customHeight="1" s="88">
       <c r="A172" s="3" t="n"/>
       <c r="P172" s="92" t="n"/>
       <c r="T172" s="93" t="n"/>
@@ -16601,7 +16601,7 @@
       <c r="KC172" s="93" t="n"/>
       <c r="KK172" s="4" t="n"/>
     </row>
-    <row r="173" ht="16.95" customHeight="1" s="88">
+    <row r="173" ht="4" customHeight="1" s="88">
       <c r="A173" s="3" t="n"/>
       <c r="P173" s="92" t="n"/>
       <c r="T173" s="93" t="n"/>
@@ -16643,7 +16643,7 @@
       <c r="KC173" s="93" t="n"/>
       <c r="KK173" s="4" t="n"/>
     </row>
-    <row r="174" ht="16.95" customHeight="1" s="88">
+    <row r="174" ht="4" customHeight="1" s="88">
       <c r="A174" s="3" t="n"/>
       <c r="P174" s="92" t="n"/>
       <c r="T174" s="93" t="n"/>
@@ -16685,7 +16685,7 @@
       <c r="KC174" s="93" t="n"/>
       <c r="KK174" s="4" t="n"/>
     </row>
-    <row r="175" ht="16.95" customHeight="1" s="88">
+    <row r="175" ht="4" customHeight="1" s="88">
       <c r="A175" s="3" t="n"/>
       <c r="P175" s="92" t="n"/>
       <c r="T175" s="93" t="n"/>
@@ -16727,7 +16727,7 @@
       <c r="KC175" s="93" t="n"/>
       <c r="KK175" s="4" t="n"/>
     </row>
-    <row r="176" ht="16.95" customHeight="1" s="88">
+    <row r="176" ht="4" customHeight="1" s="88">
       <c r="A176" s="3" t="n"/>
       <c r="P176" s="92" t="n"/>
       <c r="T176" s="93" t="n"/>
@@ -16769,7 +16769,7 @@
       <c r="KC176" s="93" t="n"/>
       <c r="KK176" s="4" t="n"/>
     </row>
-    <row r="177" ht="16.95" customHeight="1" s="88">
+    <row r="177" ht="4" customHeight="1" s="88">
       <c r="A177" s="3" t="n"/>
       <c r="P177" s="92" t="n"/>
       <c r="T177" s="93" t="n"/>
@@ -16811,7 +16811,7 @@
       <c r="KC177" s="93" t="n"/>
       <c r="KK177" s="4" t="n"/>
     </row>
-    <row r="178" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="178" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A178" s="3" t="n"/>
       <c r="P178" s="92" t="n"/>
       <c r="T178" s="93" t="n"/>
@@ -16929,7 +16929,7 @@
       <c r="KC178" s="93" t="n"/>
       <c r="KK178" s="4" t="n"/>
     </row>
-    <row r="179" ht="16.95" customHeight="1" s="88">
+    <row r="179" ht="4" customHeight="1" s="88">
       <c r="A179" s="3" t="n"/>
       <c r="P179" s="92" t="n"/>
       <c r="T179" s="93" t="n"/>
@@ -17055,7 +17055,7 @@
       <c r="KC179" s="93" t="n"/>
       <c r="KK179" s="4" t="n"/>
     </row>
-    <row r="180" ht="16.95" customHeight="1" s="88">
+    <row r="180" ht="4" customHeight="1" s="88">
       <c r="A180" s="3" t="n"/>
       <c r="P180" s="92" t="n"/>
       <c r="T180" s="93" t="n"/>
@@ -17097,7 +17097,7 @@
       <c r="KC180" s="93" t="n"/>
       <c r="KK180" s="4" t="n"/>
     </row>
-    <row r="181" ht="16.95" customHeight="1" s="88">
+    <row r="181" ht="4" customHeight="1" s="88">
       <c r="A181" s="3" t="n"/>
       <c r="P181" s="92" t="n"/>
       <c r="T181" s="93" t="n"/>
@@ -17139,7 +17139,7 @@
       <c r="KC181" s="93" t="n"/>
       <c r="KK181" s="4" t="n"/>
     </row>
-    <row r="182" ht="16.95" customHeight="1" s="88">
+    <row r="182" ht="4" customHeight="1" s="88">
       <c r="A182" s="3" t="n"/>
       <c r="P182" s="92" t="n"/>
       <c r="T182" s="93" t="n"/>
@@ -17185,7 +17185,7 @@
       <c r="KC182" s="93" t="n"/>
       <c r="KK182" s="4" t="n"/>
     </row>
-    <row r="183" ht="16.95" customHeight="1" s="88">
+    <row r="183" ht="4" customHeight="1" s="88">
       <c r="A183" s="3" t="n"/>
       <c r="P183" s="92" t="n"/>
       <c r="T183" s="93" t="n"/>
@@ -17227,7 +17227,7 @@
       <c r="KC183" s="93" t="n"/>
       <c r="KK183" s="4" t="n"/>
     </row>
-    <row r="184" ht="16.95" customHeight="1" s="88">
+    <row r="184" ht="4" customHeight="1" s="88">
       <c r="A184" s="3" t="n"/>
       <c r="P184" s="92" t="n"/>
       <c r="T184" s="93" t="n"/>
@@ -17269,7 +17269,7 @@
       <c r="KC184" s="93" t="n"/>
       <c r="KK184" s="4" t="n"/>
     </row>
-    <row r="185" ht="16.95" customHeight="1" s="88">
+    <row r="185" ht="4" customHeight="1" s="88">
       <c r="A185" s="3" t="n"/>
       <c r="P185" s="92" t="n"/>
       <c r="T185" s="93" t="n"/>
@@ -17311,7 +17311,7 @@
       <c r="KC185" s="93" t="n"/>
       <c r="KK185" s="4" t="n"/>
     </row>
-    <row r="186" ht="16.95" customHeight="1" s="88">
+    <row r="186" ht="4" customHeight="1" s="88">
       <c r="A186" s="3" t="n"/>
       <c r="P186" s="92" t="n"/>
       <c r="T186" s="93" t="n"/>
@@ -17353,7 +17353,7 @@
       <c r="KC186" s="93" t="n"/>
       <c r="KK186" s="4" t="n"/>
     </row>
-    <row r="187" ht="16.95" customHeight="1" s="88">
+    <row r="187" ht="4" customHeight="1" s="88">
       <c r="A187" s="3" t="n"/>
       <c r="P187" s="92" t="n"/>
       <c r="T187" s="93" t="n"/>
@@ -17395,7 +17395,7 @@
       <c r="KC187" s="93" t="n"/>
       <c r="KK187" s="4" t="n"/>
     </row>
-    <row r="188" ht="16.95" customHeight="1" s="88">
+    <row r="188" ht="4" customHeight="1" s="88">
       <c r="A188" s="3" t="n"/>
       <c r="P188" s="92" t="n"/>
       <c r="T188" s="93" t="n"/>
@@ -17437,7 +17437,7 @@
       <c r="KC188" s="93" t="n"/>
       <c r="KK188" s="4" t="n"/>
     </row>
-    <row r="189" ht="16.95" customHeight="1" s="88">
+    <row r="189" ht="4" customHeight="1" s="88">
       <c r="A189" s="3" t="n"/>
       <c r="P189" s="92" t="n"/>
       <c r="T189" s="93" t="n"/>
@@ -17479,7 +17479,7 @@
       <c r="KC189" s="93" t="n"/>
       <c r="KK189" s="4" t="n"/>
     </row>
-    <row r="190" ht="16.95" customHeight="1" s="88">
+    <row r="190" ht="4" customHeight="1" s="88">
       <c r="A190" s="3" t="n"/>
       <c r="P190" s="92" t="n"/>
       <c r="T190" s="93" t="n"/>
@@ -17521,7 +17521,7 @@
       <c r="KC190" s="93" t="n"/>
       <c r="KK190" s="4" t="n"/>
     </row>
-    <row r="191" ht="16.95" customHeight="1" s="88">
+    <row r="191" ht="4" customHeight="1" s="88">
       <c r="A191" s="3" t="n"/>
       <c r="P191" s="92" t="n"/>
       <c r="T191" s="93" t="n"/>
@@ -17563,7 +17563,7 @@
       <c r="KC191" s="93" t="n"/>
       <c r="KK191" s="4" t="n"/>
     </row>
-    <row r="192" ht="16.95" customHeight="1" s="88">
+    <row r="192" ht="4" customHeight="1" s="88">
       <c r="A192" s="3" t="n"/>
       <c r="P192" s="92" t="n"/>
       <c r="T192" s="93" t="n"/>
@@ -17605,7 +17605,7 @@
       <c r="KC192" s="93" t="n"/>
       <c r="KK192" s="4" t="n"/>
     </row>
-    <row r="193" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="193" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A193" s="3" t="n"/>
       <c r="P193" s="92" t="n"/>
       <c r="T193" s="93" t="n"/>
@@ -17723,7 +17723,7 @@
       <c r="KC193" s="93" t="n"/>
       <c r="KK193" s="4" t="n"/>
     </row>
-    <row r="194" ht="16.95" customHeight="1" s="88">
+    <row r="194" ht="4" customHeight="1" s="88">
       <c r="A194" s="3" t="n"/>
       <c r="P194" s="92" t="n"/>
       <c r="T194" s="93" t="n"/>
@@ -17973,7 +17973,7 @@
       <c r="KC194" s="93" t="n"/>
       <c r="KK194" s="4" t="n"/>
     </row>
-    <row r="195" ht="16.95" customHeight="1" s="88">
+    <row r="195" ht="4" customHeight="1" s="88">
       <c r="A195" s="3" t="n"/>
       <c r="P195" s="92" t="n"/>
       <c r="T195" s="93" t="n"/>
@@ -18127,7 +18127,7 @@
       <c r="KC195" s="93" t="n"/>
       <c r="KK195" s="4" t="n"/>
     </row>
-    <row r="196" ht="16.95" customHeight="1" s="88">
+    <row r="196" ht="4" customHeight="1" s="88">
       <c r="A196" s="3" t="n"/>
       <c r="P196" s="92" t="n"/>
       <c r="T196" s="93" t="n"/>
@@ -18281,7 +18281,7 @@
       <c r="KC196" s="93" t="n"/>
       <c r="KK196" s="4" t="n"/>
     </row>
-    <row r="197" ht="16.95" customHeight="1" s="88">
+    <row r="197" ht="4" customHeight="1" s="88">
       <c r="A197" s="3" t="n"/>
       <c r="P197" s="92" t="n"/>
       <c r="T197" s="93" t="n"/>
@@ -18435,7 +18435,7 @@
       <c r="KC197" s="93" t="n"/>
       <c r="KK197" s="4" t="n"/>
     </row>
-    <row r="198" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="198" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A198" s="3" t="n"/>
       <c r="P198" s="94" t="n"/>
       <c r="Q198" s="95" t="n"/>
@@ -18673,7 +18673,7 @@
       <c r="KC198" s="96" t="n"/>
       <c r="KK198" s="4" t="n"/>
     </row>
-    <row r="199" ht="16.95" customHeight="1" s="88">
+    <row r="199" ht="4" customHeight="1" s="88">
       <c r="A199" s="3" t="n"/>
       <c r="U199" s="89" t="n">
         <v>1</v>
@@ -18953,7 +18953,7 @@
       <c r="JX199" s="91" t="n"/>
       <c r="KK199" s="4" t="n"/>
     </row>
-    <row r="200" ht="16.95" customHeight="1" s="88">
+    <row r="200" ht="4" customHeight="1" s="88">
       <c r="A200" s="3" t="n"/>
       <c r="U200" s="92" t="n"/>
       <c r="BL200" s="93" t="n"/>
@@ -18969,7 +18969,7 @@
       <c r="JX200" s="93" t="n"/>
       <c r="KK200" s="4" t="n"/>
     </row>
-    <row r="201" ht="16.95" customHeight="1" s="88">
+    <row r="201" ht="4" customHeight="1" s="88">
       <c r="A201" s="3" t="n"/>
       <c r="U201" s="92" t="n"/>
       <c r="BL201" s="93" t="n"/>
@@ -18985,7 +18985,7 @@
       <c r="JX201" s="93" t="n"/>
       <c r="KK201" s="4" t="n"/>
     </row>
-    <row r="202" ht="16.95" customHeight="1" s="88">
+    <row r="202" ht="4" customHeight="1" s="88">
       <c r="A202" s="3" t="n"/>
       <c r="U202" s="92" t="n"/>
       <c r="BL202" s="93" t="n"/>
@@ -19001,7 +19001,7 @@
       <c r="JX202" s="93" t="n"/>
       <c r="KK202" s="4" t="n"/>
     </row>
-    <row r="203" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="203" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A203" s="3" t="n"/>
       <c r="U203" s="94" t="n"/>
       <c r="V203" s="95" t="n"/>
@@ -19269,31 +19269,31 @@
       <c r="JX203" s="96" t="n"/>
       <c r="KK203" s="4" t="n"/>
     </row>
-    <row r="204" ht="16.95" customHeight="1" s="88">
+    <row r="204" ht="4" customHeight="1" s="88">
       <c r="A204" s="3" t="n"/>
       <c r="KK204" s="4" t="n"/>
     </row>
-    <row r="205" ht="16.95" customHeight="1" s="88">
+    <row r="205" ht="4" customHeight="1" s="88">
       <c r="A205" s="3" t="n"/>
       <c r="KK205" s="4" t="n"/>
     </row>
-    <row r="206" ht="16.95" customHeight="1" s="88">
+    <row r="206" ht="4" customHeight="1" s="88">
       <c r="A206" s="3" t="n"/>
       <c r="KK206" s="4" t="n"/>
     </row>
-    <row r="207" ht="16.95" customHeight="1" s="88">
+    <row r="207" ht="4" customHeight="1" s="88">
       <c r="A207" s="3" t="n"/>
       <c r="KK207" s="4" t="n"/>
     </row>
-    <row r="208" ht="16.95" customHeight="1" s="88">
+    <row r="208" ht="4" customHeight="1" s="88">
       <c r="A208" s="3" t="n"/>
       <c r="KK208" s="4" t="n"/>
     </row>
-    <row r="209" ht="16.95" customHeight="1" s="88">
+    <row r="209" ht="4" customHeight="1" s="88">
       <c r="A209" s="3" t="n"/>
       <c r="KK209" s="4" t="n"/>
     </row>
-    <row r="210" ht="16.95" customHeight="1" s="88" thickBot="1">
+    <row r="210" ht="4" customHeight="1" s="88" thickBot="1">
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="6" t="n"/>
       <c r="C210" s="6" t="n"/>

--- a/제작도_도면_1.xlsx
+++ b/제작도_도면_1.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -301,11 +301,135 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -360,6 +484,38 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -892,7 +1048,7 @@
       <c r="M2" s="11" t="n"/>
       <c r="N2" s="11" t="n"/>
       <c r="O2" s="12" t="n"/>
-      <c r="P2" s="10" t="n">
+      <c r="P2" s="32" t="n">
         <v>2</v>
       </c>
       <c r="Q2" s="11" t="n"/>
@@ -906,7 +1062,7 @@
       <c r="Y2" s="11" t="n"/>
       <c r="Z2" s="11" t="n"/>
       <c r="AA2" s="12" t="n"/>
-      <c r="AB2" s="10" t="n">
+      <c r="AB2" s="32" t="n">
         <v>3</v>
       </c>
       <c r="AC2" s="11" t="n"/>
@@ -919,7 +1075,7 @@
       <c r="AJ2" s="11" t="n"/>
       <c r="AK2" s="11" t="n"/>
       <c r="AL2" s="12" t="n"/>
-      <c r="AM2" s="10" t="n">
+      <c r="AM2" s="32" t="n">
         <v>4</v>
       </c>
       <c r="AN2" s="11" t="n"/>
@@ -932,7 +1088,7 @@
       <c r="AU2" s="11" t="n"/>
       <c r="AV2" s="11" t="n"/>
       <c r="AW2" s="12" t="n"/>
-      <c r="AX2" s="10" t="n">
+      <c r="AX2" s="32" t="n">
         <v>5</v>
       </c>
       <c r="AY2" s="11" t="n"/>
@@ -946,7 +1102,7 @@
       <c r="BG2" s="11" t="n"/>
       <c r="BH2" s="11" t="n"/>
       <c r="BI2" s="12" t="n"/>
-      <c r="BJ2" s="10" t="n">
+      <c r="BJ2" s="32" t="n">
         <v>6</v>
       </c>
       <c r="BK2" s="11" t="n"/>
@@ -990,7 +1146,7 @@
         </is>
       </c>
       <c r="BT3" s="24" t="n"/>
-      <c r="BU3" s="10" t="inlineStr">
+      <c r="BU3" s="33" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1031,66 +1187,66 @@
       <c r="BR4" s="19" t="n"/>
       <c r="BS4" s="19" t="n"/>
       <c r="BT4" s="20" t="n"/>
-      <c r="BU4" s="22" t="n"/>
+      <c r="BU4" s="34" t="n"/>
       <c r="BW4" s="5" t="n"/>
     </row>
     <row r="5" ht="13.95" customHeight="1" s="14">
       <c r="A5" s="6" t="n"/>
       <c r="E5" s="22" t="n"/>
-      <c r="AZ5" s="10" t="inlineStr">
+      <c r="AZ5" s="35" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="BA5" s="17" t="n"/>
-      <c r="BB5" s="15" t="inlineStr">
+      <c r="BA5" s="36" t="n"/>
+      <c r="BB5" s="37" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="BC5" s="16" t="n"/>
-      <c r="BD5" s="16" t="n"/>
-      <c r="BE5" s="16" t="n"/>
-      <c r="BF5" s="10" t="inlineStr">
+      <c r="BC5" s="38" t="n"/>
+      <c r="BD5" s="38" t="n"/>
+      <c r="BE5" s="38" t="n"/>
+      <c r="BF5" s="35" t="inlineStr">
         <is>
           <t>MATERIAL</t>
         </is>
       </c>
-      <c r="BG5" s="16" t="n"/>
-      <c r="BH5" s="17" t="n"/>
-      <c r="BI5" s="10" t="inlineStr">
+      <c r="BG5" s="38" t="n"/>
+      <c r="BH5" s="36" t="n"/>
+      <c r="BI5" s="33" t="inlineStr">
         <is>
           <t>SIZE</t>
         </is>
       </c>
-      <c r="BJ5" s="16" t="n"/>
-      <c r="BK5" s="16" t="n"/>
-      <c r="BL5" s="16" t="n"/>
-      <c r="BM5" s="16" t="n"/>
-      <c r="BN5" s="17" t="n"/>
-      <c r="BO5" s="10" t="inlineStr">
+      <c r="BJ5" s="38" t="n"/>
+      <c r="BK5" s="38" t="n"/>
+      <c r="BL5" s="38" t="n"/>
+      <c r="BM5" s="38" t="n"/>
+      <c r="BN5" s="36" t="n"/>
+      <c r="BO5" s="33" t="inlineStr">
         <is>
           <t>Q'TY</t>
         </is>
       </c>
-      <c r="BP5" s="10" t="inlineStr">
+      <c r="BP5" s="33" t="inlineStr">
         <is>
           <t>T/W</t>
         </is>
       </c>
-      <c r="BQ5" s="16" t="n"/>
-      <c r="BR5" s="17" t="n"/>
-      <c r="BS5" s="10" t="inlineStr">
+      <c r="BQ5" s="38" t="n"/>
+      <c r="BR5" s="36" t="n"/>
+      <c r="BS5" s="33" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="BT5" s="10" t="inlineStr">
+      <c r="BT5" s="33" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
       </c>
-      <c r="BU5" s="22" t="n"/>
+      <c r="BU5" s="34" t="n"/>
       <c r="BW5" s="5" t="n"/>
     </row>
     <row r="6" ht="13.95" customHeight="1" s="14">
@@ -1098,321 +1254,321 @@
       <c r="E6" s="22" t="n"/>
       <c r="AZ6" s="18" t="n"/>
       <c r="BA6" s="20" t="n"/>
-      <c r="BB6" s="18" t="n"/>
+      <c r="BB6" s="39" t="n"/>
       <c r="BC6" s="19" t="n"/>
       <c r="BD6" s="19" t="n"/>
       <c r="BE6" s="19" t="n"/>
       <c r="BF6" s="18" t="n"/>
       <c r="BG6" s="19" t="n"/>
       <c r="BH6" s="20" t="n"/>
-      <c r="BI6" s="18" t="n"/>
+      <c r="BI6" s="39" t="n"/>
       <c r="BJ6" s="19" t="n"/>
       <c r="BK6" s="19" t="n"/>
       <c r="BL6" s="19" t="n"/>
       <c r="BM6" s="19" t="n"/>
       <c r="BN6" s="20" t="n"/>
-      <c r="BO6" s="21" t="n"/>
-      <c r="BP6" s="18" t="n"/>
+      <c r="BO6" s="40" t="n"/>
+      <c r="BP6" s="39" t="n"/>
       <c r="BQ6" s="19" t="n"/>
       <c r="BR6" s="20" t="n"/>
-      <c r="BS6" s="21" t="n"/>
-      <c r="BT6" s="21" t="n"/>
-      <c r="BU6" s="22" t="n"/>
+      <c r="BS6" s="40" t="n"/>
+      <c r="BT6" s="40" t="n"/>
+      <c r="BU6" s="34" t="n"/>
       <c r="BW6" s="5" t="n"/>
     </row>
     <row r="7" ht="13.95" customHeight="1" s="14">
       <c r="A7" s="6" t="n"/>
       <c r="E7" s="22" t="n"/>
-      <c r="AZ7" s="10" t="inlineStr">
+      <c r="AZ7" s="35" t="inlineStr">
         <is>
           <t>{Input_4}</t>
         </is>
       </c>
-      <c r="BA7" s="12" t="n"/>
-      <c r="BB7" s="10" t="inlineStr">
+      <c r="BA7" s="41" t="n"/>
+      <c r="BB7" s="33" t="inlineStr">
         <is>
           <t>{Input_24}</t>
         </is>
       </c>
-      <c r="BC7" s="11" t="n"/>
-      <c r="BD7" s="11" t="n"/>
-      <c r="BE7" s="12" t="n"/>
-      <c r="BF7" s="10" t="inlineStr">
+      <c r="BC7" s="42" t="n"/>
+      <c r="BD7" s="42" t="n"/>
+      <c r="BE7" s="41" t="n"/>
+      <c r="BF7" s="33" t="inlineStr">
         <is>
           <t>{Input_44}</t>
         </is>
       </c>
-      <c r="BG7" s="11" t="n"/>
-      <c r="BH7" s="12" t="n"/>
-      <c r="BI7" s="10" t="inlineStr">
+      <c r="BG7" s="42" t="n"/>
+      <c r="BH7" s="41" t="n"/>
+      <c r="BI7" s="33" t="inlineStr">
         <is>
           <t>{Input_64}</t>
         </is>
       </c>
-      <c r="BJ7" s="11" t="n"/>
-      <c r="BK7" s="11" t="n"/>
-      <c r="BL7" s="11" t="n"/>
-      <c r="BM7" s="11" t="n"/>
-      <c r="BN7" s="12" t="n"/>
-      <c r="BO7" s="10" t="inlineStr">
+      <c r="BJ7" s="42" t="n"/>
+      <c r="BK7" s="42" t="n"/>
+      <c r="BL7" s="42" t="n"/>
+      <c r="BM7" s="42" t="n"/>
+      <c r="BN7" s="41" t="n"/>
+      <c r="BO7" s="33" t="inlineStr">
         <is>
           <t>{Input_84}</t>
         </is>
       </c>
-      <c r="BP7" s="10" t="inlineStr">
+      <c r="BP7" s="33" t="inlineStr">
         <is>
           <t>{Input_104}</t>
         </is>
       </c>
-      <c r="BQ7" s="11" t="n"/>
-      <c r="BR7" s="12" t="n"/>
-      <c r="BS7" s="10" t="inlineStr">
+      <c r="BQ7" s="42" t="n"/>
+      <c r="BR7" s="41" t="n"/>
+      <c r="BS7" s="33" t="inlineStr">
         <is>
           <t>{Input_124}</t>
         </is>
       </c>
-      <c r="BT7" s="10" t="inlineStr">
+      <c r="BT7" s="33" t="inlineStr">
         <is>
           <t>{Input_144}</t>
         </is>
       </c>
-      <c r="BU7" s="22" t="n"/>
+      <c r="BU7" s="34" t="n"/>
       <c r="BW7" s="5" t="n"/>
     </row>
     <row r="8" ht="13.95" customHeight="1" s="14">
       <c r="A8" s="6" t="n"/>
       <c r="E8" s="22" t="n"/>
-      <c r="AZ8" s="10" t="inlineStr">
+      <c r="AZ8" s="35" t="inlineStr">
         <is>
           <t>{Input_5}</t>
         </is>
       </c>
-      <c r="BA8" s="12" t="n"/>
-      <c r="BB8" s="10" t="inlineStr">
+      <c r="BA8" s="41" t="n"/>
+      <c r="BB8" s="33" t="inlineStr">
         <is>
           <t>{Input_25}</t>
         </is>
       </c>
-      <c r="BC8" s="11" t="n"/>
-      <c r="BD8" s="11" t="n"/>
-      <c r="BE8" s="12" t="n"/>
-      <c r="BF8" s="10" t="inlineStr">
+      <c r="BC8" s="42" t="n"/>
+      <c r="BD8" s="42" t="n"/>
+      <c r="BE8" s="41" t="n"/>
+      <c r="BF8" s="33" t="inlineStr">
         <is>
           <t>{Input_45}</t>
         </is>
       </c>
-      <c r="BG8" s="11" t="n"/>
-      <c r="BH8" s="12" t="n"/>
-      <c r="BI8" s="10" t="inlineStr">
+      <c r="BG8" s="42" t="n"/>
+      <c r="BH8" s="41" t="n"/>
+      <c r="BI8" s="33" t="inlineStr">
         <is>
           <t>{Input_65}</t>
         </is>
       </c>
-      <c r="BJ8" s="11" t="n"/>
-      <c r="BK8" s="11" t="n"/>
-      <c r="BL8" s="11" t="n"/>
-      <c r="BM8" s="11" t="n"/>
-      <c r="BN8" s="12" t="n"/>
-      <c r="BO8" s="10" t="inlineStr">
+      <c r="BJ8" s="42" t="n"/>
+      <c r="BK8" s="42" t="n"/>
+      <c r="BL8" s="42" t="n"/>
+      <c r="BM8" s="42" t="n"/>
+      <c r="BN8" s="41" t="n"/>
+      <c r="BO8" s="33" t="inlineStr">
         <is>
           <t>{Input_85}</t>
         </is>
       </c>
-      <c r="BP8" s="10" t="inlineStr">
+      <c r="BP8" s="33" t="inlineStr">
         <is>
           <t>{Input_105}</t>
         </is>
       </c>
-      <c r="BQ8" s="11" t="n"/>
-      <c r="BR8" s="12" t="n"/>
-      <c r="BS8" s="10" t="inlineStr">
+      <c r="BQ8" s="42" t="n"/>
+      <c r="BR8" s="41" t="n"/>
+      <c r="BS8" s="33" t="inlineStr">
         <is>
           <t>{Input_125}</t>
         </is>
       </c>
-      <c r="BT8" s="10" t="inlineStr">
+      <c r="BT8" s="33" t="inlineStr">
         <is>
           <t>{Input_145}</t>
         </is>
       </c>
-      <c r="BU8" s="22" t="n"/>
+      <c r="BU8" s="34" t="n"/>
       <c r="BW8" s="5" t="n"/>
     </row>
     <row r="9" ht="13.95" customHeight="1" s="14">
       <c r="A9" s="6" t="n"/>
       <c r="E9" s="22" t="n"/>
-      <c r="AZ9" s="10" t="inlineStr">
+      <c r="AZ9" s="35" t="inlineStr">
         <is>
           <t>{Input_6}</t>
         </is>
       </c>
-      <c r="BA9" s="12" t="n"/>
-      <c r="BB9" s="10" t="inlineStr">
+      <c r="BA9" s="41" t="n"/>
+      <c r="BB9" s="33" t="inlineStr">
         <is>
           <t>{Input_26}</t>
         </is>
       </c>
-      <c r="BC9" s="11" t="n"/>
-      <c r="BD9" s="11" t="n"/>
-      <c r="BE9" s="12" t="n"/>
-      <c r="BF9" s="10" t="inlineStr">
+      <c r="BC9" s="42" t="n"/>
+      <c r="BD9" s="42" t="n"/>
+      <c r="BE9" s="41" t="n"/>
+      <c r="BF9" s="33" t="inlineStr">
         <is>
           <t>{Input_46}</t>
         </is>
       </c>
-      <c r="BG9" s="11" t="n"/>
-      <c r="BH9" s="12" t="n"/>
-      <c r="BI9" s="10" t="inlineStr">
+      <c r="BG9" s="42" t="n"/>
+      <c r="BH9" s="41" t="n"/>
+      <c r="BI9" s="33" t="inlineStr">
         <is>
           <t>{Input_66}</t>
         </is>
       </c>
-      <c r="BJ9" s="11" t="n"/>
-      <c r="BK9" s="11" t="n"/>
-      <c r="BL9" s="11" t="n"/>
-      <c r="BM9" s="11" t="n"/>
-      <c r="BN9" s="12" t="n"/>
-      <c r="BO9" s="10" t="inlineStr">
+      <c r="BJ9" s="42" t="n"/>
+      <c r="BK9" s="42" t="n"/>
+      <c r="BL9" s="42" t="n"/>
+      <c r="BM9" s="42" t="n"/>
+      <c r="BN9" s="41" t="n"/>
+      <c r="BO9" s="33" t="inlineStr">
         <is>
           <t>{Input_86}</t>
         </is>
       </c>
-      <c r="BP9" s="10" t="inlineStr">
+      <c r="BP9" s="33" t="inlineStr">
         <is>
           <t>{Input_106}</t>
         </is>
       </c>
-      <c r="BQ9" s="11" t="n"/>
-      <c r="BR9" s="12" t="n"/>
-      <c r="BS9" s="10" t="inlineStr">
+      <c r="BQ9" s="42" t="n"/>
+      <c r="BR9" s="41" t="n"/>
+      <c r="BS9" s="33" t="inlineStr">
         <is>
           <t>{Input_126}</t>
         </is>
       </c>
-      <c r="BT9" s="10" t="inlineStr">
+      <c r="BT9" s="33" t="inlineStr">
         <is>
           <t>{Input_146}</t>
         </is>
       </c>
-      <c r="BU9" s="22" t="n"/>
+      <c r="BU9" s="34" t="n"/>
       <c r="BW9" s="5" t="n"/>
     </row>
     <row r="10" ht="13.95" customHeight="1" s="14">
       <c r="A10" s="6" t="n"/>
       <c r="E10" s="22" t="n"/>
-      <c r="AZ10" s="10" t="inlineStr">
+      <c r="AZ10" s="35" t="inlineStr">
         <is>
           <t>{Input_7}</t>
         </is>
       </c>
-      <c r="BA10" s="12" t="n"/>
-      <c r="BB10" s="10" t="inlineStr">
+      <c r="BA10" s="41" t="n"/>
+      <c r="BB10" s="33" t="inlineStr">
         <is>
           <t>{Input_27}</t>
         </is>
       </c>
-      <c r="BC10" s="11" t="n"/>
-      <c r="BD10" s="11" t="n"/>
-      <c r="BE10" s="12" t="n"/>
-      <c r="BF10" s="10" t="inlineStr">
+      <c r="BC10" s="42" t="n"/>
+      <c r="BD10" s="42" t="n"/>
+      <c r="BE10" s="41" t="n"/>
+      <c r="BF10" s="33" t="inlineStr">
         <is>
           <t>{Input_47}</t>
         </is>
       </c>
-      <c r="BG10" s="11" t="n"/>
-      <c r="BH10" s="12" t="n"/>
-      <c r="BI10" s="10" t="inlineStr">
+      <c r="BG10" s="42" t="n"/>
+      <c r="BH10" s="41" t="n"/>
+      <c r="BI10" s="33" t="inlineStr">
         <is>
           <t>{Input_67}</t>
         </is>
       </c>
-      <c r="BJ10" s="11" t="n"/>
-      <c r="BK10" s="11" t="n"/>
-      <c r="BL10" s="11" t="n"/>
-      <c r="BM10" s="11" t="n"/>
-      <c r="BN10" s="12" t="n"/>
-      <c r="BO10" s="10" t="inlineStr">
+      <c r="BJ10" s="42" t="n"/>
+      <c r="BK10" s="42" t="n"/>
+      <c r="BL10" s="42" t="n"/>
+      <c r="BM10" s="42" t="n"/>
+      <c r="BN10" s="41" t="n"/>
+      <c r="BO10" s="33" t="inlineStr">
         <is>
           <t>{Input_87}</t>
         </is>
       </c>
-      <c r="BP10" s="10" t="inlineStr">
+      <c r="BP10" s="33" t="inlineStr">
         <is>
           <t>{Input_107}</t>
         </is>
       </c>
-      <c r="BQ10" s="11" t="n"/>
-      <c r="BR10" s="12" t="n"/>
-      <c r="BS10" s="10" t="inlineStr">
+      <c r="BQ10" s="42" t="n"/>
+      <c r="BR10" s="41" t="n"/>
+      <c r="BS10" s="33" t="inlineStr">
         <is>
           <t>{Input_127}</t>
         </is>
       </c>
-      <c r="BT10" s="10" t="inlineStr">
+      <c r="BT10" s="33" t="inlineStr">
         <is>
           <t>{Input_147}</t>
         </is>
       </c>
-      <c r="BU10" s="22" t="n"/>
+      <c r="BU10" s="34" t="n"/>
       <c r="BW10" s="5" t="n"/>
     </row>
     <row r="11" ht="13.95" customHeight="1" s="14">
       <c r="A11" s="6" t="n"/>
       <c r="E11" s="22" t="n"/>
-      <c r="AZ11" s="10" t="inlineStr">
+      <c r="AZ11" s="35" t="inlineStr">
         <is>
           <t>{Input_8}</t>
         </is>
       </c>
-      <c r="BA11" s="17" t="n"/>
-      <c r="BB11" s="10" t="inlineStr">
+      <c r="BA11" s="36" t="n"/>
+      <c r="BB11" s="33" t="inlineStr">
         <is>
           <t>{Input_28}</t>
         </is>
       </c>
-      <c r="BC11" s="16" t="n"/>
-      <c r="BD11" s="16" t="n"/>
-      <c r="BE11" s="17" t="n"/>
-      <c r="BF11" s="10" t="inlineStr">
+      <c r="BC11" s="38" t="n"/>
+      <c r="BD11" s="38" t="n"/>
+      <c r="BE11" s="36" t="n"/>
+      <c r="BF11" s="33" t="inlineStr">
         <is>
           <t>{Input_48}</t>
         </is>
       </c>
-      <c r="BG11" s="16" t="n"/>
-      <c r="BH11" s="17" t="n"/>
-      <c r="BI11" s="10" t="inlineStr">
+      <c r="BG11" s="38" t="n"/>
+      <c r="BH11" s="36" t="n"/>
+      <c r="BI11" s="33" t="inlineStr">
         <is>
           <t>{Input_68}</t>
         </is>
       </c>
-      <c r="BJ11" s="16" t="n"/>
-      <c r="BK11" s="16" t="n"/>
-      <c r="BL11" s="16" t="n"/>
-      <c r="BM11" s="16" t="n"/>
-      <c r="BN11" s="17" t="n"/>
-      <c r="BO11" s="10" t="inlineStr">
+      <c r="BJ11" s="38" t="n"/>
+      <c r="BK11" s="38" t="n"/>
+      <c r="BL11" s="38" t="n"/>
+      <c r="BM11" s="38" t="n"/>
+      <c r="BN11" s="36" t="n"/>
+      <c r="BO11" s="33" t="inlineStr">
         <is>
           <t>{Input_88}</t>
         </is>
       </c>
-      <c r="BP11" s="10" t="inlineStr">
+      <c r="BP11" s="33" t="inlineStr">
         <is>
           <t>{Input_108}</t>
         </is>
       </c>
-      <c r="BQ11" s="16" t="n"/>
-      <c r="BR11" s="17" t="n"/>
-      <c r="BS11" s="10" t="inlineStr">
+      <c r="BQ11" s="38" t="n"/>
+      <c r="BR11" s="36" t="n"/>
+      <c r="BS11" s="33" t="inlineStr">
         <is>
           <t>{Input_128}</t>
         </is>
       </c>
-      <c r="BT11" s="10" t="inlineStr">
+      <c r="BT11" s="33" t="inlineStr">
         <is>
           <t>{Input_148}</t>
         </is>
       </c>
-      <c r="BU11" s="22" t="n"/>
+      <c r="BU11" s="34" t="n"/>
       <c r="BW11" s="5" t="n"/>
     </row>
     <row r="12" ht="13.95" customHeight="1" s="14">
@@ -1420,325 +1576,325 @@
       <c r="E12" s="22" t="n"/>
       <c r="AZ12" s="18" t="n"/>
       <c r="BA12" s="20" t="n"/>
-      <c r="BB12" s="18" t="n"/>
+      <c r="BB12" s="39" t="n"/>
       <c r="BC12" s="19" t="n"/>
       <c r="BD12" s="19" t="n"/>
       <c r="BE12" s="20" t="n"/>
-      <c r="BF12" s="18" t="n"/>
+      <c r="BF12" s="39" t="n"/>
       <c r="BG12" s="19" t="n"/>
       <c r="BH12" s="20" t="n"/>
-      <c r="BI12" s="18" t="n"/>
+      <c r="BI12" s="39" t="n"/>
       <c r="BJ12" s="19" t="n"/>
       <c r="BK12" s="19" t="n"/>
       <c r="BL12" s="19" t="n"/>
       <c r="BM12" s="19" t="n"/>
       <c r="BN12" s="20" t="n"/>
-      <c r="BO12" s="21" t="n"/>
-      <c r="BP12" s="18" t="n"/>
+      <c r="BO12" s="40" t="n"/>
+      <c r="BP12" s="39" t="n"/>
       <c r="BQ12" s="19" t="n"/>
       <c r="BR12" s="20" t="n"/>
-      <c r="BS12" s="21" t="n"/>
-      <c r="BT12" s="21" t="n"/>
-      <c r="BU12" s="22" t="n"/>
+      <c r="BS12" s="40" t="n"/>
+      <c r="BT12" s="40" t="n"/>
+      <c r="BU12" s="34" t="n"/>
       <c r="BW12" s="5" t="n"/>
     </row>
     <row r="13" ht="13.95" customHeight="1" s="14">
       <c r="A13" s="6" t="n"/>
       <c r="E13" s="22" t="n"/>
-      <c r="AZ13" s="10" t="inlineStr">
+      <c r="AZ13" s="35" t="inlineStr">
         <is>
           <t>{Input_9}</t>
         </is>
       </c>
-      <c r="BA13" s="12" t="n"/>
-      <c r="BB13" s="10" t="inlineStr">
+      <c r="BA13" s="41" t="n"/>
+      <c r="BB13" s="33" t="inlineStr">
         <is>
           <t>{Input_29}</t>
         </is>
       </c>
-      <c r="BC13" s="11" t="n"/>
-      <c r="BD13" s="11" t="n"/>
-      <c r="BE13" s="12" t="n"/>
-      <c r="BF13" s="10" t="inlineStr">
+      <c r="BC13" s="42" t="n"/>
+      <c r="BD13" s="42" t="n"/>
+      <c r="BE13" s="41" t="n"/>
+      <c r="BF13" s="33" t="inlineStr">
         <is>
           <t>{Input_49}</t>
         </is>
       </c>
-      <c r="BG13" s="11" t="n"/>
-      <c r="BH13" s="12" t="n"/>
-      <c r="BI13" s="10" t="inlineStr">
+      <c r="BG13" s="42" t="n"/>
+      <c r="BH13" s="41" t="n"/>
+      <c r="BI13" s="33" t="inlineStr">
         <is>
           <t>{Input_69}</t>
         </is>
       </c>
-      <c r="BJ13" s="11" t="n"/>
-      <c r="BK13" s="11" t="n"/>
-      <c r="BL13" s="11" t="n"/>
-      <c r="BM13" s="11" t="n"/>
-      <c r="BN13" s="12" t="n"/>
-      <c r="BO13" s="10" t="inlineStr">
+      <c r="BJ13" s="42" t="n"/>
+      <c r="BK13" s="42" t="n"/>
+      <c r="BL13" s="42" t="n"/>
+      <c r="BM13" s="42" t="n"/>
+      <c r="BN13" s="41" t="n"/>
+      <c r="BO13" s="33" t="inlineStr">
         <is>
           <t>{Input_89}</t>
         </is>
       </c>
-      <c r="BP13" s="10" t="inlineStr">
+      <c r="BP13" s="33" t="inlineStr">
         <is>
           <t>{Input_109}</t>
         </is>
       </c>
-      <c r="BQ13" s="11" t="n"/>
-      <c r="BR13" s="12" t="n"/>
-      <c r="BS13" s="10" t="inlineStr">
+      <c r="BQ13" s="42" t="n"/>
+      <c r="BR13" s="41" t="n"/>
+      <c r="BS13" s="33" t="inlineStr">
         <is>
           <t>{Input_129}</t>
         </is>
       </c>
-      <c r="BT13" s="10" t="inlineStr">
+      <c r="BT13" s="33" t="inlineStr">
         <is>
           <t>{Input_149}</t>
         </is>
       </c>
-      <c r="BU13" s="22" t="n"/>
+      <c r="BU13" s="34" t="n"/>
       <c r="BW13" s="5" t="n"/>
     </row>
     <row r="14" ht="13.95" customHeight="1" s="14">
       <c r="A14" s="6" t="n"/>
       <c r="E14" s="22" t="n"/>
-      <c r="AZ14" s="10" t="inlineStr">
+      <c r="AZ14" s="35" t="inlineStr">
         <is>
           <t>{Input_10}</t>
         </is>
       </c>
-      <c r="BA14" s="12" t="n"/>
-      <c r="BB14" s="10" t="inlineStr">
+      <c r="BA14" s="41" t="n"/>
+      <c r="BB14" s="33" t="inlineStr">
         <is>
           <t>{Input_30}</t>
         </is>
       </c>
-      <c r="BC14" s="11" t="n"/>
-      <c r="BD14" s="11" t="n"/>
-      <c r="BE14" s="12" t="n"/>
-      <c r="BF14" s="10" t="inlineStr">
+      <c r="BC14" s="42" t="n"/>
+      <c r="BD14" s="42" t="n"/>
+      <c r="BE14" s="41" t="n"/>
+      <c r="BF14" s="33" t="inlineStr">
         <is>
           <t>{Input_50}</t>
         </is>
       </c>
-      <c r="BG14" s="11" t="n"/>
-      <c r="BH14" s="12" t="n"/>
-      <c r="BI14" s="10" t="inlineStr">
+      <c r="BG14" s="42" t="n"/>
+      <c r="BH14" s="41" t="n"/>
+      <c r="BI14" s="33" t="inlineStr">
         <is>
           <t>{Input_70}</t>
         </is>
       </c>
-      <c r="BJ14" s="11" t="n"/>
-      <c r="BK14" s="11" t="n"/>
-      <c r="BL14" s="11" t="n"/>
-      <c r="BM14" s="11" t="n"/>
-      <c r="BN14" s="12" t="n"/>
-      <c r="BO14" s="10" t="inlineStr">
+      <c r="BJ14" s="42" t="n"/>
+      <c r="BK14" s="42" t="n"/>
+      <c r="BL14" s="42" t="n"/>
+      <c r="BM14" s="42" t="n"/>
+      <c r="BN14" s="41" t="n"/>
+      <c r="BO14" s="33" t="inlineStr">
         <is>
           <t>{Input_90}</t>
         </is>
       </c>
-      <c r="BP14" s="10" t="inlineStr">
+      <c r="BP14" s="33" t="inlineStr">
         <is>
           <t>{Input_110}</t>
         </is>
       </c>
-      <c r="BQ14" s="11" t="n"/>
-      <c r="BR14" s="12" t="n"/>
-      <c r="BS14" s="10" t="inlineStr">
+      <c r="BQ14" s="42" t="n"/>
+      <c r="BR14" s="41" t="n"/>
+      <c r="BS14" s="33" t="inlineStr">
         <is>
           <t>{Input_130}</t>
         </is>
       </c>
-      <c r="BT14" s="10" t="inlineStr">
+      <c r="BT14" s="33" t="inlineStr">
         <is>
           <t>{Input_150}</t>
         </is>
       </c>
-      <c r="BU14" s="22" t="n"/>
+      <c r="BU14" s="34" t="n"/>
       <c r="BW14" s="5" t="n"/>
     </row>
     <row r="15" ht="13.95" customHeight="1" s="14">
       <c r="A15" s="6" t="n"/>
       <c r="E15" s="22" t="n"/>
-      <c r="AZ15" s="10" t="inlineStr">
+      <c r="AZ15" s="35" t="inlineStr">
         <is>
           <t>{Input_11}</t>
         </is>
       </c>
-      <c r="BA15" s="12" t="n"/>
-      <c r="BB15" s="10" t="inlineStr">
+      <c r="BA15" s="41" t="n"/>
+      <c r="BB15" s="33" t="inlineStr">
         <is>
           <t>{Input_31}</t>
         </is>
       </c>
-      <c r="BC15" s="11" t="n"/>
-      <c r="BD15" s="11" t="n"/>
-      <c r="BE15" s="12" t="n"/>
-      <c r="BF15" s="10" t="inlineStr">
+      <c r="BC15" s="42" t="n"/>
+      <c r="BD15" s="42" t="n"/>
+      <c r="BE15" s="41" t="n"/>
+      <c r="BF15" s="33" t="inlineStr">
         <is>
           <t>{Input_51}</t>
         </is>
       </c>
-      <c r="BG15" s="11" t="n"/>
-      <c r="BH15" s="12" t="n"/>
-      <c r="BI15" s="10" t="inlineStr">
+      <c r="BG15" s="42" t="n"/>
+      <c r="BH15" s="41" t="n"/>
+      <c r="BI15" s="33" t="inlineStr">
         <is>
           <t>{Input_71}</t>
         </is>
       </c>
-      <c r="BJ15" s="11" t="n"/>
-      <c r="BK15" s="11" t="n"/>
-      <c r="BL15" s="11" t="n"/>
-      <c r="BM15" s="11" t="n"/>
-      <c r="BN15" s="12" t="n"/>
-      <c r="BO15" s="10" t="inlineStr">
+      <c r="BJ15" s="42" t="n"/>
+      <c r="BK15" s="42" t="n"/>
+      <c r="BL15" s="42" t="n"/>
+      <c r="BM15" s="42" t="n"/>
+      <c r="BN15" s="41" t="n"/>
+      <c r="BO15" s="33" t="inlineStr">
         <is>
           <t>{Input_91}</t>
         </is>
       </c>
-      <c r="BP15" s="10" t="inlineStr">
+      <c r="BP15" s="33" t="inlineStr">
         <is>
           <t>{Input_111}</t>
         </is>
       </c>
-      <c r="BQ15" s="11" t="n"/>
-      <c r="BR15" s="12" t="n"/>
-      <c r="BS15" s="10" t="inlineStr">
+      <c r="BQ15" s="42" t="n"/>
+      <c r="BR15" s="41" t="n"/>
+      <c r="BS15" s="33" t="inlineStr">
         <is>
           <t>{Input_131}</t>
         </is>
       </c>
-      <c r="BT15" s="10" t="inlineStr">
+      <c r="BT15" s="33" t="inlineStr">
         <is>
           <t>{Input_151}</t>
         </is>
       </c>
-      <c r="BU15" s="22" t="n"/>
+      <c r="BU15" s="34" t="n"/>
       <c r="BW15" s="5" t="n"/>
     </row>
     <row r="16" ht="13.95" customHeight="1" s="14">
       <c r="A16" s="6" t="n"/>
       <c r="E16" s="21" t="n"/>
-      <c r="AZ16" s="10" t="inlineStr">
+      <c r="AZ16" s="35" t="inlineStr">
         <is>
           <t>{Input_12}</t>
         </is>
       </c>
-      <c r="BA16" s="12" t="n"/>
-      <c r="BB16" s="10" t="inlineStr">
+      <c r="BA16" s="41" t="n"/>
+      <c r="BB16" s="33" t="inlineStr">
         <is>
           <t>{Input_32}</t>
         </is>
       </c>
-      <c r="BC16" s="11" t="n"/>
-      <c r="BD16" s="11" t="n"/>
-      <c r="BE16" s="12" t="n"/>
-      <c r="BF16" s="10" t="inlineStr">
+      <c r="BC16" s="42" t="n"/>
+      <c r="BD16" s="42" t="n"/>
+      <c r="BE16" s="41" t="n"/>
+      <c r="BF16" s="33" t="inlineStr">
         <is>
           <t>{Input_52}</t>
         </is>
       </c>
-      <c r="BG16" s="11" t="n"/>
-      <c r="BH16" s="12" t="n"/>
-      <c r="BI16" s="10" t="inlineStr">
+      <c r="BG16" s="42" t="n"/>
+      <c r="BH16" s="41" t="n"/>
+      <c r="BI16" s="33" t="inlineStr">
         <is>
           <t>{Input_72}</t>
         </is>
       </c>
-      <c r="BJ16" s="11" t="n"/>
-      <c r="BK16" s="11" t="n"/>
-      <c r="BL16" s="11" t="n"/>
-      <c r="BM16" s="11" t="n"/>
-      <c r="BN16" s="12" t="n"/>
-      <c r="BO16" s="10" t="inlineStr">
+      <c r="BJ16" s="42" t="n"/>
+      <c r="BK16" s="42" t="n"/>
+      <c r="BL16" s="42" t="n"/>
+      <c r="BM16" s="42" t="n"/>
+      <c r="BN16" s="41" t="n"/>
+      <c r="BO16" s="33" t="inlineStr">
         <is>
           <t>{Input_92}</t>
         </is>
       </c>
-      <c r="BP16" s="10" t="inlineStr">
+      <c r="BP16" s="33" t="inlineStr">
         <is>
           <t>{Input_112}</t>
         </is>
       </c>
-      <c r="BQ16" s="11" t="n"/>
-      <c r="BR16" s="12" t="n"/>
-      <c r="BS16" s="10" t="inlineStr">
+      <c r="BQ16" s="42" t="n"/>
+      <c r="BR16" s="41" t="n"/>
+      <c r="BS16" s="33" t="inlineStr">
         <is>
           <t>{Input_132}</t>
         </is>
       </c>
-      <c r="BT16" s="10" t="inlineStr">
+      <c r="BT16" s="33" t="inlineStr">
         <is>
           <t>{Input_152}</t>
         </is>
       </c>
-      <c r="BU16" s="21" t="n"/>
+      <c r="BU16" s="40" t="n"/>
       <c r="BW16" s="5" t="n"/>
     </row>
     <row r="17" ht="13.95" customHeight="1" s="14">
       <c r="A17" s="6" t="n"/>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="AZ17" s="10" t="inlineStr">
+      <c r="AZ17" s="35" t="inlineStr">
         <is>
           <t>{Input_13}</t>
         </is>
       </c>
-      <c r="BA17" s="12" t="n"/>
-      <c r="BB17" s="10" t="inlineStr">
+      <c r="BA17" s="41" t="n"/>
+      <c r="BB17" s="33" t="inlineStr">
         <is>
           <t>{Input_33}</t>
         </is>
       </c>
-      <c r="BC17" s="11" t="n"/>
-      <c r="BD17" s="11" t="n"/>
-      <c r="BE17" s="12" t="n"/>
-      <c r="BF17" s="10" t="inlineStr">
+      <c r="BC17" s="42" t="n"/>
+      <c r="BD17" s="42" t="n"/>
+      <c r="BE17" s="41" t="n"/>
+      <c r="BF17" s="33" t="inlineStr">
         <is>
           <t>{Input_53}</t>
         </is>
       </c>
-      <c r="BG17" s="11" t="n"/>
-      <c r="BH17" s="12" t="n"/>
-      <c r="BI17" s="10" t="inlineStr">
+      <c r="BG17" s="42" t="n"/>
+      <c r="BH17" s="41" t="n"/>
+      <c r="BI17" s="33" t="inlineStr">
         <is>
           <t>{Input_73}</t>
         </is>
       </c>
-      <c r="BJ17" s="11" t="n"/>
-      <c r="BK17" s="11" t="n"/>
-      <c r="BL17" s="11" t="n"/>
-      <c r="BM17" s="11" t="n"/>
-      <c r="BN17" s="12" t="n"/>
-      <c r="BO17" s="10" t="inlineStr">
+      <c r="BJ17" s="42" t="n"/>
+      <c r="BK17" s="42" t="n"/>
+      <c r="BL17" s="42" t="n"/>
+      <c r="BM17" s="42" t="n"/>
+      <c r="BN17" s="41" t="n"/>
+      <c r="BO17" s="33" t="inlineStr">
         <is>
           <t>{Input_93}</t>
         </is>
       </c>
-      <c r="BP17" s="10" t="inlineStr">
+      <c r="BP17" s="33" t="inlineStr">
         <is>
           <t>{Input_113}</t>
         </is>
       </c>
-      <c r="BQ17" s="11" t="n"/>
-      <c r="BR17" s="12" t="n"/>
-      <c r="BS17" s="10" t="inlineStr">
+      <c r="BQ17" s="42" t="n"/>
+      <c r="BR17" s="41" t="n"/>
+      <c r="BS17" s="33" t="inlineStr">
         <is>
           <t>{Input_133}</t>
         </is>
       </c>
-      <c r="BT17" s="10" t="inlineStr">
+      <c r="BT17" s="33" t="inlineStr">
         <is>
           <t>{Input_153}</t>
         </is>
       </c>
-      <c r="BU17" s="10" t="inlineStr">
+      <c r="BU17" s="33" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -1748,591 +1904,591 @@
     <row r="18" ht="13.95" customHeight="1" s="14">
       <c r="A18" s="6" t="n"/>
       <c r="E18" s="22" t="n"/>
-      <c r="AZ18" s="10" t="inlineStr">
+      <c r="AZ18" s="35" t="inlineStr">
         <is>
           <t>{Input_14}</t>
         </is>
       </c>
-      <c r="BA18" s="12" t="n"/>
-      <c r="BB18" s="10" t="inlineStr">
+      <c r="BA18" s="41" t="n"/>
+      <c r="BB18" s="33" t="inlineStr">
         <is>
           <t>{Input_34}</t>
         </is>
       </c>
-      <c r="BC18" s="11" t="n"/>
-      <c r="BD18" s="11" t="n"/>
-      <c r="BE18" s="12" t="n"/>
-      <c r="BF18" s="10" t="inlineStr">
+      <c r="BC18" s="42" t="n"/>
+      <c r="BD18" s="42" t="n"/>
+      <c r="BE18" s="41" t="n"/>
+      <c r="BF18" s="33" t="inlineStr">
         <is>
           <t>{Input_54}</t>
         </is>
       </c>
-      <c r="BG18" s="11" t="n"/>
-      <c r="BH18" s="12" t="n"/>
-      <c r="BI18" s="10" t="inlineStr">
+      <c r="BG18" s="42" t="n"/>
+      <c r="BH18" s="41" t="n"/>
+      <c r="BI18" s="33" t="inlineStr">
         <is>
           <t>{Input_74}</t>
         </is>
       </c>
-      <c r="BJ18" s="11" t="n"/>
-      <c r="BK18" s="11" t="n"/>
-      <c r="BL18" s="11" t="n"/>
-      <c r="BM18" s="11" t="n"/>
-      <c r="BN18" s="12" t="n"/>
-      <c r="BO18" s="10" t="inlineStr">
+      <c r="BJ18" s="42" t="n"/>
+      <c r="BK18" s="42" t="n"/>
+      <c r="BL18" s="42" t="n"/>
+      <c r="BM18" s="42" t="n"/>
+      <c r="BN18" s="41" t="n"/>
+      <c r="BO18" s="33" t="inlineStr">
         <is>
           <t>{Input_94}</t>
         </is>
       </c>
-      <c r="BP18" s="10" t="inlineStr">
+      <c r="BP18" s="33" t="inlineStr">
         <is>
           <t>{Input_114}</t>
         </is>
       </c>
-      <c r="BQ18" s="11" t="n"/>
-      <c r="BR18" s="12" t="n"/>
-      <c r="BS18" s="10" t="inlineStr">
+      <c r="BQ18" s="42" t="n"/>
+      <c r="BR18" s="41" t="n"/>
+      <c r="BS18" s="33" t="inlineStr">
         <is>
           <t>{Input_134}</t>
         </is>
       </c>
-      <c r="BT18" s="10" t="inlineStr">
+      <c r="BT18" s="33" t="inlineStr">
         <is>
           <t>{Input_154}</t>
         </is>
       </c>
-      <c r="BU18" s="22" t="n"/>
+      <c r="BU18" s="34" t="n"/>
       <c r="BW18" s="5" t="n"/>
     </row>
     <row r="19" ht="13.95" customHeight="1" s="14">
       <c r="A19" s="6" t="n"/>
       <c r="E19" s="22" t="n"/>
-      <c r="AZ19" s="10" t="inlineStr">
+      <c r="AZ19" s="35" t="inlineStr">
         <is>
           <t>{Input_15}</t>
         </is>
       </c>
-      <c r="BA19" s="12" t="n"/>
-      <c r="BB19" s="10" t="inlineStr">
+      <c r="BA19" s="41" t="n"/>
+      <c r="BB19" s="33" t="inlineStr">
         <is>
           <t>{Input_35}</t>
         </is>
       </c>
-      <c r="BC19" s="11" t="n"/>
-      <c r="BD19" s="11" t="n"/>
-      <c r="BE19" s="12" t="n"/>
-      <c r="BF19" s="10" t="inlineStr">
+      <c r="BC19" s="42" t="n"/>
+      <c r="BD19" s="42" t="n"/>
+      <c r="BE19" s="41" t="n"/>
+      <c r="BF19" s="33" t="inlineStr">
         <is>
           <t>{Input_55}</t>
         </is>
       </c>
-      <c r="BG19" s="11" t="n"/>
-      <c r="BH19" s="12" t="n"/>
-      <c r="BI19" s="10" t="inlineStr">
+      <c r="BG19" s="42" t="n"/>
+      <c r="BH19" s="41" t="n"/>
+      <c r="BI19" s="33" t="inlineStr">
         <is>
           <t>{Input_75}</t>
         </is>
       </c>
-      <c r="BJ19" s="11" t="n"/>
-      <c r="BK19" s="11" t="n"/>
-      <c r="BL19" s="11" t="n"/>
-      <c r="BM19" s="11" t="n"/>
-      <c r="BN19" s="12" t="n"/>
-      <c r="BO19" s="10" t="inlineStr">
+      <c r="BJ19" s="42" t="n"/>
+      <c r="BK19" s="42" t="n"/>
+      <c r="BL19" s="42" t="n"/>
+      <c r="BM19" s="42" t="n"/>
+      <c r="BN19" s="41" t="n"/>
+      <c r="BO19" s="33" t="inlineStr">
         <is>
           <t>{Input_95}</t>
         </is>
       </c>
-      <c r="BP19" s="10" t="inlineStr">
+      <c r="BP19" s="33" t="inlineStr">
         <is>
           <t>{Input_115}</t>
         </is>
       </c>
-      <c r="BQ19" s="11" t="n"/>
-      <c r="BR19" s="12" t="n"/>
-      <c r="BS19" s="10" t="inlineStr">
+      <c r="BQ19" s="42" t="n"/>
+      <c r="BR19" s="41" t="n"/>
+      <c r="BS19" s="33" t="inlineStr">
         <is>
           <t>{Input_135}</t>
         </is>
       </c>
-      <c r="BT19" s="10" t="inlineStr">
+      <c r="BT19" s="33" t="inlineStr">
         <is>
           <t>{Input_155}</t>
         </is>
       </c>
-      <c r="BU19" s="22" t="n"/>
+      <c r="BU19" s="34" t="n"/>
       <c r="BW19" s="5" t="n"/>
     </row>
     <row r="20" ht="13.95" customHeight="1" s="14">
       <c r="A20" s="6" t="n"/>
       <c r="E20" s="22" t="n"/>
-      <c r="AZ20" s="10" t="inlineStr">
+      <c r="AZ20" s="35" t="inlineStr">
         <is>
           <t>{Input_16}</t>
         </is>
       </c>
-      <c r="BA20" s="12" t="n"/>
-      <c r="BB20" s="10" t="inlineStr">
+      <c r="BA20" s="41" t="n"/>
+      <c r="BB20" s="33" t="inlineStr">
         <is>
           <t>{Input_36}</t>
         </is>
       </c>
-      <c r="BC20" s="11" t="n"/>
-      <c r="BD20" s="11" t="n"/>
-      <c r="BE20" s="12" t="n"/>
-      <c r="BF20" s="10" t="inlineStr">
+      <c r="BC20" s="42" t="n"/>
+      <c r="BD20" s="42" t="n"/>
+      <c r="BE20" s="41" t="n"/>
+      <c r="BF20" s="33" t="inlineStr">
         <is>
           <t>{Input_56}</t>
         </is>
       </c>
-      <c r="BG20" s="11" t="n"/>
-      <c r="BH20" s="12" t="n"/>
-      <c r="BI20" s="10" t="inlineStr">
+      <c r="BG20" s="42" t="n"/>
+      <c r="BH20" s="41" t="n"/>
+      <c r="BI20" s="33" t="inlineStr">
         <is>
           <t>{Input_76}</t>
         </is>
       </c>
-      <c r="BJ20" s="11" t="n"/>
-      <c r="BK20" s="11" t="n"/>
-      <c r="BL20" s="11" t="n"/>
-      <c r="BM20" s="11" t="n"/>
-      <c r="BN20" s="12" t="n"/>
-      <c r="BO20" s="10" t="inlineStr">
+      <c r="BJ20" s="42" t="n"/>
+      <c r="BK20" s="42" t="n"/>
+      <c r="BL20" s="42" t="n"/>
+      <c r="BM20" s="42" t="n"/>
+      <c r="BN20" s="41" t="n"/>
+      <c r="BO20" s="33" t="inlineStr">
         <is>
           <t>{Input_96}</t>
         </is>
       </c>
-      <c r="BP20" s="10" t="inlineStr">
+      <c r="BP20" s="33" t="inlineStr">
         <is>
           <t>{Input_116}</t>
         </is>
       </c>
-      <c r="BQ20" s="11" t="n"/>
-      <c r="BR20" s="12" t="n"/>
-      <c r="BS20" s="10" t="inlineStr">
+      <c r="BQ20" s="42" t="n"/>
+      <c r="BR20" s="41" t="n"/>
+      <c r="BS20" s="33" t="inlineStr">
         <is>
           <t>{Input_136}</t>
         </is>
       </c>
-      <c r="BT20" s="10" t="inlineStr">
+      <c r="BT20" s="33" t="inlineStr">
         <is>
           <t>{Input_156}</t>
         </is>
       </c>
-      <c r="BU20" s="22" t="n"/>
+      <c r="BU20" s="34" t="n"/>
       <c r="BW20" s="5" t="n"/>
     </row>
     <row r="21" ht="13.95" customHeight="1" s="14">
       <c r="A21" s="6" t="n"/>
       <c r="E21" s="22" t="n"/>
-      <c r="AZ21" s="10" t="inlineStr">
+      <c r="AZ21" s="35" t="inlineStr">
         <is>
           <t>{Input_17}</t>
         </is>
       </c>
-      <c r="BA21" s="12" t="n"/>
-      <c r="BB21" s="10" t="inlineStr">
+      <c r="BA21" s="41" t="n"/>
+      <c r="BB21" s="33" t="inlineStr">
         <is>
           <t>{Input_37}</t>
         </is>
       </c>
-      <c r="BC21" s="11" t="n"/>
-      <c r="BD21" s="11" t="n"/>
-      <c r="BE21" s="12" t="n"/>
-      <c r="BF21" s="10" t="inlineStr">
+      <c r="BC21" s="42" t="n"/>
+      <c r="BD21" s="42" t="n"/>
+      <c r="BE21" s="41" t="n"/>
+      <c r="BF21" s="33" t="inlineStr">
         <is>
           <t>{Input_57}</t>
         </is>
       </c>
-      <c r="BG21" s="11" t="n"/>
-      <c r="BH21" s="12" t="n"/>
-      <c r="BI21" s="10" t="inlineStr">
+      <c r="BG21" s="42" t="n"/>
+      <c r="BH21" s="41" t="n"/>
+      <c r="BI21" s="33" t="inlineStr">
         <is>
           <t>{Input_77}</t>
         </is>
       </c>
-      <c r="BJ21" s="11" t="n"/>
-      <c r="BK21" s="11" t="n"/>
-      <c r="BL21" s="11" t="n"/>
-      <c r="BM21" s="11" t="n"/>
-      <c r="BN21" s="12" t="n"/>
-      <c r="BO21" s="10" t="inlineStr">
+      <c r="BJ21" s="42" t="n"/>
+      <c r="BK21" s="42" t="n"/>
+      <c r="BL21" s="42" t="n"/>
+      <c r="BM21" s="42" t="n"/>
+      <c r="BN21" s="41" t="n"/>
+      <c r="BO21" s="33" t="inlineStr">
         <is>
           <t>{Input_97}</t>
         </is>
       </c>
-      <c r="BP21" s="10" t="inlineStr">
+      <c r="BP21" s="33" t="inlineStr">
         <is>
           <t>{Input_117}</t>
         </is>
       </c>
-      <c r="BQ21" s="11" t="n"/>
-      <c r="BR21" s="12" t="n"/>
-      <c r="BS21" s="10" t="inlineStr">
+      <c r="BQ21" s="42" t="n"/>
+      <c r="BR21" s="41" t="n"/>
+      <c r="BS21" s="33" t="inlineStr">
         <is>
           <t>{Input_137}</t>
         </is>
       </c>
-      <c r="BT21" s="10" t="inlineStr">
+      <c r="BT21" s="33" t="inlineStr">
         <is>
           <t>{Input_157}</t>
         </is>
       </c>
-      <c r="BU21" s="22" t="n"/>
+      <c r="BU21" s="34" t="n"/>
       <c r="BW21" s="5" t="n"/>
     </row>
     <row r="22" ht="13.95" customHeight="1" s="14">
       <c r="A22" s="6" t="n"/>
       <c r="E22" s="22" t="n"/>
-      <c r="AZ22" s="10" t="inlineStr">
+      <c r="AZ22" s="35" t="inlineStr">
         <is>
           <t>{Input_18}</t>
         </is>
       </c>
-      <c r="BA22" s="12" t="n"/>
-      <c r="BB22" s="10" t="inlineStr">
+      <c r="BA22" s="41" t="n"/>
+      <c r="BB22" s="33" t="inlineStr">
         <is>
           <t>{Input_38}</t>
         </is>
       </c>
-      <c r="BC22" s="11" t="n"/>
-      <c r="BD22" s="11" t="n"/>
-      <c r="BE22" s="12" t="n"/>
-      <c r="BF22" s="10" t="inlineStr">
+      <c r="BC22" s="42" t="n"/>
+      <c r="BD22" s="42" t="n"/>
+      <c r="BE22" s="41" t="n"/>
+      <c r="BF22" s="33" t="inlineStr">
         <is>
           <t>{Input_58}</t>
         </is>
       </c>
-      <c r="BG22" s="11" t="n"/>
-      <c r="BH22" s="12" t="n"/>
-      <c r="BI22" s="10" t="inlineStr">
+      <c r="BG22" s="42" t="n"/>
+      <c r="BH22" s="41" t="n"/>
+      <c r="BI22" s="33" t="inlineStr">
         <is>
           <t>{Input_78}</t>
         </is>
       </c>
-      <c r="BJ22" s="11" t="n"/>
-      <c r="BK22" s="11" t="n"/>
-      <c r="BL22" s="11" t="n"/>
-      <c r="BM22" s="11" t="n"/>
-      <c r="BN22" s="12" t="n"/>
-      <c r="BO22" s="10" t="inlineStr">
+      <c r="BJ22" s="42" t="n"/>
+      <c r="BK22" s="42" t="n"/>
+      <c r="BL22" s="42" t="n"/>
+      <c r="BM22" s="42" t="n"/>
+      <c r="BN22" s="41" t="n"/>
+      <c r="BO22" s="33" t="inlineStr">
         <is>
           <t>{Input_98}</t>
         </is>
       </c>
-      <c r="BP22" s="10" t="inlineStr">
+      <c r="BP22" s="33" t="inlineStr">
         <is>
           <t>{Input_118}</t>
         </is>
       </c>
-      <c r="BQ22" s="11" t="n"/>
-      <c r="BR22" s="12" t="n"/>
-      <c r="BS22" s="10" t="inlineStr">
+      <c r="BQ22" s="42" t="n"/>
+      <c r="BR22" s="41" t="n"/>
+      <c r="BS22" s="33" t="inlineStr">
         <is>
           <t>{Input_138}</t>
         </is>
       </c>
-      <c r="BT22" s="10" t="inlineStr">
+      <c r="BT22" s="33" t="inlineStr">
         <is>
           <t>{Input_158}</t>
         </is>
       </c>
-      <c r="BU22" s="22" t="n"/>
+      <c r="BU22" s="34" t="n"/>
       <c r="BW22" s="5" t="n"/>
     </row>
     <row r="23" ht="13.95" customHeight="1" s="14">
       <c r="A23" s="6" t="n"/>
       <c r="E23" s="22" t="n"/>
-      <c r="AZ23" s="10" t="inlineStr">
+      <c r="AZ23" s="35" t="inlineStr">
         <is>
           <t>{Input_19}</t>
         </is>
       </c>
-      <c r="BA23" s="12" t="n"/>
-      <c r="BB23" s="10" t="inlineStr">
+      <c r="BA23" s="41" t="n"/>
+      <c r="BB23" s="33" t="inlineStr">
         <is>
           <t>{Input_39}</t>
         </is>
       </c>
-      <c r="BC23" s="11" t="n"/>
-      <c r="BD23" s="11" t="n"/>
-      <c r="BE23" s="12" t="n"/>
-      <c r="BF23" s="10" t="inlineStr">
+      <c r="BC23" s="42" t="n"/>
+      <c r="BD23" s="42" t="n"/>
+      <c r="BE23" s="41" t="n"/>
+      <c r="BF23" s="33" t="inlineStr">
         <is>
           <t>{Input_59}</t>
         </is>
       </c>
-      <c r="BG23" s="11" t="n"/>
-      <c r="BH23" s="12" t="n"/>
-      <c r="BI23" s="10" t="inlineStr">
+      <c r="BG23" s="42" t="n"/>
+      <c r="BH23" s="41" t="n"/>
+      <c r="BI23" s="33" t="inlineStr">
         <is>
           <t>{Input_79}</t>
         </is>
       </c>
-      <c r="BJ23" s="11" t="n"/>
-      <c r="BK23" s="11" t="n"/>
-      <c r="BL23" s="11" t="n"/>
-      <c r="BM23" s="11" t="n"/>
-      <c r="BN23" s="12" t="n"/>
-      <c r="BO23" s="10" t="inlineStr">
+      <c r="BJ23" s="42" t="n"/>
+      <c r="BK23" s="42" t="n"/>
+      <c r="BL23" s="42" t="n"/>
+      <c r="BM23" s="42" t="n"/>
+      <c r="BN23" s="41" t="n"/>
+      <c r="BO23" s="33" t="inlineStr">
         <is>
           <t>{Input_99}</t>
         </is>
       </c>
-      <c r="BP23" s="10" t="inlineStr">
+      <c r="BP23" s="33" t="inlineStr">
         <is>
           <t>{Input_119}</t>
         </is>
       </c>
-      <c r="BQ23" s="11" t="n"/>
-      <c r="BR23" s="12" t="n"/>
-      <c r="BS23" s="10" t="inlineStr">
+      <c r="BQ23" s="42" t="n"/>
+      <c r="BR23" s="41" t="n"/>
+      <c r="BS23" s="33" t="inlineStr">
         <is>
           <t>{Input_139}</t>
         </is>
       </c>
-      <c r="BT23" s="10" t="inlineStr">
+      <c r="BT23" s="33" t="inlineStr">
         <is>
           <t>{Input_159}</t>
         </is>
       </c>
-      <c r="BU23" s="22" t="n"/>
+      <c r="BU23" s="34" t="n"/>
       <c r="BW23" s="5" t="n"/>
     </row>
     <row r="24" ht="13.95" customHeight="1" s="14">
       <c r="A24" s="6" t="n"/>
       <c r="E24" s="22" t="n"/>
-      <c r="AZ24" s="10" t="inlineStr">
+      <c r="AZ24" s="35" t="inlineStr">
         <is>
           <t>{Input_20}</t>
         </is>
       </c>
-      <c r="BA24" s="12" t="n"/>
-      <c r="BB24" s="10" t="inlineStr">
+      <c r="BA24" s="41" t="n"/>
+      <c r="BB24" s="33" t="inlineStr">
         <is>
           <t>{Input_40}</t>
         </is>
       </c>
-      <c r="BC24" s="11" t="n"/>
-      <c r="BD24" s="11" t="n"/>
-      <c r="BE24" s="12" t="n"/>
-      <c r="BF24" s="10" t="inlineStr">
+      <c r="BC24" s="42" t="n"/>
+      <c r="BD24" s="42" t="n"/>
+      <c r="BE24" s="41" t="n"/>
+      <c r="BF24" s="33" t="inlineStr">
         <is>
           <t>{Input_60}</t>
         </is>
       </c>
-      <c r="BG24" s="11" t="n"/>
-      <c r="BH24" s="12" t="n"/>
-      <c r="BI24" s="10" t="inlineStr">
+      <c r="BG24" s="42" t="n"/>
+      <c r="BH24" s="41" t="n"/>
+      <c r="BI24" s="33" t="inlineStr">
         <is>
           <t>{Input_80}</t>
         </is>
       </c>
-      <c r="BJ24" s="11" t="n"/>
-      <c r="BK24" s="11" t="n"/>
-      <c r="BL24" s="11" t="n"/>
-      <c r="BM24" s="11" t="n"/>
-      <c r="BN24" s="12" t="n"/>
-      <c r="BO24" s="10" t="inlineStr">
+      <c r="BJ24" s="42" t="n"/>
+      <c r="BK24" s="42" t="n"/>
+      <c r="BL24" s="42" t="n"/>
+      <c r="BM24" s="42" t="n"/>
+      <c r="BN24" s="41" t="n"/>
+      <c r="BO24" s="33" t="inlineStr">
         <is>
           <t>{Input_100}</t>
         </is>
       </c>
-      <c r="BP24" s="10" t="inlineStr">
+      <c r="BP24" s="33" t="inlineStr">
         <is>
           <t>{Input_120}</t>
         </is>
       </c>
-      <c r="BQ24" s="11" t="n"/>
-      <c r="BR24" s="12" t="n"/>
-      <c r="BS24" s="10" t="inlineStr">
+      <c r="BQ24" s="42" t="n"/>
+      <c r="BR24" s="41" t="n"/>
+      <c r="BS24" s="33" t="inlineStr">
         <is>
           <t>{Input_140}</t>
         </is>
       </c>
-      <c r="BT24" s="10" t="inlineStr">
+      <c r="BT24" s="33" t="inlineStr">
         <is>
           <t>{Input_160}</t>
         </is>
       </c>
-      <c r="BU24" s="22" t="n"/>
+      <c r="BU24" s="34" t="n"/>
       <c r="BW24" s="5" t="n"/>
     </row>
     <row r="25" ht="13.95" customHeight="1" s="14">
       <c r="A25" s="6" t="n"/>
       <c r="E25" s="22" t="n"/>
-      <c r="AZ25" s="10" t="inlineStr">
+      <c r="AZ25" s="35" t="inlineStr">
         <is>
           <t>{Input_21}</t>
         </is>
       </c>
-      <c r="BA25" s="12" t="n"/>
-      <c r="BB25" s="10" t="inlineStr">
+      <c r="BA25" s="41" t="n"/>
+      <c r="BB25" s="33" t="inlineStr">
         <is>
           <t>{Input_41}</t>
         </is>
       </c>
-      <c r="BC25" s="11" t="n"/>
-      <c r="BD25" s="11" t="n"/>
-      <c r="BE25" s="12" t="n"/>
-      <c r="BF25" s="10" t="inlineStr">
+      <c r="BC25" s="42" t="n"/>
+      <c r="BD25" s="42" t="n"/>
+      <c r="BE25" s="41" t="n"/>
+      <c r="BF25" s="33" t="inlineStr">
         <is>
           <t>{Input_61}</t>
         </is>
       </c>
-      <c r="BG25" s="11" t="n"/>
-      <c r="BH25" s="12" t="n"/>
-      <c r="BI25" s="10" t="inlineStr">
+      <c r="BG25" s="42" t="n"/>
+      <c r="BH25" s="41" t="n"/>
+      <c r="BI25" s="33" t="inlineStr">
         <is>
           <t>{Input_81}</t>
         </is>
       </c>
-      <c r="BJ25" s="11" t="n"/>
-      <c r="BK25" s="11" t="n"/>
-      <c r="BL25" s="11" t="n"/>
-      <c r="BM25" s="11" t="n"/>
-      <c r="BN25" s="12" t="n"/>
-      <c r="BO25" s="10" t="inlineStr">
+      <c r="BJ25" s="42" t="n"/>
+      <c r="BK25" s="42" t="n"/>
+      <c r="BL25" s="42" t="n"/>
+      <c r="BM25" s="42" t="n"/>
+      <c r="BN25" s="41" t="n"/>
+      <c r="BO25" s="33" t="inlineStr">
         <is>
           <t>{Input_101}</t>
         </is>
       </c>
-      <c r="BP25" s="10" t="inlineStr">
+      <c r="BP25" s="33" t="inlineStr">
         <is>
           <t>{Input_121}</t>
         </is>
       </c>
-      <c r="BQ25" s="11" t="n"/>
-      <c r="BR25" s="12" t="n"/>
-      <c r="BS25" s="10" t="inlineStr">
+      <c r="BQ25" s="42" t="n"/>
+      <c r="BR25" s="41" t="n"/>
+      <c r="BS25" s="33" t="inlineStr">
         <is>
           <t>{Input_141}</t>
         </is>
       </c>
-      <c r="BT25" s="10" t="inlineStr">
+      <c r="BT25" s="33" t="inlineStr">
         <is>
           <t>{Input_161}</t>
         </is>
       </c>
-      <c r="BU25" s="22" t="n"/>
+      <c r="BU25" s="34" t="n"/>
       <c r="BW25" s="5" t="n"/>
     </row>
     <row r="26" ht="13.95" customHeight="1" s="14">
       <c r="A26" s="6" t="n"/>
       <c r="E26" s="22" t="n"/>
-      <c r="AZ26" s="10" t="inlineStr">
+      <c r="AZ26" s="35" t="inlineStr">
         <is>
           <t>{Input_22}</t>
         </is>
       </c>
-      <c r="BA26" s="12" t="n"/>
-      <c r="BB26" s="10" t="inlineStr">
+      <c r="BA26" s="41" t="n"/>
+      <c r="BB26" s="33" t="inlineStr">
         <is>
           <t>{Input_42}</t>
         </is>
       </c>
-      <c r="BC26" s="11" t="n"/>
-      <c r="BD26" s="11" t="n"/>
-      <c r="BE26" s="12" t="n"/>
-      <c r="BF26" s="10" t="inlineStr">
+      <c r="BC26" s="42" t="n"/>
+      <c r="BD26" s="42" t="n"/>
+      <c r="BE26" s="41" t="n"/>
+      <c r="BF26" s="33" t="inlineStr">
         <is>
           <t>{Input_62}</t>
         </is>
       </c>
-      <c r="BG26" s="11" t="n"/>
-      <c r="BH26" s="12" t="n"/>
-      <c r="BI26" s="10" t="inlineStr">
+      <c r="BG26" s="42" t="n"/>
+      <c r="BH26" s="41" t="n"/>
+      <c r="BI26" s="33" t="inlineStr">
         <is>
           <t>{Input_82}</t>
         </is>
       </c>
-      <c r="BJ26" s="11" t="n"/>
-      <c r="BK26" s="11" t="n"/>
-      <c r="BL26" s="11" t="n"/>
-      <c r="BM26" s="11" t="n"/>
-      <c r="BN26" s="12" t="n"/>
-      <c r="BO26" s="10" t="inlineStr">
+      <c r="BJ26" s="42" t="n"/>
+      <c r="BK26" s="42" t="n"/>
+      <c r="BL26" s="42" t="n"/>
+      <c r="BM26" s="42" t="n"/>
+      <c r="BN26" s="41" t="n"/>
+      <c r="BO26" s="33" t="inlineStr">
         <is>
           <t>{Input_102}</t>
         </is>
       </c>
-      <c r="BP26" s="10" t="inlineStr">
+      <c r="BP26" s="33" t="inlineStr">
         <is>
           <t>{Input_122}</t>
         </is>
       </c>
-      <c r="BQ26" s="11" t="n"/>
-      <c r="BR26" s="12" t="n"/>
-      <c r="BS26" s="10" t="inlineStr">
+      <c r="BQ26" s="42" t="n"/>
+      <c r="BR26" s="41" t="n"/>
+      <c r="BS26" s="33" t="inlineStr">
         <is>
           <t>{Input_142}</t>
         </is>
       </c>
-      <c r="BT26" s="10" t="inlineStr">
+      <c r="BT26" s="33" t="inlineStr">
         <is>
           <t>{Input_162}</t>
         </is>
       </c>
-      <c r="BU26" s="22" t="n"/>
+      <c r="BU26" s="34" t="n"/>
       <c r="BW26" s="5" t="n"/>
     </row>
     <row r="27" ht="13.95" customHeight="1" s="14">
       <c r="A27" s="6" t="n"/>
       <c r="E27" s="22" t="n"/>
-      <c r="AZ27" s="10" t="inlineStr">
+      <c r="AZ27" s="35" t="inlineStr">
         <is>
           <t>{Input_23}</t>
         </is>
       </c>
-      <c r="BA27" s="17" t="n"/>
-      <c r="BB27" s="10" t="inlineStr">
+      <c r="BA27" s="36" t="n"/>
+      <c r="BB27" s="33" t="inlineStr">
         <is>
           <t>{Input_43}</t>
         </is>
       </c>
-      <c r="BC27" s="16" t="n"/>
-      <c r="BD27" s="16" t="n"/>
-      <c r="BE27" s="17" t="n"/>
-      <c r="BF27" s="10" t="inlineStr">
+      <c r="BC27" s="38" t="n"/>
+      <c r="BD27" s="38" t="n"/>
+      <c r="BE27" s="36" t="n"/>
+      <c r="BF27" s="33" t="inlineStr">
         <is>
           <t>{Input_63}</t>
         </is>
       </c>
-      <c r="BG27" s="16" t="n"/>
-      <c r="BH27" s="17" t="n"/>
-      <c r="BI27" s="10" t="inlineStr">
+      <c r="BG27" s="38" t="n"/>
+      <c r="BH27" s="36" t="n"/>
+      <c r="BI27" s="33" t="inlineStr">
         <is>
           <t>{Input_83}</t>
         </is>
       </c>
-      <c r="BJ27" s="16" t="n"/>
-      <c r="BK27" s="16" t="n"/>
-      <c r="BL27" s="16" t="n"/>
-      <c r="BM27" s="16" t="n"/>
-      <c r="BN27" s="17" t="n"/>
-      <c r="BO27" s="10" t="inlineStr">
+      <c r="BJ27" s="38" t="n"/>
+      <c r="BK27" s="38" t="n"/>
+      <c r="BL27" s="38" t="n"/>
+      <c r="BM27" s="38" t="n"/>
+      <c r="BN27" s="36" t="n"/>
+      <c r="BO27" s="33" t="inlineStr">
         <is>
           <t>{Input_103}</t>
         </is>
       </c>
-      <c r="BP27" s="10" t="inlineStr">
+      <c r="BP27" s="33" t="inlineStr">
         <is>
           <t>{Input_123}</t>
         </is>
       </c>
-      <c r="BQ27" s="16" t="n"/>
-      <c r="BR27" s="17" t="n"/>
-      <c r="BS27" s="10" t="inlineStr">
+      <c r="BQ27" s="38" t="n"/>
+      <c r="BR27" s="36" t="n"/>
+      <c r="BS27" s="33" t="inlineStr">
         <is>
           <t>{Input_143}</t>
         </is>
       </c>
-      <c r="BT27" s="10" t="inlineStr">
+      <c r="BT27" s="33" t="inlineStr">
         <is>
           <t>{Input_163}</t>
         </is>
       </c>
-      <c r="BU27" s="22" t="n"/>
+      <c r="BU27" s="34" t="n"/>
       <c r="BW27" s="5" t="n"/>
     </row>
     <row r="28" ht="13.95" customHeight="1" s="14">
@@ -2350,26 +2506,26 @@
       </c>
       <c r="AZ28" s="18" t="n"/>
       <c r="BA28" s="20" t="n"/>
-      <c r="BB28" s="18" t="n"/>
+      <c r="BB28" s="39" t="n"/>
       <c r="BC28" s="19" t="n"/>
       <c r="BD28" s="19" t="n"/>
       <c r="BE28" s="20" t="n"/>
-      <c r="BF28" s="18" t="n"/>
+      <c r="BF28" s="39" t="n"/>
       <c r="BG28" s="19" t="n"/>
       <c r="BH28" s="20" t="n"/>
-      <c r="BI28" s="18" t="n"/>
+      <c r="BI28" s="39" t="n"/>
       <c r="BJ28" s="19" t="n"/>
       <c r="BK28" s="19" t="n"/>
       <c r="BL28" s="19" t="n"/>
       <c r="BM28" s="19" t="n"/>
       <c r="BN28" s="20" t="n"/>
-      <c r="BO28" s="21" t="n"/>
-      <c r="BP28" s="18" t="n"/>
+      <c r="BO28" s="40" t="n"/>
+      <c r="BP28" s="39" t="n"/>
       <c r="BQ28" s="19" t="n"/>
       <c r="BR28" s="20" t="n"/>
-      <c r="BS28" s="21" t="n"/>
-      <c r="BT28" s="21" t="n"/>
-      <c r="BU28" s="22" t="n"/>
+      <c r="BS28" s="40" t="n"/>
+      <c r="BT28" s="40" t="n"/>
+      <c r="BU28" s="34" t="n"/>
       <c r="BW28" s="5" t="n"/>
     </row>
     <row r="29" ht="13.95" customHeight="1" s="14">
@@ -2380,12 +2536,12 @@
     </row>
     <row r="30" ht="13.95" customHeight="1" s="14">
       <c r="A30" s="6" t="n"/>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="35" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="BU30" s="10" t="inlineStr">
+      <c r="BU30" s="35" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2424,7 +2580,7 @@
       <c r="BR31" s="16" t="n"/>
       <c r="BS31" s="16" t="n"/>
       <c r="BT31" s="17" t="n"/>
-      <c r="BU31" s="22" t="n"/>
+      <c r="BU31" s="34" t="n"/>
       <c r="BW31" s="5" t="n"/>
     </row>
     <row r="32" ht="13.95" customHeight="1" s="14">
@@ -2442,7 +2598,7 @@
       </c>
       <c r="AZ32" s="27" t="n"/>
       <c r="BT32" s="24" t="n"/>
-      <c r="BU32" s="22" t="n"/>
+      <c r="BU32" s="34" t="n"/>
       <c r="BW32" s="5" t="n"/>
     </row>
     <row r="33" ht="13.95" customHeight="1" s="14">
@@ -2450,7 +2606,7 @@
       <c r="E33" s="22" t="n"/>
       <c r="AZ33" s="27" t="n"/>
       <c r="BT33" s="24" t="n"/>
-      <c r="BU33" s="22" t="n"/>
+      <c r="BU33" s="34" t="n"/>
       <c r="BW33" s="5" t="n"/>
     </row>
     <row r="34" ht="13.95" customHeight="1" s="14">
@@ -2458,7 +2614,7 @@
       <c r="E34" s="22" t="n"/>
       <c r="AZ34" s="27" t="n"/>
       <c r="BT34" s="24" t="n"/>
-      <c r="BU34" s="22" t="n"/>
+      <c r="BU34" s="34" t="n"/>
       <c r="BW34" s="5" t="n"/>
     </row>
     <row r="35" ht="13.95" customHeight="1" s="14">
@@ -2466,7 +2622,7 @@
       <c r="E35" s="22" t="n"/>
       <c r="AZ35" s="27" t="n"/>
       <c r="BT35" s="24" t="n"/>
-      <c r="BU35" s="22" t="n"/>
+      <c r="BU35" s="34" t="n"/>
       <c r="BW35" s="5" t="n"/>
     </row>
     <row r="36" ht="13.95" customHeight="1" s="14">
@@ -2493,7 +2649,7 @@
       <c r="BR36" s="19" t="n"/>
       <c r="BS36" s="19" t="n"/>
       <c r="BT36" s="20" t="n"/>
-      <c r="BU36" s="22" t="n"/>
+      <c r="BU36" s="34" t="n"/>
       <c r="BW36" s="5" t="n"/>
     </row>
     <row r="37" ht="13.95" customHeight="1" s="14">
@@ -2516,14 +2672,14 @@
           <t>{Input_170}</t>
         </is>
       </c>
-      <c r="BA39" s="10" t="inlineStr">
+      <c r="BA39" s="32" t="inlineStr">
         <is>
           <t>{Input_171}</t>
         </is>
       </c>
       <c r="BB39" s="11" t="n"/>
       <c r="BC39" s="12" t="n"/>
-      <c r="BD39" s="10" t="inlineStr">
+      <c r="BD39" s="32" t="inlineStr">
         <is>
           <t>{Input_172}</t>
         </is>
@@ -2535,246 +2691,246 @@
       <c r="BI39" s="11" t="n"/>
       <c r="BJ39" s="11" t="n"/>
       <c r="BK39" s="12" t="n"/>
-      <c r="BL39" s="10" t="inlineStr">
+      <c r="BL39" s="32" t="inlineStr">
         <is>
           <t>{Input_173}</t>
         </is>
       </c>
       <c r="BM39" s="11" t="n"/>
       <c r="BN39" s="12" t="n"/>
-      <c r="BO39" s="10" t="inlineStr">
+      <c r="BO39" s="32" t="inlineStr">
         <is>
           <t>{Input_174}</t>
         </is>
       </c>
       <c r="BP39" s="11" t="n"/>
       <c r="BQ39" s="12" t="n"/>
-      <c r="BR39" s="10" t="inlineStr">
+      <c r="BR39" s="32" t="inlineStr">
         <is>
           <t>{Input_175}</t>
         </is>
       </c>
       <c r="BS39" s="11" t="n"/>
       <c r="BT39" s="12" t="n"/>
-      <c r="BU39" s="22" t="n"/>
+      <c r="BU39" s="34" t="n"/>
       <c r="BW39" s="5" t="n"/>
     </row>
     <row r="40" ht="13.95" customHeight="1" s="14">
       <c r="A40" s="6" t="n"/>
       <c r="E40" s="22" t="n"/>
-      <c r="AZ40" s="10" t="inlineStr">
+      <c r="AZ40" s="35" t="inlineStr">
         <is>
           <t>{Input_176}</t>
         </is>
       </c>
-      <c r="BA40" s="10" t="inlineStr">
+      <c r="BA40" s="33" t="inlineStr">
         <is>
           <t>{Input_177}</t>
         </is>
       </c>
-      <c r="BB40" s="11" t="n"/>
-      <c r="BC40" s="12" t="n"/>
-      <c r="BD40" s="10" t="inlineStr">
+      <c r="BB40" s="42" t="n"/>
+      <c r="BC40" s="41" t="n"/>
+      <c r="BD40" s="33" t="inlineStr">
         <is>
           <t>{Input_178}</t>
         </is>
       </c>
-      <c r="BE40" s="11" t="n"/>
-      <c r="BF40" s="11" t="n"/>
-      <c r="BG40" s="11" t="n"/>
-      <c r="BH40" s="11" t="n"/>
-      <c r="BI40" s="11" t="n"/>
-      <c r="BJ40" s="11" t="n"/>
-      <c r="BK40" s="12" t="n"/>
-      <c r="BL40" s="10" t="inlineStr">
+      <c r="BE40" s="42" t="n"/>
+      <c r="BF40" s="42" t="n"/>
+      <c r="BG40" s="42" t="n"/>
+      <c r="BH40" s="42" t="n"/>
+      <c r="BI40" s="42" t="n"/>
+      <c r="BJ40" s="42" t="n"/>
+      <c r="BK40" s="41" t="n"/>
+      <c r="BL40" s="33" t="inlineStr">
         <is>
           <t>{Input_179}</t>
         </is>
       </c>
-      <c r="BM40" s="11" t="n"/>
-      <c r="BN40" s="12" t="n"/>
-      <c r="BO40" s="10" t="inlineStr">
+      <c r="BM40" s="42" t="n"/>
+      <c r="BN40" s="41" t="n"/>
+      <c r="BO40" s="33" t="inlineStr">
         <is>
           <t>{Input_180}</t>
         </is>
       </c>
-      <c r="BP40" s="11" t="n"/>
-      <c r="BQ40" s="12" t="n"/>
-      <c r="BR40" s="10" t="inlineStr">
+      <c r="BP40" s="42" t="n"/>
+      <c r="BQ40" s="41" t="n"/>
+      <c r="BR40" s="33" t="inlineStr">
         <is>
           <t>{Input_181}</t>
         </is>
       </c>
-      <c r="BS40" s="11" t="n"/>
-      <c r="BT40" s="12" t="n"/>
-      <c r="BU40" s="22" t="n"/>
+      <c r="BS40" s="42" t="n"/>
+      <c r="BT40" s="41" t="n"/>
+      <c r="BU40" s="34" t="n"/>
       <c r="BW40" s="5" t="n"/>
     </row>
     <row r="41" ht="13.95" customHeight="1" s="14">
       <c r="A41" s="6" t="n"/>
       <c r="E41" s="22" t="n"/>
-      <c r="AZ41" s="10" t="inlineStr">
+      <c r="AZ41" s="35" t="inlineStr">
         <is>
           <t>{Input_182}</t>
         </is>
       </c>
-      <c r="BA41" s="10" t="inlineStr">
+      <c r="BA41" s="33" t="inlineStr">
         <is>
           <t>{Input_183}</t>
         </is>
       </c>
-      <c r="BB41" s="11" t="n"/>
-      <c r="BC41" s="12" t="n"/>
-      <c r="BD41" s="10" t="inlineStr">
+      <c r="BB41" s="42" t="n"/>
+      <c r="BC41" s="41" t="n"/>
+      <c r="BD41" s="33" t="inlineStr">
         <is>
           <t>{Input_184}</t>
         </is>
       </c>
-      <c r="BE41" s="11" t="n"/>
-      <c r="BF41" s="11" t="n"/>
-      <c r="BG41" s="11" t="n"/>
-      <c r="BH41" s="11" t="n"/>
-      <c r="BI41" s="11" t="n"/>
-      <c r="BJ41" s="11" t="n"/>
-      <c r="BK41" s="12" t="n"/>
-      <c r="BL41" s="10" t="inlineStr">
+      <c r="BE41" s="42" t="n"/>
+      <c r="BF41" s="42" t="n"/>
+      <c r="BG41" s="42" t="n"/>
+      <c r="BH41" s="42" t="n"/>
+      <c r="BI41" s="42" t="n"/>
+      <c r="BJ41" s="42" t="n"/>
+      <c r="BK41" s="41" t="n"/>
+      <c r="BL41" s="33" t="inlineStr">
         <is>
           <t>{Input_185}</t>
         </is>
       </c>
-      <c r="BM41" s="11" t="n"/>
-      <c r="BN41" s="12" t="n"/>
-      <c r="BO41" s="10" t="inlineStr">
+      <c r="BM41" s="42" t="n"/>
+      <c r="BN41" s="41" t="n"/>
+      <c r="BO41" s="33" t="inlineStr">
         <is>
           <t>{Input_186}</t>
         </is>
       </c>
-      <c r="BP41" s="11" t="n"/>
-      <c r="BQ41" s="12" t="n"/>
-      <c r="BR41" s="10" t="inlineStr">
+      <c r="BP41" s="42" t="n"/>
+      <c r="BQ41" s="41" t="n"/>
+      <c r="BR41" s="33" t="inlineStr">
         <is>
           <t>{Input_187}</t>
         </is>
       </c>
-      <c r="BS41" s="11" t="n"/>
-      <c r="BT41" s="12" t="n"/>
-      <c r="BU41" s="22" t="n"/>
+      <c r="BS41" s="42" t="n"/>
+      <c r="BT41" s="41" t="n"/>
+      <c r="BU41" s="34" t="n"/>
       <c r="BW41" s="5" t="n"/>
     </row>
     <row r="42" ht="13.95" customHeight="1" s="14">
       <c r="A42" s="6" t="n"/>
       <c r="E42" s="22" t="n"/>
-      <c r="AZ42" s="10" t="inlineStr">
+      <c r="AZ42" s="35" t="inlineStr">
         <is>
           <t>{Input_188}</t>
         </is>
       </c>
-      <c r="BA42" s="10" t="inlineStr">
+      <c r="BA42" s="33" t="inlineStr">
         <is>
           <t>{Input_189}</t>
         </is>
       </c>
-      <c r="BB42" s="11" t="n"/>
-      <c r="BC42" s="12" t="n"/>
-      <c r="BD42" s="10" t="inlineStr">
+      <c r="BB42" s="42" t="n"/>
+      <c r="BC42" s="41" t="n"/>
+      <c r="BD42" s="33" t="inlineStr">
         <is>
           <t>{Input_190}</t>
         </is>
       </c>
-      <c r="BE42" s="11" t="n"/>
-      <c r="BF42" s="11" t="n"/>
-      <c r="BG42" s="11" t="n"/>
-      <c r="BH42" s="11" t="n"/>
-      <c r="BI42" s="11" t="n"/>
-      <c r="BJ42" s="11" t="n"/>
-      <c r="BK42" s="12" t="n"/>
-      <c r="BL42" s="10" t="inlineStr">
+      <c r="BE42" s="42" t="n"/>
+      <c r="BF42" s="42" t="n"/>
+      <c r="BG42" s="42" t="n"/>
+      <c r="BH42" s="42" t="n"/>
+      <c r="BI42" s="42" t="n"/>
+      <c r="BJ42" s="42" t="n"/>
+      <c r="BK42" s="41" t="n"/>
+      <c r="BL42" s="33" t="inlineStr">
         <is>
           <t>{Input_191}</t>
         </is>
       </c>
-      <c r="BM42" s="11" t="n"/>
-      <c r="BN42" s="12" t="n"/>
-      <c r="BO42" s="10" t="inlineStr">
+      <c r="BM42" s="42" t="n"/>
+      <c r="BN42" s="41" t="n"/>
+      <c r="BO42" s="33" t="inlineStr">
         <is>
           <t>{Input_192}</t>
         </is>
       </c>
-      <c r="BP42" s="11" t="n"/>
-      <c r="BQ42" s="12" t="n"/>
-      <c r="BR42" s="10" t="inlineStr">
+      <c r="BP42" s="42" t="n"/>
+      <c r="BQ42" s="41" t="n"/>
+      <c r="BR42" s="33" t="inlineStr">
         <is>
           <t>{Input_193}</t>
         </is>
       </c>
-      <c r="BS42" s="11" t="n"/>
-      <c r="BT42" s="12" t="n"/>
-      <c r="BU42" s="22" t="n"/>
+      <c r="BS42" s="42" t="n"/>
+      <c r="BT42" s="41" t="n"/>
+      <c r="BU42" s="34" t="n"/>
       <c r="BW42" s="5" t="n"/>
     </row>
     <row r="43" ht="13.95" customHeight="1" s="14">
       <c r="A43" s="6" t="n"/>
       <c r="E43" s="21" t="n"/>
-      <c r="AZ43" s="10" t="inlineStr">
+      <c r="AZ43" s="35" t="inlineStr">
         <is>
           <t>{Input_194}</t>
         </is>
       </c>
-      <c r="BA43" s="10" t="inlineStr">
+      <c r="BA43" s="33" t="inlineStr">
         <is>
           <t>{Input_195}</t>
         </is>
       </c>
-      <c r="BB43" s="16" t="n"/>
-      <c r="BC43" s="17" t="n"/>
-      <c r="BD43" s="10" t="inlineStr">
+      <c r="BB43" s="38" t="n"/>
+      <c r="BC43" s="36" t="n"/>
+      <c r="BD43" s="33" t="inlineStr">
         <is>
           <t>{Input_196}</t>
         </is>
       </c>
-      <c r="BE43" s="16" t="n"/>
-      <c r="BF43" s="16" t="n"/>
-      <c r="BG43" s="16" t="n"/>
-      <c r="BH43" s="16" t="n"/>
-      <c r="BI43" s="16" t="n"/>
-      <c r="BJ43" s="16" t="n"/>
-      <c r="BK43" s="17" t="n"/>
-      <c r="BL43" s="10" t="inlineStr">
+      <c r="BE43" s="38" t="n"/>
+      <c r="BF43" s="38" t="n"/>
+      <c r="BG43" s="38" t="n"/>
+      <c r="BH43" s="38" t="n"/>
+      <c r="BI43" s="38" t="n"/>
+      <c r="BJ43" s="38" t="n"/>
+      <c r="BK43" s="36" t="n"/>
+      <c r="BL43" s="33" t="inlineStr">
         <is>
           <t>{Input_197}</t>
         </is>
       </c>
-      <c r="BM43" s="16" t="n"/>
-      <c r="BN43" s="17" t="n"/>
-      <c r="BO43" s="10" t="inlineStr">
+      <c r="BM43" s="38" t="n"/>
+      <c r="BN43" s="36" t="n"/>
+      <c r="BO43" s="33" t="inlineStr">
         <is>
           <t>{Input_198}</t>
         </is>
       </c>
-      <c r="BP43" s="16" t="n"/>
-      <c r="BQ43" s="17" t="n"/>
-      <c r="BR43" s="10" t="inlineStr">
+      <c r="BP43" s="38" t="n"/>
+      <c r="BQ43" s="36" t="n"/>
+      <c r="BR43" s="33" t="inlineStr">
         <is>
           <t>{Input_199}</t>
         </is>
       </c>
-      <c r="BS43" s="16" t="n"/>
-      <c r="BT43" s="17" t="n"/>
-      <c r="BU43" s="21" t="n"/>
+      <c r="BS43" s="38" t="n"/>
+      <c r="BT43" s="36" t="n"/>
+      <c r="BU43" s="40" t="n"/>
       <c r="BW43" s="5" t="n"/>
     </row>
     <row r="44" ht="13.95" customHeight="1" s="14">
       <c r="A44" s="6" t="n"/>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E44" s="35" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
       <c r="AZ44" s="21" t="n"/>
-      <c r="BA44" s="18" t="n"/>
+      <c r="BA44" s="39" t="n"/>
       <c r="BB44" s="19" t="n"/>
       <c r="BC44" s="20" t="n"/>
-      <c r="BD44" s="18" t="n"/>
+      <c r="BD44" s="39" t="n"/>
       <c r="BE44" s="19" t="n"/>
       <c r="BF44" s="19" t="n"/>
       <c r="BG44" s="19" t="n"/>
@@ -2782,16 +2938,16 @@
       <c r="BI44" s="19" t="n"/>
       <c r="BJ44" s="19" t="n"/>
       <c r="BK44" s="20" t="n"/>
-      <c r="BL44" s="18" t="n"/>
+      <c r="BL44" s="39" t="n"/>
       <c r="BM44" s="19" t="n"/>
       <c r="BN44" s="20" t="n"/>
-      <c r="BO44" s="18" t="n"/>
+      <c r="BO44" s="39" t="n"/>
       <c r="BP44" s="19" t="n"/>
       <c r="BQ44" s="20" t="n"/>
-      <c r="BR44" s="18" t="n"/>
+      <c r="BR44" s="39" t="n"/>
       <c r="BS44" s="19" t="n"/>
       <c r="BT44" s="20" t="n"/>
-      <c r="BU44" s="10" t="inlineStr">
+      <c r="BU44" s="33" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -2801,91 +2957,91 @@
     <row r="45" ht="13.95" customHeight="1" s="14">
       <c r="A45" s="6" t="n"/>
       <c r="E45" s="22" t="n"/>
-      <c r="AZ45" s="10" t="inlineStr">
+      <c r="AZ45" s="35" t="inlineStr">
         <is>
           <t>REV.</t>
         </is>
       </c>
-      <c r="BA45" s="10" t="inlineStr">
+      <c r="BA45" s="33" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="BB45" s="11" t="n"/>
-      <c r="BC45" s="12" t="n"/>
-      <c r="BD45" s="10" t="inlineStr">
+      <c r="BB45" s="42" t="n"/>
+      <c r="BC45" s="41" t="n"/>
+      <c r="BD45" s="33" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="BE45" s="11" t="n"/>
-      <c r="BF45" s="11" t="n"/>
-      <c r="BG45" s="11" t="n"/>
-      <c r="BH45" s="11" t="n"/>
-      <c r="BI45" s="11" t="n"/>
-      <c r="BJ45" s="11" t="n"/>
-      <c r="BK45" s="12" t="n"/>
-      <c r="BL45" s="10" t="inlineStr">
+      <c r="BE45" s="42" t="n"/>
+      <c r="BF45" s="42" t="n"/>
+      <c r="BG45" s="42" t="n"/>
+      <c r="BH45" s="42" t="n"/>
+      <c r="BI45" s="42" t="n"/>
+      <c r="BJ45" s="42" t="n"/>
+      <c r="BK45" s="41" t="n"/>
+      <c r="BL45" s="33" t="inlineStr">
         <is>
           <t>DRAWN</t>
         </is>
       </c>
-      <c r="BM45" s="11" t="n"/>
-      <c r="BN45" s="12" t="n"/>
-      <c r="BO45" s="10" t="inlineStr">
+      <c r="BM45" s="42" t="n"/>
+      <c r="BN45" s="41" t="n"/>
+      <c r="BO45" s="33" t="inlineStr">
         <is>
           <t>CHECKED</t>
         </is>
       </c>
-      <c r="BP45" s="11" t="n"/>
-      <c r="BQ45" s="12" t="n"/>
-      <c r="BR45" s="10" t="inlineStr">
+      <c r="BP45" s="42" t="n"/>
+      <c r="BQ45" s="41" t="n"/>
+      <c r="BR45" s="33" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="BS45" s="11" t="n"/>
-      <c r="BT45" s="12" t="n"/>
-      <c r="BU45" s="22" t="n"/>
+      <c r="BS45" s="42" t="n"/>
+      <c r="BT45" s="41" t="n"/>
+      <c r="BU45" s="34" t="n"/>
       <c r="BW45" s="5" t="n"/>
     </row>
     <row r="46" ht="13.95" customHeight="1" s="14">
       <c r="A46" s="6" t="n"/>
       <c r="E46" s="22" t="n"/>
-      <c r="AZ46" s="10" t="inlineStr">
+      <c r="AZ46" s="35" t="inlineStr">
         <is>
           <t>PAINT CODE</t>
         </is>
       </c>
-      <c r="BA46" s="11" t="n"/>
-      <c r="BB46" s="11" t="n"/>
-      <c r="BC46" s="12" t="n"/>
-      <c r="BD46" s="10" t="inlineStr">
+      <c r="BA46" s="42" t="n"/>
+      <c r="BB46" s="42" t="n"/>
+      <c r="BC46" s="41" t="n"/>
+      <c r="BD46" s="33" t="inlineStr">
         <is>
           <t>{Input_165}</t>
         </is>
       </c>
-      <c r="BE46" s="11" t="n"/>
-      <c r="BF46" s="11" t="n"/>
-      <c r="BG46" s="11" t="n"/>
-      <c r="BH46" s="11" t="n"/>
-      <c r="BI46" s="11" t="n"/>
-      <c r="BJ46" s="11" t="n"/>
-      <c r="BK46" s="12" t="n"/>
-      <c r="BL46" s="10" t="inlineStr">
+      <c r="BE46" s="42" t="n"/>
+      <c r="BF46" s="42" t="n"/>
+      <c r="BG46" s="42" t="n"/>
+      <c r="BH46" s="42" t="n"/>
+      <c r="BI46" s="42" t="n"/>
+      <c r="BJ46" s="42" t="n"/>
+      <c r="BK46" s="41" t="n"/>
+      <c r="BL46" s="33" t="inlineStr">
         <is>
           <t>DP No.</t>
         </is>
       </c>
-      <c r="BM46" s="11" t="n"/>
-      <c r="BN46" s="11" t="n"/>
-      <c r="BO46" s="11" t="n"/>
-      <c r="BP46" s="11" t="n"/>
-      <c r="BQ46" s="11" t="n"/>
-      <c r="BR46" s="11" t="n"/>
-      <c r="BS46" s="11" t="n"/>
-      <c r="BT46" s="12" t="n"/>
-      <c r="BU46" s="22" t="n"/>
+      <c r="BM46" s="42" t="n"/>
+      <c r="BN46" s="42" t="n"/>
+      <c r="BO46" s="42" t="n"/>
+      <c r="BP46" s="42" t="n"/>
+      <c r="BQ46" s="42" t="n"/>
+      <c r="BR46" s="42" t="n"/>
+      <c r="BS46" s="42" t="n"/>
+      <c r="BT46" s="41" t="n"/>
+      <c r="BU46" s="34" t="n"/>
       <c r="BW46" s="5" t="n"/>
     </row>
     <row r="47" ht="13.95" customHeight="1" s="14">
@@ -2899,7 +3055,7 @@
       <c r="BA47" s="19" t="n"/>
       <c r="BB47" s="19" t="n"/>
       <c r="BC47" s="20" t="n"/>
-      <c r="BD47" s="31" t="inlineStr">
+      <c r="BD47" s="43" t="inlineStr">
         <is>
           <t>{Input_167}</t>
         </is>
@@ -2911,55 +3067,55 @@
       <c r="BI47" s="19" t="n"/>
       <c r="BJ47" s="19" t="n"/>
       <c r="BK47" s="19" t="n"/>
-      <c r="BL47" s="10" t="inlineStr">
+      <c r="BL47" s="35" t="inlineStr">
         <is>
           <t>{Input_168}</t>
         </is>
       </c>
-      <c r="BM47" s="11" t="n"/>
-      <c r="BN47" s="11" t="n"/>
-      <c r="BO47" s="11" t="n"/>
-      <c r="BP47" s="11" t="n"/>
-      <c r="BQ47" s="11" t="n"/>
-      <c r="BR47" s="11" t="n"/>
-      <c r="BS47" s="11" t="n"/>
-      <c r="BT47" s="12" t="n"/>
-      <c r="BU47" s="22" t="n"/>
+      <c r="BM47" s="42" t="n"/>
+      <c r="BN47" s="42" t="n"/>
+      <c r="BO47" s="42" t="n"/>
+      <c r="BP47" s="42" t="n"/>
+      <c r="BQ47" s="42" t="n"/>
+      <c r="BR47" s="42" t="n"/>
+      <c r="BS47" s="42" t="n"/>
+      <c r="BT47" s="41" t="n"/>
+      <c r="BU47" s="34" t="n"/>
       <c r="BW47" s="5" t="n"/>
     </row>
     <row r="48" ht="13.95" customHeight="1" s="14">
       <c r="A48" s="6" t="n"/>
       <c r="E48" s="22" t="n"/>
-      <c r="AZ48" s="25" t="inlineStr">
+      <c r="AZ48" s="44" t="inlineStr">
         <is>
           <t>CLIENT</t>
         </is>
       </c>
-      <c r="BA48" s="16" t="n"/>
-      <c r="BB48" s="16" t="n"/>
-      <c r="BC48" s="16" t="n"/>
-      <c r="BD48" s="16" t="n"/>
-      <c r="BE48" s="16" t="n"/>
-      <c r="BF48" s="16" t="n"/>
-      <c r="BG48" s="17" t="n"/>
-      <c r="BH48" s="10" t="inlineStr">
+      <c r="BA48" s="38" t="n"/>
+      <c r="BB48" s="38" t="n"/>
+      <c r="BC48" s="38" t="n"/>
+      <c r="BD48" s="38" t="n"/>
+      <c r="BE48" s="38" t="n"/>
+      <c r="BF48" s="38" t="n"/>
+      <c r="BG48" s="36" t="n"/>
+      <c r="BH48" s="33" t="inlineStr">
         <is>
           <t>{Input_1}</t>
         </is>
       </c>
-      <c r="BI48" s="16" t="n"/>
-      <c r="BJ48" s="16" t="n"/>
-      <c r="BK48" s="16" t="n"/>
-      <c r="BL48" s="16" t="n"/>
-      <c r="BM48" s="16" t="n"/>
-      <c r="BN48" s="16" t="n"/>
-      <c r="BO48" s="16" t="n"/>
-      <c r="BP48" s="16" t="n"/>
-      <c r="BQ48" s="16" t="n"/>
-      <c r="BR48" s="16" t="n"/>
-      <c r="BS48" s="16" t="n"/>
-      <c r="BT48" s="17" t="n"/>
-      <c r="BU48" s="22" t="n"/>
+      <c r="BI48" s="38" t="n"/>
+      <c r="BJ48" s="38" t="n"/>
+      <c r="BK48" s="38" t="n"/>
+      <c r="BL48" s="38" t="n"/>
+      <c r="BM48" s="38" t="n"/>
+      <c r="BN48" s="38" t="n"/>
+      <c r="BO48" s="38" t="n"/>
+      <c r="BP48" s="38" t="n"/>
+      <c r="BQ48" s="38" t="n"/>
+      <c r="BR48" s="38" t="n"/>
+      <c r="BS48" s="38" t="n"/>
+      <c r="BT48" s="36" t="n"/>
+      <c r="BU48" s="34" t="n"/>
       <c r="BW48" s="5" t="n"/>
     </row>
     <row r="49" ht="13.95" customHeight="1" s="14">
@@ -2971,7 +3127,7 @@
         </is>
       </c>
       <c r="BG49" s="24" t="n"/>
-      <c r="BH49" s="18" t="n"/>
+      <c r="BH49" s="39" t="n"/>
       <c r="BI49" s="19" t="n"/>
       <c r="BJ49" s="19" t="n"/>
       <c r="BK49" s="19" t="n"/>
@@ -2984,7 +3140,7 @@
       <c r="BR49" s="19" t="n"/>
       <c r="BS49" s="19" t="n"/>
       <c r="BT49" s="20" t="n"/>
-      <c r="BU49" s="22" t="n"/>
+      <c r="BU49" s="34" t="n"/>
       <c r="BW49" s="5" t="n"/>
     </row>
     <row r="50" ht="13.95" customHeight="1" s="14">
@@ -2992,24 +3148,24 @@
       <c r="E50" s="22" t="n"/>
       <c r="AZ50" s="27" t="n"/>
       <c r="BG50" s="24" t="n"/>
-      <c r="BH50" s="10" t="inlineStr">
+      <c r="BH50" s="33" t="inlineStr">
         <is>
           <t>{Input_2}</t>
         </is>
       </c>
-      <c r="BI50" s="16" t="n"/>
-      <c r="BJ50" s="16" t="n"/>
-      <c r="BK50" s="16" t="n"/>
-      <c r="BL50" s="16" t="n"/>
-      <c r="BM50" s="16" t="n"/>
-      <c r="BN50" s="16" t="n"/>
-      <c r="BO50" s="16" t="n"/>
-      <c r="BP50" s="16" t="n"/>
-      <c r="BQ50" s="16" t="n"/>
-      <c r="BR50" s="16" t="n"/>
-      <c r="BS50" s="16" t="n"/>
-      <c r="BT50" s="17" t="n"/>
-      <c r="BU50" s="22" t="n"/>
+      <c r="BI50" s="38" t="n"/>
+      <c r="BJ50" s="38" t="n"/>
+      <c r="BK50" s="38" t="n"/>
+      <c r="BL50" s="38" t="n"/>
+      <c r="BM50" s="38" t="n"/>
+      <c r="BN50" s="38" t="n"/>
+      <c r="BO50" s="38" t="n"/>
+      <c r="BP50" s="38" t="n"/>
+      <c r="BQ50" s="38" t="n"/>
+      <c r="BR50" s="38" t="n"/>
+      <c r="BS50" s="38" t="n"/>
+      <c r="BT50" s="36" t="n"/>
+      <c r="BU50" s="34" t="n"/>
       <c r="BW50" s="5" t="n"/>
     </row>
     <row r="51" ht="13.95" customHeight="1" s="14">
@@ -3023,7 +3179,7 @@
       <c r="BE51" s="19" t="n"/>
       <c r="BF51" s="19" t="n"/>
       <c r="BG51" s="20" t="n"/>
-      <c r="BH51" s="18" t="n"/>
+      <c r="BH51" s="39" t="n"/>
       <c r="BI51" s="19" t="n"/>
       <c r="BJ51" s="19" t="n"/>
       <c r="BK51" s="19" t="n"/>
@@ -3036,42 +3192,42 @@
       <c r="BR51" s="19" t="n"/>
       <c r="BS51" s="19" t="n"/>
       <c r="BT51" s="20" t="n"/>
-      <c r="BU51" s="22" t="n"/>
+      <c r="BU51" s="34" t="n"/>
       <c r="BW51" s="5" t="n"/>
     </row>
     <row r="52" ht="13.95" customHeight="1" s="14">
       <c r="A52" s="6" t="n"/>
       <c r="E52" s="22" t="n"/>
-      <c r="AZ52" s="25" t="inlineStr">
+      <c r="AZ52" s="44" t="inlineStr">
         <is>
           <t>CONTRACTOR</t>
         </is>
       </c>
-      <c r="BA52" s="16" t="n"/>
-      <c r="BB52" s="16" t="n"/>
-      <c r="BC52" s="16" t="n"/>
-      <c r="BD52" s="16" t="n"/>
-      <c r="BE52" s="16" t="n"/>
-      <c r="BF52" s="16" t="n"/>
-      <c r="BG52" s="17" t="n"/>
-      <c r="BH52" s="10" t="inlineStr">
+      <c r="BA52" s="38" t="n"/>
+      <c r="BB52" s="38" t="n"/>
+      <c r="BC52" s="38" t="n"/>
+      <c r="BD52" s="38" t="n"/>
+      <c r="BE52" s="38" t="n"/>
+      <c r="BF52" s="38" t="n"/>
+      <c r="BG52" s="36" t="n"/>
+      <c r="BH52" s="33" t="inlineStr">
         <is>
           <t>{Input_3}</t>
         </is>
       </c>
-      <c r="BI52" s="16" t="n"/>
-      <c r="BJ52" s="16" t="n"/>
-      <c r="BK52" s="16" t="n"/>
-      <c r="BL52" s="16" t="n"/>
-      <c r="BM52" s="16" t="n"/>
-      <c r="BN52" s="16" t="n"/>
-      <c r="BO52" s="16" t="n"/>
-      <c r="BP52" s="16" t="n"/>
-      <c r="BQ52" s="16" t="n"/>
-      <c r="BR52" s="16" t="n"/>
-      <c r="BS52" s="16" t="n"/>
-      <c r="BT52" s="17" t="n"/>
-      <c r="BU52" s="22" t="n"/>
+      <c r="BI52" s="38" t="n"/>
+      <c r="BJ52" s="38" t="n"/>
+      <c r="BK52" s="38" t="n"/>
+      <c r="BL52" s="38" t="n"/>
+      <c r="BM52" s="38" t="n"/>
+      <c r="BN52" s="38" t="n"/>
+      <c r="BO52" s="38" t="n"/>
+      <c r="BP52" s="38" t="n"/>
+      <c r="BQ52" s="38" t="n"/>
+      <c r="BR52" s="38" t="n"/>
+      <c r="BS52" s="38" t="n"/>
+      <c r="BT52" s="36" t="n"/>
+      <c r="BU52" s="34" t="n"/>
       <c r="BW52" s="5" t="n"/>
     </row>
     <row r="53" ht="13.95" customHeight="1" s="14">
@@ -3083,9 +3239,9 @@
         </is>
       </c>
       <c r="BG53" s="24" t="n"/>
-      <c r="BH53" s="27" t="n"/>
+      <c r="BH53" s="45" t="n"/>
       <c r="BT53" s="24" t="n"/>
-      <c r="BU53" s="22" t="n"/>
+      <c r="BU53" s="34" t="n"/>
       <c r="BW53" s="5" t="n"/>
     </row>
     <row r="54" ht="13.95" customHeight="1" s="14">
@@ -3093,9 +3249,9 @@
       <c r="E54" s="22" t="n"/>
       <c r="AZ54" s="27" t="n"/>
       <c r="BG54" s="24" t="n"/>
-      <c r="BH54" s="27" t="n"/>
+      <c r="BH54" s="45" t="n"/>
       <c r="BT54" s="24" t="n"/>
-      <c r="BU54" s="22" t="n"/>
+      <c r="BU54" s="34" t="n"/>
       <c r="BW54" s="5" t="n"/>
     </row>
     <row r="55" ht="13.95" customHeight="1" s="14">
@@ -3109,7 +3265,7 @@
       <c r="BE55" s="19" t="n"/>
       <c r="BF55" s="19" t="n"/>
       <c r="BG55" s="20" t="n"/>
-      <c r="BH55" s="18" t="n"/>
+      <c r="BH55" s="39" t="n"/>
       <c r="BI55" s="19" t="n"/>
       <c r="BJ55" s="19" t="n"/>
       <c r="BK55" s="19" t="n"/>
@@ -3122,7 +3278,7 @@
       <c r="BR55" s="19" t="n"/>
       <c r="BS55" s="19" t="n"/>
       <c r="BT55" s="20" t="n"/>
-      <c r="BU55" s="22" t="n"/>
+      <c r="BU55" s="34" t="n"/>
       <c r="BW55" s="5" t="n"/>
     </row>
     <row r="56" ht="13.95" customHeight="1" s="14">
@@ -3138,36 +3294,36 @@
           <t>LOOKING '-Y'</t>
         </is>
       </c>
-      <c r="AZ56" s="15" t="inlineStr">
+      <c r="AZ56" s="46" t="inlineStr">
         <is>
           <t>TAG NO.</t>
         </is>
       </c>
-      <c r="BA56" s="11" t="n"/>
-      <c r="BB56" s="30" t="inlineStr">
+      <c r="BA56" s="42" t="n"/>
+      <c r="BB56" s="47" t="inlineStr">
         <is>
           <t>{Input_169}</t>
         </is>
       </c>
-      <c r="BC56" s="11" t="n"/>
-      <c r="BD56" s="11" t="n"/>
-      <c r="BE56" s="11" t="n"/>
-      <c r="BF56" s="11" t="n"/>
-      <c r="BG56" s="11" t="n"/>
-      <c r="BH56" s="11" t="n"/>
-      <c r="BI56" s="11" t="n"/>
-      <c r="BJ56" s="11" t="n"/>
-      <c r="BK56" s="11" t="n"/>
-      <c r="BL56" s="11" t="n"/>
-      <c r="BM56" s="11" t="n"/>
-      <c r="BN56" s="11" t="n"/>
-      <c r="BO56" s="11" t="n"/>
-      <c r="BP56" s="11" t="n"/>
-      <c r="BQ56" s="11" t="n"/>
-      <c r="BR56" s="11" t="n"/>
-      <c r="BS56" s="11" t="n"/>
-      <c r="BT56" s="12" t="n"/>
-      <c r="BU56" s="21" t="n"/>
+      <c r="BC56" s="42" t="n"/>
+      <c r="BD56" s="42" t="n"/>
+      <c r="BE56" s="42" t="n"/>
+      <c r="BF56" s="42" t="n"/>
+      <c r="BG56" s="42" t="n"/>
+      <c r="BH56" s="42" t="n"/>
+      <c r="BI56" s="42" t="n"/>
+      <c r="BJ56" s="42" t="n"/>
+      <c r="BK56" s="42" t="n"/>
+      <c r="BL56" s="42" t="n"/>
+      <c r="BM56" s="42" t="n"/>
+      <c r="BN56" s="42" t="n"/>
+      <c r="BO56" s="42" t="n"/>
+      <c r="BP56" s="42" t="n"/>
+      <c r="BQ56" s="42" t="n"/>
+      <c r="BR56" s="42" t="n"/>
+      <c r="BS56" s="42" t="n"/>
+      <c r="BT56" s="41" t="n"/>
+      <c r="BU56" s="40" t="n"/>
       <c r="BW56" s="5" t="n"/>
     </row>
     <row r="57" ht="13.95" customHeight="1" s="14">
@@ -3184,7 +3340,7 @@
       <c r="M57" s="11" t="n"/>
       <c r="N57" s="11" t="n"/>
       <c r="O57" s="12" t="n"/>
-      <c r="P57" s="10" t="n">
+      <c r="P57" s="32" t="n">
         <v>2</v>
       </c>
       <c r="Q57" s="11" t="n"/>
@@ -3198,7 +3354,7 @@
       <c r="Y57" s="11" t="n"/>
       <c r="Z57" s="11" t="n"/>
       <c r="AA57" s="12" t="n"/>
-      <c r="AB57" s="10" t="n">
+      <c r="AB57" s="32" t="n">
         <v>3</v>
       </c>
       <c r="AC57" s="11" t="n"/>
@@ -3211,7 +3367,7 @@
       <c r="AJ57" s="11" t="n"/>
       <c r="AK57" s="11" t="n"/>
       <c r="AL57" s="12" t="n"/>
-      <c r="AM57" s="10" t="n">
+      <c r="AM57" s="32" t="n">
         <v>4</v>
       </c>
       <c r="AN57" s="11" t="n"/>
@@ -3224,33 +3380,33 @@
       <c r="AU57" s="11" t="n"/>
       <c r="AV57" s="11" t="n"/>
       <c r="AW57" s="12" t="n"/>
-      <c r="AX57" s="10" t="n">
+      <c r="AX57" s="32" t="n">
         <v>5</v>
       </c>
       <c r="AY57" s="11" t="n"/>
-      <c r="AZ57" s="11" t="n"/>
-      <c r="BA57" s="11" t="n"/>
-      <c r="BB57" s="11" t="n"/>
-      <c r="BC57" s="11" t="n"/>
-      <c r="BD57" s="11" t="n"/>
-      <c r="BE57" s="11" t="n"/>
-      <c r="BF57" s="11" t="n"/>
-      <c r="BG57" s="11" t="n"/>
-      <c r="BH57" s="11" t="n"/>
-      <c r="BI57" s="12" t="n"/>
-      <c r="BJ57" s="10" t="n">
+      <c r="AZ57" s="42" t="n"/>
+      <c r="BA57" s="42" t="n"/>
+      <c r="BB57" s="42" t="n"/>
+      <c r="BC57" s="42" t="n"/>
+      <c r="BD57" s="42" t="n"/>
+      <c r="BE57" s="42" t="n"/>
+      <c r="BF57" s="42" t="n"/>
+      <c r="BG57" s="42" t="n"/>
+      <c r="BH57" s="42" t="n"/>
+      <c r="BI57" s="41" t="n"/>
+      <c r="BJ57" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="BK57" s="11" t="n"/>
-      <c r="BL57" s="11" t="n"/>
-      <c r="BM57" s="11" t="n"/>
-      <c r="BN57" s="11" t="n"/>
-      <c r="BO57" s="11" t="n"/>
-      <c r="BP57" s="11" t="n"/>
-      <c r="BQ57" s="11" t="n"/>
-      <c r="BR57" s="11" t="n"/>
-      <c r="BS57" s="11" t="n"/>
-      <c r="BT57" s="12" t="n"/>
+      <c r="BK57" s="42" t="n"/>
+      <c r="BL57" s="42" t="n"/>
+      <c r="BM57" s="42" t="n"/>
+      <c r="BN57" s="42" t="n"/>
+      <c r="BO57" s="42" t="n"/>
+      <c r="BP57" s="42" t="n"/>
+      <c r="BQ57" s="42" t="n"/>
+      <c r="BR57" s="42" t="n"/>
+      <c r="BS57" s="42" t="n"/>
+      <c r="BT57" s="41" t="n"/>
       <c r="BW57" s="5" t="n"/>
     </row>
     <row r="58" ht="13.95" customHeight="1" s="14">

--- a/제작도_도면_1.xlsx
+++ b/제작도_도면_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duddl\Desktop\Project\a2z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AB20FF-E2DC-496E-A223-B5F44A22168A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB607762-1239-4BF8-B905-A7FA8084289A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="696" yWindow="720" windowWidth="20256" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1084,111 +1084,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>26670</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>148590</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2084DD09-7A80-11DA-FC76-D78986100289}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="472440" y="377190"/>
-          <a:ext cx="472440" cy="472440"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>45</xdr:col>
-      <xdr:colOff>151116</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>85104</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="그림 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5837C2EA-6D71-2D2B-3206-FC09F47C83CD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10781016" y="350520"/>
-          <a:ext cx="406428" cy="1051560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5529,6 +5424,5 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/제작도_도면_1.xlsx
+++ b/제작도_도면_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duddl\AppData\Local\Temp\claude\C--Users-duddl-Desktop-Project-a2z\774260fd-2622-4588-9572-6413dbe29bb1\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA3AC3D-838B-42EB-90F2-3AF4AD5CEC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90BCBE3-FBD1-4AC1-A51C-D37648D898BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="277">
   <si>
     <t>A</t>
   </si>
@@ -737,15 +737,171 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BOM 늘려야 함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{Image_4}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>{Input_200}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_231}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_211}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_221}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_216}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_201}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_226}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_206}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_236}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_232}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_212}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_222}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_217}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_202}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_227}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_207}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_237}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_233}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_213}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_223}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_218}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_203}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_228}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_208}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_238}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_234}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_214}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_224}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_219}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_204}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_229}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_209}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_239}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_235}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_215}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_225}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_220}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_205}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_230}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_210}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Input_240}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1060,6 +1216,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1072,15 +1276,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1093,6 +1292,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1102,76 +1328,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1217,13 +1373,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1690,165 +1846,165 @@
       <c r="BR2" s="2"/>
     </row>
     <row r="3" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="D3" s="36"/>
+      <c r="D3" s="20"/>
       <c r="Y3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="AT3" s="15"/>
-      <c r="AU3" s="19" t="s">
+      <c r="AU3" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="AV3" s="20"/>
-      <c r="AW3" s="42" t="s">
+      <c r="AV3" s="36"/>
+      <c r="AW3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="AX3" s="43"/>
-      <c r="AY3" s="43"/>
-      <c r="AZ3" s="43"/>
-      <c r="BA3" s="43"/>
-      <c r="BB3" s="43"/>
-      <c r="BC3" s="43"/>
-      <c r="BD3" s="43"/>
-      <c r="BE3" s="43"/>
-      <c r="BF3" s="43"/>
-      <c r="BG3" s="43"/>
-      <c r="BH3" s="43"/>
-      <c r="BI3" s="43"/>
-      <c r="BJ3" s="43"/>
-      <c r="BK3" s="43"/>
-      <c r="BL3" s="43"/>
-      <c r="BM3" s="43"/>
-      <c r="BN3" s="43"/>
-      <c r="BO3" s="43"/>
-      <c r="BP3" s="43"/>
-      <c r="BQ3" s="44"/>
-      <c r="BR3" s="30" t="s">
+      <c r="AX3" s="30"/>
+      <c r="AY3" s="30"/>
+      <c r="AZ3" s="30"/>
+      <c r="BA3" s="30"/>
+      <c r="BB3" s="30"/>
+      <c r="BC3" s="30"/>
+      <c r="BD3" s="30"/>
+      <c r="BE3" s="30"/>
+      <c r="BF3" s="30"/>
+      <c r="BG3" s="30"/>
+      <c r="BH3" s="30"/>
+      <c r="BI3" s="30"/>
+      <c r="BJ3" s="30"/>
+      <c r="BK3" s="30"/>
+      <c r="BL3" s="30"/>
+      <c r="BM3" s="30"/>
+      <c r="BN3" s="30"/>
+      <c r="BO3" s="30"/>
+      <c r="BP3" s="30"/>
+      <c r="BQ3" s="31"/>
+      <c r="BR3" s="54" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="31"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="33" t="s">
+      <c r="B4" s="55"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="34"/>
-      <c r="T4" s="34"/>
-      <c r="U4" s="34"/>
-      <c r="V4" s="34"/>
-      <c r="W4" s="34"/>
-      <c r="AA4" s="33" t="s">
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+      <c r="AA4" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AB4" s="34"/>
-      <c r="AC4" s="34"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="34"/>
-      <c r="AF4" s="34"/>
-      <c r="AG4" s="34"/>
-      <c r="AH4" s="34"/>
-      <c r="AI4" s="34"/>
-      <c r="AJ4" s="34"/>
-      <c r="AK4" s="34"/>
-      <c r="AL4" s="34"/>
-      <c r="AM4" s="34"/>
-      <c r="AN4" s="34"/>
-      <c r="AO4" s="34"/>
-      <c r="AP4" s="34"/>
-      <c r="AQ4" s="34"/>
-      <c r="AR4" s="34"/>
-      <c r="AS4" s="34"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="40"/>
+      <c r="AH4" s="40"/>
+      <c r="AI4" s="40"/>
+      <c r="AJ4" s="40"/>
+      <c r="AK4" s="40"/>
+      <c r="AL4" s="40"/>
+      <c r="AM4" s="40"/>
+      <c r="AN4" s="40"/>
+      <c r="AO4" s="40"/>
+      <c r="AP4" s="40"/>
+      <c r="AQ4" s="40"/>
+      <c r="AR4" s="40"/>
+      <c r="AS4" s="40"/>
       <c r="AT4" s="9"/>
-      <c r="AU4" s="21"/>
-      <c r="AV4" s="22"/>
-      <c r="AW4" s="45"/>
-      <c r="AX4" s="46"/>
-      <c r="AY4" s="46"/>
-      <c r="AZ4" s="46"/>
-      <c r="BA4" s="46"/>
-      <c r="BB4" s="46"/>
-      <c r="BC4" s="46"/>
-      <c r="BD4" s="46"/>
-      <c r="BE4" s="46"/>
-      <c r="BF4" s="46"/>
-      <c r="BG4" s="46"/>
-      <c r="BH4" s="46"/>
-      <c r="BI4" s="46"/>
-      <c r="BJ4" s="46"/>
-      <c r="BK4" s="46"/>
-      <c r="BL4" s="46"/>
-      <c r="BM4" s="46"/>
-      <c r="BN4" s="46"/>
-      <c r="BO4" s="46"/>
-      <c r="BP4" s="46"/>
-      <c r="BQ4" s="47"/>
-      <c r="BR4" s="31"/>
+      <c r="AU4" s="37"/>
+      <c r="AV4" s="38"/>
+      <c r="AW4" s="32"/>
+      <c r="AX4" s="33"/>
+      <c r="AY4" s="33"/>
+      <c r="AZ4" s="33"/>
+      <c r="BA4" s="33"/>
+      <c r="BB4" s="33"/>
+      <c r="BC4" s="33"/>
+      <c r="BD4" s="33"/>
+      <c r="BE4" s="33"/>
+      <c r="BF4" s="33"/>
+      <c r="BG4" s="33"/>
+      <c r="BH4" s="33"/>
+      <c r="BI4" s="33"/>
+      <c r="BJ4" s="33"/>
+      <c r="BK4" s="33"/>
+      <c r="BL4" s="33"/>
+      <c r="BM4" s="33"/>
+      <c r="BN4" s="33"/>
+      <c r="BO4" s="33"/>
+      <c r="BP4" s="33"/>
+      <c r="BQ4" s="34"/>
+      <c r="BR4" s="55"/>
     </row>
     <row r="5" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="31"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="34"/>
-      <c r="S5" s="34"/>
-      <c r="T5" s="34"/>
-      <c r="U5" s="34"/>
-      <c r="V5" s="34"/>
-      <c r="W5" s="34"/>
-      <c r="AA5" s="34"/>
-      <c r="AB5" s="34"/>
-      <c r="AC5" s="34"/>
-      <c r="AD5" s="34"/>
-      <c r="AE5" s="34"/>
-      <c r="AF5" s="34"/>
-      <c r="AG5" s="34"/>
-      <c r="AH5" s="34"/>
-      <c r="AI5" s="34"/>
-      <c r="AJ5" s="34"/>
-      <c r="AK5" s="34"/>
-      <c r="AL5" s="34"/>
-      <c r="AM5" s="34"/>
-      <c r="AN5" s="34"/>
-      <c r="AO5" s="34"/>
-      <c r="AP5" s="34"/>
-      <c r="AQ5" s="34"/>
-      <c r="AR5" s="34"/>
-      <c r="AS5" s="34"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="40"/>
+      <c r="U5" s="40"/>
+      <c r="V5" s="40"/>
+      <c r="W5" s="40"/>
+      <c r="AA5" s="40"/>
+      <c r="AB5" s="40"/>
+      <c r="AC5" s="40"/>
+      <c r="AD5" s="40"/>
+      <c r="AE5" s="40"/>
+      <c r="AF5" s="40"/>
+      <c r="AG5" s="40"/>
+      <c r="AH5" s="40"/>
+      <c r="AI5" s="40"/>
+      <c r="AJ5" s="40"/>
+      <c r="AK5" s="40"/>
+      <c r="AL5" s="40"/>
+      <c r="AM5" s="40"/>
+      <c r="AN5" s="40"/>
+      <c r="AO5" s="40"/>
+      <c r="AP5" s="40"/>
+      <c r="AQ5" s="40"/>
+      <c r="AR5" s="40"/>
+      <c r="AS5" s="40"/>
       <c r="AT5" s="9"/>
-      <c r="AU5" s="21"/>
-      <c r="AV5" s="22"/>
+      <c r="AU5" s="37"/>
+      <c r="AV5" s="38"/>
       <c r="AW5" s="66" t="s">
         <v>225</v>
       </c>
@@ -1872,7 +2028,7 @@
       <c r="BI5" s="67"/>
       <c r="BJ5" s="67"/>
       <c r="BK5" s="68"/>
-      <c r="BL5" s="72" t="s">
+      <c r="BL5" s="73" t="s">
         <v>8</v>
       </c>
       <c r="BM5" s="66" t="s">
@@ -1880,57 +2036,57 @@
       </c>
       <c r="BN5" s="67"/>
       <c r="BO5" s="68"/>
-      <c r="BP5" s="72" t="s">
+      <c r="BP5" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="BQ5" s="72" t="s">
+      <c r="BQ5" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="BR5" s="31"/>
+      <c r="BR5" s="55"/>
     </row>
     <row r="6" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="31"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="34"/>
-      <c r="T6" s="34"/>
-      <c r="U6" s="34"/>
-      <c r="V6" s="34"/>
-      <c r="W6" s="34"/>
-      <c r="AA6" s="34"/>
-      <c r="AB6" s="34"/>
-      <c r="AC6" s="34"/>
-      <c r="AD6" s="34"/>
-      <c r="AE6" s="34"/>
-      <c r="AF6" s="34"/>
-      <c r="AG6" s="34"/>
-      <c r="AH6" s="34"/>
-      <c r="AI6" s="34"/>
-      <c r="AJ6" s="34"/>
-      <c r="AK6" s="34"/>
-      <c r="AL6" s="34"/>
-      <c r="AM6" s="34"/>
-      <c r="AN6" s="34"/>
-      <c r="AO6" s="34"/>
-      <c r="AP6" s="34"/>
-      <c r="AQ6" s="34"/>
-      <c r="AR6" s="34"/>
-      <c r="AS6" s="34"/>
+      <c r="B6" s="55"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="40"/>
+      <c r="W6" s="40"/>
+      <c r="AA6" s="40"/>
+      <c r="AB6" s="40"/>
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="40"/>
+      <c r="AE6" s="40"/>
+      <c r="AF6" s="40"/>
+      <c r="AG6" s="40"/>
+      <c r="AH6" s="40"/>
+      <c r="AI6" s="40"/>
+      <c r="AJ6" s="40"/>
+      <c r="AK6" s="40"/>
+      <c r="AL6" s="40"/>
+      <c r="AM6" s="40"/>
+      <c r="AN6" s="40"/>
+      <c r="AO6" s="40"/>
+      <c r="AP6" s="40"/>
+      <c r="AQ6" s="40"/>
+      <c r="AR6" s="40"/>
+      <c r="AS6" s="40"/>
       <c r="AT6" s="9"/>
-      <c r="AU6" s="21"/>
-      <c r="AV6" s="22"/>
+      <c r="AU6" s="37"/>
+      <c r="AV6" s="38"/>
       <c r="AW6" s="69"/>
       <c r="AX6" s="71"/>
       <c r="AY6" s="69"/>
@@ -1946,57 +2102,57 @@
       <c r="BI6" s="70"/>
       <c r="BJ6" s="70"/>
       <c r="BK6" s="71"/>
-      <c r="BL6" s="73"/>
+      <c r="BL6" s="74"/>
       <c r="BM6" s="69"/>
       <c r="BN6" s="70"/>
       <c r="BO6" s="71"/>
-      <c r="BP6" s="73"/>
-      <c r="BQ6" s="73"/>
-      <c r="BR6" s="31"/>
+      <c r="BP6" s="74"/>
+      <c r="BQ6" s="74"/>
+      <c r="BR6" s="55"/>
     </row>
     <row r="7" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="31"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="34"/>
-      <c r="T7" s="34"/>
-      <c r="U7" s="34"/>
-      <c r="V7" s="34"/>
-      <c r="W7" s="34"/>
-      <c r="AA7" s="34"/>
-      <c r="AB7" s="34"/>
-      <c r="AC7" s="34"/>
-      <c r="AD7" s="34"/>
-      <c r="AE7" s="34"/>
-      <c r="AF7" s="34"/>
-      <c r="AG7" s="34"/>
-      <c r="AH7" s="34"/>
-      <c r="AI7" s="34"/>
-      <c r="AJ7" s="34"/>
-      <c r="AK7" s="34"/>
-      <c r="AL7" s="34"/>
-      <c r="AM7" s="34"/>
-      <c r="AN7" s="34"/>
-      <c r="AO7" s="34"/>
-      <c r="AP7" s="34"/>
-      <c r="AQ7" s="34"/>
-      <c r="AR7" s="34"/>
-      <c r="AS7" s="34"/>
+      <c r="B7" s="55"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="40"/>
+      <c r="W7" s="40"/>
+      <c r="AA7" s="40"/>
+      <c r="AB7" s="40"/>
+      <c r="AC7" s="40"/>
+      <c r="AD7" s="40"/>
+      <c r="AE7" s="40"/>
+      <c r="AF7" s="40"/>
+      <c r="AG7" s="40"/>
+      <c r="AH7" s="40"/>
+      <c r="AI7" s="40"/>
+      <c r="AJ7" s="40"/>
+      <c r="AK7" s="40"/>
+      <c r="AL7" s="40"/>
+      <c r="AM7" s="40"/>
+      <c r="AN7" s="40"/>
+      <c r="AO7" s="40"/>
+      <c r="AP7" s="40"/>
+      <c r="AQ7" s="40"/>
+      <c r="AR7" s="40"/>
+      <c r="AS7" s="40"/>
       <c r="AT7" s="9"/>
-      <c r="AU7" s="21"/>
-      <c r="AV7" s="22"/>
+      <c r="AU7" s="37"/>
+      <c r="AV7" s="38"/>
       <c r="AW7" s="23" t="s">
         <v>12</v>
       </c>
@@ -2034,51 +2190,51 @@
       <c r="BQ7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="BR7" s="31"/>
+      <c r="BR7" s="55"/>
     </row>
     <row r="8" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="31"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="34"/>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34"/>
-      <c r="W8" s="34"/>
-      <c r="AA8" s="34"/>
-      <c r="AB8" s="34"/>
-      <c r="AC8" s="34"/>
-      <c r="AD8" s="34"/>
-      <c r="AE8" s="34"/>
-      <c r="AF8" s="34"/>
-      <c r="AG8" s="34"/>
-      <c r="AH8" s="34"/>
-      <c r="AI8" s="34"/>
-      <c r="AJ8" s="34"/>
-      <c r="AK8" s="34"/>
-      <c r="AL8" s="34"/>
-      <c r="AM8" s="34"/>
-      <c r="AN8" s="34"/>
-      <c r="AO8" s="34"/>
-      <c r="AP8" s="34"/>
-      <c r="AQ8" s="34"/>
-      <c r="AR8" s="34"/>
-      <c r="AS8" s="34"/>
+      <c r="B8" s="55"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="40"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="40"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="40"/>
+      <c r="W8" s="40"/>
+      <c r="AA8" s="40"/>
+      <c r="AB8" s="40"/>
+      <c r="AC8" s="40"/>
+      <c r="AD8" s="40"/>
+      <c r="AE8" s="40"/>
+      <c r="AF8" s="40"/>
+      <c r="AG8" s="40"/>
+      <c r="AH8" s="40"/>
+      <c r="AI8" s="40"/>
+      <c r="AJ8" s="40"/>
+      <c r="AK8" s="40"/>
+      <c r="AL8" s="40"/>
+      <c r="AM8" s="40"/>
+      <c r="AN8" s="40"/>
+      <c r="AO8" s="40"/>
+      <c r="AP8" s="40"/>
+      <c r="AQ8" s="40"/>
+      <c r="AR8" s="40"/>
+      <c r="AS8" s="40"/>
       <c r="AT8" s="9"/>
-      <c r="AU8" s="21"/>
-      <c r="AV8" s="22"/>
+      <c r="AU8" s="37"/>
+      <c r="AV8" s="38"/>
       <c r="AW8" s="23" t="s">
         <v>20</v>
       </c>
@@ -2116,48 +2272,48 @@
       <c r="BQ8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="BR8" s="31"/>
+      <c r="BR8" s="55"/>
     </row>
     <row r="9" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="31"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="34"/>
-      <c r="V9" s="34"/>
-      <c r="W9" s="34"/>
-      <c r="AA9" s="34"/>
-      <c r="AB9" s="34"/>
-      <c r="AC9" s="34"/>
-      <c r="AD9" s="34"/>
-      <c r="AE9" s="34"/>
-      <c r="AF9" s="34"/>
-      <c r="AG9" s="34"/>
-      <c r="AH9" s="34"/>
-      <c r="AI9" s="34"/>
-      <c r="AJ9" s="34"/>
-      <c r="AK9" s="34"/>
-      <c r="AL9" s="34"/>
-      <c r="AM9" s="34"/>
-      <c r="AN9" s="34"/>
-      <c r="AO9" s="34"/>
-      <c r="AP9" s="34"/>
-      <c r="AQ9" s="34"/>
-      <c r="AR9" s="34"/>
-      <c r="AS9" s="34"/>
+      <c r="B9" s="55"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="40"/>
+      <c r="AA9" s="40"/>
+      <c r="AB9" s="40"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="40"/>
+      <c r="AE9" s="40"/>
+      <c r="AF9" s="40"/>
+      <c r="AG9" s="40"/>
+      <c r="AH9" s="40"/>
+      <c r="AI9" s="40"/>
+      <c r="AJ9" s="40"/>
+      <c r="AK9" s="40"/>
+      <c r="AL9" s="40"/>
+      <c r="AM9" s="40"/>
+      <c r="AN9" s="40"/>
+      <c r="AO9" s="40"/>
+      <c r="AP9" s="40"/>
+      <c r="AQ9" s="40"/>
+      <c r="AR9" s="40"/>
+      <c r="AS9" s="40"/>
       <c r="AT9" s="11"/>
       <c r="AU9" s="11"/>
       <c r="AV9" s="12"/>
@@ -2198,48 +2354,48 @@
       <c r="BQ9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="BR9" s="31"/>
+      <c r="BR9" s="55"/>
     </row>
     <row r="10" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="31"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="34"/>
-      <c r="S10" s="34"/>
-      <c r="T10" s="34"/>
-      <c r="U10" s="34"/>
-      <c r="V10" s="34"/>
-      <c r="W10" s="34"/>
-      <c r="AA10" s="34"/>
-      <c r="AB10" s="34"/>
-      <c r="AC10" s="34"/>
-      <c r="AD10" s="34"/>
-      <c r="AE10" s="34"/>
-      <c r="AF10" s="34"/>
-      <c r="AG10" s="34"/>
-      <c r="AH10" s="34"/>
-      <c r="AI10" s="34"/>
-      <c r="AJ10" s="34"/>
-      <c r="AK10" s="34"/>
-      <c r="AL10" s="34"/>
-      <c r="AM10" s="34"/>
-      <c r="AN10" s="34"/>
-      <c r="AO10" s="34"/>
-      <c r="AP10" s="34"/>
-      <c r="AQ10" s="34"/>
-      <c r="AR10" s="34"/>
-      <c r="AS10" s="34"/>
+      <c r="B10" s="55"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="40"/>
+      <c r="S10" s="40"/>
+      <c r="T10" s="40"/>
+      <c r="U10" s="40"/>
+      <c r="V10" s="40"/>
+      <c r="W10" s="40"/>
+      <c r="AA10" s="40"/>
+      <c r="AB10" s="40"/>
+      <c r="AC10" s="40"/>
+      <c r="AD10" s="40"/>
+      <c r="AE10" s="40"/>
+      <c r="AF10" s="40"/>
+      <c r="AG10" s="40"/>
+      <c r="AH10" s="40"/>
+      <c r="AI10" s="40"/>
+      <c r="AJ10" s="40"/>
+      <c r="AK10" s="40"/>
+      <c r="AL10" s="40"/>
+      <c r="AM10" s="40"/>
+      <c r="AN10" s="40"/>
+      <c r="AO10" s="40"/>
+      <c r="AP10" s="40"/>
+      <c r="AQ10" s="40"/>
+      <c r="AR10" s="40"/>
+      <c r="AS10" s="40"/>
       <c r="AT10" s="11"/>
       <c r="AU10" s="11"/>
       <c r="AV10" s="12"/>
@@ -2280,48 +2436,48 @@
       <c r="BQ10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="BR10" s="31"/>
+      <c r="BR10" s="55"/>
     </row>
     <row r="11" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="31"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="34"/>
-      <c r="W11" s="34"/>
-      <c r="AA11" s="34"/>
-      <c r="AB11" s="34"/>
-      <c r="AC11" s="34"/>
-      <c r="AD11" s="34"/>
-      <c r="AE11" s="34"/>
-      <c r="AF11" s="34"/>
-      <c r="AG11" s="34"/>
-      <c r="AH11" s="34"/>
-      <c r="AI11" s="34"/>
-      <c r="AJ11" s="34"/>
-      <c r="AK11" s="34"/>
-      <c r="AL11" s="34"/>
-      <c r="AM11" s="34"/>
-      <c r="AN11" s="34"/>
-      <c r="AO11" s="34"/>
-      <c r="AP11" s="34"/>
-      <c r="AQ11" s="34"/>
-      <c r="AR11" s="34"/>
-      <c r="AS11" s="34"/>
+      <c r="B11" s="55"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="40"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="40"/>
+      <c r="U11" s="40"/>
+      <c r="V11" s="40"/>
+      <c r="W11" s="40"/>
+      <c r="AA11" s="40"/>
+      <c r="AB11" s="40"/>
+      <c r="AC11" s="40"/>
+      <c r="AD11" s="40"/>
+      <c r="AE11" s="40"/>
+      <c r="AF11" s="40"/>
+      <c r="AG11" s="40"/>
+      <c r="AH11" s="40"/>
+      <c r="AI11" s="40"/>
+      <c r="AJ11" s="40"/>
+      <c r="AK11" s="40"/>
+      <c r="AL11" s="40"/>
+      <c r="AM11" s="40"/>
+      <c r="AN11" s="40"/>
+      <c r="AO11" s="40"/>
+      <c r="AP11" s="40"/>
+      <c r="AQ11" s="40"/>
+      <c r="AR11" s="40"/>
+      <c r="AS11" s="40"/>
       <c r="AT11" s="11"/>
       <c r="AU11" s="11"/>
       <c r="AV11" s="12"/>
@@ -2362,48 +2518,48 @@
       <c r="BQ11" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="BR11" s="31"/>
+      <c r="BR11" s="55"/>
     </row>
     <row r="12" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="31"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="34"/>
-      <c r="V12" s="34"/>
-      <c r="W12" s="34"/>
-      <c r="AA12" s="34"/>
-      <c r="AB12" s="34"/>
-      <c r="AC12" s="34"/>
-      <c r="AD12" s="34"/>
-      <c r="AE12" s="34"/>
-      <c r="AF12" s="34"/>
-      <c r="AG12" s="34"/>
-      <c r="AH12" s="34"/>
-      <c r="AI12" s="34"/>
-      <c r="AJ12" s="34"/>
-      <c r="AK12" s="34"/>
-      <c r="AL12" s="34"/>
-      <c r="AM12" s="34"/>
-      <c r="AN12" s="34"/>
-      <c r="AO12" s="34"/>
-      <c r="AP12" s="34"/>
-      <c r="AQ12" s="34"/>
-      <c r="AR12" s="34"/>
-      <c r="AS12" s="34"/>
+      <c r="B12" s="55"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="40"/>
+      <c r="S12" s="40"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="40"/>
+      <c r="V12" s="40"/>
+      <c r="W12" s="40"/>
+      <c r="AA12" s="40"/>
+      <c r="AB12" s="40"/>
+      <c r="AC12" s="40"/>
+      <c r="AD12" s="40"/>
+      <c r="AE12" s="40"/>
+      <c r="AF12" s="40"/>
+      <c r="AG12" s="40"/>
+      <c r="AH12" s="40"/>
+      <c r="AI12" s="40"/>
+      <c r="AJ12" s="40"/>
+      <c r="AK12" s="40"/>
+      <c r="AL12" s="40"/>
+      <c r="AM12" s="40"/>
+      <c r="AN12" s="40"/>
+      <c r="AO12" s="40"/>
+      <c r="AP12" s="40"/>
+      <c r="AQ12" s="40"/>
+      <c r="AR12" s="40"/>
+      <c r="AS12" s="40"/>
       <c r="AW12" s="23" t="s">
         <v>52</v>
       </c>
@@ -2441,48 +2597,48 @@
       <c r="BQ12" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="BR12" s="31"/>
+      <c r="BR12" s="55"/>
     </row>
     <row r="13" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="31"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="34"/>
-      <c r="W13" s="34"/>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="34"/>
-      <c r="AC13" s="34"/>
-      <c r="AD13" s="34"/>
-      <c r="AE13" s="34"/>
-      <c r="AF13" s="34"/>
-      <c r="AG13" s="34"/>
-      <c r="AH13" s="34"/>
-      <c r="AI13" s="34"/>
-      <c r="AJ13" s="34"/>
-      <c r="AK13" s="34"/>
-      <c r="AL13" s="34"/>
-      <c r="AM13" s="34"/>
-      <c r="AN13" s="34"/>
-      <c r="AO13" s="34"/>
-      <c r="AP13" s="34"/>
-      <c r="AQ13" s="34"/>
-      <c r="AR13" s="34"/>
-      <c r="AS13" s="34"/>
+      <c r="B13" s="55"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="40"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="40"/>
+      <c r="W13" s="40"/>
+      <c r="AA13" s="40"/>
+      <c r="AB13" s="40"/>
+      <c r="AC13" s="40"/>
+      <c r="AD13" s="40"/>
+      <c r="AE13" s="40"/>
+      <c r="AF13" s="40"/>
+      <c r="AG13" s="40"/>
+      <c r="AH13" s="40"/>
+      <c r="AI13" s="40"/>
+      <c r="AJ13" s="40"/>
+      <c r="AK13" s="40"/>
+      <c r="AL13" s="40"/>
+      <c r="AM13" s="40"/>
+      <c r="AN13" s="40"/>
+      <c r="AO13" s="40"/>
+      <c r="AP13" s="40"/>
+      <c r="AQ13" s="40"/>
+      <c r="AR13" s="40"/>
+      <c r="AS13" s="40"/>
       <c r="AW13" s="23" t="s">
         <v>60</v>
       </c>
@@ -2520,48 +2676,48 @@
       <c r="BQ13" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="BR13" s="31"/>
+      <c r="BR13" s="55"/>
     </row>
     <row r="14" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="31"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="34"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="34"/>
-      <c r="W14" s="34"/>
-      <c r="AA14" s="34"/>
-      <c r="AB14" s="34"/>
-      <c r="AC14" s="34"/>
-      <c r="AD14" s="34"/>
-      <c r="AE14" s="34"/>
-      <c r="AF14" s="34"/>
-      <c r="AG14" s="34"/>
-      <c r="AH14" s="34"/>
-      <c r="AI14" s="34"/>
-      <c r="AJ14" s="34"/>
-      <c r="AK14" s="34"/>
-      <c r="AL14" s="34"/>
-      <c r="AM14" s="34"/>
-      <c r="AN14" s="34"/>
-      <c r="AO14" s="34"/>
-      <c r="AP14" s="34"/>
-      <c r="AQ14" s="34"/>
-      <c r="AR14" s="34"/>
-      <c r="AS14" s="34"/>
+      <c r="B14" s="55"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
+      <c r="P14" s="40"/>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="40"/>
+      <c r="S14" s="40"/>
+      <c r="T14" s="40"/>
+      <c r="U14" s="40"/>
+      <c r="V14" s="40"/>
+      <c r="W14" s="40"/>
+      <c r="AA14" s="40"/>
+      <c r="AB14" s="40"/>
+      <c r="AC14" s="40"/>
+      <c r="AD14" s="40"/>
+      <c r="AE14" s="40"/>
+      <c r="AF14" s="40"/>
+      <c r="AG14" s="40"/>
+      <c r="AH14" s="40"/>
+      <c r="AI14" s="40"/>
+      <c r="AJ14" s="40"/>
+      <c r="AK14" s="40"/>
+      <c r="AL14" s="40"/>
+      <c r="AM14" s="40"/>
+      <c r="AN14" s="40"/>
+      <c r="AO14" s="40"/>
+      <c r="AP14" s="40"/>
+      <c r="AQ14" s="40"/>
+      <c r="AR14" s="40"/>
+      <c r="AS14" s="40"/>
       <c r="AW14" s="23" t="s">
         <v>68</v>
       </c>
@@ -2599,48 +2755,48 @@
       <c r="BQ14" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="BR14" s="31"/>
+      <c r="BR14" s="55"/>
     </row>
     <row r="15" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="31"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="34"/>
-      <c r="W15" s="34"/>
-      <c r="AA15" s="34"/>
-      <c r="AB15" s="34"/>
-      <c r="AC15" s="34"/>
-      <c r="AD15" s="34"/>
-      <c r="AE15" s="34"/>
-      <c r="AF15" s="34"/>
-      <c r="AG15" s="34"/>
-      <c r="AH15" s="34"/>
-      <c r="AI15" s="34"/>
-      <c r="AJ15" s="34"/>
-      <c r="AK15" s="34"/>
-      <c r="AL15" s="34"/>
-      <c r="AM15" s="34"/>
-      <c r="AN15" s="34"/>
-      <c r="AO15" s="34"/>
-      <c r="AP15" s="34"/>
-      <c r="AQ15" s="34"/>
-      <c r="AR15" s="34"/>
-      <c r="AS15" s="34"/>
+      <c r="B15" s="55"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="40"/>
+      <c r="AA15" s="40"/>
+      <c r="AB15" s="40"/>
+      <c r="AC15" s="40"/>
+      <c r="AD15" s="40"/>
+      <c r="AE15" s="40"/>
+      <c r="AF15" s="40"/>
+      <c r="AG15" s="40"/>
+      <c r="AH15" s="40"/>
+      <c r="AI15" s="40"/>
+      <c r="AJ15" s="40"/>
+      <c r="AK15" s="40"/>
+      <c r="AL15" s="40"/>
+      <c r="AM15" s="40"/>
+      <c r="AN15" s="40"/>
+      <c r="AO15" s="40"/>
+      <c r="AP15" s="40"/>
+      <c r="AQ15" s="40"/>
+      <c r="AR15" s="40"/>
+      <c r="AS15" s="40"/>
       <c r="AW15" s="23" t="s">
         <v>76</v>
       </c>
@@ -2678,48 +2834,48 @@
       <c r="BQ15" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="BR15" s="31"/>
+      <c r="BR15" s="55"/>
     </row>
     <row r="16" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="32"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="34"/>
-      <c r="V16" s="34"/>
-      <c r="W16" s="34"/>
-      <c r="AA16" s="34"/>
-      <c r="AB16" s="34"/>
-      <c r="AC16" s="34"/>
-      <c r="AD16" s="34"/>
-      <c r="AE16" s="34"/>
-      <c r="AF16" s="34"/>
-      <c r="AG16" s="34"/>
-      <c r="AH16" s="34"/>
-      <c r="AI16" s="34"/>
-      <c r="AJ16" s="34"/>
-      <c r="AK16" s="34"/>
-      <c r="AL16" s="34"/>
-      <c r="AM16" s="34"/>
-      <c r="AN16" s="34"/>
-      <c r="AO16" s="34"/>
-      <c r="AP16" s="34"/>
-      <c r="AQ16" s="34"/>
-      <c r="AR16" s="34"/>
-      <c r="AS16" s="34"/>
+      <c r="B16" s="56"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="40"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="40"/>
+      <c r="V16" s="40"/>
+      <c r="W16" s="40"/>
+      <c r="AA16" s="40"/>
+      <c r="AB16" s="40"/>
+      <c r="AC16" s="40"/>
+      <c r="AD16" s="40"/>
+      <c r="AE16" s="40"/>
+      <c r="AF16" s="40"/>
+      <c r="AG16" s="40"/>
+      <c r="AH16" s="40"/>
+      <c r="AI16" s="40"/>
+      <c r="AJ16" s="40"/>
+      <c r="AK16" s="40"/>
+      <c r="AL16" s="40"/>
+      <c r="AM16" s="40"/>
+      <c r="AN16" s="40"/>
+      <c r="AO16" s="40"/>
+      <c r="AP16" s="40"/>
+      <c r="AQ16" s="40"/>
+      <c r="AR16" s="40"/>
+      <c r="AS16" s="40"/>
       <c r="AW16" s="23" t="s">
         <v>85</v>
       </c>
@@ -2757,50 +2913,50 @@
       <c r="BQ16" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="BR16" s="32"/>
+      <c r="BR16" s="56"/>
     </row>
     <row r="17" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="34"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="34"/>
-      <c r="W17" s="34"/>
-      <c r="AA17" s="34"/>
-      <c r="AB17" s="34"/>
-      <c r="AC17" s="34"/>
-      <c r="AD17" s="34"/>
-      <c r="AE17" s="34"/>
-      <c r="AF17" s="34"/>
-      <c r="AG17" s="34"/>
-      <c r="AH17" s="34"/>
-      <c r="AI17" s="34"/>
-      <c r="AJ17" s="34"/>
-      <c r="AK17" s="34"/>
-      <c r="AL17" s="34"/>
-      <c r="AM17" s="34"/>
-      <c r="AN17" s="34"/>
-      <c r="AO17" s="34"/>
-      <c r="AP17" s="34"/>
-      <c r="AQ17" s="34"/>
-      <c r="AR17" s="34"/>
-      <c r="AS17" s="34"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="40"/>
+      <c r="S17" s="40"/>
+      <c r="T17" s="40"/>
+      <c r="U17" s="40"/>
+      <c r="V17" s="40"/>
+      <c r="W17" s="40"/>
+      <c r="AA17" s="40"/>
+      <c r="AB17" s="40"/>
+      <c r="AC17" s="40"/>
+      <c r="AD17" s="40"/>
+      <c r="AE17" s="40"/>
+      <c r="AF17" s="40"/>
+      <c r="AG17" s="40"/>
+      <c r="AH17" s="40"/>
+      <c r="AI17" s="40"/>
+      <c r="AJ17" s="40"/>
+      <c r="AK17" s="40"/>
+      <c r="AL17" s="40"/>
+      <c r="AM17" s="40"/>
+      <c r="AN17" s="40"/>
+      <c r="AO17" s="40"/>
+      <c r="AP17" s="40"/>
+      <c r="AQ17" s="40"/>
+      <c r="AR17" s="40"/>
+      <c r="AS17" s="40"/>
       <c r="AW17" s="23" t="s">
         <v>93</v>
       </c>
@@ -2838,50 +2994,50 @@
       <c r="BQ17" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="BR17" s="30" t="s">
+      <c r="BR17" s="54" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="18" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="31"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34"/>
-      <c r="S18" s="34"/>
-      <c r="T18" s="34"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="34"/>
-      <c r="W18" s="34"/>
-      <c r="AA18" s="34"/>
-      <c r="AB18" s="34"/>
-      <c r="AC18" s="34"/>
-      <c r="AD18" s="34"/>
-      <c r="AE18" s="34"/>
-      <c r="AF18" s="34"/>
-      <c r="AG18" s="34"/>
-      <c r="AH18" s="34"/>
-      <c r="AI18" s="34"/>
-      <c r="AJ18" s="34"/>
-      <c r="AK18" s="34"/>
-      <c r="AL18" s="34"/>
-      <c r="AM18" s="34"/>
-      <c r="AN18" s="34"/>
-      <c r="AO18" s="34"/>
-      <c r="AP18" s="34"/>
-      <c r="AQ18" s="34"/>
-      <c r="AR18" s="34"/>
-      <c r="AS18" s="34"/>
+      <c r="B18" s="55"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="40"/>
+      <c r="S18" s="40"/>
+      <c r="T18" s="40"/>
+      <c r="U18" s="40"/>
+      <c r="V18" s="40"/>
+      <c r="W18" s="40"/>
+      <c r="AA18" s="40"/>
+      <c r="AB18" s="40"/>
+      <c r="AC18" s="40"/>
+      <c r="AD18" s="40"/>
+      <c r="AE18" s="40"/>
+      <c r="AF18" s="40"/>
+      <c r="AG18" s="40"/>
+      <c r="AH18" s="40"/>
+      <c r="AI18" s="40"/>
+      <c r="AJ18" s="40"/>
+      <c r="AK18" s="40"/>
+      <c r="AL18" s="40"/>
+      <c r="AM18" s="40"/>
+      <c r="AN18" s="40"/>
+      <c r="AO18" s="40"/>
+      <c r="AP18" s="40"/>
+      <c r="AQ18" s="40"/>
+      <c r="AR18" s="40"/>
+      <c r="AS18" s="40"/>
       <c r="AW18" s="23" t="s">
         <v>101</v>
       </c>
@@ -2919,48 +3075,48 @@
       <c r="BQ18" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="BR18" s="31"/>
+      <c r="BR18" s="55"/>
     </row>
     <row r="19" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="31"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="34"/>
-      <c r="V19" s="34"/>
-      <c r="W19" s="34"/>
-      <c r="AA19" s="34"/>
-      <c r="AB19" s="34"/>
-      <c r="AC19" s="34"/>
-      <c r="AD19" s="34"/>
-      <c r="AE19" s="34"/>
-      <c r="AF19" s="34"/>
-      <c r="AG19" s="34"/>
-      <c r="AH19" s="34"/>
-      <c r="AI19" s="34"/>
-      <c r="AJ19" s="34"/>
-      <c r="AK19" s="34"/>
-      <c r="AL19" s="34"/>
-      <c r="AM19" s="34"/>
-      <c r="AN19" s="34"/>
-      <c r="AO19" s="34"/>
-      <c r="AP19" s="34"/>
-      <c r="AQ19" s="34"/>
-      <c r="AR19" s="34"/>
-      <c r="AS19" s="34"/>
+      <c r="B19" s="55"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="40"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="40"/>
+      <c r="S19" s="40"/>
+      <c r="T19" s="40"/>
+      <c r="U19" s="40"/>
+      <c r="V19" s="40"/>
+      <c r="W19" s="40"/>
+      <c r="AA19" s="40"/>
+      <c r="AB19" s="40"/>
+      <c r="AC19" s="40"/>
+      <c r="AD19" s="40"/>
+      <c r="AE19" s="40"/>
+      <c r="AF19" s="40"/>
+      <c r="AG19" s="40"/>
+      <c r="AH19" s="40"/>
+      <c r="AI19" s="40"/>
+      <c r="AJ19" s="40"/>
+      <c r="AK19" s="40"/>
+      <c r="AL19" s="40"/>
+      <c r="AM19" s="40"/>
+      <c r="AN19" s="40"/>
+      <c r="AO19" s="40"/>
+      <c r="AP19" s="40"/>
+      <c r="AQ19" s="40"/>
+      <c r="AR19" s="40"/>
+      <c r="AS19" s="40"/>
       <c r="AW19" s="23" t="s">
         <v>109</v>
       </c>
@@ -2998,48 +3154,48 @@
       <c r="BQ19" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="BR19" s="31"/>
+      <c r="BR19" s="55"/>
     </row>
     <row r="20" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="31"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="34"/>
-      <c r="V20" s="34"/>
-      <c r="W20" s="34"/>
-      <c r="AA20" s="34"/>
-      <c r="AB20" s="34"/>
-      <c r="AC20" s="34"/>
-      <c r="AD20" s="34"/>
-      <c r="AE20" s="34"/>
-      <c r="AF20" s="34"/>
-      <c r="AG20" s="34"/>
-      <c r="AH20" s="34"/>
-      <c r="AI20" s="34"/>
-      <c r="AJ20" s="34"/>
-      <c r="AK20" s="34"/>
-      <c r="AL20" s="34"/>
-      <c r="AM20" s="34"/>
-      <c r="AN20" s="34"/>
-      <c r="AO20" s="34"/>
-      <c r="AP20" s="34"/>
-      <c r="AQ20" s="34"/>
-      <c r="AR20" s="34"/>
-      <c r="AS20" s="34"/>
+      <c r="B20" s="55"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="40"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="40"/>
+      <c r="R20" s="40"/>
+      <c r="S20" s="40"/>
+      <c r="T20" s="40"/>
+      <c r="U20" s="40"/>
+      <c r="V20" s="40"/>
+      <c r="W20" s="40"/>
+      <c r="AA20" s="40"/>
+      <c r="AB20" s="40"/>
+      <c r="AC20" s="40"/>
+      <c r="AD20" s="40"/>
+      <c r="AE20" s="40"/>
+      <c r="AF20" s="40"/>
+      <c r="AG20" s="40"/>
+      <c r="AH20" s="40"/>
+      <c r="AI20" s="40"/>
+      <c r="AJ20" s="40"/>
+      <c r="AK20" s="40"/>
+      <c r="AL20" s="40"/>
+      <c r="AM20" s="40"/>
+      <c r="AN20" s="40"/>
+      <c r="AO20" s="40"/>
+      <c r="AP20" s="40"/>
+      <c r="AQ20" s="40"/>
+      <c r="AR20" s="40"/>
+      <c r="AS20" s="40"/>
       <c r="AW20" s="23" t="s">
         <v>117</v>
       </c>
@@ -3077,48 +3233,48 @@
       <c r="BQ20" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="BR20" s="31"/>
+      <c r="BR20" s="55"/>
     </row>
     <row r="21" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="31"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="34"/>
-      <c r="V21" s="34"/>
-      <c r="W21" s="34"/>
-      <c r="AA21" s="34"/>
-      <c r="AB21" s="34"/>
-      <c r="AC21" s="34"/>
-      <c r="AD21" s="34"/>
-      <c r="AE21" s="34"/>
-      <c r="AF21" s="34"/>
-      <c r="AG21" s="34"/>
-      <c r="AH21" s="34"/>
-      <c r="AI21" s="34"/>
-      <c r="AJ21" s="34"/>
-      <c r="AK21" s="34"/>
-      <c r="AL21" s="34"/>
-      <c r="AM21" s="34"/>
-      <c r="AN21" s="34"/>
-      <c r="AO21" s="34"/>
-      <c r="AP21" s="34"/>
-      <c r="AQ21" s="34"/>
-      <c r="AR21" s="34"/>
-      <c r="AS21" s="34"/>
+      <c r="B21" s="55"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="40"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="40"/>
+      <c r="S21" s="40"/>
+      <c r="T21" s="40"/>
+      <c r="U21" s="40"/>
+      <c r="V21" s="40"/>
+      <c r="W21" s="40"/>
+      <c r="AA21" s="40"/>
+      <c r="AB21" s="40"/>
+      <c r="AC21" s="40"/>
+      <c r="AD21" s="40"/>
+      <c r="AE21" s="40"/>
+      <c r="AF21" s="40"/>
+      <c r="AG21" s="40"/>
+      <c r="AH21" s="40"/>
+      <c r="AI21" s="40"/>
+      <c r="AJ21" s="40"/>
+      <c r="AK21" s="40"/>
+      <c r="AL21" s="40"/>
+      <c r="AM21" s="40"/>
+      <c r="AN21" s="40"/>
+      <c r="AO21" s="40"/>
+      <c r="AP21" s="40"/>
+      <c r="AQ21" s="40"/>
+      <c r="AR21" s="40"/>
+      <c r="AS21" s="40"/>
       <c r="AW21" s="23" t="s">
         <v>125</v>
       </c>
@@ -3156,48 +3312,48 @@
       <c r="BQ21" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="BR21" s="31"/>
+      <c r="BR21" s="55"/>
     </row>
     <row r="22" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="31"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="34"/>
-      <c r="S22" s="34"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="34"/>
-      <c r="V22" s="34"/>
-      <c r="W22" s="34"/>
-      <c r="AA22" s="34"/>
-      <c r="AB22" s="34"/>
-      <c r="AC22" s="34"/>
-      <c r="AD22" s="34"/>
-      <c r="AE22" s="34"/>
-      <c r="AF22" s="34"/>
-      <c r="AG22" s="34"/>
-      <c r="AH22" s="34"/>
-      <c r="AI22" s="34"/>
-      <c r="AJ22" s="34"/>
-      <c r="AK22" s="34"/>
-      <c r="AL22" s="34"/>
-      <c r="AM22" s="34"/>
-      <c r="AN22" s="34"/>
-      <c r="AO22" s="34"/>
-      <c r="AP22" s="34"/>
-      <c r="AQ22" s="34"/>
-      <c r="AR22" s="34"/>
-      <c r="AS22" s="34"/>
+      <c r="B22" s="55"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="40"/>
+      <c r="P22" s="40"/>
+      <c r="Q22" s="40"/>
+      <c r="R22" s="40"/>
+      <c r="S22" s="40"/>
+      <c r="T22" s="40"/>
+      <c r="U22" s="40"/>
+      <c r="V22" s="40"/>
+      <c r="W22" s="40"/>
+      <c r="AA22" s="40"/>
+      <c r="AB22" s="40"/>
+      <c r="AC22" s="40"/>
+      <c r="AD22" s="40"/>
+      <c r="AE22" s="40"/>
+      <c r="AF22" s="40"/>
+      <c r="AG22" s="40"/>
+      <c r="AH22" s="40"/>
+      <c r="AI22" s="40"/>
+      <c r="AJ22" s="40"/>
+      <c r="AK22" s="40"/>
+      <c r="AL22" s="40"/>
+      <c r="AM22" s="40"/>
+      <c r="AN22" s="40"/>
+      <c r="AO22" s="40"/>
+      <c r="AP22" s="40"/>
+      <c r="AQ22" s="40"/>
+      <c r="AR22" s="40"/>
+      <c r="AS22" s="40"/>
       <c r="AW22" s="23" t="s">
         <v>133</v>
       </c>
@@ -3235,48 +3391,48 @@
       <c r="BQ22" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="BR22" s="31"/>
+      <c r="BR22" s="55"/>
     </row>
     <row r="23" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="31"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="34"/>
-      <c r="S23" s="34"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="34"/>
-      <c r="V23" s="34"/>
-      <c r="W23" s="34"/>
-      <c r="AA23" s="34"/>
-      <c r="AB23" s="34"/>
-      <c r="AC23" s="34"/>
-      <c r="AD23" s="34"/>
-      <c r="AE23" s="34"/>
-      <c r="AF23" s="34"/>
-      <c r="AG23" s="34"/>
-      <c r="AH23" s="34"/>
-      <c r="AI23" s="34"/>
-      <c r="AJ23" s="34"/>
-      <c r="AK23" s="34"/>
-      <c r="AL23" s="34"/>
-      <c r="AM23" s="34"/>
-      <c r="AN23" s="34"/>
-      <c r="AO23" s="34"/>
-      <c r="AP23" s="34"/>
-      <c r="AQ23" s="34"/>
-      <c r="AR23" s="34"/>
-      <c r="AS23" s="34"/>
+      <c r="B23" s="55"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="40"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="40"/>
+      <c r="P23" s="40"/>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="40"/>
+      <c r="S23" s="40"/>
+      <c r="T23" s="40"/>
+      <c r="U23" s="40"/>
+      <c r="V23" s="40"/>
+      <c r="W23" s="40"/>
+      <c r="AA23" s="40"/>
+      <c r="AB23" s="40"/>
+      <c r="AC23" s="40"/>
+      <c r="AD23" s="40"/>
+      <c r="AE23" s="40"/>
+      <c r="AF23" s="40"/>
+      <c r="AG23" s="40"/>
+      <c r="AH23" s="40"/>
+      <c r="AI23" s="40"/>
+      <c r="AJ23" s="40"/>
+      <c r="AK23" s="40"/>
+      <c r="AL23" s="40"/>
+      <c r="AM23" s="40"/>
+      <c r="AN23" s="40"/>
+      <c r="AO23" s="40"/>
+      <c r="AP23" s="40"/>
+      <c r="AQ23" s="40"/>
+      <c r="AR23" s="40"/>
+      <c r="AS23" s="40"/>
       <c r="AW23" s="23" t="s">
         <v>141</v>
       </c>
@@ -3314,48 +3470,48 @@
       <c r="BQ23" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="BR23" s="31"/>
+      <c r="BR23" s="55"/>
     </row>
     <row r="24" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="31"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="34"/>
-      <c r="S24" s="34"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="34"/>
-      <c r="V24" s="34"/>
-      <c r="W24" s="34"/>
-      <c r="AA24" s="34"/>
-      <c r="AB24" s="34"/>
-      <c r="AC24" s="34"/>
-      <c r="AD24" s="34"/>
-      <c r="AE24" s="34"/>
-      <c r="AF24" s="34"/>
-      <c r="AG24" s="34"/>
-      <c r="AH24" s="34"/>
-      <c r="AI24" s="34"/>
-      <c r="AJ24" s="34"/>
-      <c r="AK24" s="34"/>
-      <c r="AL24" s="34"/>
-      <c r="AM24" s="34"/>
-      <c r="AN24" s="34"/>
-      <c r="AO24" s="34"/>
-      <c r="AP24" s="34"/>
-      <c r="AQ24" s="34"/>
-      <c r="AR24" s="34"/>
-      <c r="AS24" s="34"/>
+      <c r="B24" s="55"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
+      <c r="S24" s="40"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="40"/>
+      <c r="V24" s="40"/>
+      <c r="W24" s="40"/>
+      <c r="AA24" s="40"/>
+      <c r="AB24" s="40"/>
+      <c r="AC24" s="40"/>
+      <c r="AD24" s="40"/>
+      <c r="AE24" s="40"/>
+      <c r="AF24" s="40"/>
+      <c r="AG24" s="40"/>
+      <c r="AH24" s="40"/>
+      <c r="AI24" s="40"/>
+      <c r="AJ24" s="40"/>
+      <c r="AK24" s="40"/>
+      <c r="AL24" s="40"/>
+      <c r="AM24" s="40"/>
+      <c r="AN24" s="40"/>
+      <c r="AO24" s="40"/>
+      <c r="AP24" s="40"/>
+      <c r="AQ24" s="40"/>
+      <c r="AR24" s="40"/>
+      <c r="AS24" s="40"/>
       <c r="AW24" s="23" t="s">
         <v>149</v>
       </c>
@@ -3393,48 +3549,48 @@
       <c r="BQ24" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="BR24" s="31"/>
+      <c r="BR24" s="55"/>
     </row>
     <row r="25" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="31"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="34"/>
-      <c r="O25" s="34"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="34"/>
-      <c r="R25" s="34"/>
-      <c r="S25" s="34"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="34"/>
-      <c r="V25" s="34"/>
-      <c r="W25" s="34"/>
-      <c r="AA25" s="34"/>
-      <c r="AB25" s="34"/>
-      <c r="AC25" s="34"/>
-      <c r="AD25" s="34"/>
-      <c r="AE25" s="34"/>
-      <c r="AF25" s="34"/>
-      <c r="AG25" s="34"/>
-      <c r="AH25" s="34"/>
-      <c r="AI25" s="34"/>
-      <c r="AJ25" s="34"/>
-      <c r="AK25" s="34"/>
-      <c r="AL25" s="34"/>
-      <c r="AM25" s="34"/>
-      <c r="AN25" s="34"/>
-      <c r="AO25" s="34"/>
-      <c r="AP25" s="34"/>
-      <c r="AQ25" s="34"/>
-      <c r="AR25" s="34"/>
-      <c r="AS25" s="34"/>
+      <c r="B25" s="55"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="40"/>
+      <c r="M25" s="40"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="40"/>
+      <c r="P25" s="40"/>
+      <c r="Q25" s="40"/>
+      <c r="R25" s="40"/>
+      <c r="S25" s="40"/>
+      <c r="T25" s="40"/>
+      <c r="U25" s="40"/>
+      <c r="V25" s="40"/>
+      <c r="W25" s="40"/>
+      <c r="AA25" s="40"/>
+      <c r="AB25" s="40"/>
+      <c r="AC25" s="40"/>
+      <c r="AD25" s="40"/>
+      <c r="AE25" s="40"/>
+      <c r="AF25" s="40"/>
+      <c r="AG25" s="40"/>
+      <c r="AH25" s="40"/>
+      <c r="AI25" s="40"/>
+      <c r="AJ25" s="40"/>
+      <c r="AK25" s="40"/>
+      <c r="AL25" s="40"/>
+      <c r="AM25" s="40"/>
+      <c r="AN25" s="40"/>
+      <c r="AO25" s="40"/>
+      <c r="AP25" s="40"/>
+      <c r="AQ25" s="40"/>
+      <c r="AR25" s="40"/>
+      <c r="AS25" s="40"/>
       <c r="AW25" s="23" t="s">
         <v>226</v>
       </c>
@@ -3472,48 +3628,48 @@
       <c r="BQ25" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="BR25" s="31"/>
+      <c r="BR25" s="55"/>
     </row>
     <row r="26" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="31"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="34"/>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="34"/>
-      <c r="R26" s="34"/>
-      <c r="S26" s="34"/>
-      <c r="T26" s="34"/>
-      <c r="U26" s="34"/>
-      <c r="V26" s="34"/>
-      <c r="W26" s="34"/>
-      <c r="AA26" s="34"/>
-      <c r="AB26" s="34"/>
-      <c r="AC26" s="34"/>
-      <c r="AD26" s="34"/>
-      <c r="AE26" s="34"/>
-      <c r="AF26" s="34"/>
-      <c r="AG26" s="34"/>
-      <c r="AH26" s="34"/>
-      <c r="AI26" s="34"/>
-      <c r="AJ26" s="34"/>
-      <c r="AK26" s="34"/>
-      <c r="AL26" s="34"/>
-      <c r="AM26" s="34"/>
-      <c r="AN26" s="34"/>
-      <c r="AO26" s="34"/>
-      <c r="AP26" s="34"/>
-      <c r="AQ26" s="34"/>
-      <c r="AR26" s="34"/>
-      <c r="AS26" s="34"/>
+      <c r="B26" s="55"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="40"/>
+      <c r="M26" s="40"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="40"/>
+      <c r="P26" s="40"/>
+      <c r="Q26" s="40"/>
+      <c r="R26" s="40"/>
+      <c r="S26" s="40"/>
+      <c r="T26" s="40"/>
+      <c r="U26" s="40"/>
+      <c r="V26" s="40"/>
+      <c r="W26" s="40"/>
+      <c r="AA26" s="40"/>
+      <c r="AB26" s="40"/>
+      <c r="AC26" s="40"/>
+      <c r="AD26" s="40"/>
+      <c r="AE26" s="40"/>
+      <c r="AF26" s="40"/>
+      <c r="AG26" s="40"/>
+      <c r="AH26" s="40"/>
+      <c r="AI26" s="40"/>
+      <c r="AJ26" s="40"/>
+      <c r="AK26" s="40"/>
+      <c r="AL26" s="40"/>
+      <c r="AM26" s="40"/>
+      <c r="AN26" s="40"/>
+      <c r="AO26" s="40"/>
+      <c r="AP26" s="40"/>
+      <c r="AQ26" s="40"/>
+      <c r="AR26" s="40"/>
+      <c r="AS26" s="40"/>
       <c r="AW26" s="23" t="s">
         <v>161</v>
       </c>
@@ -3551,246 +3707,324 @@
       <c r="BQ26" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="BR26" s="31"/>
+      <c r="BR26" s="55"/>
     </row>
     <row r="27" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="31"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
-      <c r="O27" s="34"/>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="34"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="34"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="34"/>
-      <c r="V27" s="34"/>
-      <c r="W27" s="34"/>
-      <c r="AA27" s="34"/>
-      <c r="AB27" s="34"/>
-      <c r="AC27" s="34"/>
-      <c r="AD27" s="34"/>
-      <c r="AE27" s="34"/>
-      <c r="AF27" s="34"/>
-      <c r="AG27" s="34"/>
-      <c r="AH27" s="34"/>
-      <c r="AI27" s="34"/>
-      <c r="AJ27" s="34"/>
-      <c r="AK27" s="34"/>
-      <c r="AL27" s="34"/>
-      <c r="AM27" s="34"/>
-      <c r="AN27" s="34"/>
-      <c r="AO27" s="34"/>
-      <c r="AP27" s="34"/>
-      <c r="AQ27" s="34"/>
-      <c r="AR27" s="34"/>
-      <c r="AS27" s="34"/>
-      <c r="AW27" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="AX27" s="19"/>
-      <c r="AY27" s="19"/>
-      <c r="AZ27" s="19"/>
-      <c r="BA27" s="19"/>
-      <c r="BB27" s="19"/>
-      <c r="BC27" s="19"/>
-      <c r="BD27" s="19"/>
-      <c r="BE27" s="19"/>
-      <c r="BF27" s="19"/>
-      <c r="BG27" s="19"/>
-      <c r="BH27" s="19"/>
-      <c r="BI27" s="19"/>
-      <c r="BJ27" s="19"/>
-      <c r="BK27" s="19"/>
-      <c r="BL27" s="19"/>
-      <c r="BM27" s="19"/>
-      <c r="BN27" s="19"/>
-      <c r="BO27" s="19"/>
-      <c r="BP27" s="19"/>
-      <c r="BQ27" s="20"/>
-      <c r="BR27" s="31"/>
+      <c r="B27" s="55"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="40"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="40"/>
+      <c r="S27" s="40"/>
+      <c r="T27" s="40"/>
+      <c r="U27" s="40"/>
+      <c r="V27" s="40"/>
+      <c r="W27" s="40"/>
+      <c r="AA27" s="40"/>
+      <c r="AB27" s="40"/>
+      <c r="AC27" s="40"/>
+      <c r="AD27" s="40"/>
+      <c r="AE27" s="40"/>
+      <c r="AF27" s="40"/>
+      <c r="AG27" s="40"/>
+      <c r="AH27" s="40"/>
+      <c r="AI27" s="40"/>
+      <c r="AJ27" s="40"/>
+      <c r="AK27" s="40"/>
+      <c r="AL27" s="40"/>
+      <c r="AM27" s="40"/>
+      <c r="AN27" s="40"/>
+      <c r="AO27" s="40"/>
+      <c r="AP27" s="40"/>
+      <c r="AQ27" s="40"/>
+      <c r="AR27" s="40"/>
+      <c r="AS27" s="40"/>
+      <c r="AW27" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="AX27" s="25"/>
+      <c r="AY27" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="AZ27" s="24"/>
+      <c r="BA27" s="24"/>
+      <c r="BB27" s="25"/>
+      <c r="BC27" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="BD27" s="24"/>
+      <c r="BE27" s="25"/>
+      <c r="BF27" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="BG27" s="24"/>
+      <c r="BH27" s="24"/>
+      <c r="BI27" s="24"/>
+      <c r="BJ27" s="24"/>
+      <c r="BK27" s="25"/>
+      <c r="BL27" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="BM27" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="BN27" s="24"/>
+      <c r="BO27" s="25"/>
+      <c r="BP27" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="BQ27" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="BR27" s="55"/>
     </row>
     <row r="28" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="31"/>
-      <c r="K28" s="33" t="s">
+      <c r="B28" s="55"/>
+      <c r="K28" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="AI28" s="33" t="s">
+      <c r="L28" s="40"/>
+      <c r="M28" s="40"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="40"/>
+      <c r="AI28" s="39" t="s">
         <v>170</v>
       </c>
-      <c r="AJ28" s="34"/>
-      <c r="AK28" s="34"/>
-      <c r="AL28" s="34"/>
-      <c r="AM28" s="34"/>
+      <c r="AJ28" s="40"/>
+      <c r="AK28" s="40"/>
+      <c r="AL28" s="40"/>
+      <c r="AM28" s="40"/>
       <c r="AV28" s="6"/>
-      <c r="AW28" s="21"/>
-      <c r="AX28" s="21"/>
-      <c r="AY28" s="21"/>
-      <c r="AZ28" s="21"/>
-      <c r="BA28" s="21"/>
-      <c r="BB28" s="21"/>
-      <c r="BC28" s="21"/>
-      <c r="BD28" s="21"/>
-      <c r="BE28" s="21"/>
-      <c r="BF28" s="21"/>
-      <c r="BG28" s="21"/>
-      <c r="BH28" s="21"/>
-      <c r="BI28" s="21"/>
-      <c r="BJ28" s="21"/>
-      <c r="BK28" s="21"/>
-      <c r="BL28" s="21"/>
-      <c r="BM28" s="21"/>
-      <c r="BN28" s="21"/>
-      <c r="BO28" s="21"/>
-      <c r="BP28" s="21"/>
-      <c r="BQ28" s="22"/>
-      <c r="BR28" s="31"/>
+      <c r="AW28" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="AX28" s="25"/>
+      <c r="AY28" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="AZ28" s="24"/>
+      <c r="BA28" s="24"/>
+      <c r="BB28" s="25"/>
+      <c r="BC28" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="BD28" s="24"/>
+      <c r="BE28" s="25"/>
+      <c r="BF28" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="BG28" s="24"/>
+      <c r="BH28" s="24"/>
+      <c r="BI28" s="24"/>
+      <c r="BJ28" s="24"/>
+      <c r="BK28" s="25"/>
+      <c r="BL28" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="BM28" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="BN28" s="24"/>
+      <c r="BO28" s="25"/>
+      <c r="BP28" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="BQ28" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="BR28" s="55"/>
     </row>
     <row r="29" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="32"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
-      <c r="O29" s="34"/>
-      <c r="AI29" s="34"/>
-      <c r="AJ29" s="34"/>
-      <c r="AK29" s="34"/>
-      <c r="AL29" s="34"/>
-      <c r="AM29" s="34"/>
-      <c r="AW29" s="21"/>
-      <c r="AX29" s="21"/>
-      <c r="AY29" s="21"/>
-      <c r="AZ29" s="21"/>
-      <c r="BA29" s="21"/>
-      <c r="BB29" s="21"/>
-      <c r="BC29" s="21"/>
-      <c r="BD29" s="21"/>
-      <c r="BE29" s="21"/>
-      <c r="BF29" s="21"/>
-      <c r="BG29" s="21"/>
-      <c r="BH29" s="21"/>
-      <c r="BI29" s="21"/>
-      <c r="BJ29" s="21"/>
-      <c r="BK29" s="21"/>
-      <c r="BL29" s="21"/>
-      <c r="BM29" s="21"/>
-      <c r="BN29" s="21"/>
-      <c r="BO29" s="21"/>
-      <c r="BP29" s="21"/>
-      <c r="BQ29" s="22"/>
-      <c r="BR29" s="32"/>
+      <c r="B29" s="56"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="AI29" s="40"/>
+      <c r="AJ29" s="40"/>
+      <c r="AK29" s="40"/>
+      <c r="AL29" s="40"/>
+      <c r="AM29" s="40"/>
+      <c r="AW29" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="AX29" s="25"/>
+      <c r="AY29" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="AZ29" s="24"/>
+      <c r="BA29" s="24"/>
+      <c r="BB29" s="25"/>
+      <c r="BC29" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="BD29" s="24"/>
+      <c r="BE29" s="25"/>
+      <c r="BF29" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="BG29" s="24"/>
+      <c r="BH29" s="24"/>
+      <c r="BI29" s="24"/>
+      <c r="BJ29" s="24"/>
+      <c r="BK29" s="25"/>
+      <c r="BL29" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="BM29" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="BN29" s="24"/>
+      <c r="BO29" s="25"/>
+      <c r="BP29" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="BQ29" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="BR29" s="56"/>
     </row>
     <row r="30" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="54" t="s">
         <v>171</v>
       </c>
-      <c r="AW30" s="21"/>
-      <c r="AX30" s="21"/>
-      <c r="AY30" s="21"/>
-      <c r="AZ30" s="21"/>
-      <c r="BA30" s="21"/>
-      <c r="BB30" s="21"/>
-      <c r="BC30" s="21"/>
-      <c r="BD30" s="21"/>
-      <c r="BE30" s="21"/>
-      <c r="BF30" s="21"/>
-      <c r="BG30" s="21"/>
-      <c r="BH30" s="21"/>
-      <c r="BI30" s="21"/>
-      <c r="BJ30" s="21"/>
-      <c r="BK30" s="21"/>
-      <c r="BL30" s="21"/>
-      <c r="BM30" s="21"/>
-      <c r="BN30" s="21"/>
-      <c r="BO30" s="21"/>
-      <c r="BP30" s="21"/>
-      <c r="BQ30" s="22"/>
-      <c r="BR30" s="30" t="s">
+      <c r="AW30" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="AX30" s="25"/>
+      <c r="AY30" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="AZ30" s="24"/>
+      <c r="BA30" s="24"/>
+      <c r="BB30" s="25"/>
+      <c r="BC30" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="BD30" s="24"/>
+      <c r="BE30" s="25"/>
+      <c r="BF30" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="BG30" s="24"/>
+      <c r="BH30" s="24"/>
+      <c r="BI30" s="24"/>
+      <c r="BJ30" s="24"/>
+      <c r="BK30" s="25"/>
+      <c r="BL30" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="BM30" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="BN30" s="24"/>
+      <c r="BO30" s="25"/>
+      <c r="BP30" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="BQ30" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="BR30" s="54" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="31" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="31"/>
-      <c r="AW31" s="21"/>
-      <c r="AX31" s="21"/>
-      <c r="AY31" s="21"/>
-      <c r="AZ31" s="21"/>
-      <c r="BA31" s="21"/>
-      <c r="BB31" s="21"/>
-      <c r="BC31" s="21"/>
-      <c r="BD31" s="21"/>
-      <c r="BE31" s="21"/>
-      <c r="BF31" s="21"/>
-      <c r="BG31" s="21"/>
-      <c r="BH31" s="21"/>
-      <c r="BI31" s="21"/>
-      <c r="BJ31" s="21"/>
-      <c r="BK31" s="21"/>
-      <c r="BL31" s="21"/>
-      <c r="BM31" s="21"/>
-      <c r="BN31" s="21"/>
-      <c r="BO31" s="21"/>
-      <c r="BP31" s="21"/>
-      <c r="BQ31" s="22"/>
-      <c r="BR31" s="31"/>
+      <c r="B31" s="55"/>
+      <c r="AW31" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="AX31" s="25"/>
+      <c r="AY31" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="AZ31" s="24"/>
+      <c r="BA31" s="24"/>
+      <c r="BB31" s="25"/>
+      <c r="BC31" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="BD31" s="24"/>
+      <c r="BE31" s="25"/>
+      <c r="BF31" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="BG31" s="24"/>
+      <c r="BH31" s="24"/>
+      <c r="BI31" s="24"/>
+      <c r="BJ31" s="24"/>
+      <c r="BK31" s="25"/>
+      <c r="BL31" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="BM31" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="BN31" s="24"/>
+      <c r="BO31" s="25"/>
+      <c r="BP31" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="BQ31" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="BR31" s="55"/>
     </row>
     <row r="32" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="31"/>
-      <c r="E32" s="33" t="s">
+      <c r="B32" s="55"/>
+      <c r="E32" s="39" t="s">
         <v>173</v>
       </c>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="34"/>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="34"/>
-      <c r="R32" s="34"/>
-      <c r="S32" s="34"/>
-      <c r="T32" s="34"/>
-      <c r="U32" s="34"/>
-      <c r="V32" s="34"/>
-      <c r="W32" s="34"/>
-      <c r="AA32" s="33" t="s">
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="40"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="40"/>
+      <c r="L32" s="40"/>
+      <c r="M32" s="40"/>
+      <c r="N32" s="40"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="40"/>
+      <c r="S32" s="40"/>
+      <c r="T32" s="40"/>
+      <c r="U32" s="40"/>
+      <c r="V32" s="40"/>
+      <c r="W32" s="40"/>
+      <c r="AA32" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="AB32" s="34"/>
-      <c r="AC32" s="34"/>
-      <c r="AD32" s="34"/>
-      <c r="AE32" s="34"/>
-      <c r="AF32" s="34"/>
-      <c r="AG32" s="34"/>
-      <c r="AH32" s="34"/>
-      <c r="AI32" s="34"/>
-      <c r="AJ32" s="34"/>
-      <c r="AK32" s="34"/>
-      <c r="AL32" s="34"/>
-      <c r="AM32" s="34"/>
-      <c r="AN32" s="34"/>
-      <c r="AO32" s="34"/>
-      <c r="AP32" s="34"/>
-      <c r="AQ32" s="34"/>
-      <c r="AR32" s="34"/>
-      <c r="AS32" s="34"/>
+      <c r="AB32" s="40"/>
+      <c r="AC32" s="40"/>
+      <c r="AD32" s="40"/>
+      <c r="AE32" s="40"/>
+      <c r="AF32" s="40"/>
+      <c r="AG32" s="40"/>
+      <c r="AH32" s="40"/>
+      <c r="AI32" s="40"/>
+      <c r="AJ32" s="40"/>
+      <c r="AK32" s="40"/>
+      <c r="AL32" s="40"/>
+      <c r="AM32" s="40"/>
+      <c r="AN32" s="40"/>
+      <c r="AO32" s="40"/>
+      <c r="AP32" s="40"/>
+      <c r="AQ32" s="40"/>
+      <c r="AR32" s="40"/>
+      <c r="AS32" s="40"/>
       <c r="AW32" s="9"/>
       <c r="AX32" s="9"/>
       <c r="AY32" s="9"/>
@@ -3812,432 +4046,432 @@
       <c r="BO32" s="9"/>
       <c r="BP32" s="9"/>
       <c r="BQ32" s="9"/>
-      <c r="BR32" s="31"/>
+      <c r="BR32" s="55"/>
     </row>
     <row r="33" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="31"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-      <c r="U33" s="34"/>
-      <c r="V33" s="34"/>
-      <c r="W33" s="34"/>
-      <c r="AA33" s="34"/>
-      <c r="AB33" s="34"/>
-      <c r="AC33" s="34"/>
-      <c r="AD33" s="34"/>
-      <c r="AE33" s="34"/>
-      <c r="AF33" s="34"/>
-      <c r="AG33" s="34"/>
-      <c r="AH33" s="34"/>
-      <c r="AI33" s="34"/>
-      <c r="AJ33" s="34"/>
-      <c r="AK33" s="34"/>
-      <c r="AL33" s="34"/>
-      <c r="AM33" s="34"/>
-      <c r="AN33" s="34"/>
-      <c r="AO33" s="34"/>
-      <c r="AP33" s="34"/>
-      <c r="AQ33" s="34"/>
-      <c r="AR33" s="34"/>
-      <c r="AS33" s="34"/>
-      <c r="AW33" s="74" t="s">
-        <v>237</v>
-      </c>
-      <c r="AX33" s="20"/>
-      <c r="AY33" s="74" t="s">
+      <c r="B33" s="55"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="40"/>
+      <c r="L33" s="40"/>
+      <c r="M33" s="40"/>
+      <c r="N33" s="40"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="40"/>
+      <c r="S33" s="40"/>
+      <c r="T33" s="40"/>
+      <c r="U33" s="40"/>
+      <c r="V33" s="40"/>
+      <c r="W33" s="40"/>
+      <c r="AA33" s="40"/>
+      <c r="AB33" s="40"/>
+      <c r="AC33" s="40"/>
+      <c r="AD33" s="40"/>
+      <c r="AE33" s="40"/>
+      <c r="AF33" s="40"/>
+      <c r="AG33" s="40"/>
+      <c r="AH33" s="40"/>
+      <c r="AI33" s="40"/>
+      <c r="AJ33" s="40"/>
+      <c r="AK33" s="40"/>
+      <c r="AL33" s="40"/>
+      <c r="AM33" s="40"/>
+      <c r="AN33" s="40"/>
+      <c r="AO33" s="40"/>
+      <c r="AP33" s="40"/>
+      <c r="AQ33" s="40"/>
+      <c r="AR33" s="40"/>
+      <c r="AS33" s="40"/>
+      <c r="AW33" s="72" t="s">
+        <v>236</v>
+      </c>
+      <c r="AX33" s="36"/>
+      <c r="AY33" s="72" t="s">
         <v>172</v>
       </c>
-      <c r="AZ33" s="19"/>
-      <c r="BA33" s="19"/>
-      <c r="BB33" s="19"/>
-      <c r="BC33" s="19"/>
-      <c r="BD33" s="19"/>
-      <c r="BE33" s="19"/>
-      <c r="BF33" s="19"/>
-      <c r="BG33" s="19"/>
-      <c r="BH33" s="19"/>
-      <c r="BI33" s="19"/>
-      <c r="BJ33" s="19"/>
-      <c r="BK33" s="19"/>
-      <c r="BL33" s="19"/>
-      <c r="BM33" s="19"/>
-      <c r="BN33" s="19"/>
-      <c r="BO33" s="19"/>
-      <c r="BP33" s="19"/>
-      <c r="BQ33" s="20"/>
-      <c r="BR33" s="31"/>
+      <c r="AZ33" s="35"/>
+      <c r="BA33" s="35"/>
+      <c r="BB33" s="35"/>
+      <c r="BC33" s="35"/>
+      <c r="BD33" s="35"/>
+      <c r="BE33" s="35"/>
+      <c r="BF33" s="35"/>
+      <c r="BG33" s="35"/>
+      <c r="BH33" s="35"/>
+      <c r="BI33" s="35"/>
+      <c r="BJ33" s="35"/>
+      <c r="BK33" s="35"/>
+      <c r="BL33" s="35"/>
+      <c r="BM33" s="35"/>
+      <c r="BN33" s="35"/>
+      <c r="BO33" s="35"/>
+      <c r="BP33" s="35"/>
+      <c r="BQ33" s="36"/>
+      <c r="BR33" s="55"/>
     </row>
     <row r="34" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="31"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="34"/>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-      <c r="U34" s="34"/>
-      <c r="V34" s="34"/>
-      <c r="W34" s="34"/>
-      <c r="AA34" s="34"/>
-      <c r="AB34" s="34"/>
-      <c r="AC34" s="34"/>
-      <c r="AD34" s="34"/>
-      <c r="AE34" s="34"/>
-      <c r="AF34" s="34"/>
-      <c r="AG34" s="34"/>
-      <c r="AH34" s="34"/>
-      <c r="AI34" s="34"/>
-      <c r="AJ34" s="34"/>
-      <c r="AK34" s="34"/>
-      <c r="AL34" s="34"/>
-      <c r="AM34" s="34"/>
-      <c r="AN34" s="34"/>
-      <c r="AO34" s="34"/>
-      <c r="AP34" s="34"/>
-      <c r="AQ34" s="34"/>
-      <c r="AR34" s="34"/>
-      <c r="AS34" s="34"/>
-      <c r="AW34" s="26"/>
-      <c r="AX34" s="22"/>
-      <c r="AY34" s="26"/>
-      <c r="AZ34" s="21"/>
-      <c r="BA34" s="21"/>
-      <c r="BB34" s="21"/>
-      <c r="BC34" s="21"/>
-      <c r="BD34" s="21"/>
-      <c r="BE34" s="21"/>
-      <c r="BF34" s="21"/>
-      <c r="BG34" s="21"/>
-      <c r="BH34" s="21"/>
-      <c r="BI34" s="21"/>
-      <c r="BJ34" s="21"/>
-      <c r="BK34" s="21"/>
-      <c r="BL34" s="21"/>
-      <c r="BM34" s="21"/>
-      <c r="BN34" s="21"/>
-      <c r="BO34" s="21"/>
-      <c r="BP34" s="21"/>
-      <c r="BQ34" s="22"/>
-      <c r="BR34" s="31"/>
+      <c r="B34" s="55"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="40"/>
+      <c r="M34" s="40"/>
+      <c r="N34" s="40"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="40"/>
+      <c r="S34" s="40"/>
+      <c r="T34" s="40"/>
+      <c r="U34" s="40"/>
+      <c r="V34" s="40"/>
+      <c r="W34" s="40"/>
+      <c r="AA34" s="40"/>
+      <c r="AB34" s="40"/>
+      <c r="AC34" s="40"/>
+      <c r="AD34" s="40"/>
+      <c r="AE34" s="40"/>
+      <c r="AF34" s="40"/>
+      <c r="AG34" s="40"/>
+      <c r="AH34" s="40"/>
+      <c r="AI34" s="40"/>
+      <c r="AJ34" s="40"/>
+      <c r="AK34" s="40"/>
+      <c r="AL34" s="40"/>
+      <c r="AM34" s="40"/>
+      <c r="AN34" s="40"/>
+      <c r="AO34" s="40"/>
+      <c r="AP34" s="40"/>
+      <c r="AQ34" s="40"/>
+      <c r="AR34" s="40"/>
+      <c r="AS34" s="40"/>
+      <c r="AW34" s="41"/>
+      <c r="AX34" s="38"/>
+      <c r="AY34" s="41"/>
+      <c r="AZ34" s="37"/>
+      <c r="BA34" s="37"/>
+      <c r="BB34" s="37"/>
+      <c r="BC34" s="37"/>
+      <c r="BD34" s="37"/>
+      <c r="BE34" s="37"/>
+      <c r="BF34" s="37"/>
+      <c r="BG34" s="37"/>
+      <c r="BH34" s="37"/>
+      <c r="BI34" s="37"/>
+      <c r="BJ34" s="37"/>
+      <c r="BK34" s="37"/>
+      <c r="BL34" s="37"/>
+      <c r="BM34" s="37"/>
+      <c r="BN34" s="37"/>
+      <c r="BO34" s="37"/>
+      <c r="BP34" s="37"/>
+      <c r="BQ34" s="38"/>
+      <c r="BR34" s="55"/>
     </row>
     <row r="35" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="31"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
-      <c r="S35" s="34"/>
-      <c r="T35" s="34"/>
-      <c r="U35" s="34"/>
-      <c r="V35" s="34"/>
-      <c r="W35" s="34"/>
-      <c r="AA35" s="34"/>
-      <c r="AB35" s="34"/>
-      <c r="AC35" s="34"/>
-      <c r="AD35" s="34"/>
-      <c r="AE35" s="34"/>
-      <c r="AF35" s="34"/>
-      <c r="AG35" s="34"/>
-      <c r="AH35" s="34"/>
-      <c r="AI35" s="34"/>
-      <c r="AJ35" s="34"/>
-      <c r="AK35" s="34"/>
-      <c r="AL35" s="34"/>
-      <c r="AM35" s="34"/>
-      <c r="AN35" s="34"/>
-      <c r="AO35" s="34"/>
-      <c r="AP35" s="34"/>
-      <c r="AQ35" s="34"/>
-      <c r="AR35" s="34"/>
-      <c r="AS35" s="34"/>
-      <c r="AW35" s="26"/>
-      <c r="AX35" s="22"/>
-      <c r="AY35" s="26"/>
-      <c r="AZ35" s="21"/>
-      <c r="BA35" s="21"/>
-      <c r="BB35" s="21"/>
-      <c r="BC35" s="21"/>
-      <c r="BD35" s="21"/>
-      <c r="BE35" s="21"/>
-      <c r="BF35" s="21"/>
-      <c r="BG35" s="21"/>
-      <c r="BH35" s="21"/>
-      <c r="BI35" s="21"/>
-      <c r="BJ35" s="21"/>
-      <c r="BK35" s="21"/>
-      <c r="BL35" s="21"/>
-      <c r="BM35" s="21"/>
-      <c r="BN35" s="21"/>
-      <c r="BO35" s="21"/>
-      <c r="BP35" s="21"/>
-      <c r="BQ35" s="22"/>
-      <c r="BR35" s="31"/>
+      <c r="B35" s="55"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="40"/>
+      <c r="M35" s="40"/>
+      <c r="N35" s="40"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="40"/>
+      <c r="S35" s="40"/>
+      <c r="T35" s="40"/>
+      <c r="U35" s="40"/>
+      <c r="V35" s="40"/>
+      <c r="W35" s="40"/>
+      <c r="AA35" s="40"/>
+      <c r="AB35" s="40"/>
+      <c r="AC35" s="40"/>
+      <c r="AD35" s="40"/>
+      <c r="AE35" s="40"/>
+      <c r="AF35" s="40"/>
+      <c r="AG35" s="40"/>
+      <c r="AH35" s="40"/>
+      <c r="AI35" s="40"/>
+      <c r="AJ35" s="40"/>
+      <c r="AK35" s="40"/>
+      <c r="AL35" s="40"/>
+      <c r="AM35" s="40"/>
+      <c r="AN35" s="40"/>
+      <c r="AO35" s="40"/>
+      <c r="AP35" s="40"/>
+      <c r="AQ35" s="40"/>
+      <c r="AR35" s="40"/>
+      <c r="AS35" s="40"/>
+      <c r="AW35" s="41"/>
+      <c r="AX35" s="38"/>
+      <c r="AY35" s="41"/>
+      <c r="AZ35" s="37"/>
+      <c r="BA35" s="37"/>
+      <c r="BB35" s="37"/>
+      <c r="BC35" s="37"/>
+      <c r="BD35" s="37"/>
+      <c r="BE35" s="37"/>
+      <c r="BF35" s="37"/>
+      <c r="BG35" s="37"/>
+      <c r="BH35" s="37"/>
+      <c r="BI35" s="37"/>
+      <c r="BJ35" s="37"/>
+      <c r="BK35" s="37"/>
+      <c r="BL35" s="37"/>
+      <c r="BM35" s="37"/>
+      <c r="BN35" s="37"/>
+      <c r="BO35" s="37"/>
+      <c r="BP35" s="37"/>
+      <c r="BQ35" s="38"/>
+      <c r="BR35" s="55"/>
     </row>
     <row r="36" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="31"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="34"/>
-      <c r="V36" s="34"/>
-      <c r="W36" s="34"/>
-      <c r="AA36" s="34"/>
-      <c r="AB36" s="34"/>
-      <c r="AC36" s="34"/>
-      <c r="AD36" s="34"/>
-      <c r="AE36" s="34"/>
-      <c r="AF36" s="34"/>
-      <c r="AG36" s="34"/>
-      <c r="AH36" s="34"/>
-      <c r="AI36" s="34"/>
-      <c r="AJ36" s="34"/>
-      <c r="AK36" s="34"/>
-      <c r="AL36" s="34"/>
-      <c r="AM36" s="34"/>
-      <c r="AN36" s="34"/>
-      <c r="AO36" s="34"/>
-      <c r="AP36" s="34"/>
-      <c r="AQ36" s="34"/>
-      <c r="AR36" s="34"/>
-      <c r="AS36" s="34"/>
+      <c r="B36" s="55"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="40"/>
+      <c r="M36" s="40"/>
+      <c r="N36" s="40"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="40"/>
+      <c r="S36" s="40"/>
+      <c r="T36" s="40"/>
+      <c r="U36" s="40"/>
+      <c r="V36" s="40"/>
+      <c r="W36" s="40"/>
+      <c r="AA36" s="40"/>
+      <c r="AB36" s="40"/>
+      <c r="AC36" s="40"/>
+      <c r="AD36" s="40"/>
+      <c r="AE36" s="40"/>
+      <c r="AF36" s="40"/>
+      <c r="AG36" s="40"/>
+      <c r="AH36" s="40"/>
+      <c r="AI36" s="40"/>
+      <c r="AJ36" s="40"/>
+      <c r="AK36" s="40"/>
+      <c r="AL36" s="40"/>
+      <c r="AM36" s="40"/>
+      <c r="AN36" s="40"/>
+      <c r="AO36" s="40"/>
+      <c r="AP36" s="40"/>
+      <c r="AQ36" s="40"/>
+      <c r="AR36" s="40"/>
+      <c r="AS36" s="40"/>
       <c r="AU36" s="6"/>
-      <c r="AW36" s="26"/>
-      <c r="AX36" s="22"/>
-      <c r="AY36" s="26"/>
-      <c r="AZ36" s="21"/>
-      <c r="BA36" s="21"/>
-      <c r="BB36" s="21"/>
-      <c r="BC36" s="21"/>
-      <c r="BD36" s="21"/>
-      <c r="BE36" s="21"/>
-      <c r="BF36" s="21"/>
-      <c r="BG36" s="21"/>
-      <c r="BH36" s="21"/>
-      <c r="BI36" s="21"/>
-      <c r="BJ36" s="21"/>
-      <c r="BK36" s="21"/>
-      <c r="BL36" s="21"/>
-      <c r="BM36" s="21"/>
-      <c r="BN36" s="21"/>
-      <c r="BO36" s="21"/>
-      <c r="BP36" s="21"/>
-      <c r="BQ36" s="22"/>
-      <c r="BR36" s="31"/>
+      <c r="AW36" s="41"/>
+      <c r="AX36" s="38"/>
+      <c r="AY36" s="41"/>
+      <c r="AZ36" s="37"/>
+      <c r="BA36" s="37"/>
+      <c r="BB36" s="37"/>
+      <c r="BC36" s="37"/>
+      <c r="BD36" s="37"/>
+      <c r="BE36" s="37"/>
+      <c r="BF36" s="37"/>
+      <c r="BG36" s="37"/>
+      <c r="BH36" s="37"/>
+      <c r="BI36" s="37"/>
+      <c r="BJ36" s="37"/>
+      <c r="BK36" s="37"/>
+      <c r="BL36" s="37"/>
+      <c r="BM36" s="37"/>
+      <c r="BN36" s="37"/>
+      <c r="BO36" s="37"/>
+      <c r="BP36" s="37"/>
+      <c r="BQ36" s="38"/>
+      <c r="BR36" s="55"/>
     </row>
     <row r="37" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="31"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="34"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="34"/>
-      <c r="T37" s="34"/>
-      <c r="U37" s="34"/>
-      <c r="V37" s="34"/>
-      <c r="W37" s="34"/>
-      <c r="AA37" s="34"/>
-      <c r="AB37" s="34"/>
-      <c r="AC37" s="34"/>
-      <c r="AD37" s="34"/>
-      <c r="AE37" s="34"/>
-      <c r="AF37" s="34"/>
-      <c r="AG37" s="34"/>
-      <c r="AH37" s="34"/>
-      <c r="AI37" s="34"/>
-      <c r="AJ37" s="34"/>
-      <c r="AK37" s="34"/>
-      <c r="AL37" s="34"/>
-      <c r="AM37" s="34"/>
-      <c r="AN37" s="34"/>
-      <c r="AO37" s="34"/>
-      <c r="AP37" s="34"/>
-      <c r="AQ37" s="34"/>
-      <c r="AR37" s="34"/>
-      <c r="AS37" s="34"/>
+      <c r="B37" s="55"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="40"/>
+      <c r="M37" s="40"/>
+      <c r="N37" s="40"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="40"/>
+      <c r="S37" s="40"/>
+      <c r="T37" s="40"/>
+      <c r="U37" s="40"/>
+      <c r="V37" s="40"/>
+      <c r="W37" s="40"/>
+      <c r="AA37" s="40"/>
+      <c r="AB37" s="40"/>
+      <c r="AC37" s="40"/>
+      <c r="AD37" s="40"/>
+      <c r="AE37" s="40"/>
+      <c r="AF37" s="40"/>
+      <c r="AG37" s="40"/>
+      <c r="AH37" s="40"/>
+      <c r="AI37" s="40"/>
+      <c r="AJ37" s="40"/>
+      <c r="AK37" s="40"/>
+      <c r="AL37" s="40"/>
+      <c r="AM37" s="40"/>
+      <c r="AN37" s="40"/>
+      <c r="AO37" s="40"/>
+      <c r="AP37" s="40"/>
+      <c r="AQ37" s="40"/>
+      <c r="AR37" s="40"/>
+      <c r="AS37" s="40"/>
       <c r="AU37" s="14"/>
-      <c r="AW37" s="26"/>
-      <c r="AX37" s="22"/>
-      <c r="AY37" s="26"/>
-      <c r="AZ37" s="21"/>
-      <c r="BA37" s="21"/>
-      <c r="BB37" s="21"/>
-      <c r="BC37" s="21"/>
-      <c r="BD37" s="21"/>
-      <c r="BE37" s="21"/>
-      <c r="BF37" s="21"/>
-      <c r="BG37" s="21"/>
-      <c r="BH37" s="21"/>
-      <c r="BI37" s="21"/>
-      <c r="BJ37" s="21"/>
-      <c r="BK37" s="21"/>
-      <c r="BL37" s="21"/>
-      <c r="BM37" s="21"/>
-      <c r="BN37" s="21"/>
-      <c r="BO37" s="21"/>
-      <c r="BP37" s="21"/>
-      <c r="BQ37" s="22"/>
-      <c r="BR37" s="31"/>
+      <c r="AW37" s="41"/>
+      <c r="AX37" s="38"/>
+      <c r="AY37" s="41"/>
+      <c r="AZ37" s="37"/>
+      <c r="BA37" s="37"/>
+      <c r="BB37" s="37"/>
+      <c r="BC37" s="37"/>
+      <c r="BD37" s="37"/>
+      <c r="BE37" s="37"/>
+      <c r="BF37" s="37"/>
+      <c r="BG37" s="37"/>
+      <c r="BH37" s="37"/>
+      <c r="BI37" s="37"/>
+      <c r="BJ37" s="37"/>
+      <c r="BK37" s="37"/>
+      <c r="BL37" s="37"/>
+      <c r="BM37" s="37"/>
+      <c r="BN37" s="37"/>
+      <c r="BO37" s="37"/>
+      <c r="BP37" s="37"/>
+      <c r="BQ37" s="38"/>
+      <c r="BR37" s="55"/>
     </row>
     <row r="38" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="31"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="34"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="34"/>
-      <c r="N38" s="34"/>
-      <c r="O38" s="34"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="34"/>
-      <c r="R38" s="34"/>
-      <c r="S38" s="34"/>
-      <c r="T38" s="34"/>
-      <c r="U38" s="34"/>
-      <c r="V38" s="34"/>
-      <c r="W38" s="34"/>
-      <c r="AA38" s="34"/>
-      <c r="AB38" s="34"/>
-      <c r="AC38" s="34"/>
-      <c r="AD38" s="34"/>
-      <c r="AE38" s="34"/>
-      <c r="AF38" s="34"/>
-      <c r="AG38" s="34"/>
-      <c r="AH38" s="34"/>
-      <c r="AI38" s="34"/>
-      <c r="AJ38" s="34"/>
-      <c r="AK38" s="34"/>
-      <c r="AL38" s="34"/>
-      <c r="AM38" s="34"/>
-      <c r="AN38" s="34"/>
-      <c r="AO38" s="34"/>
-      <c r="AP38" s="34"/>
-      <c r="AQ38" s="34"/>
-      <c r="AR38" s="34"/>
-      <c r="AS38" s="34"/>
-      <c r="AW38" s="27"/>
-      <c r="AX38" s="29"/>
-      <c r="AY38" s="27"/>
-      <c r="AZ38" s="28"/>
-      <c r="BA38" s="28"/>
-      <c r="BB38" s="28"/>
-      <c r="BC38" s="28"/>
-      <c r="BD38" s="28"/>
-      <c r="BE38" s="28"/>
-      <c r="BF38" s="28"/>
-      <c r="BG38" s="28"/>
-      <c r="BH38" s="28"/>
-      <c r="BI38" s="28"/>
-      <c r="BJ38" s="28"/>
-      <c r="BK38" s="28"/>
-      <c r="BL38" s="28"/>
-      <c r="BM38" s="28"/>
-      <c r="BN38" s="28"/>
-      <c r="BO38" s="28"/>
-      <c r="BP38" s="28"/>
-      <c r="BQ38" s="29"/>
-      <c r="BR38" s="31"/>
+      <c r="B38" s="55"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="40"/>
+      <c r="K38" s="40"/>
+      <c r="L38" s="40"/>
+      <c r="M38" s="40"/>
+      <c r="N38" s="40"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="40"/>
+      <c r="S38" s="40"/>
+      <c r="T38" s="40"/>
+      <c r="U38" s="40"/>
+      <c r="V38" s="40"/>
+      <c r="W38" s="40"/>
+      <c r="AA38" s="40"/>
+      <c r="AB38" s="40"/>
+      <c r="AC38" s="40"/>
+      <c r="AD38" s="40"/>
+      <c r="AE38" s="40"/>
+      <c r="AF38" s="40"/>
+      <c r="AG38" s="40"/>
+      <c r="AH38" s="40"/>
+      <c r="AI38" s="40"/>
+      <c r="AJ38" s="40"/>
+      <c r="AK38" s="40"/>
+      <c r="AL38" s="40"/>
+      <c r="AM38" s="40"/>
+      <c r="AN38" s="40"/>
+      <c r="AO38" s="40"/>
+      <c r="AP38" s="40"/>
+      <c r="AQ38" s="40"/>
+      <c r="AR38" s="40"/>
+      <c r="AS38" s="40"/>
+      <c r="AW38" s="42"/>
+      <c r="AX38" s="44"/>
+      <c r="AY38" s="42"/>
+      <c r="AZ38" s="43"/>
+      <c r="BA38" s="43"/>
+      <c r="BB38" s="43"/>
+      <c r="BC38" s="43"/>
+      <c r="BD38" s="43"/>
+      <c r="BE38" s="43"/>
+      <c r="BF38" s="43"/>
+      <c r="BG38" s="43"/>
+      <c r="BH38" s="43"/>
+      <c r="BI38" s="43"/>
+      <c r="BJ38" s="43"/>
+      <c r="BK38" s="43"/>
+      <c r="BL38" s="43"/>
+      <c r="BM38" s="43"/>
+      <c r="BN38" s="43"/>
+      <c r="BO38" s="43"/>
+      <c r="BP38" s="43"/>
+      <c r="BQ38" s="44"/>
+      <c r="BR38" s="55"/>
     </row>
     <row r="39" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="31"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="34"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="34"/>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="34"/>
-      <c r="R39" s="34"/>
-      <c r="S39" s="34"/>
-      <c r="T39" s="34"/>
-      <c r="U39" s="34"/>
-      <c r="V39" s="34"/>
-      <c r="W39" s="34"/>
-      <c r="AA39" s="34"/>
-      <c r="AB39" s="34"/>
-      <c r="AC39" s="34"/>
-      <c r="AD39" s="34"/>
-      <c r="AE39" s="34"/>
-      <c r="AF39" s="34"/>
-      <c r="AG39" s="34"/>
-      <c r="AH39" s="34"/>
-      <c r="AI39" s="34"/>
-      <c r="AJ39" s="34"/>
-      <c r="AK39" s="34"/>
-      <c r="AL39" s="34"/>
-      <c r="AM39" s="34"/>
-      <c r="AN39" s="34"/>
-      <c r="AO39" s="34"/>
-      <c r="AP39" s="34"/>
-      <c r="AQ39" s="34"/>
-      <c r="AR39" s="34"/>
-      <c r="AS39" s="34"/>
+      <c r="B39" s="55"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="40"/>
+      <c r="M39" s="40"/>
+      <c r="N39" s="40"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="40"/>
+      <c r="S39" s="40"/>
+      <c r="T39" s="40"/>
+      <c r="U39" s="40"/>
+      <c r="V39" s="40"/>
+      <c r="W39" s="40"/>
+      <c r="AA39" s="40"/>
+      <c r="AB39" s="40"/>
+      <c r="AC39" s="40"/>
+      <c r="AD39" s="40"/>
+      <c r="AE39" s="40"/>
+      <c r="AF39" s="40"/>
+      <c r="AG39" s="40"/>
+      <c r="AH39" s="40"/>
+      <c r="AI39" s="40"/>
+      <c r="AJ39" s="40"/>
+      <c r="AK39" s="40"/>
+      <c r="AL39" s="40"/>
+      <c r="AM39" s="40"/>
+      <c r="AN39" s="40"/>
+      <c r="AO39" s="40"/>
+      <c r="AP39" s="40"/>
+      <c r="AQ39" s="40"/>
+      <c r="AR39" s="40"/>
+      <c r="AS39" s="40"/>
       <c r="AW39" s="14"/>
       <c r="AX39" s="9"/>
       <c r="AY39" s="9"/>
@@ -4259,48 +4493,48 @@
       <c r="BO39" s="9"/>
       <c r="BP39" s="9"/>
       <c r="BQ39" s="9"/>
-      <c r="BR39" s="31"/>
+      <c r="BR39" s="55"/>
     </row>
     <row r="40" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="31"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="34"/>
-      <c r="M40" s="34"/>
-      <c r="N40" s="34"/>
-      <c r="O40" s="34"/>
-      <c r="P40" s="34"/>
-      <c r="Q40" s="34"/>
-      <c r="R40" s="34"/>
-      <c r="S40" s="34"/>
-      <c r="T40" s="34"/>
-      <c r="U40" s="34"/>
-      <c r="V40" s="34"/>
-      <c r="W40" s="34"/>
-      <c r="AA40" s="34"/>
-      <c r="AB40" s="34"/>
-      <c r="AC40" s="34"/>
-      <c r="AD40" s="34"/>
-      <c r="AE40" s="34"/>
-      <c r="AF40" s="34"/>
-      <c r="AG40" s="34"/>
-      <c r="AH40" s="34"/>
-      <c r="AI40" s="34"/>
-      <c r="AJ40" s="34"/>
-      <c r="AK40" s="34"/>
-      <c r="AL40" s="34"/>
-      <c r="AM40" s="34"/>
-      <c r="AN40" s="34"/>
-      <c r="AO40" s="34"/>
-      <c r="AP40" s="34"/>
-      <c r="AQ40" s="34"/>
-      <c r="AR40" s="34"/>
-      <c r="AS40" s="34"/>
+      <c r="B40" s="55"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="40"/>
+      <c r="L40" s="40"/>
+      <c r="M40" s="40"/>
+      <c r="N40" s="40"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="40"/>
+      <c r="S40" s="40"/>
+      <c r="T40" s="40"/>
+      <c r="U40" s="40"/>
+      <c r="V40" s="40"/>
+      <c r="W40" s="40"/>
+      <c r="AA40" s="40"/>
+      <c r="AB40" s="40"/>
+      <c r="AC40" s="40"/>
+      <c r="AD40" s="40"/>
+      <c r="AE40" s="40"/>
+      <c r="AF40" s="40"/>
+      <c r="AG40" s="40"/>
+      <c r="AH40" s="40"/>
+      <c r="AI40" s="40"/>
+      <c r="AJ40" s="40"/>
+      <c r="AK40" s="40"/>
+      <c r="AL40" s="40"/>
+      <c r="AM40" s="40"/>
+      <c r="AN40" s="40"/>
+      <c r="AO40" s="40"/>
+      <c r="AP40" s="40"/>
+      <c r="AQ40" s="40"/>
+      <c r="AR40" s="40"/>
+      <c r="AS40" s="40"/>
       <c r="AW40" s="1" t="s">
         <v>175</v>
       </c>
@@ -4334,48 +4568,48 @@
       </c>
       <c r="BP40" s="24"/>
       <c r="BQ40" s="24"/>
-      <c r="BR40" s="31"/>
+      <c r="BR40" s="55"/>
     </row>
     <row r="41" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="31"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
-      <c r="I41" s="34"/>
-      <c r="J41" s="34"/>
-      <c r="K41" s="34"/>
-      <c r="L41" s="34"/>
-      <c r="M41" s="34"/>
-      <c r="N41" s="34"/>
-      <c r="O41" s="34"/>
-      <c r="P41" s="34"/>
-      <c r="Q41" s="34"/>
-      <c r="R41" s="34"/>
-      <c r="S41" s="34"/>
-      <c r="T41" s="34"/>
-      <c r="U41" s="34"/>
-      <c r="V41" s="34"/>
-      <c r="W41" s="34"/>
-      <c r="AA41" s="34"/>
-      <c r="AB41" s="34"/>
-      <c r="AC41" s="34"/>
-      <c r="AD41" s="34"/>
-      <c r="AE41" s="34"/>
-      <c r="AF41" s="34"/>
-      <c r="AG41" s="34"/>
-      <c r="AH41" s="34"/>
-      <c r="AI41" s="34"/>
-      <c r="AJ41" s="34"/>
-      <c r="AK41" s="34"/>
-      <c r="AL41" s="34"/>
-      <c r="AM41" s="34"/>
-      <c r="AN41" s="34"/>
-      <c r="AO41" s="34"/>
-      <c r="AP41" s="34"/>
-      <c r="AQ41" s="34"/>
-      <c r="AR41" s="34"/>
-      <c r="AS41" s="34"/>
+      <c r="B41" s="55"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="40"/>
+      <c r="S41" s="40"/>
+      <c r="T41" s="40"/>
+      <c r="U41" s="40"/>
+      <c r="V41" s="40"/>
+      <c r="W41" s="40"/>
+      <c r="AA41" s="40"/>
+      <c r="AB41" s="40"/>
+      <c r="AC41" s="40"/>
+      <c r="AD41" s="40"/>
+      <c r="AE41" s="40"/>
+      <c r="AF41" s="40"/>
+      <c r="AG41" s="40"/>
+      <c r="AH41" s="40"/>
+      <c r="AI41" s="40"/>
+      <c r="AJ41" s="40"/>
+      <c r="AK41" s="40"/>
+      <c r="AL41" s="40"/>
+      <c r="AM41" s="40"/>
+      <c r="AN41" s="40"/>
+      <c r="AO41" s="40"/>
+      <c r="AP41" s="40"/>
+      <c r="AQ41" s="40"/>
+      <c r="AR41" s="40"/>
+      <c r="AS41" s="40"/>
       <c r="AW41" s="5" t="s">
         <v>181</v>
       </c>
@@ -4409,48 +4643,48 @@
       </c>
       <c r="BP41" s="17"/>
       <c r="BQ41" s="17"/>
-      <c r="BR41" s="31"/>
+      <c r="BR41" s="55"/>
     </row>
     <row r="42" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="31"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
-      <c r="M42" s="34"/>
-      <c r="N42" s="34"/>
-      <c r="O42" s="34"/>
-      <c r="P42" s="34"/>
-      <c r="Q42" s="34"/>
-      <c r="R42" s="34"/>
-      <c r="S42" s="34"/>
-      <c r="T42" s="34"/>
-      <c r="U42" s="34"/>
-      <c r="V42" s="34"/>
-      <c r="W42" s="34"/>
-      <c r="AA42" s="34"/>
-      <c r="AB42" s="34"/>
-      <c r="AC42" s="34"/>
-      <c r="AD42" s="34"/>
-      <c r="AE42" s="34"/>
-      <c r="AF42" s="34"/>
-      <c r="AG42" s="34"/>
-      <c r="AH42" s="34"/>
-      <c r="AI42" s="34"/>
-      <c r="AJ42" s="34"/>
-      <c r="AK42" s="34"/>
-      <c r="AL42" s="34"/>
-      <c r="AM42" s="34"/>
-      <c r="AN42" s="34"/>
-      <c r="AO42" s="34"/>
-      <c r="AP42" s="34"/>
-      <c r="AQ42" s="34"/>
-      <c r="AR42" s="34"/>
-      <c r="AS42" s="34"/>
+      <c r="B42" s="55"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="40"/>
+      <c r="I42" s="40"/>
+      <c r="J42" s="40"/>
+      <c r="K42" s="40"/>
+      <c r="L42" s="40"/>
+      <c r="M42" s="40"/>
+      <c r="N42" s="40"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="40"/>
+      <c r="S42" s="40"/>
+      <c r="T42" s="40"/>
+      <c r="U42" s="40"/>
+      <c r="V42" s="40"/>
+      <c r="W42" s="40"/>
+      <c r="AA42" s="40"/>
+      <c r="AB42" s="40"/>
+      <c r="AC42" s="40"/>
+      <c r="AD42" s="40"/>
+      <c r="AE42" s="40"/>
+      <c r="AF42" s="40"/>
+      <c r="AG42" s="40"/>
+      <c r="AH42" s="40"/>
+      <c r="AI42" s="40"/>
+      <c r="AJ42" s="40"/>
+      <c r="AK42" s="40"/>
+      <c r="AL42" s="40"/>
+      <c r="AM42" s="40"/>
+      <c r="AN42" s="40"/>
+      <c r="AO42" s="40"/>
+      <c r="AP42" s="40"/>
+      <c r="AQ42" s="40"/>
+      <c r="AR42" s="40"/>
+      <c r="AS42" s="40"/>
       <c r="AW42" s="5" t="s">
         <v>187</v>
       </c>
@@ -4484,48 +4718,48 @@
       </c>
       <c r="BP42" s="24"/>
       <c r="BQ42" s="24"/>
-      <c r="BR42" s="31"/>
+      <c r="BR42" s="55"/>
     </row>
     <row r="43" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="32"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="34"/>
-      <c r="K43" s="34"/>
-      <c r="L43" s="34"/>
-      <c r="M43" s="34"/>
-      <c r="N43" s="34"/>
-      <c r="O43" s="34"/>
-      <c r="P43" s="34"/>
-      <c r="Q43" s="34"/>
-      <c r="R43" s="34"/>
-      <c r="S43" s="34"/>
-      <c r="T43" s="34"/>
-      <c r="U43" s="34"/>
-      <c r="V43" s="34"/>
-      <c r="W43" s="34"/>
-      <c r="AA43" s="34"/>
-      <c r="AB43" s="34"/>
-      <c r="AC43" s="34"/>
-      <c r="AD43" s="34"/>
-      <c r="AE43" s="34"/>
-      <c r="AF43" s="34"/>
-      <c r="AG43" s="34"/>
-      <c r="AH43" s="34"/>
-      <c r="AI43" s="34"/>
-      <c r="AJ43" s="34"/>
-      <c r="AK43" s="34"/>
-      <c r="AL43" s="34"/>
-      <c r="AM43" s="34"/>
-      <c r="AN43" s="34"/>
-      <c r="AO43" s="34"/>
-      <c r="AP43" s="34"/>
-      <c r="AQ43" s="34"/>
-      <c r="AR43" s="34"/>
-      <c r="AS43" s="34"/>
+      <c r="B43" s="56"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="40"/>
+      <c r="I43" s="40"/>
+      <c r="J43" s="40"/>
+      <c r="K43" s="40"/>
+      <c r="L43" s="40"/>
+      <c r="M43" s="40"/>
+      <c r="N43" s="40"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="40"/>
+      <c r="S43" s="40"/>
+      <c r="T43" s="40"/>
+      <c r="U43" s="40"/>
+      <c r="V43" s="40"/>
+      <c r="W43" s="40"/>
+      <c r="AA43" s="40"/>
+      <c r="AB43" s="40"/>
+      <c r="AC43" s="40"/>
+      <c r="AD43" s="40"/>
+      <c r="AE43" s="40"/>
+      <c r="AF43" s="40"/>
+      <c r="AG43" s="40"/>
+      <c r="AH43" s="40"/>
+      <c r="AI43" s="40"/>
+      <c r="AJ43" s="40"/>
+      <c r="AK43" s="40"/>
+      <c r="AL43" s="40"/>
+      <c r="AM43" s="40"/>
+      <c r="AN43" s="40"/>
+      <c r="AO43" s="40"/>
+      <c r="AP43" s="40"/>
+      <c r="AQ43" s="40"/>
+      <c r="AR43" s="40"/>
+      <c r="AS43" s="40"/>
       <c r="AW43" s="5" t="s">
         <v>193</v>
       </c>
@@ -4559,127 +4793,127 @@
       </c>
       <c r="BP43" s="24"/>
       <c r="BQ43" s="24"/>
-      <c r="BR43" s="32"/>
+      <c r="BR43" s="56"/>
     </row>
     <row r="44" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="30" t="s">
+      <c r="B44" s="54" t="s">
         <v>204</v>
       </c>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
-      <c r="J44" s="34"/>
-      <c r="K44" s="34"/>
-      <c r="L44" s="34"/>
-      <c r="M44" s="34"/>
-      <c r="N44" s="34"/>
-      <c r="O44" s="34"/>
-      <c r="P44" s="34"/>
-      <c r="Q44" s="34"/>
-      <c r="R44" s="34"/>
-      <c r="S44" s="34"/>
-      <c r="T44" s="34"/>
-      <c r="U44" s="34"/>
-      <c r="V44" s="34"/>
-      <c r="W44" s="34"/>
-      <c r="AA44" s="34"/>
-      <c r="AB44" s="34"/>
-      <c r="AC44" s="34"/>
-      <c r="AD44" s="34"/>
-      <c r="AE44" s="34"/>
-      <c r="AF44" s="34"/>
-      <c r="AG44" s="34"/>
-      <c r="AH44" s="34"/>
-      <c r="AI44" s="34"/>
-      <c r="AJ44" s="34"/>
-      <c r="AK44" s="34"/>
-      <c r="AL44" s="34"/>
-      <c r="AM44" s="34"/>
-      <c r="AN44" s="34"/>
-      <c r="AO44" s="34"/>
-      <c r="AP44" s="34"/>
-      <c r="AQ44" s="34"/>
-      <c r="AR44" s="34"/>
-      <c r="AS44" s="34"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="40"/>
+      <c r="J44" s="40"/>
+      <c r="K44" s="40"/>
+      <c r="L44" s="40"/>
+      <c r="M44" s="40"/>
+      <c r="N44" s="40"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="40"/>
+      <c r="S44" s="40"/>
+      <c r="T44" s="40"/>
+      <c r="U44" s="40"/>
+      <c r="V44" s="40"/>
+      <c r="W44" s="40"/>
+      <c r="AA44" s="40"/>
+      <c r="AB44" s="40"/>
+      <c r="AC44" s="40"/>
+      <c r="AD44" s="40"/>
+      <c r="AE44" s="40"/>
+      <c r="AF44" s="40"/>
+      <c r="AG44" s="40"/>
+      <c r="AH44" s="40"/>
+      <c r="AI44" s="40"/>
+      <c r="AJ44" s="40"/>
+      <c r="AK44" s="40"/>
+      <c r="AL44" s="40"/>
+      <c r="AM44" s="40"/>
+      <c r="AN44" s="40"/>
+      <c r="AO44" s="40"/>
+      <c r="AP44" s="40"/>
+      <c r="AQ44" s="40"/>
+      <c r="AR44" s="40"/>
+      <c r="AS44" s="40"/>
       <c r="AW44" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="AX44" s="27" t="s">
+      <c r="AX44" s="42" t="s">
         <v>199</v>
       </c>
-      <c r="AY44" s="28"/>
-      <c r="AZ44" s="29"/>
-      <c r="BA44" s="27" t="s">
+      <c r="AY44" s="43"/>
+      <c r="AZ44" s="44"/>
+      <c r="BA44" s="42" t="s">
         <v>200</v>
       </c>
-      <c r="BB44" s="28"/>
-      <c r="BC44" s="28"/>
-      <c r="BD44" s="28"/>
-      <c r="BE44" s="28"/>
-      <c r="BF44" s="28"/>
-      <c r="BG44" s="28"/>
-      <c r="BH44" s="29"/>
-      <c r="BI44" s="27" t="s">
+      <c r="BB44" s="43"/>
+      <c r="BC44" s="43"/>
+      <c r="BD44" s="43"/>
+      <c r="BE44" s="43"/>
+      <c r="BF44" s="43"/>
+      <c r="BG44" s="43"/>
+      <c r="BH44" s="44"/>
+      <c r="BI44" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="BJ44" s="28"/>
-      <c r="BK44" s="29"/>
-      <c r="BL44" s="27" t="s">
+      <c r="BJ44" s="43"/>
+      <c r="BK44" s="44"/>
+      <c r="BL44" s="42" t="s">
         <v>202</v>
       </c>
-      <c r="BM44" s="28"/>
-      <c r="BN44" s="29"/>
-      <c r="BO44" s="27" t="s">
+      <c r="BM44" s="43"/>
+      <c r="BN44" s="44"/>
+      <c r="BO44" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="BP44" s="28"/>
-      <c r="BQ44" s="29"/>
-      <c r="BR44" s="30" t="s">
+      <c r="BP44" s="43"/>
+      <c r="BQ44" s="44"/>
+      <c r="BR44" s="54" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="45" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="31"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="34"/>
-      <c r="H45" s="34"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="34"/>
-      <c r="K45" s="34"/>
-      <c r="L45" s="34"/>
-      <c r="M45" s="34"/>
-      <c r="N45" s="34"/>
-      <c r="O45" s="34"/>
-      <c r="P45" s="34"/>
-      <c r="Q45" s="34"/>
-      <c r="R45" s="34"/>
-      <c r="S45" s="34"/>
-      <c r="T45" s="34"/>
-      <c r="U45" s="34"/>
-      <c r="V45" s="34"/>
-      <c r="W45" s="34"/>
-      <c r="AA45" s="34"/>
-      <c r="AB45" s="34"/>
-      <c r="AC45" s="34"/>
-      <c r="AD45" s="34"/>
-      <c r="AE45" s="34"/>
-      <c r="AF45" s="34"/>
-      <c r="AG45" s="34"/>
-      <c r="AH45" s="34"/>
-      <c r="AI45" s="34"/>
-      <c r="AJ45" s="34"/>
-      <c r="AK45" s="34"/>
-      <c r="AL45" s="34"/>
-      <c r="AM45" s="34"/>
-      <c r="AN45" s="34"/>
-      <c r="AO45" s="34"/>
-      <c r="AP45" s="34"/>
-      <c r="AQ45" s="34"/>
-      <c r="AR45" s="34"/>
-      <c r="AS45" s="34"/>
+      <c r="B45" s="55"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="40"/>
+      <c r="K45" s="40"/>
+      <c r="L45" s="40"/>
+      <c r="M45" s="40"/>
+      <c r="N45" s="40"/>
+      <c r="O45" s="40"/>
+      <c r="P45" s="40"/>
+      <c r="Q45" s="40"/>
+      <c r="R45" s="40"/>
+      <c r="S45" s="40"/>
+      <c r="T45" s="40"/>
+      <c r="U45" s="40"/>
+      <c r="V45" s="40"/>
+      <c r="W45" s="40"/>
+      <c r="AA45" s="40"/>
+      <c r="AB45" s="40"/>
+      <c r="AC45" s="40"/>
+      <c r="AD45" s="40"/>
+      <c r="AE45" s="40"/>
+      <c r="AF45" s="40"/>
+      <c r="AG45" s="40"/>
+      <c r="AH45" s="40"/>
+      <c r="AI45" s="40"/>
+      <c r="AJ45" s="40"/>
+      <c r="AK45" s="40"/>
+      <c r="AL45" s="40"/>
+      <c r="AM45" s="40"/>
+      <c r="AN45" s="40"/>
+      <c r="AO45" s="40"/>
+      <c r="AP45" s="40"/>
+      <c r="AQ45" s="40"/>
+      <c r="AR45" s="40"/>
+      <c r="AS45" s="40"/>
       <c r="AW45" s="5" t="s">
         <v>234</v>
       </c>
@@ -4713,48 +4947,48 @@
       </c>
       <c r="BP45" s="24"/>
       <c r="BQ45" s="25"/>
-      <c r="BR45" s="31"/>
+      <c r="BR45" s="55"/>
     </row>
     <row r="46" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="31"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34"/>
-      <c r="J46" s="34"/>
-      <c r="K46" s="34"/>
-      <c r="L46" s="34"/>
-      <c r="M46" s="34"/>
-      <c r="N46" s="34"/>
-      <c r="O46" s="34"/>
-      <c r="P46" s="34"/>
-      <c r="Q46" s="34"/>
-      <c r="R46" s="34"/>
-      <c r="S46" s="34"/>
-      <c r="T46" s="34"/>
-      <c r="U46" s="34"/>
-      <c r="V46" s="34"/>
-      <c r="W46" s="34"/>
-      <c r="AA46" s="34"/>
-      <c r="AB46" s="34"/>
-      <c r="AC46" s="34"/>
-      <c r="AD46" s="34"/>
-      <c r="AE46" s="34"/>
-      <c r="AF46" s="34"/>
-      <c r="AG46" s="34"/>
-      <c r="AH46" s="34"/>
-      <c r="AI46" s="34"/>
-      <c r="AJ46" s="34"/>
-      <c r="AK46" s="34"/>
-      <c r="AL46" s="34"/>
-      <c r="AM46" s="34"/>
-      <c r="AN46" s="34"/>
-      <c r="AO46" s="34"/>
-      <c r="AP46" s="34"/>
-      <c r="AQ46" s="34"/>
-      <c r="AR46" s="34"/>
-      <c r="AS46" s="34"/>
+      <c r="B46" s="55"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="40"/>
+      <c r="J46" s="40"/>
+      <c r="K46" s="40"/>
+      <c r="L46" s="40"/>
+      <c r="M46" s="40"/>
+      <c r="N46" s="40"/>
+      <c r="O46" s="40"/>
+      <c r="P46" s="40"/>
+      <c r="Q46" s="40"/>
+      <c r="R46" s="40"/>
+      <c r="S46" s="40"/>
+      <c r="T46" s="40"/>
+      <c r="U46" s="40"/>
+      <c r="V46" s="40"/>
+      <c r="W46" s="40"/>
+      <c r="AA46" s="40"/>
+      <c r="AB46" s="40"/>
+      <c r="AC46" s="40"/>
+      <c r="AD46" s="40"/>
+      <c r="AE46" s="40"/>
+      <c r="AF46" s="40"/>
+      <c r="AG46" s="40"/>
+      <c r="AH46" s="40"/>
+      <c r="AI46" s="40"/>
+      <c r="AJ46" s="40"/>
+      <c r="AK46" s="40"/>
+      <c r="AL46" s="40"/>
+      <c r="AM46" s="40"/>
+      <c r="AN46" s="40"/>
+      <c r="AO46" s="40"/>
+      <c r="AP46" s="40"/>
+      <c r="AQ46" s="40"/>
+      <c r="AR46" s="40"/>
+      <c r="AS46" s="40"/>
       <c r="AW46" s="23" t="s">
         <v>210</v>
       </c>
@@ -4782,48 +5016,48 @@
       <c r="BO46" s="24"/>
       <c r="BP46" s="24"/>
       <c r="BQ46" s="25"/>
-      <c r="BR46" s="31"/>
+      <c r="BR46" s="55"/>
     </row>
     <row r="47" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="31"/>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34"/>
-      <c r="J47" s="34"/>
-      <c r="K47" s="34"/>
-      <c r="L47" s="34"/>
-      <c r="M47" s="34"/>
-      <c r="N47" s="34"/>
-      <c r="O47" s="34"/>
-      <c r="P47" s="34"/>
-      <c r="Q47" s="34"/>
-      <c r="R47" s="34"/>
-      <c r="S47" s="34"/>
-      <c r="T47" s="34"/>
-      <c r="U47" s="34"/>
-      <c r="V47" s="34"/>
-      <c r="W47" s="34"/>
-      <c r="AA47" s="34"/>
-      <c r="AB47" s="34"/>
-      <c r="AC47" s="34"/>
-      <c r="AD47" s="34"/>
-      <c r="AE47" s="34"/>
-      <c r="AF47" s="34"/>
-      <c r="AG47" s="34"/>
-      <c r="AH47" s="34"/>
-      <c r="AI47" s="34"/>
-      <c r="AJ47" s="34"/>
-      <c r="AK47" s="34"/>
-      <c r="AL47" s="34"/>
-      <c r="AM47" s="34"/>
-      <c r="AN47" s="34"/>
-      <c r="AO47" s="34"/>
-      <c r="AP47" s="34"/>
-      <c r="AQ47" s="34"/>
-      <c r="AR47" s="34"/>
-      <c r="AS47" s="34"/>
+      <c r="B47" s="55"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="40"/>
+      <c r="J47" s="40"/>
+      <c r="K47" s="40"/>
+      <c r="L47" s="40"/>
+      <c r="M47" s="40"/>
+      <c r="N47" s="40"/>
+      <c r="O47" s="40"/>
+      <c r="P47" s="40"/>
+      <c r="Q47" s="40"/>
+      <c r="R47" s="40"/>
+      <c r="S47" s="40"/>
+      <c r="T47" s="40"/>
+      <c r="U47" s="40"/>
+      <c r="V47" s="40"/>
+      <c r="W47" s="40"/>
+      <c r="AA47" s="40"/>
+      <c r="AB47" s="40"/>
+      <c r="AC47" s="40"/>
+      <c r="AD47" s="40"/>
+      <c r="AE47" s="40"/>
+      <c r="AF47" s="40"/>
+      <c r="AG47" s="40"/>
+      <c r="AH47" s="40"/>
+      <c r="AI47" s="40"/>
+      <c r="AJ47" s="40"/>
+      <c r="AK47" s="40"/>
+      <c r="AL47" s="40"/>
+      <c r="AM47" s="40"/>
+      <c r="AN47" s="40"/>
+      <c r="AO47" s="40"/>
+      <c r="AP47" s="40"/>
+      <c r="AQ47" s="40"/>
+      <c r="AR47" s="40"/>
+      <c r="AS47" s="40"/>
       <c r="AW47" s="23" t="s">
         <v>213</v>
       </c>
@@ -4851,58 +5085,58 @@
       <c r="BO47" s="24"/>
       <c r="BP47" s="24"/>
       <c r="BQ47" s="25"/>
-      <c r="BR47" s="31"/>
+      <c r="BR47" s="55"/>
     </row>
     <row r="48" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="31"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
-      <c r="H48" s="34"/>
-      <c r="I48" s="34"/>
-      <c r="J48" s="34"/>
-      <c r="K48" s="34"/>
-      <c r="L48" s="34"/>
-      <c r="M48" s="34"/>
-      <c r="N48" s="34"/>
-      <c r="O48" s="34"/>
-      <c r="P48" s="34"/>
-      <c r="Q48" s="34"/>
-      <c r="R48" s="34"/>
-      <c r="S48" s="34"/>
-      <c r="T48" s="34"/>
-      <c r="U48" s="34"/>
-      <c r="V48" s="34"/>
-      <c r="W48" s="34"/>
-      <c r="AA48" s="34"/>
-      <c r="AB48" s="34"/>
-      <c r="AC48" s="34"/>
-      <c r="AD48" s="34"/>
-      <c r="AE48" s="34"/>
-      <c r="AF48" s="34"/>
-      <c r="AG48" s="34"/>
-      <c r="AH48" s="34"/>
-      <c r="AI48" s="34"/>
-      <c r="AJ48" s="34"/>
-      <c r="AK48" s="34"/>
-      <c r="AL48" s="34"/>
-      <c r="AM48" s="34"/>
-      <c r="AN48" s="34"/>
-      <c r="AO48" s="34"/>
-      <c r="AP48" s="34"/>
-      <c r="AQ48" s="34"/>
-      <c r="AR48" s="34"/>
-      <c r="AS48" s="34"/>
-      <c r="AW48" s="39" t="s">
+      <c r="B48" s="55"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="40"/>
+      <c r="J48" s="40"/>
+      <c r="K48" s="40"/>
+      <c r="L48" s="40"/>
+      <c r="M48" s="40"/>
+      <c r="N48" s="40"/>
+      <c r="O48" s="40"/>
+      <c r="P48" s="40"/>
+      <c r="Q48" s="40"/>
+      <c r="R48" s="40"/>
+      <c r="S48" s="40"/>
+      <c r="T48" s="40"/>
+      <c r="U48" s="40"/>
+      <c r="V48" s="40"/>
+      <c r="W48" s="40"/>
+      <c r="AA48" s="40"/>
+      <c r="AB48" s="40"/>
+      <c r="AC48" s="40"/>
+      <c r="AD48" s="40"/>
+      <c r="AE48" s="40"/>
+      <c r="AF48" s="40"/>
+      <c r="AG48" s="40"/>
+      <c r="AH48" s="40"/>
+      <c r="AI48" s="40"/>
+      <c r="AJ48" s="40"/>
+      <c r="AK48" s="40"/>
+      <c r="AL48" s="40"/>
+      <c r="AM48" s="40"/>
+      <c r="AN48" s="40"/>
+      <c r="AO48" s="40"/>
+      <c r="AP48" s="40"/>
+      <c r="AQ48" s="40"/>
+      <c r="AR48" s="40"/>
+      <c r="AS48" s="40"/>
+      <c r="AW48" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="AX48" s="40"/>
-      <c r="AY48" s="40"/>
-      <c r="AZ48" s="40"/>
-      <c r="BA48" s="40"/>
-      <c r="BB48" s="40"/>
-      <c r="BC48" s="40"/>
-      <c r="BD48" s="41"/>
+      <c r="AX48" s="27"/>
+      <c r="AY48" s="27"/>
+      <c r="AZ48" s="27"/>
+      <c r="BA48" s="27"/>
+      <c r="BB48" s="27"/>
+      <c r="BC48" s="27"/>
+      <c r="BD48" s="28"/>
       <c r="BE48" s="57" t="s">
         <v>217</v>
       </c>
@@ -4918,58 +5152,58 @@
       <c r="BO48" s="58"/>
       <c r="BP48" s="58"/>
       <c r="BQ48" s="59"/>
-      <c r="BR48" s="31"/>
+      <c r="BR48" s="55"/>
     </row>
     <row r="49" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="31"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
-      <c r="H49" s="34"/>
-      <c r="I49" s="34"/>
-      <c r="J49" s="34"/>
-      <c r="K49" s="34"/>
-      <c r="L49" s="34"/>
-      <c r="M49" s="34"/>
-      <c r="N49" s="34"/>
-      <c r="O49" s="34"/>
-      <c r="P49" s="34"/>
-      <c r="Q49" s="34"/>
-      <c r="R49" s="34"/>
-      <c r="S49" s="34"/>
-      <c r="T49" s="34"/>
-      <c r="U49" s="34"/>
-      <c r="V49" s="34"/>
-      <c r="W49" s="34"/>
-      <c r="AA49" s="34"/>
-      <c r="AB49" s="34"/>
-      <c r="AC49" s="34"/>
-      <c r="AD49" s="34"/>
-      <c r="AE49" s="34"/>
-      <c r="AF49" s="34"/>
-      <c r="AG49" s="34"/>
-      <c r="AH49" s="34"/>
-      <c r="AI49" s="34"/>
-      <c r="AJ49" s="34"/>
-      <c r="AK49" s="34"/>
-      <c r="AL49" s="34"/>
-      <c r="AM49" s="34"/>
-      <c r="AN49" s="34"/>
-      <c r="AO49" s="34"/>
-      <c r="AP49" s="34"/>
-      <c r="AQ49" s="34"/>
-      <c r="AR49" s="34"/>
-      <c r="AS49" s="34"/>
-      <c r="AW49" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="AX49" s="21"/>
-      <c r="AY49" s="21"/>
-      <c r="AZ49" s="21"/>
-      <c r="BA49" s="21"/>
-      <c r="BB49" s="21"/>
-      <c r="BC49" s="21"/>
-      <c r="BD49" s="22"/>
+      <c r="B49" s="55"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="40"/>
+      <c r="I49" s="40"/>
+      <c r="J49" s="40"/>
+      <c r="K49" s="40"/>
+      <c r="L49" s="40"/>
+      <c r="M49" s="40"/>
+      <c r="N49" s="40"/>
+      <c r="O49" s="40"/>
+      <c r="P49" s="40"/>
+      <c r="Q49" s="40"/>
+      <c r="R49" s="40"/>
+      <c r="S49" s="40"/>
+      <c r="T49" s="40"/>
+      <c r="U49" s="40"/>
+      <c r="V49" s="40"/>
+      <c r="W49" s="40"/>
+      <c r="AA49" s="40"/>
+      <c r="AB49" s="40"/>
+      <c r="AC49" s="40"/>
+      <c r="AD49" s="40"/>
+      <c r="AE49" s="40"/>
+      <c r="AF49" s="40"/>
+      <c r="AG49" s="40"/>
+      <c r="AH49" s="40"/>
+      <c r="AI49" s="40"/>
+      <c r="AJ49" s="40"/>
+      <c r="AK49" s="40"/>
+      <c r="AL49" s="40"/>
+      <c r="AM49" s="40"/>
+      <c r="AN49" s="40"/>
+      <c r="AO49" s="40"/>
+      <c r="AP49" s="40"/>
+      <c r="AQ49" s="40"/>
+      <c r="AR49" s="40"/>
+      <c r="AS49" s="40"/>
+      <c r="AW49" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="AX49" s="37"/>
+      <c r="AY49" s="37"/>
+      <c r="AZ49" s="37"/>
+      <c r="BA49" s="37"/>
+      <c r="BB49" s="37"/>
+      <c r="BC49" s="37"/>
+      <c r="BD49" s="38"/>
       <c r="BE49" s="60"/>
       <c r="BF49" s="61"/>
       <c r="BG49" s="61"/>
@@ -4983,56 +5217,56 @@
       <c r="BO49" s="61"/>
       <c r="BP49" s="61"/>
       <c r="BQ49" s="62"/>
-      <c r="BR49" s="31"/>
+      <c r="BR49" s="55"/>
     </row>
     <row r="50" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="31"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="34"/>
-      <c r="H50" s="34"/>
-      <c r="I50" s="34"/>
-      <c r="J50" s="34"/>
-      <c r="K50" s="34"/>
-      <c r="L50" s="34"/>
-      <c r="M50" s="34"/>
-      <c r="N50" s="34"/>
-      <c r="O50" s="34"/>
-      <c r="P50" s="34"/>
-      <c r="Q50" s="34"/>
-      <c r="R50" s="34"/>
-      <c r="S50" s="34"/>
-      <c r="T50" s="34"/>
-      <c r="U50" s="34"/>
-      <c r="V50" s="34"/>
-      <c r="W50" s="34"/>
-      <c r="AA50" s="34"/>
-      <c r="AB50" s="34"/>
-      <c r="AC50" s="34"/>
-      <c r="AD50" s="34"/>
-      <c r="AE50" s="34"/>
-      <c r="AF50" s="34"/>
-      <c r="AG50" s="34"/>
-      <c r="AH50" s="34"/>
-      <c r="AI50" s="34"/>
-      <c r="AJ50" s="34"/>
-      <c r="AK50" s="34"/>
-      <c r="AL50" s="34"/>
-      <c r="AM50" s="34"/>
-      <c r="AN50" s="34"/>
-      <c r="AO50" s="34"/>
-      <c r="AP50" s="34"/>
-      <c r="AQ50" s="34"/>
-      <c r="AR50" s="34"/>
-      <c r="AS50" s="34"/>
-      <c r="AW50" s="26"/>
-      <c r="AX50" s="21"/>
-      <c r="AY50" s="21"/>
-      <c r="AZ50" s="21"/>
-      <c r="BA50" s="21"/>
-      <c r="BB50" s="21"/>
-      <c r="BC50" s="21"/>
-      <c r="BD50" s="22"/>
+      <c r="B50" s="55"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="40"/>
+      <c r="J50" s="40"/>
+      <c r="K50" s="40"/>
+      <c r="L50" s="40"/>
+      <c r="M50" s="40"/>
+      <c r="N50" s="40"/>
+      <c r="O50" s="40"/>
+      <c r="P50" s="40"/>
+      <c r="Q50" s="40"/>
+      <c r="R50" s="40"/>
+      <c r="S50" s="40"/>
+      <c r="T50" s="40"/>
+      <c r="U50" s="40"/>
+      <c r="V50" s="40"/>
+      <c r="W50" s="40"/>
+      <c r="AA50" s="40"/>
+      <c r="AB50" s="40"/>
+      <c r="AC50" s="40"/>
+      <c r="AD50" s="40"/>
+      <c r="AE50" s="40"/>
+      <c r="AF50" s="40"/>
+      <c r="AG50" s="40"/>
+      <c r="AH50" s="40"/>
+      <c r="AI50" s="40"/>
+      <c r="AJ50" s="40"/>
+      <c r="AK50" s="40"/>
+      <c r="AL50" s="40"/>
+      <c r="AM50" s="40"/>
+      <c r="AN50" s="40"/>
+      <c r="AO50" s="40"/>
+      <c r="AP50" s="40"/>
+      <c r="AQ50" s="40"/>
+      <c r="AR50" s="40"/>
+      <c r="AS50" s="40"/>
+      <c r="AW50" s="41"/>
+      <c r="AX50" s="37"/>
+      <c r="AY50" s="37"/>
+      <c r="AZ50" s="37"/>
+      <c r="BA50" s="37"/>
+      <c r="BB50" s="37"/>
+      <c r="BC50" s="37"/>
+      <c r="BD50" s="38"/>
       <c r="BE50" s="57" t="s">
         <v>218</v>
       </c>
@@ -5048,56 +5282,56 @@
       <c r="BO50" s="58"/>
       <c r="BP50" s="58"/>
       <c r="BQ50" s="59"/>
-      <c r="BR50" s="31"/>
+      <c r="BR50" s="55"/>
     </row>
     <row r="51" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="31"/>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
-      <c r="G51" s="34"/>
-      <c r="H51" s="34"/>
-      <c r="I51" s="34"/>
-      <c r="J51" s="34"/>
-      <c r="K51" s="34"/>
-      <c r="L51" s="34"/>
-      <c r="M51" s="34"/>
-      <c r="N51" s="34"/>
-      <c r="O51" s="34"/>
-      <c r="P51" s="34"/>
-      <c r="Q51" s="34"/>
-      <c r="R51" s="34"/>
-      <c r="S51" s="34"/>
-      <c r="T51" s="34"/>
-      <c r="U51" s="34"/>
-      <c r="V51" s="34"/>
-      <c r="W51" s="34"/>
-      <c r="AA51" s="34"/>
-      <c r="AB51" s="34"/>
-      <c r="AC51" s="34"/>
-      <c r="AD51" s="34"/>
-      <c r="AE51" s="34"/>
-      <c r="AF51" s="34"/>
-      <c r="AG51" s="34"/>
-      <c r="AH51" s="34"/>
-      <c r="AI51" s="34"/>
-      <c r="AJ51" s="34"/>
-      <c r="AK51" s="34"/>
-      <c r="AL51" s="34"/>
-      <c r="AM51" s="34"/>
-      <c r="AN51" s="34"/>
-      <c r="AO51" s="34"/>
-      <c r="AP51" s="34"/>
-      <c r="AQ51" s="34"/>
-      <c r="AR51" s="34"/>
-      <c r="AS51" s="34"/>
-      <c r="AW51" s="27"/>
-      <c r="AX51" s="28"/>
-      <c r="AY51" s="28"/>
-      <c r="AZ51" s="28"/>
-      <c r="BA51" s="28"/>
-      <c r="BB51" s="28"/>
-      <c r="BC51" s="28"/>
-      <c r="BD51" s="29"/>
+      <c r="B51" s="55"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="40"/>
+      <c r="M51" s="40"/>
+      <c r="N51" s="40"/>
+      <c r="O51" s="40"/>
+      <c r="P51" s="40"/>
+      <c r="Q51" s="40"/>
+      <c r="R51" s="40"/>
+      <c r="S51" s="40"/>
+      <c r="T51" s="40"/>
+      <c r="U51" s="40"/>
+      <c r="V51" s="40"/>
+      <c r="W51" s="40"/>
+      <c r="AA51" s="40"/>
+      <c r="AB51" s="40"/>
+      <c r="AC51" s="40"/>
+      <c r="AD51" s="40"/>
+      <c r="AE51" s="40"/>
+      <c r="AF51" s="40"/>
+      <c r="AG51" s="40"/>
+      <c r="AH51" s="40"/>
+      <c r="AI51" s="40"/>
+      <c r="AJ51" s="40"/>
+      <c r="AK51" s="40"/>
+      <c r="AL51" s="40"/>
+      <c r="AM51" s="40"/>
+      <c r="AN51" s="40"/>
+      <c r="AO51" s="40"/>
+      <c r="AP51" s="40"/>
+      <c r="AQ51" s="40"/>
+      <c r="AR51" s="40"/>
+      <c r="AS51" s="40"/>
+      <c r="AW51" s="42"/>
+      <c r="AX51" s="43"/>
+      <c r="AY51" s="43"/>
+      <c r="AZ51" s="43"/>
+      <c r="BA51" s="43"/>
+      <c r="BB51" s="43"/>
+      <c r="BC51" s="43"/>
+      <c r="BD51" s="44"/>
       <c r="BE51" s="60"/>
       <c r="BF51" s="61"/>
       <c r="BG51" s="61"/>
@@ -5111,282 +5345,282 @@
       <c r="BO51" s="61"/>
       <c r="BP51" s="61"/>
       <c r="BQ51" s="62"/>
-      <c r="BR51" s="31"/>
+      <c r="BR51" s="55"/>
     </row>
     <row r="52" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="31"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="34"/>
-      <c r="H52" s="34"/>
-      <c r="I52" s="34"/>
-      <c r="J52" s="34"/>
-      <c r="K52" s="34"/>
-      <c r="L52" s="34"/>
-      <c r="M52" s="34"/>
-      <c r="N52" s="34"/>
-      <c r="O52" s="34"/>
-      <c r="P52" s="34"/>
-      <c r="Q52" s="34"/>
-      <c r="R52" s="34"/>
-      <c r="S52" s="34"/>
-      <c r="T52" s="34"/>
-      <c r="U52" s="34"/>
-      <c r="V52" s="34"/>
-      <c r="W52" s="34"/>
-      <c r="AA52" s="34"/>
-      <c r="AB52" s="34"/>
-      <c r="AC52" s="34"/>
-      <c r="AD52" s="34"/>
-      <c r="AE52" s="34"/>
-      <c r="AF52" s="34"/>
-      <c r="AG52" s="34"/>
-      <c r="AH52" s="34"/>
-      <c r="AI52" s="34"/>
-      <c r="AJ52" s="34"/>
-      <c r="AK52" s="34"/>
-      <c r="AL52" s="34"/>
-      <c r="AM52" s="34"/>
-      <c r="AN52" s="34"/>
-      <c r="AO52" s="34"/>
-      <c r="AP52" s="34"/>
-      <c r="AQ52" s="34"/>
-      <c r="AR52" s="34"/>
-      <c r="AS52" s="34"/>
-      <c r="AW52" s="39" t="s">
+      <c r="B52" s="55"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="40"/>
+      <c r="I52" s="40"/>
+      <c r="J52" s="40"/>
+      <c r="K52" s="40"/>
+      <c r="L52" s="40"/>
+      <c r="M52" s="40"/>
+      <c r="N52" s="40"/>
+      <c r="O52" s="40"/>
+      <c r="P52" s="40"/>
+      <c r="Q52" s="40"/>
+      <c r="R52" s="40"/>
+      <c r="S52" s="40"/>
+      <c r="T52" s="40"/>
+      <c r="U52" s="40"/>
+      <c r="V52" s="40"/>
+      <c r="W52" s="40"/>
+      <c r="AA52" s="40"/>
+      <c r="AB52" s="40"/>
+      <c r="AC52" s="40"/>
+      <c r="AD52" s="40"/>
+      <c r="AE52" s="40"/>
+      <c r="AF52" s="40"/>
+      <c r="AG52" s="40"/>
+      <c r="AH52" s="40"/>
+      <c r="AI52" s="40"/>
+      <c r="AJ52" s="40"/>
+      <c r="AK52" s="40"/>
+      <c r="AL52" s="40"/>
+      <c r="AM52" s="40"/>
+      <c r="AN52" s="40"/>
+      <c r="AO52" s="40"/>
+      <c r="AP52" s="40"/>
+      <c r="AQ52" s="40"/>
+      <c r="AR52" s="40"/>
+      <c r="AS52" s="40"/>
+      <c r="AW52" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="AX52" s="40"/>
-      <c r="AY52" s="40"/>
-      <c r="AZ52" s="40"/>
-      <c r="BA52" s="40"/>
-      <c r="BB52" s="40"/>
-      <c r="BC52" s="40"/>
-      <c r="BD52" s="41"/>
-      <c r="BE52" s="48" t="s">
+      <c r="AX52" s="27"/>
+      <c r="AY52" s="27"/>
+      <c r="AZ52" s="27"/>
+      <c r="BA52" s="27"/>
+      <c r="BB52" s="27"/>
+      <c r="BC52" s="27"/>
+      <c r="BD52" s="28"/>
+      <c r="BE52" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="BF52" s="49"/>
-      <c r="BG52" s="49"/>
-      <c r="BH52" s="49"/>
-      <c r="BI52" s="49"/>
-      <c r="BJ52" s="49"/>
-      <c r="BK52" s="49"/>
-      <c r="BL52" s="49"/>
-      <c r="BM52" s="49"/>
-      <c r="BN52" s="49"/>
-      <c r="BO52" s="49"/>
-      <c r="BP52" s="49"/>
-      <c r="BQ52" s="50"/>
-      <c r="BR52" s="31"/>
+      <c r="BF52" s="46"/>
+      <c r="BG52" s="46"/>
+      <c r="BH52" s="46"/>
+      <c r="BI52" s="46"/>
+      <c r="BJ52" s="46"/>
+      <c r="BK52" s="46"/>
+      <c r="BL52" s="46"/>
+      <c r="BM52" s="46"/>
+      <c r="BN52" s="46"/>
+      <c r="BO52" s="46"/>
+      <c r="BP52" s="46"/>
+      <c r="BQ52" s="47"/>
+      <c r="BR52" s="55"/>
     </row>
     <row r="53" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="31"/>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="34"/>
-      <c r="H53" s="34"/>
-      <c r="I53" s="34"/>
-      <c r="J53" s="34"/>
-      <c r="K53" s="34"/>
-      <c r="L53" s="34"/>
-      <c r="M53" s="34"/>
-      <c r="N53" s="34"/>
-      <c r="O53" s="34"/>
-      <c r="P53" s="34"/>
-      <c r="Q53" s="34"/>
-      <c r="R53" s="34"/>
-      <c r="S53" s="34"/>
-      <c r="T53" s="34"/>
-      <c r="U53" s="34"/>
-      <c r="V53" s="34"/>
-      <c r="W53" s="34"/>
-      <c r="AA53" s="34"/>
-      <c r="AB53" s="34"/>
-      <c r="AC53" s="34"/>
-      <c r="AD53" s="34"/>
-      <c r="AE53" s="34"/>
-      <c r="AF53" s="34"/>
-      <c r="AG53" s="34"/>
-      <c r="AH53" s="34"/>
-      <c r="AI53" s="34"/>
-      <c r="AJ53" s="34"/>
-      <c r="AK53" s="34"/>
-      <c r="AL53" s="34"/>
-      <c r="AM53" s="34"/>
-      <c r="AN53" s="34"/>
-      <c r="AO53" s="34"/>
-      <c r="AP53" s="34"/>
-      <c r="AQ53" s="34"/>
-      <c r="AR53" s="34"/>
-      <c r="AS53" s="34"/>
-      <c r="AW53" s="26" t="s">
+      <c r="B53" s="55"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="40"/>
+      <c r="I53" s="40"/>
+      <c r="J53" s="40"/>
+      <c r="K53" s="40"/>
+      <c r="L53" s="40"/>
+      <c r="M53" s="40"/>
+      <c r="N53" s="40"/>
+      <c r="O53" s="40"/>
+      <c r="P53" s="40"/>
+      <c r="Q53" s="40"/>
+      <c r="R53" s="40"/>
+      <c r="S53" s="40"/>
+      <c r="T53" s="40"/>
+      <c r="U53" s="40"/>
+      <c r="V53" s="40"/>
+      <c r="W53" s="40"/>
+      <c r="AA53" s="40"/>
+      <c r="AB53" s="40"/>
+      <c r="AC53" s="40"/>
+      <c r="AD53" s="40"/>
+      <c r="AE53" s="40"/>
+      <c r="AF53" s="40"/>
+      <c r="AG53" s="40"/>
+      <c r="AH53" s="40"/>
+      <c r="AI53" s="40"/>
+      <c r="AJ53" s="40"/>
+      <c r="AK53" s="40"/>
+      <c r="AL53" s="40"/>
+      <c r="AM53" s="40"/>
+      <c r="AN53" s="40"/>
+      <c r="AO53" s="40"/>
+      <c r="AP53" s="40"/>
+      <c r="AQ53" s="40"/>
+      <c r="AR53" s="40"/>
+      <c r="AS53" s="40"/>
+      <c r="AW53" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="AX53" s="21"/>
-      <c r="AY53" s="21"/>
-      <c r="AZ53" s="21"/>
-      <c r="BA53" s="21"/>
-      <c r="BB53" s="21"/>
-      <c r="BC53" s="21"/>
-      <c r="BD53" s="22"/>
-      <c r="BE53" s="51"/>
-      <c r="BF53" s="52"/>
-      <c r="BG53" s="52"/>
-      <c r="BH53" s="52"/>
-      <c r="BI53" s="52"/>
-      <c r="BJ53" s="52"/>
-      <c r="BK53" s="52"/>
-      <c r="BL53" s="52"/>
-      <c r="BM53" s="52"/>
-      <c r="BN53" s="52"/>
-      <c r="BO53" s="52"/>
-      <c r="BP53" s="52"/>
-      <c r="BQ53" s="53"/>
-      <c r="BR53" s="31"/>
+      <c r="AX53" s="37"/>
+      <c r="AY53" s="37"/>
+      <c r="AZ53" s="37"/>
+      <c r="BA53" s="37"/>
+      <c r="BB53" s="37"/>
+      <c r="BC53" s="37"/>
+      <c r="BD53" s="38"/>
+      <c r="BE53" s="48"/>
+      <c r="BF53" s="49"/>
+      <c r="BG53" s="49"/>
+      <c r="BH53" s="49"/>
+      <c r="BI53" s="49"/>
+      <c r="BJ53" s="49"/>
+      <c r="BK53" s="49"/>
+      <c r="BL53" s="49"/>
+      <c r="BM53" s="49"/>
+      <c r="BN53" s="49"/>
+      <c r="BO53" s="49"/>
+      <c r="BP53" s="49"/>
+      <c r="BQ53" s="50"/>
+      <c r="BR53" s="55"/>
     </row>
     <row r="54" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="31"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="34"/>
-      <c r="H54" s="34"/>
-      <c r="I54" s="34"/>
-      <c r="J54" s="34"/>
-      <c r="K54" s="34"/>
-      <c r="L54" s="34"/>
-      <c r="M54" s="34"/>
-      <c r="N54" s="34"/>
-      <c r="O54" s="34"/>
-      <c r="P54" s="34"/>
-      <c r="Q54" s="34"/>
-      <c r="R54" s="34"/>
-      <c r="S54" s="34"/>
-      <c r="T54" s="34"/>
-      <c r="U54" s="34"/>
-      <c r="V54" s="34"/>
-      <c r="W54" s="34"/>
-      <c r="AA54" s="34"/>
-      <c r="AB54" s="34"/>
-      <c r="AC54" s="34"/>
-      <c r="AD54" s="34"/>
-      <c r="AE54" s="34"/>
-      <c r="AF54" s="34"/>
-      <c r="AG54" s="34"/>
-      <c r="AH54" s="34"/>
-      <c r="AI54" s="34"/>
-      <c r="AJ54" s="34"/>
-      <c r="AK54" s="34"/>
-      <c r="AL54" s="34"/>
-      <c r="AM54" s="34"/>
-      <c r="AN54" s="34"/>
-      <c r="AO54" s="34"/>
-      <c r="AP54" s="34"/>
-      <c r="AQ54" s="34"/>
-      <c r="AR54" s="34"/>
-      <c r="AS54" s="34"/>
-      <c r="AW54" s="26"/>
-      <c r="AX54" s="21"/>
-      <c r="AY54" s="21"/>
-      <c r="AZ54" s="21"/>
-      <c r="BA54" s="21"/>
-      <c r="BB54" s="21"/>
-      <c r="BC54" s="21"/>
-      <c r="BD54" s="22"/>
-      <c r="BE54" s="51"/>
-      <c r="BF54" s="52"/>
-      <c r="BG54" s="52"/>
-      <c r="BH54" s="52"/>
-      <c r="BI54" s="52"/>
-      <c r="BJ54" s="52"/>
-      <c r="BK54" s="52"/>
-      <c r="BL54" s="52"/>
-      <c r="BM54" s="52"/>
-      <c r="BN54" s="52"/>
-      <c r="BO54" s="52"/>
-      <c r="BP54" s="52"/>
-      <c r="BQ54" s="53"/>
-      <c r="BR54" s="31"/>
+      <c r="B54" s="55"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="40"/>
+      <c r="I54" s="40"/>
+      <c r="J54" s="40"/>
+      <c r="K54" s="40"/>
+      <c r="L54" s="40"/>
+      <c r="M54" s="40"/>
+      <c r="N54" s="40"/>
+      <c r="O54" s="40"/>
+      <c r="P54" s="40"/>
+      <c r="Q54" s="40"/>
+      <c r="R54" s="40"/>
+      <c r="S54" s="40"/>
+      <c r="T54" s="40"/>
+      <c r="U54" s="40"/>
+      <c r="V54" s="40"/>
+      <c r="W54" s="40"/>
+      <c r="AA54" s="40"/>
+      <c r="AB54" s="40"/>
+      <c r="AC54" s="40"/>
+      <c r="AD54" s="40"/>
+      <c r="AE54" s="40"/>
+      <c r="AF54" s="40"/>
+      <c r="AG54" s="40"/>
+      <c r="AH54" s="40"/>
+      <c r="AI54" s="40"/>
+      <c r="AJ54" s="40"/>
+      <c r="AK54" s="40"/>
+      <c r="AL54" s="40"/>
+      <c r="AM54" s="40"/>
+      <c r="AN54" s="40"/>
+      <c r="AO54" s="40"/>
+      <c r="AP54" s="40"/>
+      <c r="AQ54" s="40"/>
+      <c r="AR54" s="40"/>
+      <c r="AS54" s="40"/>
+      <c r="AW54" s="41"/>
+      <c r="AX54" s="37"/>
+      <c r="AY54" s="37"/>
+      <c r="AZ54" s="37"/>
+      <c r="BA54" s="37"/>
+      <c r="BB54" s="37"/>
+      <c r="BC54" s="37"/>
+      <c r="BD54" s="38"/>
+      <c r="BE54" s="48"/>
+      <c r="BF54" s="49"/>
+      <c r="BG54" s="49"/>
+      <c r="BH54" s="49"/>
+      <c r="BI54" s="49"/>
+      <c r="BJ54" s="49"/>
+      <c r="BK54" s="49"/>
+      <c r="BL54" s="49"/>
+      <c r="BM54" s="49"/>
+      <c r="BN54" s="49"/>
+      <c r="BO54" s="49"/>
+      <c r="BP54" s="49"/>
+      <c r="BQ54" s="50"/>
+      <c r="BR54" s="55"/>
     </row>
     <row r="55" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="31"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="34"/>
-      <c r="G55" s="34"/>
-      <c r="H55" s="34"/>
-      <c r="I55" s="34"/>
-      <c r="J55" s="34"/>
-      <c r="K55" s="34"/>
-      <c r="L55" s="34"/>
-      <c r="M55" s="34"/>
-      <c r="N55" s="34"/>
-      <c r="O55" s="34"/>
-      <c r="P55" s="34"/>
-      <c r="Q55" s="34"/>
-      <c r="R55" s="34"/>
-      <c r="S55" s="34"/>
-      <c r="T55" s="34"/>
-      <c r="U55" s="34"/>
-      <c r="V55" s="34"/>
-      <c r="W55" s="34"/>
-      <c r="AA55" s="34"/>
-      <c r="AB55" s="34"/>
-      <c r="AC55" s="34"/>
-      <c r="AD55" s="34"/>
-      <c r="AE55" s="34"/>
-      <c r="AF55" s="34"/>
-      <c r="AG55" s="34"/>
-      <c r="AH55" s="34"/>
-      <c r="AI55" s="34"/>
-      <c r="AJ55" s="34"/>
-      <c r="AK55" s="34"/>
-      <c r="AL55" s="34"/>
-      <c r="AM55" s="34"/>
-      <c r="AN55" s="34"/>
-      <c r="AO55" s="34"/>
-      <c r="AP55" s="34"/>
-      <c r="AQ55" s="34"/>
-      <c r="AR55" s="34"/>
-      <c r="AS55" s="34"/>
-      <c r="AW55" s="27"/>
-      <c r="AX55" s="28"/>
-      <c r="AY55" s="28"/>
-      <c r="AZ55" s="28"/>
-      <c r="BA55" s="28"/>
-      <c r="BB55" s="28"/>
-      <c r="BC55" s="28"/>
-      <c r="BD55" s="29"/>
-      <c r="BE55" s="54"/>
-      <c r="BF55" s="55"/>
-      <c r="BG55" s="55"/>
-      <c r="BH55" s="55"/>
-      <c r="BI55" s="55"/>
-      <c r="BJ55" s="55"/>
-      <c r="BK55" s="55"/>
-      <c r="BL55" s="55"/>
-      <c r="BM55" s="55"/>
-      <c r="BN55" s="55"/>
-      <c r="BO55" s="55"/>
-      <c r="BP55" s="55"/>
-      <c r="BQ55" s="56"/>
-      <c r="BR55" s="31"/>
+      <c r="B55" s="55"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="40"/>
+      <c r="I55" s="40"/>
+      <c r="J55" s="40"/>
+      <c r="K55" s="40"/>
+      <c r="L55" s="40"/>
+      <c r="M55" s="40"/>
+      <c r="N55" s="40"/>
+      <c r="O55" s="40"/>
+      <c r="P55" s="40"/>
+      <c r="Q55" s="40"/>
+      <c r="R55" s="40"/>
+      <c r="S55" s="40"/>
+      <c r="T55" s="40"/>
+      <c r="U55" s="40"/>
+      <c r="V55" s="40"/>
+      <c r="W55" s="40"/>
+      <c r="AA55" s="40"/>
+      <c r="AB55" s="40"/>
+      <c r="AC55" s="40"/>
+      <c r="AD55" s="40"/>
+      <c r="AE55" s="40"/>
+      <c r="AF55" s="40"/>
+      <c r="AG55" s="40"/>
+      <c r="AH55" s="40"/>
+      <c r="AI55" s="40"/>
+      <c r="AJ55" s="40"/>
+      <c r="AK55" s="40"/>
+      <c r="AL55" s="40"/>
+      <c r="AM55" s="40"/>
+      <c r="AN55" s="40"/>
+      <c r="AO55" s="40"/>
+      <c r="AP55" s="40"/>
+      <c r="AQ55" s="40"/>
+      <c r="AR55" s="40"/>
+      <c r="AS55" s="40"/>
+      <c r="AW55" s="42"/>
+      <c r="AX55" s="43"/>
+      <c r="AY55" s="43"/>
+      <c r="AZ55" s="43"/>
+      <c r="BA55" s="43"/>
+      <c r="BB55" s="43"/>
+      <c r="BC55" s="43"/>
+      <c r="BD55" s="44"/>
+      <c r="BE55" s="51"/>
+      <c r="BF55" s="52"/>
+      <c r="BG55" s="52"/>
+      <c r="BH55" s="52"/>
+      <c r="BI55" s="52"/>
+      <c r="BJ55" s="52"/>
+      <c r="BK55" s="52"/>
+      <c r="BL55" s="52"/>
+      <c r="BM55" s="52"/>
+      <c r="BN55" s="52"/>
+      <c r="BO55" s="52"/>
+      <c r="BP55" s="52"/>
+      <c r="BQ55" s="53"/>
+      <c r="BR55" s="55"/>
     </row>
     <row r="56" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="32"/>
-      <c r="K56" s="33" t="s">
+      <c r="B56" s="56"/>
+      <c r="K56" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="L56" s="34"/>
-      <c r="M56" s="34"/>
-      <c r="N56" s="34"/>
-      <c r="O56" s="34"/>
-      <c r="AI56" s="33" t="s">
+      <c r="L56" s="40"/>
+      <c r="M56" s="40"/>
+      <c r="N56" s="40"/>
+      <c r="O56" s="40"/>
+      <c r="AI56" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="AJ56" s="34"/>
-      <c r="AK56" s="34"/>
-      <c r="AL56" s="34"/>
-      <c r="AM56" s="34"/>
+      <c r="AJ56" s="40"/>
+      <c r="AK56" s="40"/>
+      <c r="AL56" s="40"/>
+      <c r="AM56" s="40"/>
       <c r="AW56" s="23" t="s">
         <v>223</v>
       </c>
@@ -5412,7 +5646,7 @@
       <c r="BO56" s="24"/>
       <c r="BP56" s="24"/>
       <c r="BQ56" s="25"/>
-      <c r="BR56" s="32"/>
+      <c r="BR56" s="56"/>
     </row>
     <row r="57" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="23">
@@ -5497,8 +5731,27 @@
     </row>
     <row r="58" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <mergeCells count="184">
-    <mergeCell ref="Y57:AI57"/>
+  <mergeCells count="208">
+    <mergeCell ref="AW30:AX30"/>
+    <mergeCell ref="AY30:BB30"/>
+    <mergeCell ref="BC30:BE30"/>
+    <mergeCell ref="BF30:BK30"/>
+    <mergeCell ref="BM30:BO30"/>
+    <mergeCell ref="AW31:AX31"/>
+    <mergeCell ref="AY31:BB31"/>
+    <mergeCell ref="BC31:BE31"/>
+    <mergeCell ref="BF31:BK31"/>
+    <mergeCell ref="BM31:BO31"/>
+    <mergeCell ref="AW28:AX28"/>
+    <mergeCell ref="AY28:BB28"/>
+    <mergeCell ref="BC28:BE28"/>
+    <mergeCell ref="BF28:BK28"/>
+    <mergeCell ref="BM28:BO28"/>
+    <mergeCell ref="AW29:AX29"/>
+    <mergeCell ref="AY29:BB29"/>
+    <mergeCell ref="BC29:BE29"/>
+    <mergeCell ref="BF29:BK29"/>
+    <mergeCell ref="BM29:BO29"/>
     <mergeCell ref="C2:L2"/>
     <mergeCell ref="BF16:BK16"/>
     <mergeCell ref="E4:W27"/>
@@ -5512,19 +5765,14 @@
     <mergeCell ref="BF24:BK24"/>
     <mergeCell ref="BC20:BE20"/>
     <mergeCell ref="AY15:BB15"/>
-    <mergeCell ref="AA32:AS55"/>
     <mergeCell ref="AW22:AX22"/>
-    <mergeCell ref="BA41:BH41"/>
     <mergeCell ref="AW26:AX26"/>
     <mergeCell ref="AY26:BB26"/>
-    <mergeCell ref="AW52:BD52"/>
     <mergeCell ref="AW16:AX16"/>
-    <mergeCell ref="AX44:AZ44"/>
-    <mergeCell ref="BA43:BH43"/>
-    <mergeCell ref="BI43:BK43"/>
-    <mergeCell ref="BM7:BO7"/>
-    <mergeCell ref="BM15:BO15"/>
-    <mergeCell ref="BC25:BE25"/>
+    <mergeCell ref="AW27:AX27"/>
+    <mergeCell ref="AY27:BB27"/>
+    <mergeCell ref="BC27:BE27"/>
+    <mergeCell ref="BF27:BK27"/>
     <mergeCell ref="BC13:BE13"/>
     <mergeCell ref="BM13:BO13"/>
     <mergeCell ref="AY20:BB20"/>
@@ -5537,7 +5785,6 @@
     <mergeCell ref="AX43:AZ43"/>
     <mergeCell ref="AY33:BQ38"/>
     <mergeCell ref="AW33:AX38"/>
-    <mergeCell ref="AW27:BQ31"/>
     <mergeCell ref="BO42:BQ42"/>
     <mergeCell ref="BP5:BP6"/>
     <mergeCell ref="BO40:BQ40"/>
@@ -5546,8 +5793,9 @@
     <mergeCell ref="BF13:BK13"/>
     <mergeCell ref="BL5:BL6"/>
     <mergeCell ref="AY7:BB7"/>
-    <mergeCell ref="BR17:BR29"/>
-    <mergeCell ref="BM9:BO9"/>
+    <mergeCell ref="BA41:BH41"/>
+    <mergeCell ref="AW52:BD52"/>
+    <mergeCell ref="AX44:AZ44"/>
     <mergeCell ref="AY16:BB16"/>
     <mergeCell ref="BM19:BO19"/>
     <mergeCell ref="BF14:BK14"/>
@@ -5563,6 +5811,15 @@
     <mergeCell ref="BM18:BO18"/>
     <mergeCell ref="BF19:BK19"/>
     <mergeCell ref="BM5:BO6"/>
+    <mergeCell ref="BC9:BE9"/>
+    <mergeCell ref="AY18:BB18"/>
+    <mergeCell ref="AY13:BB13"/>
+    <mergeCell ref="BC12:BE12"/>
+    <mergeCell ref="BC7:BE7"/>
+    <mergeCell ref="BC15:BE15"/>
+    <mergeCell ref="BM7:BO7"/>
+    <mergeCell ref="BM15:BO15"/>
+    <mergeCell ref="BC25:BE25"/>
     <mergeCell ref="AW5:AX6"/>
     <mergeCell ref="AW13:AX13"/>
     <mergeCell ref="BA45:BH45"/>
@@ -5610,8 +5867,7 @@
     <mergeCell ref="AY24:BB24"/>
     <mergeCell ref="BC5:BE6"/>
     <mergeCell ref="BC24:BE24"/>
-    <mergeCell ref="M57:X57"/>
-    <mergeCell ref="AX42:AZ42"/>
+    <mergeCell ref="B3:B16"/>
     <mergeCell ref="BR30:BR43"/>
     <mergeCell ref="BM8:BO8"/>
     <mergeCell ref="BM16:BO16"/>
@@ -5634,9 +5890,8 @@
     <mergeCell ref="BM22:BO22"/>
     <mergeCell ref="BE50:BQ51"/>
     <mergeCell ref="BI45:BK45"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="BC9:BE9"/>
-    <mergeCell ref="AY18:BB18"/>
+    <mergeCell ref="BR17:BR29"/>
+    <mergeCell ref="BM9:BO9"/>
     <mergeCell ref="BI47:BQ47"/>
     <mergeCell ref="AW21:AX21"/>
     <mergeCell ref="AJ57:AT57"/>
@@ -5646,11 +5901,21 @@
     <mergeCell ref="BM24:BO24"/>
     <mergeCell ref="BC21:BE21"/>
     <mergeCell ref="AY19:BB19"/>
-    <mergeCell ref="AY13:BB13"/>
     <mergeCell ref="AX40:AZ40"/>
     <mergeCell ref="AY22:BB22"/>
     <mergeCell ref="BL40:BN40"/>
-    <mergeCell ref="BC12:BE12"/>
+    <mergeCell ref="BA40:BH40"/>
+    <mergeCell ref="AW19:AX19"/>
+    <mergeCell ref="AW53:BD55"/>
+    <mergeCell ref="K28:O29"/>
+    <mergeCell ref="BE52:BQ55"/>
+    <mergeCell ref="M57:X57"/>
+    <mergeCell ref="AX42:AZ42"/>
+    <mergeCell ref="Y57:AI57"/>
+    <mergeCell ref="AA32:AS55"/>
+    <mergeCell ref="BA43:BH43"/>
+    <mergeCell ref="BI43:BK43"/>
+    <mergeCell ref="BM27:BO27"/>
     <mergeCell ref="C3:D5"/>
     <mergeCell ref="C57:L57"/>
     <mergeCell ref="AW48:BD48"/>
@@ -5675,13 +5940,6 @@
     <mergeCell ref="AY8:BB8"/>
     <mergeCell ref="AW17:AX17"/>
     <mergeCell ref="BG57:BQ57"/>
-    <mergeCell ref="BC7:BE7"/>
-    <mergeCell ref="BC15:BE15"/>
-    <mergeCell ref="BA40:BH40"/>
-    <mergeCell ref="AW19:AX19"/>
-    <mergeCell ref="AW53:BD55"/>
-    <mergeCell ref="K28:O29"/>
-    <mergeCell ref="BE52:BQ55"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
